--- a/tame_output/ON/bt/strategyON_20241006.xlsx
+++ b/tame_output/ON/bt/strategyON_20241006.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>57.6%</t>
+          <t>57.2%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>68.2%</t>
+          <t>68.1%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>17.8%</t>
+          <t>17.7%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>64.7%</t>
+          <t>63.0%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>84.8%</t>
+          <t>84.9%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -921,7 +921,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>107.3%</t>
+          <t>107.1%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.6%</t>
+          <t>123.3%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>90.0%</t>
+          <t>89.9%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-42.4%</t>
+          <t>-37.7%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>21.9%</t>
+          <t>21.6%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-48.4%</t>
+          <t>-48.0%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1012,7 +1012,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>88.9%</t>
+          <t>88.8%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>421.8%</t>
+          <t>421.6%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-6.1%</t>
+          <t>-6.3%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-667.3%</t>
+          <t>-667.1%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>30.4%</t>
+          <t>30.5%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.2%</t>
+          <t>57.1%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.7%</t>
+          <t>63.6%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1140,7 +1140,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-11.8%</t>
+          <t>-9.6%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-31.4%</t>
+          <t>-31.1%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1170,7 +1170,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>49.7%</t>
+          <t>49.6%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-4.4%</t>
+          <t>-4.3%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13.8%</t>
+          <t>14.0%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-119.9%</t>
+          <t>-119.8%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-2.2%</t>
+          <t>-3.1%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>67.1%</t>
+          <t>66.9%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.9%</t>
+          <t>54.8%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>62.9%</t>
+          <t>62.8%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>74.4%</t>
+          <t>74.2%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>-7.5%</t>
+          <t>-5.5%</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>10.7%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-24.2%</t>
+          <t>-24.0%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>4.6%</t>
+          <t>3.6%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.8%</t>
+          <t>55.7%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>60.2%</t>
+          <t>44.8%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-545.2%</t>
+          <t>-203.6%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-92.1%</t>
+          <t>-98.1%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>114.3%</t>
+          <t>113.0%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>60.3%</t>
+          <t>60.2%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1447,7 +1447,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-8.9%</t>
+          <t>-7.8%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>14.1%</t>
+          <t>14.2%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-20.3%</t>
+          <t>-18.8%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>103.6%</t>
+          <t>102.4%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.6%</t>
+          <t>-16.4%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>36.6%</t>
+          <t>36.7%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>91.7%</t>
+          <t>88.1%</t>
         </is>
       </c>
     </row>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191735</v>
+        <v>3.302618194191734</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44463,7 +44463,7 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108636</v>
+        <v>3.305023265108635</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097818</v>
+        <v>3.341378723097817</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094114</v>
+        <v>3.374439043094112</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199281</v>
+        <v>3.40596051119928</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.42463335496959</v>
+        <v>3.424633354969588</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923083</v>
+        <v>3.41997943392308</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297745</v>
+        <v>3.458100091297743</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317614</v>
+        <v>3.447750501317611</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737167</v>
+        <v>3.503515506737165</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.50317028234131</v>
+        <v>3.503170282341308</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.501052558539461</v>
+        <v>3.50105255853946</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -45176,7 +45176,7 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.78468452131195</v>
+        <v>3.784684521311949</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
@@ -45199,7 +45199,7 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800829354097244</v>
+        <v>3.800829354097242</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
@@ -45222,7 +45222,7 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017772</v>
+        <v>3.789311112017769</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
@@ -45245,7 +45245,7 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833252747839725</v>
+        <v>3.833252747839722</v>
       </c>
       <c r="C1900" t="n">
         <v>3.151116350215413</v>
@@ -45268,7 +45268,7 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839374447388729</v>
+        <v>3.839374447388725</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
@@ -45291,7 +45291,7 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856161751626475</v>
+        <v>3.856161751626471</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
@@ -45314,7 +45314,7 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787330429291814</v>
+        <v>3.787330429291812</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
@@ -45337,7 +45337,7 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801637122785788</v>
+        <v>3.801637122785786</v>
       </c>
       <c r="C1904" t="n">
         <v>3.155859013848905</v>
@@ -45360,7 +45360,7 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763182248390429</v>
+        <v>3.763182248390427</v>
       </c>
       <c r="C1905" t="n">
         <v>3.057119799856059</v>
@@ -45383,7 +45383,7 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105954</v>
+        <v>3.784718794105952</v>
       </c>
       <c r="C1906" t="n">
         <v>3.059934860543696</v>
@@ -45406,7 +45406,7 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960987</v>
+        <v>3.753882571960985</v>
       </c>
       <c r="C1907" t="n">
         <v>3.072841201767355</v>
@@ -45429,7 +45429,7 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607646</v>
+        <v>3.692931855607644</v>
       </c>
       <c r="C1908" t="n">
         <v>2.944865272168136</v>
@@ -45452,7 +45452,7 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770422583987903</v>
+        <v>3.770422583987902</v>
       </c>
       <c r="C1909" t="n">
         <v>2.993409614045222</v>
@@ -45475,7 +45475,7 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710813</v>
+        <v>3.760333686710811</v>
       </c>
       <c r="C1910" t="n">
         <v>2.876788805406815</v>
@@ -45498,7 +45498,7 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409205</v>
+        <v>3.723566229409204</v>
       </c>
       <c r="C1911" t="n">
         <v>2.868074819153337</v>
@@ -45521,7 +45521,7 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.72996971609811</v>
+        <v>3.729969716098108</v>
       </c>
       <c r="C1912" t="n">
         <v>2.861114207058244</v>
@@ -45544,7 +45544,7 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493421</v>
+        <v>3.782922533493419</v>
       </c>
       <c r="C1913" t="n">
         <v>2.875576561439387</v>
@@ -45567,7 +45567,7 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722819</v>
+        <v>3.828551486722817</v>
       </c>
       <c r="C1914" t="n">
         <v>2.870108681898582</v>
@@ -45590,7 +45590,7 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792047</v>
+        <v>3.828052928792046</v>
       </c>
       <c r="C1915" t="n">
         <v>2.867606775909159</v>
@@ -45613,7 +45613,7 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919907</v>
+        <v>3.812453678919905</v>
       </c>
       <c r="C1916" t="n">
         <v>2.875307754146484</v>
@@ -45636,7 +45636,7 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318092</v>
+        <v>3.74832840831809</v>
       </c>
       <c r="C1917" t="n">
         <v>2.871088462493535</v>
@@ -45659,7 +45659,7 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057527</v>
+        <v>3.824311233057525</v>
       </c>
       <c r="C1918" t="n">
         <v>2.873212776413551</v>
@@ -45682,7 +45682,7 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279186</v>
+        <v>3.826354974279184</v>
       </c>
       <c r="C1919" t="n">
         <v>2.865954851397253</v>
@@ -45705,7 +45705,7 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011499</v>
+        <v>3.835957987011497</v>
       </c>
       <c r="C1920" t="n">
         <v>2.869553974917902</v>
@@ -45728,7 +45728,7 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392988</v>
+        <v>3.780933911392986</v>
       </c>
       <c r="C1921" t="n">
         <v>2.882881480972455</v>
@@ -45751,7 +45751,7 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632782</v>
+        <v>3.773765222632781</v>
       </c>
       <c r="C1922" t="n">
         <v>2.881901958588752</v>
@@ -45774,7 +45774,7 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883074</v>
+        <v>3.764617879883073</v>
       </c>
       <c r="C1923" t="n">
         <v>2.88659675964307</v>
@@ -45797,7 +45797,7 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074784</v>
+        <v>3.798814771074782</v>
       </c>
       <c r="C1924" t="n">
         <v>2.867791018426865</v>
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242294</v>
+        <v>3.797694884242293</v>
       </c>
       <c r="C1925" t="n">
         <v>2.869534095051743</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.771051089888987</v>
+        <v>-4.872379156295804</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.9607572347824</v>
+        <v>0.9202260082196729</v>
       </c>
       <c r="F1925" t="n">
-        <v>0.3045898422982123</v>
+        <v>0.2032617758913947</v>
       </c>
       <c r="G1925" t="n">
-        <v>3.052288000430671</v>
+        <v>2.99149116058658</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821593509367686</v>
+        <v>3.821593509367682</v>
       </c>
       <c r="C1926" t="n">
         <v>2.873463408886563</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.658564829220111</v>
+        <v>-4.75989289562693</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.00968105288477</v>
+        <v>0.9691498263220431</v>
       </c>
       <c r="F1926" t="n">
-        <v>0.3045898422982123</v>
+        <v>0.2032617758913947</v>
       </c>
       <c r="G1926" t="n">
-        <v>3.056217314265491</v>
+        <v>2.9954204744214</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879966</v>
+        <v>3.822326997879962</v>
       </c>
       <c r="C1927" t="n">
         <v>2.874141992803903</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.640851142342246</v>
+        <v>-4.742179208749064</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.017445111553257</v>
+        <v>0.9769138849905292</v>
       </c>
       <c r="F1927" t="n">
-        <v>0.3077711711951291</v>
+        <v>0.2064431047883115</v>
       </c>
       <c r="G1927" t="n">
-        <v>3.058804695520981</v>
+        <v>2.99800785567689</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.84861662650234</v>
+        <v>3.848616626502333</v>
       </c>
       <c r="C1928" t="n">
         <v>2.871140064023896</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.517376871029228</v>
+        <v>-4.618704937436046</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.063832891298457</v>
+        <v>1.02330166473573</v>
       </c>
       <c r="F1928" t="n">
-        <v>0.3077711711951291</v>
+        <v>0.2064431047883115</v>
       </c>
       <c r="G1928" t="n">
-        <v>3.055802766740974</v>
+        <v>2.995005926896884</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.81866895167594</v>
+        <v>3.818668951675935</v>
       </c>
       <c r="C1929" t="n">
         <v>2.872719101034511</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.459441039031012</v>
+        <v>-4.560769105437831</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.088586261108358</v>
+        <v>1.04805503454563</v>
       </c>
       <c r="F1929" t="n">
-        <v>0.3333330458778784</v>
+        <v>0.2320049794710608</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.072718928561238</v>
+        <v>3.011922088717147</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539952</v>
+        <v>3.843274527539947</v>
       </c>
       <c r="C1930" t="n">
         <v>2.888613283836334</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.326573349967735</v>
+        <v>-4.427901416374553</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.157627519535492</v>
+        <v>1.117096292972765</v>
       </c>
       <c r="F1930" t="n">
-        <v>0.3333330458778784</v>
+        <v>0.2320049794710608</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.088613111363061</v>
+        <v>3.02781627151897</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496263</v>
+        <v>3.845047386496259</v>
       </c>
       <c r="C1931" t="n">
         <v>2.889759128276636</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.206400266603236</v>
+        <v>-4.307728333010054</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.206842597321593</v>
+        <v>1.166311370758866</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.4535061292423774</v>
+        <v>0.3521780628355597</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.161862805822063</v>
+        <v>3.101065965977972</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551577</v>
+        <v>3.791273551576996</v>
       </c>
       <c r="C1932" t="n">
         <v>2.899847230838076</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.071146905273259</v>
+        <v>-4.172474971680077</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.271032044415024</v>
+        <v>1.230500817852297</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.5887594905723545</v>
+        <v>0.4874314241655369</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.253102925181488</v>
+        <v>3.192306085337398</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942106</v>
+        <v>3.735839222942102</v>
       </c>
       <c r="C1933" t="n">
         <v>2.885884722239501</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.131021732630951</v>
+        <v>-4.232349799037769</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.233119604873373</v>
+        <v>1.192588378310646</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.5288846632146624</v>
+        <v>0.4275565968078447</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.203215520168299</v>
+        <v>3.142418680324209</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674515</v>
+        <v>3.762647477674512</v>
       </c>
       <c r="C1934" t="n">
         <v>2.90117389147371</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.011201501720114</v>
+        <v>-4.112529568126932</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.296336866471916</v>
+        <v>1.255805639909189</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.5288846632146624</v>
+        <v>0.4275565968078447</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.218504689402508</v>
+        <v>3.157707849558417</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430697</v>
+        <v>3.729146398430693</v>
       </c>
       <c r="C1935" t="n">
         <v>2.808818090796152</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.01367120818192</v>
+        <v>-4.114999274588738</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.202993183209635</v>
+        <v>1.162461956646908</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.5264149567528562</v>
+        <v>0.4250868903460386</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.124667064847865</v>
+        <v>3.063870225003775</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003604</v>
+        <v>3.7432201960036</v>
       </c>
       <c r="C1936" t="n">
         <v>2.728079952281453</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.08204139450593</v>
+        <v>-4.183369460912749</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.094906970165333</v>
+        <v>1.054375743602606</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.5356906557890712</v>
+        <v>0.4343625893822535</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.049494345754896</v>
+        <v>2.988697505910805</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508372</v>
+        <v>3.714179139508368</v>
       </c>
       <c r="C1937" t="n">
         <v>2.718516660913344</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.193913674132081</v>
+        <v>-4.295241740538899</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.040594766946764</v>
+        <v>1.000063540384037</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.5356906557890712</v>
+        <v>0.4343625893822535</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.039931054386787</v>
+        <v>2.979134214542697</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417706</v>
+        <v>3.710906731417702</v>
       </c>
       <c r="C1938" t="n">
         <v>2.685091185837372</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.177939008645813</v>
+        <v>-4.279267075052632</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.013559158065298</v>
+        <v>0.9730279315025709</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.5356906557890712</v>
+        <v>0.4343625893822535</v>
       </c>
       <c r="G1938" t="n">
-        <v>3.006505579310815</v>
+        <v>2.945708739466724</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205901</v>
+        <v>3.746042526205895</v>
       </c>
       <c r="C1939" t="n">
         <v>2.689658417829159</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.182033555316811</v>
+        <v>-4.283361621723629</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.016488571388687</v>
+        <v>0.9759573448259597</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.5356906557890712</v>
+        <v>0.4343625893822535</v>
       </c>
       <c r="G1939" t="n">
-        <v>3.011072811302602</v>
+        <v>2.950275971458512</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225445</v>
+        <v>3.765024323225438</v>
       </c>
       <c r="C1940" t="n">
         <v>2.665400446590366</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.174109180731897</v>
+        <v>-4.275437247138715</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.9954003499838597</v>
+        <v>0.9548691234211324</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.5356906557890712</v>
+        <v>0.4343625893822535</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.986814840063809</v>
+        <v>2.926018000219719</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111296</v>
+        <v>3.773210297111292</v>
       </c>
       <c r="C1941" t="n">
         <v>2.593938759991816</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.167830978162048</v>
+        <v>-4.269159044568866</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.9264499444132492</v>
+        <v>0.8859187178505219</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.5419688583589202</v>
+        <v>0.4406407919521026</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.919120075007168</v>
+        <v>2.858323235163078</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264166</v>
+        <v>3.784343952264162</v>
       </c>
       <c r="C1942" t="n">
         <v>2.604111146423949</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.107978358958325</v>
+        <v>-4.209306425365143</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.9605633785268708</v>
+        <v>0.9200321519641435</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.5419688583589202</v>
+        <v>0.4406407919521026</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.929292461439301</v>
+        <v>2.86849562159521</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742301</v>
+        <v>3.786949957742298</v>
       </c>
       <c r="C1943" t="n">
         <v>2.599057416997809</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.021734895931947</v>
+        <v>-4.123062962338765</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.9900070343112821</v>
+        <v>0.9494758077485548</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.5419688583589202</v>
+        <v>0.4406407919521026</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.924238732013161</v>
+        <v>2.863441892169071</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316048</v>
+        <v>3.752027499316045</v>
       </c>
       <c r="C1944" t="n">
         <v>2.590833192442334</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.067041715330927</v>
+        <v>-4.168369781737745</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.9636600819962158</v>
+        <v>0.9231288554334884</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.5011586953496894</v>
+        <v>0.3998306289428718</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.891528409652148</v>
+        <v>2.830731569808058</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803192</v>
+        <v>3.753571165803189</v>
       </c>
       <c r="C1945" t="n">
         <v>2.591385065475436</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.096074820033228</v>
+        <v>-4.197402886440046</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.9525987131483968</v>
+        <v>0.9120674865856695</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.5011586953496894</v>
+        <v>0.3998306289428718</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.89208028268525</v>
+        <v>2.831283442841159</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809501</v>
+        <v>3.733390600809497</v>
       </c>
       <c r="C1946" t="n">
         <v>2.520657757366802</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.003264338582369</v>
+        <v>-4.104592404989186</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.9189955976201063</v>
+        <v>0.8784643710573792</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.5939691768005487</v>
+        <v>0.4926411103937312</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.877039263447131</v>
+        <v>2.816242423603041</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560427</v>
+        <v>3.748285816560424</v>
       </c>
       <c r="C1947" t="n">
         <v>2.522531233291402</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.047653807911797</v>
+        <v>-4.148981874318614</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.9031132858129358</v>
+        <v>0.8625820592502089</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.5495797074711211</v>
+        <v>0.4482516410643035</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.852279057774076</v>
+        <v>2.791482217929985</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472738</v>
+        <v>3.721077195472734</v>
       </c>
       <c r="C1948" t="n">
         <v>2.517606941803125</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.027150114026299</v>
+        <v>-4.128478180433117</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.9063904718788578</v>
+        <v>0.8658592453161309</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.5700834013566184</v>
+        <v>0.4687553349498008</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.859656982617097</v>
+        <v>2.798860142773006</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798539</v>
+        <v>3.743047603798535</v>
       </c>
       <c r="C1949" t="n">
         <v>2.523098237633793</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.110822210738632</v>
+        <v>-4.212150277145449</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.8784129290245921</v>
+        <v>0.837881702461865</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.5700834013566184</v>
+        <v>0.4687553349498008</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.865148278447764</v>
+        <v>2.804351438603673</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498865</v>
+        <v>3.689597840498862</v>
       </c>
       <c r="C1950" t="n">
         <v>2.534595439402332</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.138602608639984</v>
+        <v>-4.239930675046802</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.87879797163259</v>
+        <v>0.8382667450698631</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.5423030034552654</v>
+        <v>0.4409749370484478</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.859977241475491</v>
+        <v>2.799180401631401</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705326</v>
+        <v>3.643069621705322</v>
       </c>
       <c r="C1951" t="n">
         <v>2.372951159402985</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.256983281370123</v>
+        <v>-4.35831134777694</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.6698014225411879</v>
+        <v>0.629270195978461</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.4750851513042892</v>
+        <v>0.3737570848974716</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.658002250185559</v>
+        <v>2.597205410341468</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729271</v>
+        <v>3.682716310729267</v>
       </c>
       <c r="C1952" t="n">
         <v>2.493100820122191</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.365597359813454</v>
+        <v>-4.466925426220271</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.7465054518830612</v>
+        <v>0.7059742253203343</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.4750851513042892</v>
+        <v>0.3737570848974716</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.778151910904764</v>
+        <v>2.717355071060674</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.73301244119077</v>
+        <v>3.733012441190766</v>
       </c>
       <c r="C1953" t="n">
         <v>2.507613846224514</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.330188321565311</v>
+        <v>-4.431516387972128</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.7751820932846414</v>
+        <v>0.7346508667219143</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.4750851513042892</v>
+        <v>0.3737570848974716</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.792664937007087</v>
+        <v>2.731868097162997</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913428</v>
+        <v>3.741174069913424</v>
       </c>
       <c r="C1954" t="n">
         <v>2.505033287566882</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.338649490220772</v>
+        <v>-4.439977556627589</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.7692170671648257</v>
+        <v>0.7286858406020986</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.4666239826488282</v>
+        <v>0.3652959162420105</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.785007677156179</v>
+        <v>2.724210837312089</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532488</v>
+        <v>3.751147197532484</v>
       </c>
       <c r="C1955" t="n">
         <v>2.501762316412185</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.161533160185606</v>
+        <v>-4.262861226592423</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.8367926280241944</v>
+        <v>0.7962614014614675</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.4666239826488282</v>
+        <v>0.3652959162420105</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.781736706001482</v>
+        <v>2.720939866157391</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793904</v>
+        <v>3.741328448793901</v>
       </c>
       <c r="C1956" t="n">
         <v>2.502445708174098</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.206625405019151</v>
+        <v>-4.307953471425969</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.8194391218526893</v>
+        <v>0.7789078952899624</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.4047279394794384</v>
+        <v>0.3033998730726207</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.745282471861761</v>
+        <v>2.684485632017671</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011237</v>
+        <v>3.750729377011231</v>
       </c>
       <c r="C1957" t="n">
         <v>2.496232683480512</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.027249983780384</v>
+        <v>-4.128578050187201</v>
       </c>
       <c r="E1957" t="n">
-        <v>0.8849762656546107</v>
+        <v>0.8444450390918838</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.561504697650157</v>
+        <v>0.4601766312433394</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.833135502070607</v>
+        <v>2.772338662226516</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.71699171898223</v>
+        <v>3.716991718982224</v>
       </c>
       <c r="C1958" t="n">
         <v>2.477040138812102</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.07226419730099</v>
+        <v>-4.173592263707807</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.8477780355779578</v>
+        <v>0.8072468090152312</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.5311558023355524</v>
+        <v>0.4298277359287348</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.795733620213434</v>
+        <v>2.734936780369343</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509539</v>
+        <v>3.737026608509533</v>
       </c>
       <c r="C1959" t="n">
         <v>2.482731701151048</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.160275383859688</v>
+        <v>-4.261603450266504</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.8182651232934246</v>
+        <v>0.7777338967306981</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.4656792944763794</v>
+        <v>0.3643512280695618</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.762139277836876</v>
+        <v>2.701342437992785</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760813</v>
+        <v>3.702309454760809</v>
       </c>
       <c r="C1960" t="n">
         <v>2.481935623047549</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.26147316529686</v>
+        <v>-4.362801231703677</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.7769899326150571</v>
+        <v>0.7364587060523304</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.3972704809310602</v>
+        <v>0.2959424145242426</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.720297911606186</v>
+        <v>2.659501071762095</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815457</v>
+        <v>3.705571661815453</v>
       </c>
       <c r="C1961" t="n">
         <v>2.479535584601866</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.254962198682548</v>
+        <v>-4.356290265089364</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.7771942808150989</v>
+        <v>0.7366630542523722</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.3972704809310602</v>
+        <v>0.2959424145242426</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.717897873160502</v>
+        <v>2.657101033316412</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378102</v>
+        <v>3.709510443378099</v>
       </c>
       <c r="C1962" t="n">
         <v>2.476060303810111</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.23592407097525</v>
+        <v>-4.337252137382067</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.7813342511062626</v>
+        <v>0.740803024543536</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.3390868695998657</v>
+        <v>0.2377588031930481</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.679512425570031</v>
+        <v>2.61871558572594</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.73106447313125</v>
+        <v>3.731064473131246</v>
       </c>
       <c r="C1963" t="n">
         <v>2.595354705444301</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.288439873250071</v>
+        <v>-4.389767939656887</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.8796223318305247</v>
+        <v>0.8390911052677983</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.3390868695998657</v>
+        <v>0.2377588031930481</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.798806827204221</v>
+        <v>2.73800998736013</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067864</v>
+        <v>3.722447362067861</v>
       </c>
       <c r="C1964" t="n">
         <v>2.596188034430435</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.291848184684651</v>
+        <v>-4.393176251091467</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.8790923362428265</v>
+        <v>0.8385611096800998</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.3716034386092431</v>
+        <v>0.2702753722024255</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.819150097595981</v>
+        <v>2.75835325775189</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789123</v>
+        <v>3.78742558078912</v>
       </c>
       <c r="C1965" t="n">
         <v>2.602196564827361</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.272492048790803</v>
+        <v>-4.37382011519762</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.8928433209972915</v>
+        <v>0.8523120944345648</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.3716034386092431</v>
+        <v>0.2702753722024255</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.825158627992907</v>
+        <v>2.764361788148816</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519908</v>
+        <v>3.781501250519905</v>
       </c>
       <c r="C1966" t="n">
         <v>2.50014678610456</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.345821577528896</v>
+        <v>-4.447149643935712</v>
       </c>
       <c r="E1966" t="n">
-        <v>0.7614617307792537</v>
+        <v>0.7209305042165273</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.371998101028865</v>
+        <v>0.2706700346220474</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.723345646721879</v>
+        <v>2.662548806877789</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.80224592918117</v>
+        <v>3.802245929181165</v>
       </c>
       <c r="C1967" t="n">
         <v>2.409870503348191</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.429642798803594</v>
+        <v>-4.530970865210411</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.6376569595130057</v>
+        <v>0.597125732950279</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.371998101028865</v>
+        <v>0.2706700346220474</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.633069363965511</v>
+        <v>2.57227252412142</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394731</v>
+        <v>3.805608985394725</v>
       </c>
       <c r="C1968" t="n">
         <v>2.41053285173985</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.42349009275081</v>
+        <v>-4.524818159157626</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.6407803903257778</v>
+        <v>0.6002491637630512</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.3781508070816493</v>
+        <v>0.2768227406748317</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.637423335988839</v>
+        <v>2.576626496144749</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890613</v>
+        <v>3.798239794890609</v>
       </c>
       <c r="C1969" t="n">
         <v>2.40961332847996</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.440299390901312</v>
+        <v>-4.541627457308128</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.6331371478056873</v>
+        <v>0.5926059212429606</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.3613415089311476</v>
+        <v>0.2600134425243301</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.626418233838649</v>
+        <v>2.565621393994558</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798427</v>
+        <v>3.867362636798424</v>
       </c>
       <c r="C1970" t="n">
         <v>2.475948882276781</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.378001392125189</v>
+        <v>-4.479329458532006</v>
       </c>
       <c r="E1970" t="n">
-        <v>0.7243919011129569</v>
+        <v>0.6838606745502305</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.4066357732055897</v>
+        <v>0.3053077067987721</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.719930346200135</v>
+        <v>2.659133506356044</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992193</v>
+        <v>3.848729139992188</v>
       </c>
       <c r="C1971" t="n">
         <v>2.278240883990908</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.176211194460032</v>
+        <v>-4.277539260866848</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.6073999818931473</v>
+        <v>0.5668687553304206</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.604653965374744</v>
+        <v>0.5033258989679266</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.641033263215755</v>
+        <v>2.580236423371664</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852424</v>
+        <v>3.841444817852421</v>
       </c>
       <c r="C1972" t="n">
         <v>2.348531116313083</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.227097907146226</v>
+        <v>-4.328425973553043</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.6573355291408447</v>
+        <v>0.616804302578118</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.5537672526885495</v>
+        <v>0.452439186281732</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.680791467926213</v>
+        <v>2.619994628082122</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319546</v>
+        <v>3.81906330031954</v>
       </c>
       <c r="C1973" t="n">
         <v>2.363158852429127</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.140487164496419</v>
+        <v>-4.241815230903236</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.7066075623168109</v>
+        <v>0.6660763357540844</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.6323929838937078</v>
+        <v>0.5310649174868902</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.742594642765352</v>
+        <v>2.681797802921261</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489386</v>
+        <v>3.83181903248938</v>
       </c>
       <c r="C1974" t="n">
         <v>2.361694833253798</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.200696462501704</v>
+        <v>-4.302024528908521</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.6810598239393686</v>
+        <v>0.6405285973766421</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.5721836858884233</v>
+        <v>0.4708556194816057</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.705005044786853</v>
+        <v>2.644208204942762</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397796</v>
+        <v>3.83641167239779</v>
       </c>
       <c r="C1975" t="n">
         <v>2.360186451293727</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.151509813817353</v>
+        <v>-4.25283788022417</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.6992261014530379</v>
+        <v>0.6586948748903112</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.5721836858884233</v>
+        <v>0.4708556194816057</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.703496662826781</v>
+        <v>2.642699822982691</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316252</v>
+        <v>3.833513460316245</v>
       </c>
       <c r="C1976" t="n">
         <v>2.360049318729163</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.107136682178784</v>
+        <v>-4.208464748585601</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.7168382215439015</v>
+        <v>0.6763069949811749</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.6165568175269919</v>
+        <v>0.5152287511201743</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.729983409245358</v>
+        <v>2.669186569401268</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105966</v>
+        <v>3.821562117105962</v>
       </c>
       <c r="C1977" t="n">
         <v>2.354443112867754</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.072405360860284</v>
+        <v>-4.1737334272671</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.7251245442098921</v>
+        <v>0.6845933176471655</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.6165568175269919</v>
+        <v>0.5152287511201743</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.724377203383949</v>
+        <v>2.663580363539858</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190325</v>
+        <v>3.833011148190321</v>
       </c>
       <c r="C1978" t="n">
         <v>2.360824869895558</v>
       </c>
       <c r="D1978" t="n">
-        <v>-4.024749630299228</v>
+        <v>-4.126077696706044</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.7505685934621191</v>
+        <v>0.7100373668993925</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.6642125480880475</v>
+        <v>0.56288448168123</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.759352398748387</v>
+        <v>2.698555558904296</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569618</v>
+        <v>3.822678210569614</v>
       </c>
       <c r="C1979" t="n">
         <v>2.365717243270283</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.924231471800473</v>
+        <v>-4.02555953820729</v>
       </c>
       <c r="E1979" t="n">
-        <v>0.7956682302363458</v>
+        <v>0.7551370036736191</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.7647307065868021</v>
+        <v>0.6634026401799845</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.824555667222365</v>
+        <v>2.763758827378274</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557295</v>
+        <v>3.828808877557291</v>
       </c>
       <c r="C1980" t="n">
         <v>2.352471915746155</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.908326142368121</v>
+        <v>-4.009654208774937</v>
       </c>
       <c r="E1980" t="n">
-        <v>0.788785034485159</v>
+        <v>0.7482538079224326</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.6856180458775631</v>
+        <v>0.5842899794707457</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.763842743272694</v>
+        <v>2.703045903428603</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932769</v>
+        <v>3.816837033932766</v>
       </c>
       <c r="C1981" t="n">
         <v>2.356569618356784</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.863487740759723</v>
+        <v>-3.964815807166539</v>
       </c>
       <c r="E1981" t="n">
-        <v>0.8108180977391468</v>
+        <v>0.7702868711764204</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.6901614788224326</v>
+        <v>0.5888334124156152</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.770666505650244</v>
+        <v>2.709869665806153</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917051</v>
+        <v>3.817932354917048</v>
       </c>
       <c r="C1982" t="n">
         <v>2.360730557987862</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.882986197001731</v>
+        <v>-3.984314263408547</v>
       </c>
       <c r="E1982" t="n">
-        <v>0.8071796548734216</v>
+        <v>0.7666484283106949</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.6420768375425283</v>
+        <v>0.5407487711357108</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.745976660513379</v>
+        <v>2.685179820669289</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405961</v>
+        <v>3.826684745405958</v>
       </c>
       <c r="C1983" t="n">
         <v>2.366610160515699</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.83878335991583</v>
+        <v>-3.940111426322647</v>
       </c>
       <c r="E1983" t="n">
-        <v>0.8307403922356189</v>
+        <v>0.7902091656728922</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.6862796746284288</v>
+        <v>0.5849516082216113</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.778377965292757</v>
+        <v>2.717581125448666</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265645</v>
+        <v>3.838199629265642</v>
       </c>
       <c r="C1984" t="n">
         <v>2.365020160984947</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.846343025752877</v>
+        <v>-3.947671092159694</v>
       </c>
       <c r="E1984" t="n">
-        <v>0.8261265263700477</v>
+        <v>0.785595299807321</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.7410830786382481</v>
+        <v>0.6397550122314306</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.809670008167896</v>
+        <v>2.748873168323805</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.86389508028488</v>
+        <v>3.863895080284877</v>
       </c>
       <c r="C1985" t="n">
         <v>2.416267926167986</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.688051608213605</v>
+        <v>-3.789379674620422</v>
       </c>
       <c r="E1985" t="n">
-        <v>0.9406908585687963</v>
+        <v>0.9001596320060696</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.7410830786382481</v>
+        <v>0.6397550122314306</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.860917773350935</v>
+        <v>2.800120933506845</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865338681321023</v>
+        <v>3.86533868132102</v>
       </c>
       <c r="C1986" t="n">
         <v>2.414708630762239</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.480409604579129</v>
+        <v>-3.581737670985945</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.02218836461684</v>
+        <v>0.9816571380541133</v>
       </c>
       <c r="F1986" t="n">
-        <v>0.9487250822727242</v>
+        <v>0.8473970158659068</v>
       </c>
       <c r="G1986" t="n">
-        <v>2.983943680125874</v>
+        <v>2.923146840281784</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475139</v>
+        <v>3.864489842475136</v>
       </c>
       <c r="C1987" t="n">
         <v>2.409656859000509</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.429377511856601</v>
+        <v>-3.530705578263417</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.037549429944121</v>
+        <v>0.9970182033813946</v>
       </c>
       <c r="F1987" t="n">
-        <v>0.9997571749952523</v>
+        <v>0.8984291085884347</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.009511163997661</v>
+        <v>2.94871432415357</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404854</v>
+        <v>3.84254736040485</v>
       </c>
       <c r="C1988" t="n">
         <v>2.426844263093214</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.364153330729395</v>
+        <v>-3.465481397136212</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.080826506487708</v>
+        <v>1.040295279924982</v>
       </c>
       <c r="F1988" t="n">
-        <v>1.064981356122458</v>
+        <v>0.9636532897156403</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.065833076766689</v>
+        <v>3.005036236922599</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882558</v>
+        <v>3.840061186882552</v>
       </c>
       <c r="C1989" t="n">
         <v>2.422805235392495</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.326726310658261</v>
+        <v>-3.428054377065078</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.091758286815442</v>
+        <v>1.051227060252716</v>
       </c>
       <c r="F1989" t="n">
-        <v>1.07023289415164</v>
+        <v>0.968904827744822</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.064944971883479</v>
+        <v>3.004148132039388</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992662</v>
+        <v>3.845169808992655</v>
       </c>
       <c r="C1990" t="n">
         <v>2.424062027723735</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.325368325684716</v>
+        <v>-3.426696392091532</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.093558273136101</v>
+        <v>1.053027046573374</v>
       </c>
       <c r="F1990" t="n">
-        <v>1.144571019689458</v>
+        <v>1.043242953282641</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.11080463953741</v>
+        <v>3.050007799693319</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636287</v>
+        <v>3.828661445636283</v>
       </c>
       <c r="C1991" t="n">
         <v>2.584619798744946</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.296955062584832</v>
+        <v>-3.398283128991649</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.265481349397265</v>
+        <v>1.224950122834538</v>
       </c>
       <c r="F1991" t="n">
-        <v>1.08559545694303</v>
+        <v>0.9842673905362118</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.235977072910764</v>
+        <v>3.175180233066673</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957627</v>
+        <v>3.813222820957621</v>
       </c>
       <c r="C1992" t="n">
         <v>2.704732707962763</v>
       </c>
       <c r="D1992" t="n">
-        <v>-3.222172801559819</v>
+        <v>-3.323500867966636</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.415507163025087</v>
+        <v>1.374975936462361</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.160377717968042</v>
+        <v>1.059049651561224</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.400959338743589</v>
+        <v>3.340162498899498</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998754</v>
+        <v>3.81423072799875</v>
       </c>
       <c r="C1993" t="n">
         <v>2.696440683976622</v>
       </c>
       <c r="D1993" t="n">
-        <v>-3.196088717296012</v>
+        <v>-3.297416783702828</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.417648772744469</v>
+        <v>1.377117546181743</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.160377717968042</v>
+        <v>1.059049651561224</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.392667314757448</v>
+        <v>3.331870474913357</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896929</v>
+        <v>3.803397818896926</v>
       </c>
       <c r="C1994" t="n">
         <v>2.694633879560401</v>
       </c>
       <c r="D1994" t="n">
-        <v>-3.108210804186891</v>
+        <v>-3.209538870593708</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.450993133571897</v>
+        <v>1.41046190700917</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.276303360391393</v>
+        <v>1.174975293984576</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.460415895795237</v>
+        <v>3.399619055951147</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959858</v>
+        <v>3.796264143959855</v>
       </c>
       <c r="C1995" t="n">
         <v>2.712188285287193</v>
       </c>
       <c r="D1995" t="n">
-        <v>-3.099318342793608</v>
+        <v>-3.200646409200425</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.472104523856002</v>
+        <v>1.431573297293275</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.276303360391393</v>
+        <v>1.174975293984576</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.477970301522029</v>
+        <v>3.417173461677939</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945367</v>
+        <v>3.794424941945364</v>
       </c>
       <c r="C1996" t="n">
         <v>2.704043332691777</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.267794459763486</v>
+        <v>-3.369122526170302</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.396569124472634</v>
+        <v>1.356037897909908</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.248355524674812</v>
+        <v>1.147027458267995</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.453056647496664</v>
+        <v>3.392259807652574</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782709</v>
+        <v>3.795574066782706</v>
       </c>
       <c r="C1997" t="n">
         <v>2.685313029879639</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.821538267134046</v>
+        <v>-2.922866333540862</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.556341298712272</v>
+        <v>1.515810072149546</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.15363685500518</v>
+        <v>1.052308788598362</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.377495142882747</v>
+        <v>3.316698303038656</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632637</v>
+        <v>3.784671345632633</v>
       </c>
       <c r="C1998" t="n">
         <v>2.675977052376543</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.798817163450893</v>
+        <v>-2.90014522985771</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.556093762682438</v>
+        <v>1.515562536119711</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.15363685500518</v>
+        <v>1.052308788598362</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.368159165379651</v>
+        <v>3.307362325535561</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777674</v>
+        <v>3.783205696777668</v>
       </c>
       <c r="C1999" t="n">
         <v>2.834883178227712</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.928018976744936</v>
+        <v>-3.029347043151752</v>
       </c>
       <c r="E1999" t="n">
-        <v>1.66331916321599</v>
+        <v>1.622787936653263</v>
       </c>
       <c r="F1999" t="n">
-        <v>1.024435041711137</v>
+        <v>0.92310697530432</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.449544203254395</v>
+        <v>3.388747363410304</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644414</v>
+        <v>3.779933725644408</v>
       </c>
       <c r="C2000" t="n">
         <v>2.871961000721359</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.953893375218962</v>
+        <v>-3.055221441625778</v>
       </c>
       <c r="E2000" t="n">
-        <v>1.690047226320026</v>
+        <v>1.649515999757299</v>
       </c>
       <c r="F2000" t="n">
-        <v>1.069346650422879</v>
+        <v>0.9680185840160611</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.513568990975086</v>
+        <v>3.452772151130996</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799962</v>
+        <v>3.76944361979996</v>
       </c>
       <c r="C2001" t="n">
         <v>2.868636356710904</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.946838685003788</v>
+        <v>-3.048166751410605</v>
       </c>
       <c r="E2001" t="n">
-        <v>1.689544458395641</v>
+        <v>1.649013231832914</v>
       </c>
       <c r="F2001" t="n">
-        <v>1.076401340638052</v>
+        <v>0.9750732742312349</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.514477161093736</v>
+        <v>3.453680321249645</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331116</v>
+        <v>3.766673496331113</v>
       </c>
       <c r="C2002" t="n">
         <v>2.878642510355645</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.9198874606773</v>
+        <v>-3.021215527084117</v>
       </c>
       <c r="E2002" t="n">
-        <v>1.710331101770977</v>
+        <v>1.669799875208251</v>
       </c>
       <c r="F2002" t="n">
-        <v>1.091281686665772</v>
+        <v>0.9899536202589541</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.533411522355109</v>
+        <v>3.472614682511018</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784108</v>
+        <v>3.768052067784105</v>
       </c>
       <c r="C2003" t="n">
         <v>3.062745642500605</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.941431688508087</v>
+        <v>-3.042759754914904</v>
       </c>
       <c r="E2003" t="n">
-        <v>1.885816542783622</v>
+        <v>1.845285316220896</v>
       </c>
       <c r="F2003" t="n">
-        <v>1.091281686665772</v>
+        <v>0.9899536202589541</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.717514654500068</v>
+        <v>3.656717814655978</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714424</v>
+        <v>3.743925505714421</v>
       </c>
       <c r="C2004" t="n">
         <v>3.054862337403598</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.963839806312959</v>
+        <v>-3.065167872719776</v>
       </c>
       <c r="E2004" t="n">
-        <v>1.868969990564667</v>
+        <v>1.82843876400194</v>
       </c>
       <c r="F2004" t="n">
-        <v>1.091281686665772</v>
+        <v>0.9899536202589541</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.709631349403061</v>
+        <v>3.648834509558971</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155034</v>
+        <v>3.719118627155028</v>
       </c>
       <c r="C2005" t="n">
         <v>3.056916336953236</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.99206404189056</v>
+        <v>-3.093392108297376</v>
       </c>
       <c r="E2005" t="n">
-        <v>1.859734295883264</v>
+        <v>1.819203069320537</v>
       </c>
       <c r="F2005" t="n">
-        <v>1.10925843911708</v>
+        <v>1.007930372710263</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.722471400423484</v>
+        <v>3.661674560579394</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.72945228516198</v>
+        <v>3.729452285161972</v>
       </c>
       <c r="C2006" t="n">
         <v>3.113170054675083</v>
       </c>
       <c r="D2006" t="n">
-        <v>-3.001504967779089</v>
+        <v>-3.102833034185906</v>
       </c>
       <c r="E2006" t="n">
-        <v>1.912211643249699</v>
+        <v>1.871680416686972</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.231685556660472</v>
+        <v>1.130357490253654</v>
       </c>
       <c r="G2006" t="n">
-        <v>3.852181388671366</v>
+        <v>3.791384548827275</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321637</v>
+        <v>3.714941193321629</v>
       </c>
       <c r="C2007" t="n">
         <v>3.116061149220384</v>
       </c>
       <c r="D2007" t="n">
-        <v>-3.207743905567523</v>
+        <v>-3.30907197197434</v>
       </c>
       <c r="E2007" t="n">
-        <v>1.832607162679627</v>
+        <v>1.7920759361169</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.025446618872038</v>
+        <v>0.9241185524652205</v>
       </c>
       <c r="G2007" t="n">
-        <v>3.731329120543607</v>
+        <v>3.670532280699516</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347708</v>
+        <v>3.7278981863477</v>
       </c>
       <c r="C2008" t="n">
         <v>3.114172962114159</v>
       </c>
       <c r="D2008" t="n">
-        <v>-3.284073883168429</v>
+        <v>-3.385401949575245</v>
       </c>
       <c r="E2008" t="n">
-        <v>1.800186984533039</v>
+        <v>1.759655757970313</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.025446618872038</v>
+        <v>0.9241185524652205</v>
       </c>
       <c r="G2008" t="n">
-        <v>3.729440933437382</v>
+        <v>3.668644093593291</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887753</v>
+        <v>3.710654104887745</v>
       </c>
       <c r="C2009" t="n">
         <v>3.108993191717021</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.439030668568558</v>
+        <v>-3.540358734975375</v>
       </c>
       <c r="E2009" t="n">
-        <v>1.73302449997585</v>
+        <v>1.692493273413124</v>
       </c>
       <c r="F2009" t="n">
-        <v>0.8704898334719087</v>
+        <v>0.7691617670650912</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.631287091800167</v>
+        <v>3.570490251956076</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343071</v>
+        <v>3.712897612343062</v>
       </c>
       <c r="C2010" t="n">
         <v>3.107427201927174</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.600599094095813</v>
+        <v>-3.70192716050263</v>
       </c>
       <c r="E2010" t="n">
-        <v>1.6668311399751</v>
+        <v>1.626299913412374</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.7437069096740293</v>
+        <v>0.6423788432672118</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.553651347731591</v>
+        <v>3.492854507887501</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754596135389354</v>
+        <v>3.754596135389345</v>
       </c>
       <c r="C2011" t="n">
         <v>3.120500608793092</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.708899755965933</v>
+        <v>-3.810227822372749</v>
       </c>
       <c r="E2011" t="n">
-        <v>1.636584282092971</v>
+        <v>1.596053055530245</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.7437069096740293</v>
+        <v>0.6423788432672118</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.56672475459751</v>
+        <v>3.505927914753419</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.74988269137839</v>
+        <v>3.749882691378388</v>
       </c>
       <c r="C2012" t="n">
         <v>3.112505805576032</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.86845082872945</v>
+        <v>-3.969778895136266</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.564769049770504</v>
+        <v>1.524237823207778</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.5914292428122778</v>
+        <v>0.4901011764054604</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.467363351263399</v>
+        <v>3.406566511419308</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715819895006973</v>
+        <v>3.715819895006971</v>
       </c>
       <c r="C2013" t="n">
         <v>3.111029846703034</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.896351615838923</v>
+        <v>-3.997679682245739</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.552132776053717</v>
+        <v>1.51160154949099</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.556832318669343</v>
+        <v>0.4555042522625256</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.44512923790464</v>
+        <v>3.38433239806055</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684895778787386</v>
+        <v>3.684895778787384</v>
       </c>
       <c r="C2014" t="n">
         <v>3.107794290680233</v>
       </c>
       <c r="D2014" t="n">
-        <v>-4.018877718541816</v>
+        <v>-4.120205784948633</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.499886778949759</v>
+        <v>1.459355552387032</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.4343062159664491</v>
+        <v>0.3329781495596317</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.368378020260103</v>
+        <v>3.307581180416012</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619348081585936</v>
+        <v>3.619348081585934</v>
       </c>
       <c r="C2015" t="n">
         <v>3.174500250270737</v>
       </c>
       <c r="D2015" t="n">
-        <v>-4.249392214727405</v>
+        <v>-4.350720281134222</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.474386940066027</v>
+        <v>1.4338557135033</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.2037917197808604</v>
+        <v>0.102463653374043</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.296775282139253</v>
+        <v>3.235978442295163</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640750087814666</v>
+        <v>3.640750087814664</v>
       </c>
       <c r="C2016" t="n">
         <v>3.314811969272584</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.598137299951849</v>
+        <v>-4.699465366358665</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.475200624978096</v>
+        <v>1.43466939841537</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.09504376586196261</v>
+        <v>-0.006284300544854848</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.371838228789762</v>
+        <v>3.311041388945671</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668289004237095</v>
+        <v>3.668289004237093</v>
       </c>
       <c r="C2017" t="n">
         <v>3.383792238418224</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.752123717727989</v>
+        <v>-4.853451784134806</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.48258632701328</v>
+        <v>1.442055100450553</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.09504376586196261</v>
+        <v>-0.006284300544854848</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.440818497935402</v>
+        <v>3.380021658091311</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619923016423388</v>
+        <v>3.619923016423386</v>
       </c>
       <c r="C2018" t="n">
         <v>3.369843440538344</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.956723152590998</v>
+        <v>-5.058051218997814</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.386797755188197</v>
+        <v>1.34626652862547</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.09504376586196261</v>
+        <v>-0.006284300544854848</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.426869700055522</v>
+        <v>3.366072860211432</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656332733609753</v>
+        <v>3.656332733609752</v>
       </c>
       <c r="C2019" t="n">
         <v>3.381713929593758</v>
       </c>
       <c r="D2019" t="n">
-        <v>-5.209198306598722</v>
+        <v>-5.310526373005539</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.297678182640522</v>
+        <v>1.257146956077795</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.09504376586196261</v>
+        <v>-0.006284300544854848</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.438740189110936</v>
+        <v>3.377943349266846</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674028535973157</v>
+        <v>3.674028535973155</v>
       </c>
       <c r="C2020" t="n">
         <v>3.382924464112702</v>
       </c>
       <c r="D2020" t="n">
-        <v>-5.502094063078134</v>
+        <v>-5.603422129484951</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.181730414567701</v>
+        <v>1.141199188004974</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.09504376586196261</v>
+        <v>-0.006284300544854848</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.43995072362988</v>
+        <v>3.37915388378579</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663509457251946</v>
+        <v>3.663509457251942</v>
       </c>
       <c r="C2021" t="n">
         <v>3.387046206340024</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.688758191212942</v>
+        <v>-5.790086257619759</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.111186505541099</v>
+        <v>1.070655278978372</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.06830479503740272</v>
+        <v>-0.03302327136941474</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.428029083362465</v>
+        <v>3.367232243518375</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652149152916202</v>
+        <v>3.652149152916197</v>
       </c>
       <c r="C2022" t="n">
         <v>3.382124059076213</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.834778878126905</v>
+        <v>-5.936106944533721</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.047856083511703</v>
+        <v>1.007324856948976</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.05922170324354575</v>
+        <v>-0.04210636316327171</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.417657081022341</v>
+        <v>3.35686024117825</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667962306830328</v>
+        <v>3.667962306830325</v>
       </c>
       <c r="C2023" t="n">
         <v>3.544328115775257</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.92649288723649</v>
+        <v>-6.027820953643307</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.173374536566913</v>
+        <v>1.132843310004186</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.05922170324354575</v>
+        <v>-0.04210636316327171</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.579861137721385</v>
+        <v>3.519064297877294</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696539468071552</v>
+        <v>3.696539468071547</v>
       </c>
       <c r="C2024" t="n">
         <v>3.539174753739071</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.95814454629646</v>
+        <v>-6.059472612703276</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.15556051090674</v>
+        <v>1.115029284344013</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.05405324599910555</v>
+        <v>-0.04727482040771191</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.571606701338535</v>
+        <v>3.510809861494444</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750044015868149</v>
+        <v>3.750044015868143</v>
       </c>
       <c r="C2025" t="n">
         <v>3.549404171307562</v>
       </c>
       <c r="D2025" t="n">
-        <v>-6.027210600869396</v>
+        <v>-6.128538667276213</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.138163506646056</v>
+        <v>1.097632280083329</v>
       </c>
       <c r="F2025" t="n">
-        <v>-0.008317631494504485</v>
+        <v>-0.1096456979013219</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.54441359241086</v>
+        <v>3.483616752566769</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783632867332695</v>
+        <v>3.783632867332689</v>
       </c>
       <c r="C2026" t="n">
         <v>3.558329809763465</v>
       </c>
       <c r="D2026" t="n">
-        <v>-6.129186723117804</v>
+        <v>-6.23051478952462</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.106298696202595</v>
+        <v>1.065767469639868</v>
       </c>
       <c r="F2026" t="n">
-        <v>-0.1102937537429121</v>
+        <v>-0.2116218201497295</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.492153557517718</v>
+        <v>3.431356717673627</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798296784231812</v>
+        <v>3.798296784231805</v>
       </c>
       <c r="C2027" t="n">
         <v>3.55048269700764</v>
       </c>
       <c r="D2027" t="n">
-        <v>-6.019180439640582</v>
+        <v>-6.120508506047399</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.142454096837659</v>
+        <v>1.101922870274933</v>
       </c>
       <c r="F2027" t="n">
-        <v>-0.08708918182563685</v>
+        <v>-0.1884172482324543</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.498229187912258</v>
+        <v>3.437432348068168</v>
       </c>
     </row>
     <row r="2028">
@@ -48195,16 +48195,16 @@
         <v>3.554732707729614</v>
       </c>
       <c r="D2028" t="n">
-        <v>-6.031710144752461</v>
+        <v>-6.133038211159278</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.141692225514882</v>
+        <v>1.101160998952155</v>
       </c>
       <c r="F2028" t="n">
-        <v>-0.1009156812921599</v>
+        <v>-0.2022437476989773</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.494183298954319</v>
+        <v>3.433386459110229</v>
       </c>
     </row>
     <row r="2029">
@@ -48218,16 +48218,16 @@
         <v>3.56199359061215</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.730263419280623</v>
+        <v>-5.83159148568744</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.269531798586153</v>
+        <v>1.229000572023426</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.2005310441796774</v>
+        <v>0.09920297777285991</v>
       </c>
       <c r="G2029" t="n">
-        <v>3.682312217119957</v>
+        <v>3.621515377275867</v>
       </c>
     </row>
     <row r="2030">
@@ -48241,16 +48241,16 @@
         <v>3.562964768364861</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.754853663515807</v>
+        <v>-5.856181729922624</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.26066687864479</v>
+        <v>1.220135652082063</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.2005310441796774</v>
+        <v>0.09920297777285991</v>
       </c>
       <c r="G2030" t="n">
-        <v>3.683283394872668</v>
+        <v>3.622486555028577</v>
       </c>
     </row>
     <row r="2031">
@@ -48264,16 +48264,16 @@
         <v>3.563807672744617</v>
       </c>
       <c r="D2031" t="n">
-        <v>-5.703815287509287</v>
+        <v>-5.805143353916104</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.281925133427154</v>
+        <v>1.241393906864427</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.2005310441796774</v>
+        <v>0.09920297777285991</v>
       </c>
       <c r="G2031" t="n">
-        <v>3.684126299252423</v>
+        <v>3.623329459408333</v>
       </c>
     </row>
     <row r="2032">
@@ -48281,22 +48281,22 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831734516969543</v>
+        <v>3.831734516969542</v>
       </c>
       <c r="C2032" t="n">
         <v>3.582845771618762</v>
       </c>
       <c r="D2032" t="n">
-        <v>-5.674966610685827</v>
+        <v>-5.776294677092643</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.312502703030683</v>
+        <v>1.271971476467957</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.2293797210031376</v>
+        <v>0.1280516545963202</v>
       </c>
       <c r="G2032" t="n">
-        <v>3.720473604220645</v>
+        <v>3.659676764376554</v>
       </c>
     </row>
     <row r="2033">
@@ -48304,22 +48304,22 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825752932700478</v>
+        <v>3.825752932700476</v>
       </c>
       <c r="C2033" t="n">
         <v>3.399029767742697</v>
       </c>
       <c r="D2033" t="n">
-        <v>-5.578331698667187</v>
+        <v>-5.679659765074003</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.167340663962074</v>
+        <v>1.126809437399347</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.3260146330217776</v>
+        <v>0.2246865666149601</v>
       </c>
       <c r="G2033" t="n">
-        <v>3.594638547555764</v>
+        <v>3.533841707711673</v>
       </c>
     </row>
     <row r="2034">
@@ -48327,22 +48327,22 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.804688961077642</v>
+        <v>3.804688961077638</v>
       </c>
       <c r="C2034" t="n">
         <v>3.402531811816661</v>
       </c>
       <c r="D2034" t="n">
-        <v>-5.509293687718719</v>
+        <v>-5.610621754125535</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.198457912415425</v>
+        <v>1.157926685852698</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.3950526439702456</v>
+        <v>0.2937245775634282</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.639563398198808</v>
+        <v>3.578766558354718</v>
       </c>
     </row>
     <row r="2035">
@@ -48350,22 +48350,22 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775028860833462</v>
+        <v>3.775028860833456</v>
       </c>
       <c r="C2035" t="n">
         <v>3.386958630892743</v>
       </c>
       <c r="D2035" t="n">
-        <v>-5.49050658734978</v>
+        <v>-5.591834653756597</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.190399571639083</v>
+        <v>1.149868345076356</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.4138397443391841</v>
+        <v>0.3125116779323667</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.635262477496254</v>
+        <v>3.574465637652164</v>
       </c>
     </row>
     <row r="2036">
@@ -48373,22 +48373,22 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821030660077627</v>
+        <v>3.821030660077626</v>
       </c>
       <c r="C2036" t="n">
         <v>3.386146341329173</v>
       </c>
       <c r="D2036" t="n">
-        <v>-5.413407985807908</v>
+        <v>-5.514736052214724</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.220426722692262</v>
+        <v>1.179895496129535</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.4138397443391841</v>
+        <v>0.3125116779323667</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.634450187932684</v>
+        <v>3.573653348088593</v>
       </c>
     </row>
     <row r="2037">
@@ -48396,22 +48396,22 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.832307024147909</v>
+        <v>3.832307024147908</v>
       </c>
       <c r="C2037" t="n">
         <v>3.396015120454245</v>
       </c>
       <c r="D2037" t="n">
-        <v>-5.423793180697797</v>
+        <v>-5.525121247104614</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.226141423861379</v>
+        <v>1.185610197298652</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.4034545494492948</v>
+        <v>0.3021264830424774</v>
       </c>
       <c r="G2037" t="n">
-        <v>3.638087850123823</v>
+        <v>3.577291010279732</v>
       </c>
     </row>
     <row r="2038">
@@ -48419,22 +48419,22 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.834415493735285</v>
+        <v>3.834415493735278</v>
       </c>
       <c r="C2038" t="n">
         <v>3.466852126230671</v>
       </c>
       <c r="D2038" t="n">
-        <v>-5.442381339420022</v>
+        <v>-5.543709405826839</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.289543166148914</v>
+        <v>1.249011939586187</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.3848663907270695</v>
+        <v>0.283538324320252</v>
       </c>
       <c r="G2038" t="n">
-        <v>3.697771960666913</v>
+        <v>3.636975120822822</v>
       </c>
     </row>
     <row r="2039">
@@ -48442,22 +48442,22 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.855120535496553</v>
+        <v>3.855120535496552</v>
       </c>
       <c r="C2039" t="n">
         <v>3.463721137048969</v>
       </c>
       <c r="D2039" t="n">
-        <v>-5.442679886116058</v>
+        <v>-5.544007952522874</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.286292758288798</v>
+        <v>1.245761531726072</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.3845678440310336</v>
+        <v>0.2832397776242161</v>
       </c>
       <c r="G2039" t="n">
-        <v>3.69446184346759</v>
+        <v>3.633665003623499</v>
       </c>
     </row>
     <row r="2040">
@@ -48465,22 +48465,22 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.81564321210886</v>
+        <v>3.815643212108854</v>
       </c>
       <c r="C2040" t="n">
         <v>3.468252031988361</v>
       </c>
       <c r="D2040" t="n">
-        <v>-5.34185675242563</v>
+        <v>-5.443184818832447</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.33115290670436</v>
+        <v>1.290621680141634</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.3970320595153874</v>
+        <v>0.2957039931085699</v>
       </c>
       <c r="G2040" t="n">
-        <v>3.706471267697593</v>
+        <v>3.645674427853503</v>
       </c>
     </row>
     <row r="2041">
@@ -48488,22 +48488,22 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.807356168121472</v>
+        <v>3.807356168121464</v>
       </c>
       <c r="C2041" t="n">
         <v>3.468381285466904</v>
       </c>
       <c r="D2041" t="n">
-        <v>-5.151075391673222</v>
+        <v>-5.252403458080039</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.407594704483867</v>
+        <v>1.36706347792114</v>
       </c>
       <c r="F2041" t="n">
-        <v>0.5878134202677947</v>
+        <v>0.4864853538609773</v>
       </c>
       <c r="G2041" t="n">
-        <v>3.821069337627581</v>
+        <v>3.76027249778349</v>
       </c>
     </row>
     <row r="2042">
@@ -48511,22 +48511,22 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.775233033906085</v>
+        <v>3.775233033906077</v>
       </c>
       <c r="C2042" t="n">
         <v>3.4482181312045</v>
       </c>
       <c r="D2042" t="n">
-        <v>-5.044112033823801</v>
+        <v>-5.145440100230617</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.430216893361232</v>
+        <v>1.389685666798505</v>
       </c>
       <c r="F2042" t="n">
-        <v>0.6462780282275962</v>
+        <v>0.5449499618207787</v>
       </c>
       <c r="G2042" t="n">
-        <v>3.835984948141058</v>
+        <v>3.775188108296968</v>
       </c>
     </row>
     <row r="2043">
@@ -48534,22 +48534,22 @@
         <v>45505</v>
       </c>
       <c r="B2043" t="n">
-        <v>3.785761685912989</v>
+        <v>3.785761685912981</v>
       </c>
       <c r="C2043" t="n">
         <v>3.483185067816559</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.988781445922038</v>
+        <v>-5.090109512328855</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.487316065133995</v>
+        <v>1.446784838571269</v>
       </c>
       <c r="F2043" t="n">
-        <v>0.7016086161293583</v>
+        <v>0.6002805497225409</v>
       </c>
       <c r="G2043" t="n">
-        <v>3.904150237494174</v>
+        <v>3.843353397650084</v>
       </c>
     </row>
     <row r="2044">
@@ -48557,22 +48557,22 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.743767956539899</v>
+        <v>3.743767956539891</v>
       </c>
       <c r="C2044" t="n">
         <v>3.476871635717997</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.976727319009076</v>
+        <v>-5.078055385415892</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.485824283800618</v>
+        <v>1.445293057237892</v>
       </c>
       <c r="F2044" t="n">
-        <v>0.7136627430423211</v>
+        <v>0.6123346766355037</v>
       </c>
       <c r="G2044" t="n">
-        <v>3.90506928154339</v>
+        <v>3.844272441699299</v>
       </c>
     </row>
     <row r="2045">
@@ -48580,22 +48580,22 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.725010844811014</v>
+        <v>3.725010844811005</v>
       </c>
       <c r="C2045" t="n">
         <v>3.478752265902132</v>
       </c>
       <c r="D2045" t="n">
-        <v>-5.054082809137045</v>
+        <v>-5.155410875543861</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.456762717933567</v>
+        <v>1.41623149137084</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.6363072529143518</v>
+        <v>0.5349791865075343</v>
       </c>
       <c r="G2045" t="n">
-        <v>3.860536617650744</v>
+        <v>3.799739777806653</v>
       </c>
     </row>
     <row r="2046">
@@ -48603,22 +48603,22 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.612322444382925</v>
+        <v>3.612322444382916</v>
       </c>
       <c r="C2046" t="n">
         <v>3.491603291780015</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.986034246445515</v>
+        <v>-5.087362312852331</v>
       </c>
       <c r="E2046" t="n">
-        <v>1.496833168888061</v>
+        <v>1.456301942325334</v>
       </c>
       <c r="F2046" t="n">
-        <v>0.7043558156058816</v>
+        <v>0.6030277491990641</v>
       </c>
       <c r="G2046" t="n">
-        <v>3.914216781143544</v>
+        <v>3.853419941299454</v>
       </c>
     </row>
     <row r="2047">
@@ -48626,22 +48626,22 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.645256780013432</v>
+        <v>3.645256780013423</v>
       </c>
       <c r="C2047" t="n">
         <v>3.511805961953609</v>
       </c>
       <c r="D2047" t="n">
-        <v>-5.217634639615016</v>
+        <v>-5.318962706021832</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.424395681793855</v>
+        <v>1.383864455231128</v>
       </c>
       <c r="F2047" t="n">
-        <v>0.7043558156058816</v>
+        <v>0.6030277491990641</v>
       </c>
       <c r="G2047" t="n">
-        <v>3.934419451317138</v>
+        <v>3.873622611473048</v>
       </c>
     </row>
     <row r="2048">
@@ -48649,22 +48649,22 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666747201498968</v>
+        <v>3.666747201498967</v>
       </c>
       <c r="C2048" t="n">
         <v>3.495412198020491</v>
       </c>
       <c r="D2048" t="n">
-        <v>-5.267686185144235</v>
+        <v>-5.369014251551052</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.387981299649049</v>
+        <v>1.347450073086322</v>
       </c>
       <c r="F2048" t="n">
-        <v>0.7043558156058816</v>
+        <v>0.6030277491990641</v>
       </c>
       <c r="G2048" t="n">
-        <v>3.91802568738402</v>
+        <v>3.85722884753993</v>
       </c>
     </row>
     <row r="2049">
@@ -48672,22 +48672,22 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.670048702800097</v>
+        <v>3.670048702800096</v>
       </c>
       <c r="C2049" t="n">
         <v>3.455664111613958</v>
       </c>
       <c r="D2049" t="n">
-        <v>-5.44279301772068</v>
+        <v>-5.544121084127497</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.278190480211938</v>
+        <v>1.237659253649211</v>
       </c>
       <c r="F2049" t="n">
-        <v>0.7043558156058816</v>
+        <v>0.6030277491990641</v>
       </c>
       <c r="G2049" t="n">
-        <v>3.878277600977487</v>
+        <v>3.817480761133397</v>
       </c>
     </row>
     <row r="2050">
@@ -48695,22 +48695,22 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.745573148660849</v>
+        <v>3.745573148660848</v>
       </c>
       <c r="C2050" t="n">
         <v>3.462686730610898</v>
       </c>
       <c r="D2050" t="n">
-        <v>-5.246692864290157</v>
+        <v>-5.348020930696974</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.363653160581087</v>
+        <v>1.32312193401836</v>
       </c>
       <c r="F2050" t="n">
-        <v>0.9004559690364045</v>
+        <v>0.799127902629587</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.002960312032741</v>
+        <v>3.94216347218865</v>
       </c>
     </row>
     <row r="2051">
@@ -48718,22 +48718,22 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.730570473395087</v>
+        <v>3.730570473395085</v>
       </c>
       <c r="C2051" t="n">
         <v>3.561857730183802</v>
       </c>
       <c r="D2051" t="n">
-        <v>-5.093667472176873</v>
+        <v>-5.194995538583689</v>
       </c>
       <c r="E2051" t="n">
-        <v>1.524034316999305</v>
+        <v>1.483503090436578</v>
       </c>
       <c r="F2051" t="n">
-        <v>1.053481361149688</v>
+        <v>0.9521532947428711</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.193946546873615</v>
+        <v>4.133149707029525</v>
       </c>
     </row>
     <row r="2052">
@@ -48741,22 +48741,22 @@
         <v>45514</v>
       </c>
       <c r="B2052" t="n">
-        <v>3.741278332791149</v>
+        <v>3.741278332791147</v>
       </c>
       <c r="C2052" t="n">
         <v>3.749323955092095</v>
       </c>
       <c r="D2052" t="n">
-        <v>-5.121974786050143</v>
+        <v>-5.22330285245696</v>
       </c>
       <c r="E2052" t="n">
-        <v>1.700177616358289</v>
+        <v>1.659646389795563</v>
       </c>
       <c r="F2052" t="n">
-        <v>1.053481361149688</v>
+        <v>0.9521532947428711</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.381412771781908</v>
+        <v>4.320615931937818</v>
       </c>
     </row>
     <row r="2053">
@@ -48764,22 +48764,22 @@
         <v>45515</v>
       </c>
       <c r="B2053" t="n">
-        <v>3.699115615620435</v>
+        <v>3.699115615620433</v>
       </c>
       <c r="C2053" t="n">
         <v>3.718726906446177</v>
       </c>
       <c r="D2053" t="n">
-        <v>-5.288568011163665</v>
+        <v>-5.389896077570482</v>
       </c>
       <c r="E2053" t="n">
-        <v>1.602943277666963</v>
+        <v>1.562412051104237</v>
       </c>
       <c r="F2053" t="n">
-        <v>0.886888136036166</v>
+        <v>0.7855600696293488</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.250859788067877</v>
+        <v>4.190062948223787</v>
       </c>
     </row>
     <row r="2054">
@@ -48787,22 +48787,22 @@
         <v>45516</v>
       </c>
       <c r="B2054" t="n">
-        <v>3.708182519285647</v>
+        <v>3.708182519285645</v>
       </c>
       <c r="C2054" t="n">
         <v>3.722403309107895</v>
       </c>
       <c r="D2054" t="n">
-        <v>-5.265532217802099</v>
+        <v>-5.366860284208916</v>
       </c>
       <c r="E2054" t="n">
-        <v>1.615833997673307</v>
+        <v>1.575302771110581</v>
       </c>
       <c r="F2054" t="n">
-        <v>0.886888136036166</v>
+        <v>0.7855600696293488</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.254536190729595</v>
+        <v>4.193739350885505</v>
       </c>
     </row>
     <row r="2055">
@@ -48810,22 +48810,22 @@
         <v>45517</v>
       </c>
       <c r="B2055" t="n">
-        <v>3.740581401399469</v>
+        <v>3.740581401399467</v>
       </c>
       <c r="C2055" t="n">
         <v>3.72002136423139</v>
       </c>
       <c r="D2055" t="n">
-        <v>-5.236286237346403</v>
+        <v>-5.337614303753219</v>
       </c>
       <c r="E2055" t="n">
-        <v>1.625150444979081</v>
+        <v>1.584619218416355</v>
       </c>
       <c r="F2055" t="n">
-        <v>0.886888136036166</v>
+        <v>0.7855600696293488</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.25215424585309</v>
+        <v>4.191357406009</v>
       </c>
     </row>
     <row r="2056">
@@ -48833,22 +48833,22 @@
         <v>45518</v>
       </c>
       <c r="B2056" t="n">
-        <v>3.699404642256372</v>
+        <v>3.699404642256368</v>
       </c>
       <c r="C2056" t="n">
         <v>3.717314603389025</v>
       </c>
       <c r="D2056" t="n">
-        <v>-5.343211785224254</v>
+        <v>-5.44453985163107</v>
       </c>
       <c r="E2056" t="n">
-        <v>1.579673464985576</v>
+        <v>1.539142238422849</v>
       </c>
       <c r="F2056" t="n">
-        <v>0.7799625881583147</v>
+        <v>0.6786345217514974</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.185292156284015</v>
+        <v>4.124495316439925</v>
       </c>
     </row>
     <row r="2057">
@@ -48856,22 +48856,22 @@
         <v>45519</v>
       </c>
       <c r="B2057" t="n">
-        <v>3.689942600701002</v>
+        <v>3.689942600700998</v>
       </c>
       <c r="C2057" t="n">
         <v>3.71874340553226</v>
       </c>
       <c r="D2057" t="n">
-        <v>-5.488230343731503</v>
+        <v>-5.589558410138319</v>
       </c>
       <c r="E2057" t="n">
-        <v>1.523094843725911</v>
+        <v>1.482563617163184</v>
       </c>
       <c r="F2057" t="n">
-        <v>0.6349440296510661</v>
+        <v>0.5336159632442489</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.099709823322899</v>
+        <v>4.038912983478809</v>
       </c>
     </row>
     <row r="2058">
@@ -48879,22 +48879,22 @@
         <v>45520</v>
       </c>
       <c r="B2058" t="n">
-        <v>3.711852429687013</v>
+        <v>3.71185242968701</v>
       </c>
       <c r="C2058" t="n">
         <v>3.818674644790013</v>
       </c>
       <c r="D2058" t="n">
-        <v>-5.60657210951622</v>
+        <v>-5.707900175923037</v>
       </c>
       <c r="E2058" t="n">
-        <v>1.575689376669777</v>
+        <v>1.53515815010705</v>
       </c>
       <c r="F2058" t="n">
-        <v>0.6456300682139562</v>
+        <v>0.5443020018071389</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.206052685718387</v>
+        <v>4.145255845874297</v>
       </c>
     </row>
     <row r="2059">
@@ -48902,22 +48902,22 @@
         <v>45521</v>
       </c>
       <c r="B2059" t="n">
-        <v>3.714879051790806</v>
+        <v>3.7148790517908</v>
       </c>
       <c r="C2059" t="n">
         <v>3.816460341915952</v>
       </c>
       <c r="D2059" t="n">
-        <v>-5.657982531836928</v>
+        <v>-5.759310598243744</v>
       </c>
       <c r="E2059" t="n">
-        <v>1.552910904867433</v>
+        <v>1.512379678304706</v>
       </c>
       <c r="F2059" t="n">
-        <v>0.6456300682139562</v>
+        <v>0.5443020018071389</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.203838382844325</v>
+        <v>4.143041543000235</v>
       </c>
     </row>
     <row r="2060">
@@ -48925,22 +48925,22 @@
         <v>45522</v>
       </c>
       <c r="B2060" t="n">
-        <v>3.704757949437335</v>
+        <v>3.704757949437328</v>
       </c>
       <c r="C2060" t="n">
         <v>3.816363469990241</v>
       </c>
       <c r="D2060" t="n">
-        <v>-5.73740198304468</v>
+        <v>-5.838730049451496</v>
       </c>
       <c r="E2060" t="n">
-        <v>1.521046252458621</v>
+        <v>1.480515025895894</v>
       </c>
       <c r="F2060" t="n">
-        <v>0.6456300682139562</v>
+        <v>0.5443020018071389</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.203741510918615</v>
+        <v>4.142944671074525</v>
       </c>
     </row>
     <row r="2061">
@@ -48948,22 +48948,22 @@
         <v>45523</v>
       </c>
       <c r="B2061" t="n">
-        <v>3.736804952298403</v>
+        <v>3.736804952298394</v>
       </c>
       <c r="C2061" t="n">
         <v>3.816357363548284</v>
       </c>
       <c r="D2061" t="n">
-        <v>-5.832864980961897</v>
+        <v>-5.934193047368714</v>
       </c>
       <c r="E2061" t="n">
-        <v>1.482854946849777</v>
+        <v>1.44232372028705</v>
       </c>
       <c r="F2061" t="n">
-        <v>0.6456300682139562</v>
+        <v>0.5443020018071389</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.203735404476658</v>
+        <v>4.142938564632567</v>
       </c>
     </row>
     <row r="2062">
@@ -48971,22 +48971,22 @@
         <v>45524</v>
       </c>
       <c r="B2062" t="n">
-        <v>3.715372960218006</v>
+        <v>3.715372960217997</v>
       </c>
       <c r="C2062" t="n">
         <v>3.814453760110895</v>
       </c>
       <c r="D2062" t="n">
-        <v>-5.768489070111182</v>
+        <v>-5.869817136517999</v>
       </c>
       <c r="E2062" t="n">
-        <v>1.506701707752673</v>
+        <v>1.466170481189947</v>
       </c>
       <c r="F2062" t="n">
-        <v>0.7100059790646713</v>
+        <v>0.6086779126578541</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.240457347549698</v>
+        <v>4.179660507705607</v>
       </c>
     </row>
     <row r="2063">
@@ -48994,22 +48994,22 @@
         <v>45525</v>
       </c>
       <c r="B2063" t="n">
-        <v>3.736089413353541</v>
+        <v>3.736089413353533</v>
       </c>
       <c r="C2063" t="n">
         <v>3.820187577858621</v>
       </c>
       <c r="D2063" t="n">
-        <v>-5.823858232243376</v>
+        <v>-5.925186298650193</v>
       </c>
       <c r="E2063" t="n">
-        <v>1.490287860647523</v>
+        <v>1.449756634084796</v>
       </c>
       <c r="F2063" t="n">
-        <v>0.7100059790646713</v>
+        <v>0.6086779126578541</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.246191165297424</v>
+        <v>4.185394325453334</v>
       </c>
     </row>
     <row r="2064">
@@ -49017,22 +49017,22 @@
         <v>45526</v>
       </c>
       <c r="B2064" t="n">
-        <v>3.736822870113285</v>
+        <v>3.736822870113276</v>
       </c>
       <c r="C2064" t="n">
         <v>3.819725941201554</v>
       </c>
       <c r="D2064" t="n">
-        <v>-5.842076699240985</v>
+        <v>-5.943404765647801</v>
       </c>
       <c r="E2064" t="n">
-        <v>1.482538837191412</v>
+        <v>1.442007610628685</v>
       </c>
       <c r="F2064" t="n">
-        <v>0.6848995418088292</v>
+        <v>0.5835714754020119</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.230665666286852</v>
+        <v>4.169868826442761</v>
       </c>
     </row>
     <row r="2065">
@@ -49040,22 +49040,22 @@
         <v>45527</v>
       </c>
       <c r="B2065" t="n">
-        <v>3.790272500113693</v>
+        <v>3.790272500113684</v>
       </c>
       <c r="C2065" t="n">
         <v>3.839600334051872</v>
       </c>
       <c r="D2065" t="n">
-        <v>-5.803393263897054</v>
+        <v>-5.904721330303871</v>
       </c>
       <c r="E2065" t="n">
-        <v>1.517886604179302</v>
+        <v>1.477355377616576</v>
       </c>
       <c r="F2065" t="n">
-        <v>0.6848995418088292</v>
+        <v>0.5835714754020119</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.25054005913717</v>
+        <v>4.18974321929308</v>
       </c>
     </row>
     <row r="2066">
@@ -49063,22 +49063,22 @@
         <v>45528</v>
       </c>
       <c r="B2066" t="n">
-        <v>3.794486844016438</v>
+        <v>3.794486844016436</v>
       </c>
       <c r="C2066" t="n">
         <v>3.8233010345766</v>
       </c>
       <c r="D2066" t="n">
-        <v>-5.697358268691745</v>
+        <v>-5.798686335098561</v>
       </c>
       <c r="E2066" t="n">
-        <v>1.544001302786154</v>
+        <v>1.503470076223428</v>
       </c>
       <c r="F2066" t="n">
-        <v>0.6848995418088292</v>
+        <v>0.5835714754020119</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.234240759661898</v>
+        <v>4.173443919817807</v>
       </c>
     </row>
     <row r="2067">
@@ -49086,22 +49086,22 @@
         <v>45529</v>
       </c>
       <c r="B2067" t="n">
-        <v>3.79470509330767</v>
+        <v>3.794705093307668</v>
       </c>
       <c r="C2067" t="n">
         <v>3.825731984040646</v>
       </c>
       <c r="D2067" t="n">
-        <v>-5.51414660555865</v>
+        <v>-5.615474671965466</v>
       </c>
       <c r="E2067" t="n">
-        <v>1.619716917503438</v>
+        <v>1.579185690940712</v>
       </c>
       <c r="F2067" t="n">
-        <v>0.6848995418088292</v>
+        <v>0.5835714754020119</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.236671709125944</v>
+        <v>4.175874869281854</v>
       </c>
     </row>
     <row r="2068">
@@ -49109,22 +49109,22 @@
         <v>45530</v>
       </c>
       <c r="B2068" t="n">
-        <v>3.776846557863551</v>
+        <v>3.776846557863549</v>
       </c>
       <c r="C2068" t="n">
         <v>3.808676390120023</v>
       </c>
       <c r="D2068" t="n">
-        <v>-5.442425158544799</v>
+        <v>-5.543753224951615</v>
       </c>
       <c r="E2068" t="n">
-        <v>1.631349902388356</v>
+        <v>1.590818675825629</v>
       </c>
       <c r="F2068" t="n">
-        <v>0.7566209888226798</v>
+        <v>0.6552929224158626</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.262648983413631</v>
+        <v>4.201852143569541</v>
       </c>
     </row>
     <row r="2069">
@@ -49132,22 +49132,22 @@
         <v>45531</v>
       </c>
       <c r="B2069" t="n">
-        <v>3.723789705394113</v>
+        <v>3.723789705394109</v>
       </c>
       <c r="C2069" t="n">
         <v>3.755592136041195</v>
       </c>
       <c r="D2069" t="n">
-        <v>-5.420052132937093</v>
+        <v>-5.521380199343909</v>
       </c>
       <c r="E2069" t="n">
-        <v>1.58721485855261</v>
+        <v>1.546683631989883</v>
       </c>
       <c r="F2069" t="n">
-        <v>0.7678767399355814</v>
+        <v>0.6665486735287641</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.216318180002544</v>
+        <v>4.155521340158454</v>
       </c>
     </row>
     <row r="2070">
@@ -49155,22 +49155,22 @@
         <v>45532</v>
       </c>
       <c r="B2070" t="n">
-        <v>3.715607446456731</v>
+        <v>3.715607446456726</v>
       </c>
       <c r="C2070" t="n">
         <v>3.94079034092655</v>
       </c>
       <c r="D2070" t="n">
-        <v>-5.453068428847837</v>
+        <v>-5.554396495254654</v>
       </c>
       <c r="E2070" t="n">
-        <v>1.759206545073667</v>
+        <v>1.71867531851094</v>
       </c>
       <c r="F2070" t="n">
-        <v>0.6984393632688297</v>
+        <v>0.5971112968620125</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.359853958887848</v>
+        <v>4.299057119043757</v>
       </c>
     </row>
     <row r="2071">
@@ -49178,22 +49178,22 @@
         <v>45533</v>
       </c>
       <c r="B2071" t="n">
-        <v>3.713762536883682</v>
+        <v>3.713762536883674</v>
       </c>
       <c r="C2071" t="n">
         <v>3.932711566754799</v>
       </c>
       <c r="D2071" t="n">
-        <v>-5.441540793198229</v>
+        <v>-5.542868859605045</v>
       </c>
       <c r="E2071" t="n">
-        <v>1.755738825161759</v>
+        <v>1.715207598599033</v>
       </c>
       <c r="F2071" t="n">
-        <v>0.7574400214701922</v>
+        <v>0.6561119550633749</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.387175579636915</v>
+        <v>4.326378739792824</v>
       </c>
     </row>
     <row r="2072">
@@ -49201,22 +49201,22 @@
         <v>45534</v>
       </c>
       <c r="B2072" t="n">
-        <v>3.717150699236303</v>
+        <v>3.717150699236295</v>
       </c>
       <c r="C2072" t="n">
         <v>3.936379679276587</v>
       </c>
       <c r="D2072" t="n">
-        <v>-5.538882294540597</v>
+        <v>-5.640210360947414</v>
       </c>
       <c r="E2072" t="n">
-        <v>1.720470337146601</v>
+        <v>1.679939110583874</v>
       </c>
       <c r="F2072" t="n">
-        <v>0.7130198393047038</v>
+        <v>0.6116917728978866</v>
       </c>
       <c r="G2072" t="n">
-        <v>4.36419158285941</v>
+        <v>4.303394743015319</v>
       </c>
     </row>
     <row r="2073">
@@ -49224,22 +49224,22 @@
         <v>45535</v>
       </c>
       <c r="B2073" t="n">
-        <v>3.70520107942769</v>
+        <v>3.705201079427681</v>
       </c>
       <c r="C2073" t="n">
         <v>3.937630761469426</v>
       </c>
       <c r="D2073" t="n">
-        <v>-5.624738323880564</v>
+        <v>-5.726066390287381</v>
       </c>
       <c r="E2073" t="n">
-        <v>1.687379007603452</v>
+        <v>1.646847781040726</v>
       </c>
       <c r="F2073" t="n">
-        <v>0.6706437700785688</v>
+        <v>0.5693157036717515</v>
       </c>
       <c r="G2073" t="n">
-        <v>4.340017023516567</v>
+        <v>4.279220183672477</v>
       </c>
     </row>
     <row r="2074">
@@ -49247,22 +49247,22 @@
         <v>45536</v>
       </c>
       <c r="B2074" t="n">
-        <v>3.69183549961038</v>
+        <v>3.691835499610379</v>
       </c>
       <c r="C2074" t="n">
         <v>3.920049963289927</v>
       </c>
       <c r="D2074" t="n">
-        <v>-5.633575121296683</v>
+        <v>-5.7349031877035</v>
       </c>
       <c r="E2074" t="n">
-        <v>1.666263490457506</v>
+        <v>1.62573226389478</v>
       </c>
       <c r="F2074" t="n">
-        <v>0.6632015974372181</v>
+        <v>0.5618735310304008</v>
       </c>
       <c r="G2074" t="n">
-        <v>4.317970921752258</v>
+        <v>4.257174081908168</v>
       </c>
     </row>
     <row r="2075">
@@ -49270,22 +49270,22 @@
         <v>45537</v>
       </c>
       <c r="B2075" t="n">
-        <v>3.715544411667459</v>
+        <v>3.715544411667452</v>
       </c>
       <c r="C2075" t="n">
         <v>3.930214474334977</v>
       </c>
       <c r="D2075" t="n">
-        <v>-5.724957683862142</v>
+        <v>-5.826285750268958</v>
       </c>
       <c r="E2075" t="n">
-        <v>1.639874976476372</v>
+        <v>1.599343749913646</v>
       </c>
       <c r="F2075" t="n">
-        <v>0.6266367127178734</v>
+        <v>0.5253086463110561</v>
       </c>
       <c r="G2075" t="n">
-        <v>4.306196501965701</v>
+        <v>4.245399662121611</v>
       </c>
     </row>
     <row r="2076">
@@ -49293,22 +49293,22 @@
         <v>45538</v>
       </c>
       <c r="B2076" t="n">
-        <v>3.673978374889197</v>
+        <v>3.673978374889188</v>
       </c>
       <c r="C2076" t="n">
         <v>4.032342732159245</v>
       </c>
       <c r="D2076" t="n">
-        <v>-5.713250965875136</v>
+        <v>-5.814579032281952</v>
       </c>
       <c r="E2076" t="n">
-        <v>1.746685921495443</v>
+        <v>1.706154694932716</v>
       </c>
       <c r="F2076" t="n">
-        <v>0.6383434307048798</v>
+        <v>0.5370153642980625</v>
       </c>
       <c r="G2076" t="n">
-        <v>4.415348790582173</v>
+        <v>4.354551950738083</v>
       </c>
     </row>
     <row r="2077">
@@ -49316,22 +49316,22 @@
         <v>45539</v>
       </c>
       <c r="B2077" t="n">
-        <v>3.682476099409572</v>
+        <v>3.682476099409563</v>
       </c>
       <c r="C2077" t="n">
         <v>4.03537507089065</v>
       </c>
       <c r="D2077" t="n">
-        <v>-5.784163039617413</v>
+        <v>-5.885491106024229</v>
       </c>
       <c r="E2077" t="n">
-        <v>1.721353430729937</v>
+        <v>1.68082220416721</v>
       </c>
       <c r="F2077" t="n">
-        <v>0.6383434307048798</v>
+        <v>0.5370153642980625</v>
       </c>
       <c r="G2077" t="n">
-        <v>4.418381129313578</v>
+        <v>4.357584289469488</v>
       </c>
     </row>
     <row r="2078">
@@ -49339,22 +49339,22 @@
         <v>45540</v>
       </c>
       <c r="B2078" t="n">
-        <v>3.67289517745257</v>
+        <v>3.672895177452569</v>
       </c>
       <c r="C2078" t="n">
         <v>4.036193896622915</v>
       </c>
       <c r="D2078" t="n">
-        <v>-5.794479137783765</v>
+        <v>-5.895807204190581</v>
       </c>
       <c r="E2078" t="n">
-        <v>1.718045817195661</v>
+        <v>1.677514590632934</v>
       </c>
       <c r="F2078" t="n">
-        <v>0.6383434307048798</v>
+        <v>0.5370153642980625</v>
       </c>
       <c r="G2078" t="n">
-        <v>4.419199955045842</v>
+        <v>4.358403115201752</v>
       </c>
     </row>
     <row r="2079">
@@ -49362,22 +49362,22 @@
         <v>45541</v>
       </c>
       <c r="B2079" t="n">
-        <v>3.623960959762292</v>
+        <v>3.623960959762283</v>
       </c>
       <c r="C2079" t="n">
         <v>4.035372563535004</v>
       </c>
       <c r="D2079" t="n">
-        <v>-5.794385169766392</v>
+        <v>-5.895713236173209</v>
       </c>
       <c r="E2079" t="n">
-        <v>1.717262071314699</v>
+        <v>1.676730844751973</v>
       </c>
       <c r="F2079" t="n">
-        <v>0.6387132920521977</v>
+        <v>0.5373852256453805</v>
       </c>
       <c r="G2079" t="n">
-        <v>4.418600538766323</v>
+        <v>4.357803698922233</v>
       </c>
     </row>
     <row r="2080">
@@ -49385,22 +49385,22 @@
         <v>45542</v>
       </c>
       <c r="B2080" t="n">
-        <v>3.800870306884084</v>
+        <v>3.800870306884075</v>
       </c>
       <c r="C2080" t="n">
         <v>4.029604549479358</v>
       </c>
       <c r="D2080" t="n">
-        <v>-5.937986333789778</v>
+        <v>-6.039314400196594</v>
       </c>
       <c r="E2080" t="n">
-        <v>1.654053591649699</v>
+        <v>1.613522365086972</v>
       </c>
       <c r="F2080" t="n">
-        <v>0.6387132920521977</v>
+        <v>0.5373852256453805</v>
       </c>
       <c r="G2080" t="n">
-        <v>4.412832524710677</v>
+        <v>4.352035684866586</v>
       </c>
     </row>
     <row r="2081">
@@ -49408,22 +49408,22 @@
         <v>45543</v>
       </c>
       <c r="B2081" t="n">
-        <v>3.671015692129648</v>
+        <v>3.671015692129645</v>
       </c>
       <c r="C2081" t="n">
         <v>4.029604549479358</v>
       </c>
       <c r="D2081" t="n">
-        <v>-5.937037910671739</v>
+        <v>-6.038365977078556</v>
       </c>
       <c r="E2081" t="n">
-        <v>1.654432960896914</v>
+        <v>1.613901734334187</v>
       </c>
       <c r="F2081" t="n">
-        <v>0.6387132920521977</v>
+        <v>0.5373852256453805</v>
       </c>
       <c r="G2081" t="n">
-        <v>4.412832524710677</v>
+        <v>4.352035684866586</v>
       </c>
     </row>
     <row r="2082">
@@ -49431,22 +49431,22 @@
         <v>45544</v>
       </c>
       <c r="B2082" t="n">
-        <v>3.904173816052351</v>
+        <v>3.904173816052348</v>
       </c>
       <c r="C2082" t="n">
         <v>4.04233215746045</v>
       </c>
       <c r="D2082" t="n">
-        <v>-6.037307728630759</v>
+        <v>-6.138635795037576</v>
       </c>
       <c r="E2082" t="n">
-        <v>1.627052641694398</v>
+        <v>1.586521415131672</v>
       </c>
       <c r="F2082" t="n">
-        <v>0.6387132920521977</v>
+        <v>0.5373852256453805</v>
       </c>
       <c r="G2082" t="n">
-        <v>4.425560132691769</v>
+        <v>4.364763292847678</v>
       </c>
     </row>
     <row r="2083">
@@ -49454,22 +49454,22 @@
         <v>45545</v>
       </c>
       <c r="B2083" t="n">
-        <v>3.740179607813495</v>
+        <v>3.740179607813492</v>
       </c>
       <c r="C2083" t="n">
         <v>4.044278155884838</v>
       </c>
       <c r="D2083" t="n">
-        <v>-6.031315481841948</v>
+        <v>-6.132643548248764</v>
       </c>
       <c r="E2083" t="n">
-        <v>1.63139553883431</v>
+        <v>1.590864312271584</v>
       </c>
       <c r="F2083" t="n">
-        <v>0.6387132920521977</v>
+        <v>0.5373852256453805</v>
       </c>
       <c r="G2083" t="n">
-        <v>4.427506131116156</v>
+        <v>4.366709291272066</v>
       </c>
     </row>
     <row r="2084">
@@ -49477,22 +49477,22 @@
         <v>45546</v>
       </c>
       <c r="B2084" t="n">
-        <v>3.765050796537944</v>
+        <v>3.765050796537942</v>
       </c>
       <c r="C2084" t="n">
         <v>4.037932291902607</v>
       </c>
       <c r="D2084" t="n">
-        <v>-5.94275752071118</v>
+        <v>-6.044085587117997</v>
       </c>
       <c r="E2084" t="n">
-        <v>1.660472859304387</v>
+        <v>1.61994163274166</v>
       </c>
       <c r="F2084" t="n">
-        <v>0.6387132920521977</v>
+        <v>0.5373852256453805</v>
       </c>
       <c r="G2084" t="n">
-        <v>4.421160267133925</v>
+        <v>4.360363427289835</v>
       </c>
     </row>
     <row r="2085">
@@ -49500,22 +49500,22 @@
         <v>45547</v>
       </c>
       <c r="B2085" t="n">
-        <v>3.758409170771816</v>
+        <v>3.758409170771814</v>
       </c>
       <c r="C2085" t="n">
         <v>4.037240969341602</v>
       </c>
       <c r="D2085" t="n">
-        <v>-5.924998443208106</v>
+        <v>-6.026326509614923</v>
       </c>
       <c r="E2085" t="n">
-        <v>1.666885167744612</v>
+        <v>1.626353941181885</v>
       </c>
       <c r="F2085" t="n">
-        <v>0.6387132920521977</v>
+        <v>0.5373852256453805</v>
       </c>
       <c r="G2085" t="n">
-        <v>4.420468944572921</v>
+        <v>4.359672104728831</v>
       </c>
     </row>
     <row r="2086">
@@ -49523,22 +49523,22 @@
         <v>45548</v>
       </c>
       <c r="B2086" t="n">
-        <v>3.801340597109721</v>
+        <v>3.80134059710972</v>
       </c>
       <c r="C2086" t="n">
         <v>4.050023155250189</v>
       </c>
       <c r="D2086" t="n">
-        <v>-5.825368292159038</v>
+        <v>-5.926696358565855</v>
       </c>
       <c r="E2086" t="n">
-        <v>1.719519414072826</v>
+        <v>1.678988187510099</v>
       </c>
       <c r="F2086" t="n">
-        <v>0.7383434431012652</v>
+        <v>0.637015376694448</v>
       </c>
       <c r="G2086" t="n">
-        <v>4.493029221110948</v>
+        <v>4.432232381266858</v>
       </c>
     </row>
     <row r="2087">
@@ -49546,22 +49546,22 @@
         <v>45549</v>
       </c>
       <c r="B2087" t="n">
-        <v>3.798465546843996</v>
+        <v>3.798465546843994</v>
       </c>
       <c r="C2087" t="n">
         <v>4.239177420748915</v>
       </c>
       <c r="D2087" t="n">
-        <v>-5.87476780084805</v>
+        <v>-5.976095867254866</v>
       </c>
       <c r="E2087" t="n">
-        <v>1.888913876095948</v>
+        <v>1.848382649533221</v>
       </c>
       <c r="F2087" t="n">
-        <v>0.7486022765330099</v>
+        <v>0.6472742101261927</v>
       </c>
       <c r="G2087" t="n">
-        <v>4.688338786668722</v>
+        <v>4.627541946824631</v>
       </c>
     </row>
     <row r="2088">
@@ -49569,22 +49569,22 @@
         <v>45550</v>
       </c>
       <c r="B2088" t="n">
-        <v>3.77218650835186</v>
+        <v>3.772186508351855</v>
       </c>
       <c r="C2088" t="n">
         <v>4.226366093851778</v>
       </c>
       <c r="D2088" t="n">
-        <v>-5.668083327205673</v>
+        <v>-5.76941139361249</v>
       </c>
       <c r="E2088" t="n">
-        <v>1.95877633865576</v>
+        <v>1.918245112093034</v>
       </c>
       <c r="F2088" t="n">
-        <v>0.9552867501753856</v>
+        <v>0.8539586837685683</v>
       </c>
       <c r="G2088" t="n">
-        <v>4.799538143957009</v>
+        <v>4.738741304112919</v>
       </c>
     </row>
     <row r="2089">
@@ -49592,22 +49592,22 @@
         <v>45551</v>
       </c>
       <c r="B2089" t="n">
-        <v>3.76339283855127</v>
+        <v>3.763392838551265</v>
       </c>
       <c r="C2089" t="n">
         <v>4.228367607505882</v>
       </c>
       <c r="D2089" t="n">
-        <v>-5.7022402222032</v>
+        <v>-5.803568288610016</v>
       </c>
       <c r="E2089" t="n">
-        <v>1.947115094310855</v>
+        <v>1.906583867748128</v>
       </c>
       <c r="F2089" t="n">
-        <v>0.8717029806345731</v>
+        <v>0.7703749142277558</v>
       </c>
       <c r="G2089" t="n">
-        <v>4.751389395886626</v>
+        <v>4.690592556042536</v>
       </c>
     </row>
     <row r="2090">
@@ -49615,22 +49615,22 @@
         <v>45552</v>
       </c>
       <c r="B2090" t="n">
-        <v>3.805590565041111</v>
+        <v>3.805590565041106</v>
       </c>
       <c r="C2090" t="n">
         <v>4.58186472149555</v>
       </c>
       <c r="D2090" t="n">
-        <v>-5.609650743141743</v>
+        <v>-5.71097880954856</v>
       </c>
       <c r="E2090" t="n">
-        <v>2.337647999925105</v>
+        <v>2.297116773362378</v>
       </c>
       <c r="F2090" t="n">
-        <v>0.8717029806345731</v>
+        <v>0.7703749142277558</v>
       </c>
       <c r="G2090" t="n">
-        <v>5.104886509876294</v>
+        <v>5.044089670032204</v>
       </c>
     </row>
     <row r="2091">
@@ -49638,22 +49638,22 @@
         <v>45553</v>
       </c>
       <c r="B2091" t="n">
-        <v>3.832164354497403</v>
+        <v>3.832164354497396</v>
       </c>
       <c r="C2091" t="n">
         <v>4.586427833062654</v>
       </c>
       <c r="D2091" t="n">
-        <v>-5.682811346914888</v>
+        <v>-5.784139413321705</v>
       </c>
       <c r="E2091" t="n">
-        <v>2.312946869982951</v>
+        <v>2.272415643420224</v>
       </c>
       <c r="F2091" t="n">
-        <v>0.8436817806003301</v>
+        <v>0.7423537141935128</v>
       </c>
       <c r="G2091" t="n">
-        <v>5.092636901422853</v>
+        <v>5.031840061578762</v>
       </c>
     </row>
     <row r="2092">
@@ -49661,22 +49661,22 @@
         <v>45554</v>
       </c>
       <c r="B2092" t="n">
-        <v>3.858310890492296</v>
+        <v>3.858310890492286</v>
       </c>
       <c r="C2092" t="n">
         <v>4.636257774386181</v>
       </c>
       <c r="D2092" t="n">
-        <v>-5.630595037118546</v>
+        <v>-5.731923103525363</v>
       </c>
       <c r="E2092" t="n">
-        <v>2.383663335225015</v>
+        <v>2.343132108662288</v>
       </c>
       <c r="F2092" t="n">
-        <v>0.8436817806003301</v>
+        <v>0.7423537141935128</v>
       </c>
       <c r="G2092" t="n">
-        <v>5.14246684274638</v>
+        <v>5.081670002902289</v>
       </c>
     </row>
     <row r="2093">
@@ -49684,22 +49684,22 @@
         <v>45555</v>
       </c>
       <c r="B2093" t="n">
-        <v>3.844935596436478</v>
+        <v>3.844935596436468</v>
       </c>
       <c r="C2093" t="n">
         <v>4.645071744596192</v>
       </c>
       <c r="D2093" t="n">
-        <v>-5.578087709608051</v>
+        <v>-5.679415776014868</v>
       </c>
       <c r="E2093" t="n">
-        <v>2.413480236439224</v>
+        <v>2.372949009876497</v>
       </c>
       <c r="F2093" t="n">
-        <v>0.896189108110825</v>
+        <v>0.7948610417040077</v>
       </c>
       <c r="G2093" t="n">
-        <v>5.182785209462688</v>
+        <v>5.121988369618597</v>
       </c>
     </row>
     <row r="2094">
@@ -49707,22 +49707,22 @@
         <v>45556</v>
       </c>
       <c r="B2094" t="n">
-        <v>3.848376866039487</v>
+        <v>3.848376866039477</v>
       </c>
       <c r="C2094" t="n">
         <v>4.640709328635389</v>
       </c>
       <c r="D2094" t="n">
-        <v>-5.592843033808192</v>
+        <v>-5.694171100215009</v>
       </c>
       <c r="E2094" t="n">
-        <v>2.403215690798365</v>
+        <v>2.362684464235638</v>
       </c>
       <c r="F2094" t="n">
-        <v>0.896189108110825</v>
+        <v>0.7948610417040077</v>
       </c>
       <c r="G2094" t="n">
-        <v>5.178422793501884</v>
+        <v>5.117625953657794</v>
       </c>
     </row>
     <row r="2095">
@@ -49730,22 +49730,22 @@
         <v>45557</v>
       </c>
       <c r="B2095" t="n">
-        <v>3.868153115524482</v>
+        <v>3.868153115524471</v>
       </c>
       <c r="C2095" t="n">
         <v>4.631633832051669</v>
       </c>
       <c r="D2095" t="n">
-        <v>-5.54337841043828</v>
+        <v>-5.644706476845097</v>
       </c>
       <c r="E2095" t="n">
-        <v>2.413926043562609</v>
+        <v>2.373394816999883</v>
       </c>
       <c r="F2095" t="n">
-        <v>0.9456537314807366</v>
+        <v>0.8443256650739194</v>
       </c>
       <c r="G2095" t="n">
-        <v>5.199026070940111</v>
+        <v>5.138229231096021</v>
       </c>
     </row>
     <row r="2096">
@@ -49753,22 +49753,22 @@
         <v>45558</v>
       </c>
       <c r="B2096" t="n">
-        <v>3.849040239867955</v>
+        <v>3.849040239867945</v>
       </c>
       <c r="C2096" t="n">
         <v>4.628041499766604</v>
       </c>
       <c r="D2096" t="n">
-        <v>-5.380270418284665</v>
+        <v>-5.481598484691482</v>
       </c>
       <c r="E2096" t="n">
-        <v>2.47557690813899</v>
+        <v>2.435045681576263</v>
       </c>
       <c r="F2096" t="n">
-        <v>1.108761723634352</v>
+        <v>1.007433657227535</v>
       </c>
       <c r="G2096" t="n">
-        <v>5.293298533947215</v>
+        <v>5.232501694103124</v>
       </c>
     </row>
     <row r="2097">
@@ -49776,22 +49776,22 @@
         <v>45559</v>
       </c>
       <c r="B2097" t="n">
-        <v>3.870204928232971</v>
+        <v>3.870204928232968</v>
       </c>
       <c r="C2097" t="n">
         <v>4.637088536457732</v>
       </c>
       <c r="D2097" t="n">
-        <v>-5.359627327483437</v>
+        <v>-5.460955393890254</v>
       </c>
       <c r="E2097" t="n">
-        <v>2.492881181150609</v>
+        <v>2.452349954587882</v>
       </c>
       <c r="F2097" t="n">
-        <v>1.108761723634352</v>
+        <v>1.007433657227535</v>
       </c>
       <c r="G2097" t="n">
-        <v>5.302345570638344</v>
+        <v>5.241548730794253</v>
       </c>
     </row>
     <row r="2098">
@@ -49799,22 +49799,22 @@
         <v>45560</v>
       </c>
       <c r="B2098" t="n">
-        <v>3.855534437179674</v>
+        <v>3.855534437179672</v>
       </c>
       <c r="C2098" t="n">
         <v>4.637946001443853</v>
       </c>
       <c r="D2098" t="n">
-        <v>-5.422335243957995</v>
+        <v>-5.523663310364812</v>
       </c>
       <c r="E2098" t="n">
-        <v>2.468655479546907</v>
+        <v>2.428124252984181</v>
       </c>
       <c r="F2098" t="n">
-        <v>1.046053807159794</v>
+        <v>0.9447257407529769</v>
       </c>
       <c r="G2098" t="n">
-        <v>5.26557828573973</v>
+        <v>5.20478144589564</v>
       </c>
     </row>
     <row r="2099">
@@ -49822,22 +49822,22 @@
         <v>45561</v>
       </c>
       <c r="B2099" t="n">
-        <v>3.884687848967721</v>
+        <v>3.884687848967719</v>
       </c>
       <c r="C2099" t="n">
         <v>4.600855418234206</v>
       </c>
       <c r="D2099" t="n">
-        <v>-5.374327120114303</v>
+        <v>-5.475655186521119</v>
       </c>
       <c r="E2099" t="n">
-        <v>2.450768145874737</v>
+        <v>2.41023691931201</v>
       </c>
       <c r="F2099" t="n">
-        <v>1.046053807159794</v>
+        <v>0.9447257407529769</v>
       </c>
       <c r="G2099" t="n">
-        <v>5.228487702530082</v>
+        <v>5.167690862685992</v>
       </c>
     </row>
     <row r="2100">
@@ -49845,22 +49845,22 @@
         <v>45562</v>
       </c>
       <c r="B2100" t="n">
-        <v>3.895362357018612</v>
+        <v>3.895362357018607</v>
       </c>
       <c r="C2100" t="n">
         <v>4.604787671792156</v>
       </c>
       <c r="D2100" t="n">
-        <v>-5.224209064892405</v>
+        <v>-5.325537131299222</v>
       </c>
       <c r="E2100" t="n">
-        <v>2.514747621521446</v>
+        <v>2.474216394958719</v>
       </c>
       <c r="F2100" t="n">
-        <v>1.196171862381691</v>
+        <v>1.094843795974874</v>
       </c>
       <c r="G2100" t="n">
-        <v>5.322490789221171</v>
+        <v>5.261693949377081</v>
       </c>
     </row>
     <row r="2101">
@@ -49868,22 +49868,22 @@
         <v>45563</v>
       </c>
       <c r="B2101" t="n">
-        <v>3.891610981075135</v>
+        <v>3.89161098107513</v>
       </c>
       <c r="C2101" t="n">
         <v>4.599686764399193</v>
       </c>
       <c r="D2101" t="n">
-        <v>-5.032274263638532</v>
+        <v>-5.133602330045348</v>
       </c>
       <c r="E2101" t="n">
-        <v>2.586420634630032</v>
+        <v>2.545889408067306</v>
       </c>
       <c r="F2101" t="n">
-        <v>1.196171862381691</v>
+        <v>1.094843795974874</v>
       </c>
       <c r="G2101" t="n">
-        <v>5.317389881828208</v>
+        <v>5.256593041984118</v>
       </c>
     </row>
     <row r="2102">
@@ -49891,22 +49891,22 @@
         <v>45564</v>
       </c>
       <c r="B2102" t="n">
-        <v>3.872432493435445</v>
+        <v>3.872432493435436</v>
       </c>
       <c r="C2102" t="n">
         <v>4.595040673788288</v>
       </c>
       <c r="D2102" t="n">
-        <v>-4.914100885620604</v>
+        <v>-5.01542895202742</v>
       </c>
       <c r="E2102" t="n">
-        <v>2.629043895226299</v>
+        <v>2.588512668663572</v>
       </c>
       <c r="F2102" t="n">
-        <v>1.314345240399619</v>
+        <v>1.213017173992801</v>
       </c>
       <c r="G2102" t="n">
-        <v>5.383647818028059</v>
+        <v>5.322850978183969</v>
       </c>
     </row>
     <row r="2103">
@@ -49914,22 +49914,22 @@
         <v>45565</v>
       </c>
       <c r="B2103" t="n">
-        <v>3.859571723917734</v>
+        <v>3.859571723917725</v>
       </c>
       <c r="C2103" t="n">
         <v>4.624129266651315</v>
       </c>
       <c r="D2103" t="n">
-        <v>-4.825253768761106</v>
+        <v>-4.926581835167923</v>
       </c>
       <c r="E2103" t="n">
-        <v>2.693671334833125</v>
+        <v>2.653140108270398</v>
       </c>
       <c r="F2103" t="n">
-        <v>1.403192357259116</v>
+        <v>1.301864290852299</v>
       </c>
       <c r="G2103" t="n">
-        <v>5.466044681006785</v>
+        <v>5.405247841162694</v>
       </c>
     </row>
     <row r="2104">
@@ -49937,22 +49937,22 @@
         <v>45566</v>
       </c>
       <c r="B2104" t="n">
-        <v>3.82800627401364</v>
+        <v>3.828006274013631</v>
       </c>
       <c r="C2104" t="n">
         <v>4.617689489662492</v>
       </c>
       <c r="D2104" t="n">
-        <v>-4.798204731067853</v>
+        <v>-4.899532797474669</v>
       </c>
       <c r="E2104" t="n">
-        <v>2.698051172921603</v>
+        <v>2.657519946358876</v>
       </c>
       <c r="F2104" t="n">
-        <v>1.43024139495237</v>
+        <v>1.328913328545553</v>
       </c>
       <c r="G2104" t="n">
-        <v>5.475834326633914</v>
+        <v>5.415037486789824</v>
       </c>
     </row>
     <row r="2105">
@@ -49960,22 +49960,22 @@
         <v>45567</v>
       </c>
       <c r="B2105" t="n">
-        <v>3.82398744526377</v>
+        <v>3.823987445263768</v>
       </c>
       <c r="C2105" t="n">
         <v>4.617689489662492</v>
       </c>
       <c r="D2105" t="n">
-        <v>-4.804238011254623</v>
+        <v>-4.905566077661439</v>
       </c>
       <c r="E2105" t="n">
-        <v>2.695637860846895</v>
+        <v>2.655106634284168</v>
       </c>
       <c r="F2105" t="n">
-        <v>1.43024139495237</v>
+        <v>1.328913328545553</v>
       </c>
       <c r="G2105" t="n">
-        <v>5.475834326633914</v>
+        <v>5.415037486789824</v>
       </c>
     </row>
     <row r="2106">
@@ -49983,22 +49983,22 @@
         <v>45568</v>
       </c>
       <c r="B2106" t="n">
-        <v>3.815657203170844</v>
+        <v>3.815657203170835</v>
       </c>
       <c r="C2106" t="n">
         <v>4.621327656804905</v>
       </c>
       <c r="D2106" t="n">
-        <v>-4.856089786827784</v>
+        <v>-4.924608441760276</v>
       </c>
       <c r="E2106" t="n">
-        <v>2.678535317760043</v>
+        <v>2.651127855787046</v>
       </c>
       <c r="F2106" t="n">
-        <v>1.378389619379209</v>
+        <v>1.309870964446716</v>
       </c>
       <c r="G2106" t="n">
-        <v>5.44836142843243</v>
+        <v>5.407250235472935</v>
       </c>
     </row>
     <row r="2107">
@@ -50006,22 +50006,22 @@
         <v>45569</v>
       </c>
       <c r="B2107" t="n">
-        <v>3.830586986431407</v>
+        <v>3.830586986431405</v>
       </c>
       <c r="C2107" t="n">
         <v>4.584819403988742</v>
       </c>
       <c r="D2107" t="n">
-        <v>-4.883147232959611</v>
+        <v>-4.951665887892102</v>
       </c>
       <c r="E2107" t="n">
-        <v>2.631204086491149</v>
+        <v>2.603796624518153</v>
       </c>
       <c r="F2107" t="n">
-        <v>1.378389619379209</v>
+        <v>1.309870964446716</v>
       </c>
       <c r="G2107" t="n">
-        <v>5.411853175616267</v>
+        <v>5.370741982656772</v>
       </c>
     </row>
     <row r="2108">
@@ -50029,22 +50029,22 @@
         <v>45570</v>
       </c>
       <c r="B2108" t="n">
-        <v>3.927642060152758</v>
+        <v>3.910581988208739</v>
       </c>
       <c r="C2108" t="n">
         <v>4.586227353735933</v>
       </c>
       <c r="D2108" t="n">
-        <v>-5.057753313163176</v>
+        <v>-5.054804165250326</v>
       </c>
       <c r="E2108" t="n">
-        <v>2.562769604156915</v>
+        <v>2.563949263322054</v>
       </c>
       <c r="F2108" t="n">
-        <v>1.318722427954065</v>
+        <v>1.258672345020671</v>
       </c>
       <c r="G2108" t="n">
-        <v>5.377460810508373</v>
+        <v>5.341430760748336</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20241006.xlsx
+++ b/tame_output/ON/bt/strategyON_20241006.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>57.2%</t>
+          <t>57.3%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>68.1%</t>
+          <t>68.2%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>17.7%</t>
+          <t>17.8%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>63.0%</t>
+          <t>63.7%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-78.1%</t>
+          <t>-77.8%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>107.1%</t>
+          <t>107.2%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.3%</t>
+          <t>123.2%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>89.9%</t>
+          <t>90.1%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-37.7%</t>
+          <t>-37.8%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>21.6%</t>
+          <t>21.8%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-74.3%</t>
+          <t>-73.9%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>421.6%</t>
+          <t>421.8%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-667.1%</t>
+          <t>-658.5%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>30.5%</t>
+          <t>31.3%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.6%</t>
+          <t>63.5%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1140,7 +1140,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-9.6%</t>
+          <t>-9.7%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>26.3%</t>
+          <t>27.0%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-4.3%</t>
+          <t>-4.4%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-119.8%</t>
+          <t>-116.4%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-3.1%</t>
+          <t>-2.2%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>74.2%</t>
+          <t>74.3%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.7%</t>
+          <t>10.8%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>4.5%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.7%</t>
+          <t>55.8%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>44.8%</t>
+          <t>53.1%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-203.6%</t>
+          <t>-365.2%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-98.1%</t>
+          <t>-92.5%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>113.0%</t>
+          <t>114.2%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-7.8%</t>
+          <t>-7.7%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>14.2%</t>
+          <t>14.0%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-18.8%</t>
+          <t>-20.1%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>102.4%</t>
+          <t>103.5%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.4%</t>
+          <t>-16.5%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>36.7%</t>
+          <t>36.6%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>88.1%</t>
+          <t>91.5%</t>
         </is>
       </c>
     </row>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191734</v>
+        <v>3.302618194191735</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44463,7 +44463,7 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108635</v>
+        <v>3.305023265108636</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097817</v>
+        <v>3.341378723097818</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094112</v>
+        <v>3.374439043094114</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.40596051119928</v>
+        <v>3.405960511199281</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969588</v>
+        <v>3.42463335496959</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.41997943392308</v>
+        <v>3.419979433923083</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297743</v>
+        <v>3.458100091297745</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317611</v>
+        <v>3.447750501317614</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737165</v>
+        <v>3.503515506737167</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341308</v>
+        <v>3.50317028234131</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.50105255853946</v>
+        <v>3.501052558539461</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -45176,7 +45176,7 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311949</v>
+        <v>3.78468452131195</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
@@ -45199,7 +45199,7 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800829354097242</v>
+        <v>3.800829354097244</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
@@ -45222,7 +45222,7 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017769</v>
+        <v>3.789311112017772</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
@@ -45245,7 +45245,7 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833252747839722</v>
+        <v>3.833252747839725</v>
       </c>
       <c r="C1900" t="n">
         <v>3.151116350215413</v>
@@ -45268,7 +45268,7 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839374447388725</v>
+        <v>3.839374447388729</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
@@ -45291,7 +45291,7 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856161751626471</v>
+        <v>3.856161751626475</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
@@ -45314,7 +45314,7 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787330429291812</v>
+        <v>3.787330429291814</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
@@ -45337,7 +45337,7 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801637122785786</v>
+        <v>3.801637122785788</v>
       </c>
       <c r="C1904" t="n">
         <v>3.155859013848905</v>
@@ -45360,7 +45360,7 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763182248390427</v>
+        <v>3.763182248390429</v>
       </c>
       <c r="C1905" t="n">
         <v>3.057119799856059</v>
@@ -45383,7 +45383,7 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105952</v>
+        <v>3.784718794105954</v>
       </c>
       <c r="C1906" t="n">
         <v>3.059934860543696</v>
@@ -45406,7 +45406,7 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960985</v>
+        <v>3.753882571960987</v>
       </c>
       <c r="C1907" t="n">
         <v>3.072841201767355</v>
@@ -45429,7 +45429,7 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607644</v>
+        <v>3.692931855607646</v>
       </c>
       <c r="C1908" t="n">
         <v>2.944865272168136</v>
@@ -45452,7 +45452,7 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770422583987902</v>
+        <v>3.770422583987903</v>
       </c>
       <c r="C1909" t="n">
         <v>2.993409614045222</v>
@@ -45475,7 +45475,7 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710811</v>
+        <v>3.760333686710813</v>
       </c>
       <c r="C1910" t="n">
         <v>2.876788805406815</v>
@@ -45498,7 +45498,7 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409204</v>
+        <v>3.723566229409205</v>
       </c>
       <c r="C1911" t="n">
         <v>2.868074819153337</v>
@@ -45521,7 +45521,7 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729969716098108</v>
+        <v>3.72996971609811</v>
       </c>
       <c r="C1912" t="n">
         <v>2.861114207058244</v>
@@ -45544,7 +45544,7 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493419</v>
+        <v>3.782922533493421</v>
       </c>
       <c r="C1913" t="n">
         <v>2.875576561439387</v>
@@ -45567,7 +45567,7 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722817</v>
+        <v>3.828551486722819</v>
       </c>
       <c r="C1914" t="n">
         <v>2.870108681898582</v>
@@ -45590,7 +45590,7 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792046</v>
+        <v>3.828052928792047</v>
       </c>
       <c r="C1915" t="n">
         <v>2.867606775909159</v>
@@ -45613,7 +45613,7 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919905</v>
+        <v>3.812453678919907</v>
       </c>
       <c r="C1916" t="n">
         <v>2.875307754146484</v>
@@ -45636,7 +45636,7 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.74832840831809</v>
+        <v>3.748328408318092</v>
       </c>
       <c r="C1917" t="n">
         <v>2.871088462493535</v>
@@ -45659,7 +45659,7 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057525</v>
+        <v>3.824311233057527</v>
       </c>
       <c r="C1918" t="n">
         <v>2.873212776413551</v>
@@ -45682,7 +45682,7 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279184</v>
+        <v>3.826354974279186</v>
       </c>
       <c r="C1919" t="n">
         <v>2.865954851397253</v>
@@ -45705,7 +45705,7 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011497</v>
+        <v>3.835957987011499</v>
       </c>
       <c r="C1920" t="n">
         <v>2.869553974917902</v>
@@ -45728,7 +45728,7 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392986</v>
+        <v>3.780933911392988</v>
       </c>
       <c r="C1921" t="n">
         <v>2.882881480972455</v>
@@ -45751,7 +45751,7 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632781</v>
+        <v>3.773765222632782</v>
       </c>
       <c r="C1922" t="n">
         <v>2.881901958588752</v>
@@ -45774,7 +45774,7 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883073</v>
+        <v>3.764617879883074</v>
       </c>
       <c r="C1923" t="n">
         <v>2.88659675964307</v>
@@ -45797,7 +45797,7 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074782</v>
+        <v>3.798814771074784</v>
       </c>
       <c r="C1924" t="n">
         <v>2.867791018426865</v>
@@ -45820,7 +45820,7 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242293</v>
+        <v>3.797694884242294</v>
       </c>
       <c r="C1925" t="n">
         <v>2.869534095051743</v>
@@ -45843,7 +45843,7 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821593509367682</v>
+        <v>3.821593509367686</v>
       </c>
       <c r="C1926" t="n">
         <v>2.873463408886563</v>
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879962</v>
+        <v>3.822326997879966</v>
       </c>
       <c r="C1927" t="n">
         <v>2.874141992803903</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.742179208749064</v>
+        <v>-4.65352219721759</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.9769138849905292</v>
+        <v>1.012376689603119</v>
       </c>
       <c r="F1927" t="n">
-        <v>0.2064431047883115</v>
+        <v>0.2578397241163622</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.99800785567689</v>
+        <v>3.028845827273721</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502333</v>
+        <v>3.84861662650234</v>
       </c>
       <c r="C1928" t="n">
         <v>2.871140064023896</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.618704937436046</v>
+        <v>-4.530047925904572</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.02330166473573</v>
+        <v>1.05876446934832</v>
       </c>
       <c r="F1928" t="n">
-        <v>0.2064431047883115</v>
+        <v>0.2578397241163622</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.995005926896884</v>
+        <v>3.025843898493714</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675935</v>
+        <v>3.81866895167594</v>
       </c>
       <c r="C1929" t="n">
         <v>2.872719101034511</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.560769105437831</v>
+        <v>-4.472112093906357</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.04805503454563</v>
+        <v>1.08351783915822</v>
       </c>
       <c r="F1929" t="n">
-        <v>0.2320049794710608</v>
+        <v>0.2834015987991115</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.011922088717147</v>
+        <v>3.042760060313978</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539947</v>
+        <v>3.843274527539952</v>
       </c>
       <c r="C1930" t="n">
         <v>2.888613283836334</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.427901416374553</v>
+        <v>-4.339244404843079</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.117096292972765</v>
+        <v>1.152559097585354</v>
       </c>
       <c r="F1930" t="n">
-        <v>0.2320049794710608</v>
+        <v>0.2834015987991115</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.02781627151897</v>
+        <v>3.058654243115801</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496259</v>
+        <v>3.845047386496263</v>
       </c>
       <c r="C1931" t="n">
         <v>2.889759128276636</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.307728333010054</v>
+        <v>-4.21907132147858</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.166311370758866</v>
+        <v>1.201774175371456</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.3521780628355597</v>
+        <v>0.4035746821636105</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.101065965977972</v>
+        <v>3.131903937574802</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576996</v>
+        <v>3.791273551577</v>
       </c>
       <c r="C1932" t="n">
         <v>2.899847230838076</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.172474971680077</v>
+        <v>-4.083817960148603</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.230500817852297</v>
+        <v>1.265963622464886</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.4874314241655369</v>
+        <v>0.5388280434935876</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.192306085337398</v>
+        <v>3.223144056934228</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942102</v>
+        <v>3.735839222942106</v>
       </c>
       <c r="C1933" t="n">
         <v>2.885884722239501</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.232349799037769</v>
+        <v>-4.143692787506295</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.192588378310646</v>
+        <v>1.228051182923235</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.4275565968078447</v>
+        <v>0.4789532161358955</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.142418680324209</v>
+        <v>3.173256651921039</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674512</v>
+        <v>3.762647477674515</v>
       </c>
       <c r="C1934" t="n">
         <v>2.90117389147371</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.112529568126932</v>
+        <v>-4.023872556595459</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.255805639909189</v>
+        <v>1.291268444521779</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.4275565968078447</v>
+        <v>0.4789532161358955</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.157707849558417</v>
+        <v>3.188545821155247</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430693</v>
+        <v>3.729146398430697</v>
       </c>
       <c r="C1935" t="n">
         <v>2.808818090796152</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.114999274588738</v>
+        <v>-4.026342263057265</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.162461956646908</v>
+        <v>1.197924761259498</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.4250868903460386</v>
+        <v>0.4764835096740893</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.063870225003775</v>
+        <v>3.094708196600605</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.7432201960036</v>
+        <v>3.743220196003604</v>
       </c>
       <c r="C1936" t="n">
         <v>2.728079952281453</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.183369460912749</v>
+        <v>-4.094712449381275</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.054375743602606</v>
+        <v>1.089838548215195</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.4343625893822535</v>
+        <v>0.4857592087103043</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.988697505910805</v>
+        <v>3.019535477507636</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508368</v>
+        <v>3.714179139508372</v>
       </c>
       <c r="C1937" t="n">
         <v>2.718516660913344</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.295241740538899</v>
+        <v>-4.206584729007425</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.000063540384037</v>
+        <v>1.035526344996626</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.4343625893822535</v>
+        <v>0.4857592087103043</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.979134214542697</v>
+        <v>3.009972186139527</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417702</v>
+        <v>3.710906731417706</v>
       </c>
       <c r="C1938" t="n">
         <v>2.685091185837372</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.279267075052632</v>
+        <v>-4.190610063521158</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.9730279315025709</v>
+        <v>1.00849073611516</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.4343625893822535</v>
+        <v>0.4857592087103043</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.945708739466724</v>
+        <v>2.976546711063555</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205895</v>
+        <v>3.746042526205901</v>
       </c>
       <c r="C1939" t="n">
         <v>2.689658417829159</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.283361621723629</v>
+        <v>-4.194704610192155</v>
       </c>
       <c r="E1939" t="n">
-        <v>0.9759573448259597</v>
+        <v>1.011420149438549</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.4343625893822535</v>
+        <v>0.4857592087103043</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.950275971458512</v>
+        <v>2.981113943055342</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225438</v>
+        <v>3.765024323225445</v>
       </c>
       <c r="C1940" t="n">
         <v>2.665400446590366</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.275437247138715</v>
+        <v>-4.186780235607241</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.9548691234211324</v>
+        <v>0.9903319280337222</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.4343625893822535</v>
+        <v>0.4857592087103043</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.926018000219719</v>
+        <v>2.956855971816549</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111292</v>
+        <v>3.773210297111296</v>
       </c>
       <c r="C1941" t="n">
         <v>2.593938759991816</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.269159044568866</v>
+        <v>-4.180502033037392</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.8859187178505219</v>
+        <v>0.9213815224631114</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.4406407919521026</v>
+        <v>0.4920374112801533</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.858323235163078</v>
+        <v>2.889161206759908</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264162</v>
+        <v>3.784343952264166</v>
       </c>
       <c r="C1942" t="n">
         <v>2.604111146423949</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.209306425365143</v>
+        <v>-4.120649413833669</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.9200321519641435</v>
+        <v>0.955494956576733</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.4406407919521026</v>
+        <v>0.4920374112801533</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.86849562159521</v>
+        <v>2.899333593192041</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742298</v>
+        <v>3.786949957742301</v>
       </c>
       <c r="C1943" t="n">
         <v>2.599057416997809</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.123062962338765</v>
+        <v>-4.034405950807291</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.9494758077485548</v>
+        <v>0.9849386123611445</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.4406407919521026</v>
+        <v>0.4920374112801533</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.863441892169071</v>
+        <v>2.894279863765901</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316045</v>
+        <v>3.752027499316048</v>
       </c>
       <c r="C1944" t="n">
         <v>2.590833192442334</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.168369781737745</v>
+        <v>-4.079712770206271</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.9231288554334884</v>
+        <v>0.958591660046078</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.3998306289428718</v>
+        <v>0.4512272482709225</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.830731569808058</v>
+        <v>2.861569541404888</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803189</v>
+        <v>3.753571165803192</v>
       </c>
       <c r="C1945" t="n">
         <v>2.591385065475436</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.197402886440046</v>
+        <v>-4.108745874908572</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.9120674865856695</v>
+        <v>0.9475302911982593</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.3998306289428718</v>
+        <v>0.4512272482709225</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.831283442841159</v>
+        <v>2.86212141443799</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809497</v>
+        <v>3.733390600809501</v>
       </c>
       <c r="C1946" t="n">
         <v>2.520657757366802</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.104592404989186</v>
+        <v>-4.015935393457712</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.8784643710573792</v>
+        <v>0.9139271756699687</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.4926411103937312</v>
+        <v>0.5440377297217819</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.816242423603041</v>
+        <v>2.847080395199871</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560424</v>
+        <v>3.748285816560427</v>
       </c>
       <c r="C1947" t="n">
         <v>2.522531233291402</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.148981874318614</v>
+        <v>-4.06032486278714</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.8625820592502089</v>
+        <v>0.8980448638627985</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.4482516410643035</v>
+        <v>0.4996482603923542</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.791482217929985</v>
+        <v>2.822320189526815</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472734</v>
+        <v>3.721077195472738</v>
       </c>
       <c r="C1948" t="n">
         <v>2.517606941803125</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.128478180433117</v>
+        <v>-4.039821168901643</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.8658592453161309</v>
+        <v>0.9013220499287204</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.4687553349498008</v>
+        <v>0.5201519542778515</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.798860142773006</v>
+        <v>2.829698114369837</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798535</v>
+        <v>3.743047603798539</v>
       </c>
       <c r="C1949" t="n">
         <v>2.523098237633793</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.212150277145449</v>
+        <v>-4.123493265613975</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.837881702461865</v>
+        <v>0.8733445070744548</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.4687553349498008</v>
+        <v>0.5201519542778515</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.804351438603673</v>
+        <v>2.835189410200504</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498862</v>
+        <v>3.689597840498865</v>
       </c>
       <c r="C1950" t="n">
         <v>2.534595439402332</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.239930675046802</v>
+        <v>-4.151273663515328</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.8382667450698631</v>
+        <v>0.8737295496824526</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.4409749370484478</v>
+        <v>0.4923715563764985</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.799180401631401</v>
+        <v>2.830018373228231</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705322</v>
+        <v>3.643069621705326</v>
       </c>
       <c r="C1951" t="n">
         <v>2.372951159402985</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.35831134777694</v>
+        <v>-4.269654336245466</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.629270195978461</v>
+        <v>0.6647330005910506</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.3737570848974716</v>
+        <v>0.4251537042255223</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.597205410341468</v>
+        <v>2.628043381938299</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729267</v>
+        <v>3.682716310729271</v>
       </c>
       <c r="C1952" t="n">
         <v>2.493100820122191</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.466925426220271</v>
+        <v>-4.378268414688797</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.7059742253203343</v>
+        <v>0.7414370299329238</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.3737570848974716</v>
+        <v>0.4251537042255223</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.717355071060674</v>
+        <v>2.748193042657504</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190766</v>
+        <v>3.73301244119077</v>
       </c>
       <c r="C1953" t="n">
         <v>2.507613846224514</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.431516387972128</v>
+        <v>-4.342859376440654</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.7346508667219143</v>
+        <v>0.7701136713345038</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.3737570848974716</v>
+        <v>0.4251537042255223</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.731868097162997</v>
+        <v>2.762706068759827</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913424</v>
+        <v>3.741174069913428</v>
       </c>
       <c r="C1954" t="n">
         <v>2.505033287566882</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.439977556627589</v>
+        <v>-4.351320545096115</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.7286858406020986</v>
+        <v>0.7641486452146884</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.3652959162420105</v>
+        <v>0.4166925355700613</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.724210837312089</v>
+        <v>2.755048808908919</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532484</v>
+        <v>3.751147197532488</v>
       </c>
       <c r="C1955" t="n">
         <v>2.501762316412185</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.262861226592423</v>
+        <v>-4.174204215060949</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.7962614014614675</v>
+        <v>0.8317242060740571</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.3652959162420105</v>
+        <v>0.4166925355700613</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.720939866157391</v>
+        <v>2.751777837754222</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793901</v>
+        <v>3.741328448793904</v>
       </c>
       <c r="C1956" t="n">
         <v>2.502445708174098</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.307953471425969</v>
+        <v>-4.219296459894495</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.7789078952899624</v>
+        <v>0.814370699902552</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.3033998730726207</v>
+        <v>0.3547964924006715</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.684485632017671</v>
+        <v>2.715323603614501</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011231</v>
+        <v>3.750729377011237</v>
       </c>
       <c r="C1957" t="n">
         <v>2.496232683480512</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.128578050187201</v>
+        <v>-4.039921038655727</v>
       </c>
       <c r="E1957" t="n">
-        <v>0.8444450390918838</v>
+        <v>0.8799078437044734</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.4601766312433394</v>
+        <v>0.5115732505713901</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.772338662226516</v>
+        <v>2.803176633823346</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982224</v>
+        <v>3.71699171898223</v>
       </c>
       <c r="C1958" t="n">
         <v>2.477040138812102</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.173592263707807</v>
+        <v>-4.084935252176333</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.8072468090152312</v>
+        <v>0.8427096136278207</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.4298277359287348</v>
+        <v>0.4812243552567855</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.734936780369343</v>
+        <v>2.765774751966173</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509533</v>
+        <v>3.737026608509539</v>
       </c>
       <c r="C1959" t="n">
         <v>2.482731701151048</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.261603450266504</v>
+        <v>-4.17294643873503</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.7777338967306981</v>
+        <v>0.8131967013432877</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.3643512280695618</v>
+        <v>0.4157478473976126</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.701342437992785</v>
+        <v>2.732180409589616</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760809</v>
+        <v>3.702309454760813</v>
       </c>
       <c r="C1960" t="n">
         <v>2.481935623047549</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.362801231703677</v>
+        <v>-4.274144220172203</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.7364587060523304</v>
+        <v>0.77192151066492</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.2959424145242426</v>
+        <v>0.3473390338522934</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.659501071762095</v>
+        <v>2.690339043358926</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815453</v>
+        <v>3.705571661815457</v>
       </c>
       <c r="C1961" t="n">
         <v>2.479535584601866</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.356290265089364</v>
+        <v>-4.26763325355789</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.7366630542523722</v>
+        <v>0.7721258588649618</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.2959424145242426</v>
+        <v>0.3473390338522934</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.657101033316412</v>
+        <v>2.687939004913242</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378099</v>
+        <v>3.709510443378102</v>
       </c>
       <c r="C1962" t="n">
         <v>2.476060303810111</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.337252137382067</v>
+        <v>-4.248595125850593</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.740803024543536</v>
+        <v>0.7762658291561255</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.2377588031930481</v>
+        <v>0.2891554225210988</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.61871558572594</v>
+        <v>2.64955355732277</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131246</v>
+        <v>3.73106447313125</v>
       </c>
       <c r="C1963" t="n">
         <v>2.595354705444301</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.389767939656887</v>
+        <v>-4.301110928125413</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.8390911052677983</v>
+        <v>0.8745539098803878</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.2377588031930481</v>
+        <v>0.2891554225210988</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.73800998736013</v>
+        <v>2.768847958956961</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067861</v>
+        <v>3.722447362067864</v>
       </c>
       <c r="C1964" t="n">
         <v>2.596188034430435</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.393176251091467</v>
+        <v>-4.304519239559993</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.8385611096800998</v>
+        <v>0.8740239142926893</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.2702753722024255</v>
+        <v>0.3216719915304762</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.75835325775189</v>
+        <v>2.789191229348721</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.78742558078912</v>
+        <v>3.787425580789123</v>
       </c>
       <c r="C1965" t="n">
         <v>2.602196564827361</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.37382011519762</v>
+        <v>-4.285163103666146</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.8523120944345648</v>
+        <v>0.8877748990471543</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.2702753722024255</v>
+        <v>0.3216719915304762</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.764361788148816</v>
+        <v>2.795199759745647</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519905</v>
+        <v>3.781501250519908</v>
       </c>
       <c r="C1966" t="n">
         <v>2.50014678610456</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.447149643935712</v>
+        <v>-4.358492632404238</v>
       </c>
       <c r="E1966" t="n">
-        <v>0.7209305042165273</v>
+        <v>0.7563933088291168</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.2706700346220474</v>
+        <v>0.3220666539500981</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.662548806877789</v>
+        <v>2.693386778474619</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181165</v>
+        <v>3.80224592918117</v>
       </c>
       <c r="C1967" t="n">
         <v>2.409870503348191</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.530970865210411</v>
+        <v>-4.442313853678937</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.597125732950279</v>
+        <v>0.6325885375628686</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.2706700346220474</v>
+        <v>0.3220666539500981</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.57227252412142</v>
+        <v>2.60311049571825</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394725</v>
+        <v>3.805608985394731</v>
       </c>
       <c r="C1968" t="n">
         <v>2.41053285173985</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.524818159157626</v>
+        <v>-4.436161147626152</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.6002491637630512</v>
+        <v>0.6357119683756407</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.2768227406748317</v>
+        <v>0.3282193600028824</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.576626496144749</v>
+        <v>2.607464467741579</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890609</v>
+        <v>3.798239794890613</v>
       </c>
       <c r="C1969" t="n">
         <v>2.40961332847996</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.541627457308128</v>
+        <v>-4.452970445776654</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.5926059212429606</v>
+        <v>0.6280687258555502</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.2600134425243301</v>
+        <v>0.3114100618523808</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.565621393994558</v>
+        <v>2.596459365591389</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798424</v>
+        <v>3.867362636798427</v>
       </c>
       <c r="C1970" t="n">
         <v>2.475948882276781</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.479329458532006</v>
+        <v>-4.390672447000532</v>
       </c>
       <c r="E1970" t="n">
-        <v>0.6838606745502305</v>
+        <v>0.71932347916282</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.3053077067987721</v>
+        <v>0.3567043261268228</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.659133506356044</v>
+        <v>2.689971477952875</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992188</v>
+        <v>3.848729139992193</v>
       </c>
       <c r="C1971" t="n">
         <v>2.278240883990908</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.277539260866848</v>
+        <v>-4.188882249335374</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.5668687553304206</v>
+        <v>0.6023315599430101</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.5033258989679266</v>
+        <v>0.5547225182959772</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.580236423371664</v>
+        <v>2.611074394968494</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852421</v>
+        <v>3.841444817852424</v>
       </c>
       <c r="C1972" t="n">
         <v>2.348531116313083</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.328425973553043</v>
+        <v>-4.239768962021569</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.616804302578118</v>
+        <v>0.6522671071907076</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.452439186281732</v>
+        <v>0.5038358056097827</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.619994628082122</v>
+        <v>2.650832599678953</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.81906330031954</v>
+        <v>3.819063300319546</v>
       </c>
       <c r="C1973" t="n">
         <v>2.363158852429127</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.241815230903236</v>
+        <v>-4.153158219371762</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.6660763357540844</v>
+        <v>0.701539140366674</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.5310649174868902</v>
+        <v>0.582461536814941</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.681797802921261</v>
+        <v>2.712635774518092</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.83181903248938</v>
+        <v>3.831819032489386</v>
       </c>
       <c r="C1974" t="n">
         <v>2.361694833253798</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.302024528908521</v>
+        <v>-4.213367517377047</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.6405285973766421</v>
+        <v>0.6759914019892317</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.4708556194816057</v>
+        <v>0.5222522388096564</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.644208204942762</v>
+        <v>2.675046176539592</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.83641167239779</v>
+        <v>3.836411672397796</v>
       </c>
       <c r="C1975" t="n">
         <v>2.360186451293727</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.25283788022417</v>
+        <v>-4.164180868692696</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.6586948748903112</v>
+        <v>0.6941576795029007</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.4708556194816057</v>
+        <v>0.5222522388096564</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.642699822982691</v>
+        <v>2.673537794579521</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316245</v>
+        <v>3.833513460316252</v>
       </c>
       <c r="C1976" t="n">
         <v>2.360049318729163</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.208464748585601</v>
+        <v>-4.119807737054127</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.6763069949811749</v>
+        <v>0.7117697995937644</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.5152287511201743</v>
+        <v>0.566625370448225</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.669186569401268</v>
+        <v>2.700024540998098</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105962</v>
+        <v>3.821562117105966</v>
       </c>
       <c r="C1977" t="n">
         <v>2.354443112867754</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.1737334272671</v>
+        <v>-4.085076415735626</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.6845933176471655</v>
+        <v>0.7200561222597552</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.5152287511201743</v>
+        <v>0.566625370448225</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.663580363539858</v>
+        <v>2.694418335136689</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190321</v>
+        <v>3.833011148190325</v>
       </c>
       <c r="C1978" t="n">
         <v>2.360824869895558</v>
       </c>
       <c r="D1978" t="n">
-        <v>-4.126077696706044</v>
+        <v>-4.03742068517457</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.7100373668993925</v>
+        <v>0.7455001715119822</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.56288448168123</v>
+        <v>0.6142811010092807</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.698555558904296</v>
+        <v>2.729393530501127</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569614</v>
+        <v>3.822678210569618</v>
       </c>
       <c r="C1979" t="n">
         <v>2.365717243270283</v>
       </c>
       <c r="D1979" t="n">
-        <v>-4.02555953820729</v>
+        <v>-3.936902526675816</v>
       </c>
       <c r="E1979" t="n">
-        <v>0.7551370036736191</v>
+        <v>0.7905998082862089</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.6634026401799845</v>
+        <v>0.7147992595080352</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.763758827378274</v>
+        <v>2.794596798975105</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557291</v>
+        <v>3.828808877557295</v>
       </c>
       <c r="C1980" t="n">
         <v>2.352471915746155</v>
       </c>
       <c r="D1980" t="n">
-        <v>-4.009654208774937</v>
+        <v>-3.920997197243463</v>
       </c>
       <c r="E1980" t="n">
-        <v>0.7482538079224326</v>
+        <v>0.7837166125350221</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.5842899794707457</v>
+        <v>0.6356865987987963</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.703045903428603</v>
+        <v>2.733883875025434</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932766</v>
+        <v>3.816837033932769</v>
       </c>
       <c r="C1981" t="n">
         <v>2.356569618356784</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.964815807166539</v>
+        <v>-3.876158795635065</v>
       </c>
       <c r="E1981" t="n">
-        <v>0.7702868711764204</v>
+        <v>0.8057496757890099</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.5888334124156152</v>
+        <v>0.6402300317436658</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.709869665806153</v>
+        <v>2.740707637402984</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917048</v>
+        <v>3.817932354917051</v>
       </c>
       <c r="C1982" t="n">
         <v>2.360730557987862</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.984314263408547</v>
+        <v>-3.895657251877073</v>
       </c>
       <c r="E1982" t="n">
-        <v>0.7666484283106949</v>
+        <v>0.8021112329232847</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.5407487711357108</v>
+        <v>0.5921453904637615</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.685179820669289</v>
+        <v>2.716017792266119</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405958</v>
+        <v>3.826684745405961</v>
       </c>
       <c r="C1983" t="n">
         <v>2.366610160515699</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.940111426322647</v>
+        <v>-3.851454414791173</v>
       </c>
       <c r="E1983" t="n">
-        <v>0.7902091656728922</v>
+        <v>0.825671970285482</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.5849516082216113</v>
+        <v>0.6363482275496619</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.717581125448666</v>
+        <v>2.748419097045496</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265642</v>
+        <v>3.838199629265645</v>
       </c>
       <c r="C1984" t="n">
         <v>2.365020160984947</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.947671092159694</v>
+        <v>-3.85901408062822</v>
       </c>
       <c r="E1984" t="n">
-        <v>0.785595299807321</v>
+        <v>0.8210581044199108</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.6397550122314306</v>
+        <v>0.6911516315594812</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.748873168323805</v>
+        <v>2.779711139920636</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284877</v>
+        <v>3.86389508028488</v>
       </c>
       <c r="C1985" t="n">
         <v>2.416267926167986</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.789379674620422</v>
+        <v>-3.700722663088948</v>
       </c>
       <c r="E1985" t="n">
-        <v>0.9001596320060696</v>
+        <v>0.9356224366186592</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.6397550122314306</v>
+        <v>0.6911516315594812</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.800120933506845</v>
+        <v>2.830958905103675</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.86533868132102</v>
+        <v>3.865338681321023</v>
       </c>
       <c r="C1986" t="n">
         <v>2.414708630762239</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.581737670985945</v>
+        <v>-3.493080659454471</v>
       </c>
       <c r="E1986" t="n">
-        <v>0.9816571380541133</v>
+        <v>1.017119942666703</v>
       </c>
       <c r="F1986" t="n">
-        <v>0.8473970158659068</v>
+        <v>0.8987936351939574</v>
       </c>
       <c r="G1986" t="n">
-        <v>2.923146840281784</v>
+        <v>2.953984811878614</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475136</v>
+        <v>3.864489842475139</v>
       </c>
       <c r="C1987" t="n">
         <v>2.409656859000509</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.530705578263417</v>
+        <v>-3.442048566731943</v>
       </c>
       <c r="E1987" t="n">
-        <v>0.9970182033813946</v>
+        <v>1.032481007993984</v>
       </c>
       <c r="F1987" t="n">
-        <v>0.8984291085884347</v>
+        <v>0.9498257279164853</v>
       </c>
       <c r="G1987" t="n">
-        <v>2.94871432415357</v>
+        <v>2.979552295750401</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.84254736040485</v>
+        <v>3.842547360404854</v>
       </c>
       <c r="C1988" t="n">
         <v>2.426844263093214</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.465481397136212</v>
+        <v>-3.376824385604738</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.040295279924982</v>
+        <v>1.075758084537571</v>
       </c>
       <c r="F1988" t="n">
-        <v>0.9636532897156403</v>
+        <v>1.015049909043691</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.005036236922599</v>
+        <v>3.035874208519429</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882552</v>
+        <v>3.840061186882558</v>
       </c>
       <c r="C1989" t="n">
         <v>2.422805235392495</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.428054377065078</v>
+        <v>-3.339397365533604</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.051227060252716</v>
+        <v>1.086689864865305</v>
       </c>
       <c r="F1989" t="n">
-        <v>0.968904827744822</v>
+        <v>1.020301447072872</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.004148132039388</v>
+        <v>3.034986103636218</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992655</v>
+        <v>3.845169808992662</v>
       </c>
       <c r="C1990" t="n">
         <v>2.424062027723735</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.426696392091532</v>
+        <v>-3.338039380560058</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.053027046573374</v>
+        <v>1.088489851185964</v>
       </c>
       <c r="F1990" t="n">
-        <v>1.043242953282641</v>
+        <v>1.094639572610691</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.050007799693319</v>
+        <v>3.08084577129015</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636283</v>
+        <v>3.828661445636287</v>
       </c>
       <c r="C1991" t="n">
         <v>2.584619798744946</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.398283128991649</v>
+        <v>-3.309626117460175</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.224950122834538</v>
+        <v>1.260412927447128</v>
       </c>
       <c r="F1991" t="n">
-        <v>0.9842673905362118</v>
+        <v>1.035664009864262</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.175180233066673</v>
+        <v>3.206018204663503</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957621</v>
+        <v>3.813222820957627</v>
       </c>
       <c r="C1992" t="n">
         <v>2.704732707962763</v>
       </c>
       <c r="D1992" t="n">
-        <v>-3.323500867966636</v>
+        <v>-3.234843856435162</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.374975936462361</v>
+        <v>1.41043874107495</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.059049651561224</v>
+        <v>1.110446270889275</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.340162498899498</v>
+        <v>3.371000470496328</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.81423072799875</v>
+        <v>3.814230727998754</v>
       </c>
       <c r="C1993" t="n">
         <v>2.696440683976622</v>
       </c>
       <c r="D1993" t="n">
-        <v>-3.297416783702828</v>
+        <v>-3.208759772171354</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.377117546181743</v>
+        <v>1.412580350794332</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.059049651561224</v>
+        <v>1.110446270889275</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.331870474913357</v>
+        <v>3.362708446510187</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896926</v>
+        <v>3.803397818896929</v>
       </c>
       <c r="C1994" t="n">
         <v>2.694633879560401</v>
       </c>
       <c r="D1994" t="n">
-        <v>-3.209538870593708</v>
+        <v>-3.120881859062234</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.41046190700917</v>
+        <v>1.44592471162176</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.174975293984576</v>
+        <v>1.226371913312626</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.399619055951147</v>
+        <v>3.430457027547977</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959855</v>
+        <v>3.796264143959858</v>
       </c>
       <c r="C1995" t="n">
         <v>2.712188285287193</v>
       </c>
       <c r="D1995" t="n">
-        <v>-3.200646409200425</v>
+        <v>-3.111989397668951</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.431573297293275</v>
+        <v>1.467036101905865</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.174975293984576</v>
+        <v>1.226371913312626</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.417173461677939</v>
+        <v>3.448011433274769</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945364</v>
+        <v>3.794424941945367</v>
       </c>
       <c r="C1996" t="n">
         <v>2.704043332691777</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.369122526170302</v>
+        <v>-3.280465514638828</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.356037897909908</v>
+        <v>1.391500702522497</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.147027458267995</v>
+        <v>1.198424077596045</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.392259807652574</v>
+        <v>3.423097779249404</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782706</v>
+        <v>3.795574066782709</v>
       </c>
       <c r="C1997" t="n">
         <v>2.685313029879639</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.922866333540862</v>
+        <v>-2.834209322009388</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.515810072149546</v>
+        <v>1.551272876762135</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.052308788598362</v>
+        <v>1.103705407926412</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.316698303038656</v>
+        <v>3.347536274635486</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632633</v>
+        <v>3.784671345632637</v>
       </c>
       <c r="C1998" t="n">
         <v>2.675977052376543</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.90014522985771</v>
+        <v>-2.811488218326236</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.515562536119711</v>
+        <v>1.551025340732301</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.052308788598362</v>
+        <v>1.103705407926412</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.307362325535561</v>
+        <v>3.338200297132391</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777668</v>
+        <v>3.783205696777674</v>
       </c>
       <c r="C1999" t="n">
         <v>2.834883178227712</v>
       </c>
       <c r="D1999" t="n">
-        <v>-3.029347043151752</v>
+        <v>-2.940690031620278</v>
       </c>
       <c r="E1999" t="n">
-        <v>1.622787936653263</v>
+        <v>1.658250741265853</v>
       </c>
       <c r="F1999" t="n">
-        <v>0.92310697530432</v>
+        <v>0.9745035946323701</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.388747363410304</v>
+        <v>3.419585335007135</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644408</v>
+        <v>3.779933725644414</v>
       </c>
       <c r="C2000" t="n">
         <v>2.871961000721359</v>
       </c>
       <c r="D2000" t="n">
-        <v>-3.055221441625778</v>
+        <v>-2.966564430094304</v>
       </c>
       <c r="E2000" t="n">
-        <v>1.649515999757299</v>
+        <v>1.684978804369889</v>
       </c>
       <c r="F2000" t="n">
-        <v>0.9680185840160611</v>
+        <v>1.019415203344111</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.452772151130996</v>
+        <v>3.483610122727826</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.76944361979996</v>
+        <v>3.769443619799962</v>
       </c>
       <c r="C2001" t="n">
         <v>2.868636356710904</v>
       </c>
       <c r="D2001" t="n">
-        <v>-3.048166751410605</v>
+        <v>-2.959509739879131</v>
       </c>
       <c r="E2001" t="n">
-        <v>1.649013231832914</v>
+        <v>1.684476036445504</v>
       </c>
       <c r="F2001" t="n">
-        <v>0.9750732742312349</v>
+        <v>1.026469893559285</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.453680321249645</v>
+        <v>3.484518292846475</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331113</v>
+        <v>3.766673496331116</v>
       </c>
       <c r="C2002" t="n">
         <v>2.878642510355645</v>
       </c>
       <c r="D2002" t="n">
-        <v>-3.021215527084117</v>
+        <v>-2.932558515552643</v>
       </c>
       <c r="E2002" t="n">
-        <v>1.669799875208251</v>
+        <v>1.705262679820841</v>
       </c>
       <c r="F2002" t="n">
-        <v>0.9899536202589541</v>
+        <v>1.041350239587004</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.472614682511018</v>
+        <v>3.503452654107848</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784105</v>
+        <v>3.768052067784108</v>
       </c>
       <c r="C2003" t="n">
         <v>3.062745642500605</v>
       </c>
       <c r="D2003" t="n">
-        <v>-3.042759754914904</v>
+        <v>-2.95410274338343</v>
       </c>
       <c r="E2003" t="n">
-        <v>1.845285316220896</v>
+        <v>1.880748120833485</v>
       </c>
       <c r="F2003" t="n">
-        <v>0.9899536202589541</v>
+        <v>1.041350239587004</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.656717814655978</v>
+        <v>3.687555786252808</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714421</v>
+        <v>3.743925505714424</v>
       </c>
       <c r="C2004" t="n">
         <v>3.054862337403598</v>
       </c>
       <c r="D2004" t="n">
-        <v>-3.065167872719776</v>
+        <v>-2.976510861188302</v>
       </c>
       <c r="E2004" t="n">
-        <v>1.82843876400194</v>
+        <v>1.86390156861453</v>
       </c>
       <c r="F2004" t="n">
-        <v>0.9899536202589541</v>
+        <v>1.041350239587004</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.648834509558971</v>
+        <v>3.679672481155801</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155028</v>
+        <v>3.719118627155034</v>
       </c>
       <c r="C2005" t="n">
         <v>3.056916336953236</v>
       </c>
       <c r="D2005" t="n">
-        <v>-3.093392108297376</v>
+        <v>-3.004735096765902</v>
       </c>
       <c r="E2005" t="n">
-        <v>1.819203069320537</v>
+        <v>1.854665873933127</v>
       </c>
       <c r="F2005" t="n">
-        <v>1.007930372710263</v>
+        <v>1.059326992038313</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.661674560579394</v>
+        <v>3.692512532176224</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161972</v>
+        <v>3.72945228516198</v>
       </c>
       <c r="C2006" t="n">
         <v>3.113170054675083</v>
       </c>
       <c r="D2006" t="n">
-        <v>-3.102833034185906</v>
+        <v>-3.014176022654432</v>
       </c>
       <c r="E2006" t="n">
-        <v>1.871680416686972</v>
+        <v>1.907143221299562</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.130357490253654</v>
+        <v>1.181754109581704</v>
       </c>
       <c r="G2006" t="n">
-        <v>3.791384548827275</v>
+        <v>3.822222520424106</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321629</v>
+        <v>3.714941193321637</v>
       </c>
       <c r="C2007" t="n">
         <v>3.116061149220384</v>
       </c>
       <c r="D2007" t="n">
-        <v>-3.30907197197434</v>
+        <v>-3.220414960442866</v>
       </c>
       <c r="E2007" t="n">
-        <v>1.7920759361169</v>
+        <v>1.82753874072949</v>
       </c>
       <c r="F2007" t="n">
-        <v>0.9241185524652205</v>
+        <v>0.9755151717932706</v>
       </c>
       <c r="G2007" t="n">
-        <v>3.670532280699516</v>
+        <v>3.701370252296346</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.7278981863477</v>
+        <v>3.727898186347708</v>
       </c>
       <c r="C2008" t="n">
         <v>3.114172962114159</v>
       </c>
       <c r="D2008" t="n">
-        <v>-3.385401949575245</v>
+        <v>-3.296744938043771</v>
       </c>
       <c r="E2008" t="n">
-        <v>1.759655757970313</v>
+        <v>1.795118562582902</v>
       </c>
       <c r="F2008" t="n">
-        <v>0.9241185524652205</v>
+        <v>0.9755151717932706</v>
       </c>
       <c r="G2008" t="n">
-        <v>3.668644093593291</v>
+        <v>3.699482065190121</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887745</v>
+        <v>3.710654104887753</v>
       </c>
       <c r="C2009" t="n">
         <v>3.108993191717021</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.540358734975375</v>
+        <v>-3.451701723443901</v>
       </c>
       <c r="E2009" t="n">
-        <v>1.692493273413124</v>
+        <v>1.727956078025713</v>
       </c>
       <c r="F2009" t="n">
-        <v>0.7691617670650912</v>
+        <v>0.8205583863931414</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.570490251956076</v>
+        <v>3.601328223552906</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343062</v>
+        <v>3.712897612343071</v>
       </c>
       <c r="C2010" t="n">
         <v>3.107427201927174</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.70192716050263</v>
+        <v>-3.613270148971156</v>
       </c>
       <c r="E2010" t="n">
-        <v>1.626299913412374</v>
+        <v>1.661762718024963</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.6423788432672118</v>
+        <v>0.693775462595262</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.492854507887501</v>
+        <v>3.523692479484331</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754596135389345</v>
+        <v>3.754596135389354</v>
       </c>
       <c r="C2011" t="n">
         <v>3.120500608793092</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.810227822372749</v>
+        <v>-3.721570810841275</v>
       </c>
       <c r="E2011" t="n">
-        <v>1.596053055530245</v>
+        <v>1.631515860142834</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.6423788432672118</v>
+        <v>0.693775462595262</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.505927914753419</v>
+        <v>3.53676588635025</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749882691378388</v>
+        <v>3.74988269137839</v>
       </c>
       <c r="C2012" t="n">
         <v>3.112505805576032</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.969778895136266</v>
+        <v>-3.881121883604792</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.524237823207778</v>
+        <v>1.559700627820367</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.4901011764054604</v>
+        <v>0.5414977957335105</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.406566511419308</v>
+        <v>3.437404483016139</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715819895006971</v>
+        <v>3.715819895006973</v>
       </c>
       <c r="C2013" t="n">
         <v>3.111029846703034</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.997679682245739</v>
+        <v>-3.909022670714265</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.51160154949099</v>
+        <v>1.54706435410358</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.4555042522625256</v>
+        <v>0.5069008715905757</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.38433239806055</v>
+        <v>3.41517036965738</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684895778787384</v>
+        <v>3.684895778787386</v>
       </c>
       <c r="C2014" t="n">
         <v>3.107794290680233</v>
       </c>
       <c r="D2014" t="n">
-        <v>-4.120205784948633</v>
+        <v>-4.031548773417159</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.459355552387032</v>
+        <v>1.494818356999621</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.3329781495596317</v>
+        <v>0.3843747688876819</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.307581180416012</v>
+        <v>3.338419152012842</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619348081585934</v>
+        <v>3.619348081585936</v>
       </c>
       <c r="C2015" t="n">
         <v>3.174500250270737</v>
       </c>
       <c r="D2015" t="n">
-        <v>-4.350720281134222</v>
+        <v>-4.262063269602748</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.4338557135033</v>
+        <v>1.46931851811589</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.102463653374043</v>
+        <v>0.1538602727020931</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.235978442295163</v>
+        <v>3.266816413891993</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640750087814664</v>
+        <v>3.640750087814666</v>
       </c>
       <c r="C2016" t="n">
         <v>3.314811969272584</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.699465366358665</v>
+        <v>-4.610808354827191</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.43466939841537</v>
+        <v>1.470132203027959</v>
       </c>
       <c r="F2016" t="n">
-        <v>-0.006284300544854848</v>
+        <v>0.04511231878319533</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.311041388945671</v>
+        <v>3.341879360542501</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668289004237093</v>
+        <v>3.668289004237095</v>
       </c>
       <c r="C2017" t="n">
         <v>3.383792238418224</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.853451784134806</v>
+        <v>-4.764794772603332</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.442055100450553</v>
+        <v>1.477517905063143</v>
       </c>
       <c r="F2017" t="n">
-        <v>-0.006284300544854848</v>
+        <v>0.04511231878319533</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.380021658091311</v>
+        <v>3.410859629688141</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619923016423386</v>
+        <v>3.619923016423388</v>
       </c>
       <c r="C2018" t="n">
         <v>3.369843440538344</v>
       </c>
       <c r="D2018" t="n">
-        <v>-5.058051218997814</v>
+        <v>-4.96939420746634</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.34626652862547</v>
+        <v>1.38172933323806</v>
       </c>
       <c r="F2018" t="n">
-        <v>-0.006284300544854848</v>
+        <v>0.04511231878319533</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.366072860211432</v>
+        <v>3.396910831808262</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656332733609752</v>
+        <v>3.656332733609753</v>
       </c>
       <c r="C2019" t="n">
         <v>3.381713929593758</v>
       </c>
       <c r="D2019" t="n">
-        <v>-5.310526373005539</v>
+        <v>-5.221869361474065</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.257146956077795</v>
+        <v>1.292609760690385</v>
       </c>
       <c r="F2019" t="n">
-        <v>-0.006284300544854848</v>
+        <v>0.04511231878319533</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.377943349266846</v>
+        <v>3.408781320863676</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674028535973155</v>
+        <v>3.674028535973157</v>
       </c>
       <c r="C2020" t="n">
         <v>3.382924464112702</v>
       </c>
       <c r="D2020" t="n">
-        <v>-5.603422129484951</v>
+        <v>-5.514765117953477</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.141199188004974</v>
+        <v>1.176661992617563</v>
       </c>
       <c r="F2020" t="n">
-        <v>-0.006284300544854848</v>
+        <v>0.04511231878319533</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.37915388378579</v>
+        <v>3.40999185538262</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663509457251942</v>
+        <v>3.663509457251946</v>
       </c>
       <c r="C2021" t="n">
         <v>3.387046206340024</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.790086257619759</v>
+        <v>-5.701429246088285</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.070655278978372</v>
+        <v>1.106118083590962</v>
       </c>
       <c r="F2021" t="n">
-        <v>-0.03302327136941474</v>
+        <v>0.01837334795863543</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.367232243518375</v>
+        <v>3.398070215115205</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652149152916197</v>
+        <v>3.652149152916202</v>
       </c>
       <c r="C2022" t="n">
         <v>3.382124059076213</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.936106944533721</v>
+        <v>-5.847449933002247</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.007324856948976</v>
+        <v>1.042787661561566</v>
       </c>
       <c r="F2022" t="n">
-        <v>-0.04210636316327171</v>
+        <v>0.009290256164778465</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.35686024117825</v>
+        <v>3.38769821277508</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667962306830325</v>
+        <v>3.667962306830328</v>
       </c>
       <c r="C2023" t="n">
         <v>3.544328115775257</v>
       </c>
       <c r="D2023" t="n">
-        <v>-6.027820953643307</v>
+        <v>-5.939163942111833</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.132843310004186</v>
+        <v>1.168306114616776</v>
       </c>
       <c r="F2023" t="n">
-        <v>-0.04210636316327171</v>
+        <v>0.009290256164778465</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.519064297877294</v>
+        <v>3.549902269474124</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696539468071547</v>
+        <v>3.696539468071552</v>
       </c>
       <c r="C2024" t="n">
         <v>3.539174753739071</v>
       </c>
       <c r="D2024" t="n">
-        <v>-6.059472612703276</v>
+        <v>-5.970815601171802</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.115029284344013</v>
+        <v>1.150492088956602</v>
       </c>
       <c r="F2024" t="n">
-        <v>-0.04727482040771191</v>
+        <v>0.00412179892033826</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.510809861494444</v>
+        <v>3.541647833091274</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750044015868143</v>
+        <v>3.750044015868149</v>
       </c>
       <c r="C2025" t="n">
         <v>3.549404171307562</v>
       </c>
       <c r="D2025" t="n">
-        <v>-6.128538667276213</v>
+        <v>-6.039881655744739</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.097632280083329</v>
+        <v>1.133095084695919</v>
       </c>
       <c r="F2025" t="n">
-        <v>-0.1096456979013219</v>
+        <v>-0.05824907857327177</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.483616752566769</v>
+        <v>3.514454724163599</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783632867332689</v>
+        <v>3.783632867332695</v>
       </c>
       <c r="C2026" t="n">
         <v>3.558329809763465</v>
       </c>
       <c r="D2026" t="n">
-        <v>-6.23051478952462</v>
+        <v>-6.141857777993146</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.065767469639868</v>
+        <v>1.101230274252458</v>
       </c>
       <c r="F2026" t="n">
-        <v>-0.2116218201497295</v>
+        <v>-0.1602252008216793</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.431356717673627</v>
+        <v>3.462194689270457</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798296784231805</v>
+        <v>3.798296784231812</v>
       </c>
       <c r="C2027" t="n">
         <v>3.55048269700764</v>
       </c>
       <c r="D2027" t="n">
-        <v>-6.120508506047399</v>
+        <v>-6.031851494515925</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.101922870274933</v>
+        <v>1.137385674887522</v>
       </c>
       <c r="F2027" t="n">
-        <v>-0.1884172482324543</v>
+        <v>-0.1370206289044041</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.437432348068168</v>
+        <v>3.468270319664998</v>
       </c>
     </row>
     <row r="2028">
@@ -48195,16 +48195,16 @@
         <v>3.554732707729614</v>
       </c>
       <c r="D2028" t="n">
-        <v>-6.133038211159278</v>
+        <v>-6.044381199627804</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.101160998952155</v>
+        <v>1.136623803564745</v>
       </c>
       <c r="F2028" t="n">
-        <v>-0.2022437476989773</v>
+        <v>-0.1508471283709272</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.433386459110229</v>
+        <v>3.464224430707058</v>
       </c>
     </row>
     <row r="2029">
@@ -48218,16 +48218,16 @@
         <v>3.56199359061215</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.83159148568744</v>
+        <v>-5.742934474155966</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.229000572023426</v>
+        <v>1.264463376636016</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.09920297777285991</v>
+        <v>0.1505995971009101</v>
       </c>
       <c r="G2029" t="n">
-        <v>3.621515377275867</v>
+        <v>3.652353348872697</v>
       </c>
     </row>
     <row r="2030">
@@ -48241,16 +48241,16 @@
         <v>3.562964768364861</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.856181729922624</v>
+        <v>-5.76752471839115</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.220135652082063</v>
+        <v>1.255598456694653</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.09920297777285991</v>
+        <v>0.1505995971009101</v>
       </c>
       <c r="G2030" t="n">
-        <v>3.622486555028577</v>
+        <v>3.653324526625407</v>
       </c>
     </row>
     <row r="2031">
@@ -48264,16 +48264,16 @@
         <v>3.563807672744617</v>
       </c>
       <c r="D2031" t="n">
-        <v>-5.805143353916104</v>
+        <v>-5.71648634238463</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.241393906864427</v>
+        <v>1.276856711477017</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.09920297777285991</v>
+        <v>0.1505995971009101</v>
       </c>
       <c r="G2031" t="n">
-        <v>3.623329459408333</v>
+        <v>3.654167431005163</v>
       </c>
     </row>
     <row r="2032">
@@ -48281,22 +48281,22 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831734516969542</v>
+        <v>3.831734516969543</v>
       </c>
       <c r="C2032" t="n">
         <v>3.582845771618762</v>
       </c>
       <c r="D2032" t="n">
-        <v>-5.776294677092643</v>
+        <v>-5.687637665561169</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.271971476467957</v>
+        <v>1.307434281080546</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.1280516545963202</v>
+        <v>0.1794482739243703</v>
       </c>
       <c r="G2032" t="n">
-        <v>3.659676764376554</v>
+        <v>3.690514735973385</v>
       </c>
     </row>
     <row r="2033">
@@ -48304,22 +48304,22 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825752932700476</v>
+        <v>3.825752932700478</v>
       </c>
       <c r="C2033" t="n">
         <v>3.399029767742697</v>
       </c>
       <c r="D2033" t="n">
-        <v>-5.679659765074003</v>
+        <v>-5.591002753542529</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.126809437399347</v>
+        <v>1.162272242011937</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.2246865666149601</v>
+        <v>0.2760831859430103</v>
       </c>
       <c r="G2033" t="n">
-        <v>3.533841707711673</v>
+        <v>3.564679679308503</v>
       </c>
     </row>
     <row r="2034">
@@ -48327,22 +48327,22 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.804688961077638</v>
+        <v>3.804688961077642</v>
       </c>
       <c r="C2034" t="n">
         <v>3.402531811816661</v>
       </c>
       <c r="D2034" t="n">
-        <v>-5.610621754125535</v>
+        <v>-5.521964742594061</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.157926685852698</v>
+        <v>1.193389490465288</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.2937245775634282</v>
+        <v>0.3451211968914784</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.578766558354718</v>
+        <v>3.609604529951548</v>
       </c>
     </row>
     <row r="2035">
@@ -48350,22 +48350,22 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775028860833456</v>
+        <v>3.775028860833462</v>
       </c>
       <c r="C2035" t="n">
         <v>3.386958630892743</v>
       </c>
       <c r="D2035" t="n">
-        <v>-5.591834653756597</v>
+        <v>-5.503177642225123</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.149868345076356</v>
+        <v>1.185331149688946</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.3125116779323667</v>
+        <v>0.3639082972604168</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.574465637652164</v>
+        <v>3.605303609248994</v>
       </c>
     </row>
     <row r="2036">
@@ -48373,22 +48373,22 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821030660077626</v>
+        <v>3.821030660077627</v>
       </c>
       <c r="C2036" t="n">
         <v>3.386146341329173</v>
       </c>
       <c r="D2036" t="n">
-        <v>-5.514736052214724</v>
+        <v>-5.42607904068325</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.179895496129535</v>
+        <v>1.215358300742125</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.3125116779323667</v>
+        <v>0.3639082972604168</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.573653348088593</v>
+        <v>3.604491319685423</v>
       </c>
     </row>
     <row r="2037">
@@ -48396,22 +48396,22 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.832307024147908</v>
+        <v>3.832307024147909</v>
       </c>
       <c r="C2037" t="n">
         <v>3.396015120454245</v>
       </c>
       <c r="D2037" t="n">
-        <v>-5.525121247104614</v>
+        <v>-5.43646423557314</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.185610197298652</v>
+        <v>1.221073001911241</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.3021264830424774</v>
+        <v>0.3535231023705275</v>
       </c>
       <c r="G2037" t="n">
-        <v>3.577291010279732</v>
+        <v>3.608128981876562</v>
       </c>
     </row>
     <row r="2038">
@@ -48419,22 +48419,22 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.834415493735278</v>
+        <v>3.834415493735285</v>
       </c>
       <c r="C2038" t="n">
         <v>3.466852126230671</v>
       </c>
       <c r="D2038" t="n">
-        <v>-5.543709405826839</v>
+        <v>-5.455052394295365</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.249011939586187</v>
+        <v>1.284474744198777</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.283538324320252</v>
+        <v>0.3349349436483022</v>
       </c>
       <c r="G2038" t="n">
-        <v>3.636975120822822</v>
+        <v>3.667813092419652</v>
       </c>
     </row>
     <row r="2039">
@@ -48442,22 +48442,22 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.855120535496552</v>
+        <v>3.855120535496553</v>
       </c>
       <c r="C2039" t="n">
         <v>3.463721137048969</v>
       </c>
       <c r="D2039" t="n">
-        <v>-5.544007952522874</v>
+        <v>-5.4553509409914</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.245761531726072</v>
+        <v>1.281224336338661</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.2832397776242161</v>
+        <v>0.3346363969522663</v>
       </c>
       <c r="G2039" t="n">
-        <v>3.633665003623499</v>
+        <v>3.664502975220329</v>
       </c>
     </row>
     <row r="2040">
@@ -48465,22 +48465,22 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.815643212108854</v>
+        <v>3.81564321210886</v>
       </c>
       <c r="C2040" t="n">
         <v>3.468252031988361</v>
       </c>
       <c r="D2040" t="n">
-        <v>-5.443184818832447</v>
+        <v>-5.354527807300973</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.290621680141634</v>
+        <v>1.326084484754223</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.2957039931085699</v>
+        <v>0.3471006124366201</v>
       </c>
       <c r="G2040" t="n">
-        <v>3.645674427853503</v>
+        <v>3.676512399450333</v>
       </c>
     </row>
     <row r="2041">
@@ -48488,22 +48488,22 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.807356168121464</v>
+        <v>3.807356168121472</v>
       </c>
       <c r="C2041" t="n">
         <v>3.468381285466904</v>
       </c>
       <c r="D2041" t="n">
-        <v>-5.252403458080039</v>
+        <v>-5.163746446548565</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.36706347792114</v>
+        <v>1.40252628253373</v>
       </c>
       <c r="F2041" t="n">
-        <v>0.4864853538609773</v>
+        <v>0.5378819731890274</v>
       </c>
       <c r="G2041" t="n">
-        <v>3.76027249778349</v>
+        <v>3.791110469380321</v>
       </c>
     </row>
     <row r="2042">
@@ -48511,22 +48511,22 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.775233033906077</v>
+        <v>3.775233033906085</v>
       </c>
       <c r="C2042" t="n">
         <v>3.4482181312045</v>
       </c>
       <c r="D2042" t="n">
-        <v>-5.145440100230617</v>
+        <v>-5.056783088699143</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.389685666798505</v>
+        <v>1.425148471411095</v>
       </c>
       <c r="F2042" t="n">
-        <v>0.5449499618207787</v>
+        <v>0.5963465811488289</v>
       </c>
       <c r="G2042" t="n">
-        <v>3.775188108296968</v>
+        <v>3.806026079893798</v>
       </c>
     </row>
     <row r="2043">
@@ -48534,22 +48534,22 @@
         <v>45505</v>
       </c>
       <c r="B2043" t="n">
-        <v>3.785761685912981</v>
+        <v>3.785761685912989</v>
       </c>
       <c r="C2043" t="n">
         <v>3.483185067816559</v>
       </c>
       <c r="D2043" t="n">
-        <v>-5.090109512328855</v>
+        <v>-5.001452500797381</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.446784838571269</v>
+        <v>1.482247643183858</v>
       </c>
       <c r="F2043" t="n">
-        <v>0.6002805497225409</v>
+        <v>0.651677169050591</v>
       </c>
       <c r="G2043" t="n">
-        <v>3.843353397650084</v>
+        <v>3.874191369246914</v>
       </c>
     </row>
     <row r="2044">
@@ -48557,22 +48557,22 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.743767956539891</v>
+        <v>3.743767956539899</v>
       </c>
       <c r="C2044" t="n">
         <v>3.476871635717997</v>
       </c>
       <c r="D2044" t="n">
-        <v>-5.078055385415892</v>
+        <v>-4.989398373884418</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.445293057237892</v>
+        <v>1.480755861850481</v>
       </c>
       <c r="F2044" t="n">
-        <v>0.6123346766355037</v>
+        <v>0.6637312959635538</v>
       </c>
       <c r="G2044" t="n">
-        <v>3.844272441699299</v>
+        <v>3.875110413296129</v>
       </c>
     </row>
     <row r="2045">
@@ -48580,22 +48580,22 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.725010844811005</v>
+        <v>3.725010844811014</v>
       </c>
       <c r="C2045" t="n">
         <v>3.478752265902132</v>
       </c>
       <c r="D2045" t="n">
-        <v>-5.155410875543861</v>
+        <v>-5.066753864012387</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.41623149137084</v>
+        <v>1.45169429598343</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.5349791865075343</v>
+        <v>0.5863758058355845</v>
       </c>
       <c r="G2045" t="n">
-        <v>3.799739777806653</v>
+        <v>3.830577749403483</v>
       </c>
     </row>
     <row r="2046">
@@ -48603,22 +48603,22 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.612322444382916</v>
+        <v>3.612322444382925</v>
       </c>
       <c r="C2046" t="n">
         <v>3.491603291780015</v>
       </c>
       <c r="D2046" t="n">
-        <v>-5.087362312852331</v>
+        <v>-4.998705301320857</v>
       </c>
       <c r="E2046" t="n">
-        <v>1.456301942325334</v>
+        <v>1.491764746937924</v>
       </c>
       <c r="F2046" t="n">
-        <v>0.6030277491990641</v>
+        <v>0.6544243685271143</v>
       </c>
       <c r="G2046" t="n">
-        <v>3.853419941299454</v>
+        <v>3.884257912896284</v>
       </c>
     </row>
     <row r="2047">
@@ -48626,22 +48626,22 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.645256780013423</v>
+        <v>3.645256780013432</v>
       </c>
       <c r="C2047" t="n">
         <v>3.511805961953609</v>
       </c>
       <c r="D2047" t="n">
-        <v>-5.318962706021832</v>
+        <v>-5.230305694490358</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.383864455231128</v>
+        <v>1.419327259843718</v>
       </c>
       <c r="F2047" t="n">
-        <v>0.6030277491990641</v>
+        <v>0.6544243685271143</v>
       </c>
       <c r="G2047" t="n">
-        <v>3.873622611473048</v>
+        <v>3.904460583069878</v>
       </c>
     </row>
     <row r="2048">
@@ -48649,22 +48649,22 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666747201498967</v>
+        <v>3.666747201498968</v>
       </c>
       <c r="C2048" t="n">
         <v>3.495412198020491</v>
       </c>
       <c r="D2048" t="n">
-        <v>-5.369014251551052</v>
+        <v>-5.280357240019578</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.347450073086322</v>
+        <v>1.382912877698912</v>
       </c>
       <c r="F2048" t="n">
-        <v>0.6030277491990641</v>
+        <v>0.6544243685271143</v>
       </c>
       <c r="G2048" t="n">
-        <v>3.85722884753993</v>
+        <v>3.88806681913676</v>
       </c>
     </row>
     <row r="2049">
@@ -48672,22 +48672,22 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.670048702800096</v>
+        <v>3.670048702800097</v>
       </c>
       <c r="C2049" t="n">
         <v>3.455664111613958</v>
       </c>
       <c r="D2049" t="n">
-        <v>-5.544121084127497</v>
+        <v>-5.455464072596023</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.237659253649211</v>
+        <v>1.273122058261801</v>
       </c>
       <c r="F2049" t="n">
-        <v>0.6030277491990641</v>
+        <v>0.6544243685271143</v>
       </c>
       <c r="G2049" t="n">
-        <v>3.817480761133397</v>
+        <v>3.848318732730227</v>
       </c>
     </row>
     <row r="2050">
@@ -48695,22 +48695,22 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.745573148660848</v>
+        <v>3.745573148660849</v>
       </c>
       <c r="C2050" t="n">
         <v>3.462686730610898</v>
       </c>
       <c r="D2050" t="n">
-        <v>-5.348020930696974</v>
+        <v>-5.2593639191655</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.32312193401836</v>
+        <v>1.35858473863095</v>
       </c>
       <c r="F2050" t="n">
-        <v>0.799127902629587</v>
+        <v>0.8505245219576372</v>
       </c>
       <c r="G2050" t="n">
-        <v>3.94216347218865</v>
+        <v>3.97300144378548</v>
       </c>
     </row>
     <row r="2051">
@@ -48718,22 +48718,22 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.730570473395085</v>
+        <v>3.730570473395087</v>
       </c>
       <c r="C2051" t="n">
         <v>3.561857730183802</v>
       </c>
       <c r="D2051" t="n">
-        <v>-5.194995538583689</v>
+        <v>-5.106338527052215</v>
       </c>
       <c r="E2051" t="n">
-        <v>1.483503090436578</v>
+        <v>1.518965895049168</v>
       </c>
       <c r="F2051" t="n">
-        <v>0.9521532947428711</v>
+        <v>1.003549914070921</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.133149707029525</v>
+        <v>4.163987678626355</v>
       </c>
     </row>
     <row r="2052">
@@ -48741,22 +48741,22 @@
         <v>45514</v>
       </c>
       <c r="B2052" t="n">
-        <v>3.741278332791147</v>
+        <v>3.741278332791149</v>
       </c>
       <c r="C2052" t="n">
         <v>3.749323955092095</v>
       </c>
       <c r="D2052" t="n">
-        <v>-5.22330285245696</v>
+        <v>-5.134645840925486</v>
       </c>
       <c r="E2052" t="n">
-        <v>1.659646389795563</v>
+        <v>1.695109194408153</v>
       </c>
       <c r="F2052" t="n">
-        <v>0.9521532947428711</v>
+        <v>1.003549914070921</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.320615931937818</v>
+        <v>4.351453903534647</v>
       </c>
     </row>
     <row r="2053">
@@ -48764,22 +48764,22 @@
         <v>45515</v>
       </c>
       <c r="B2053" t="n">
-        <v>3.699115615620433</v>
+        <v>3.699115615620435</v>
       </c>
       <c r="C2053" t="n">
         <v>3.718726906446177</v>
       </c>
       <c r="D2053" t="n">
-        <v>-5.389896077570482</v>
+        <v>-5.301239066039008</v>
       </c>
       <c r="E2053" t="n">
-        <v>1.562412051104237</v>
+        <v>1.597874855716826</v>
       </c>
       <c r="F2053" t="n">
-        <v>0.7855600696293488</v>
+        <v>0.8369566889573987</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.190062948223787</v>
+        <v>4.220900919820616</v>
       </c>
     </row>
     <row r="2054">
@@ -48787,22 +48787,22 @@
         <v>45516</v>
       </c>
       <c r="B2054" t="n">
-        <v>3.708182519285645</v>
+        <v>3.708182519285647</v>
       </c>
       <c r="C2054" t="n">
         <v>3.722403309107895</v>
       </c>
       <c r="D2054" t="n">
-        <v>-5.366860284208916</v>
+        <v>-5.278203272677442</v>
       </c>
       <c r="E2054" t="n">
-        <v>1.575302771110581</v>
+        <v>1.61076557572317</v>
       </c>
       <c r="F2054" t="n">
-        <v>0.7855600696293488</v>
+        <v>0.8369566889573987</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.193739350885505</v>
+        <v>4.224577322482334</v>
       </c>
     </row>
     <row r="2055">
@@ -48810,22 +48810,22 @@
         <v>45517</v>
       </c>
       <c r="B2055" t="n">
-        <v>3.740581401399467</v>
+        <v>3.740581401399469</v>
       </c>
       <c r="C2055" t="n">
         <v>3.72002136423139</v>
       </c>
       <c r="D2055" t="n">
-        <v>-5.337614303753219</v>
+        <v>-5.248957292221745</v>
       </c>
       <c r="E2055" t="n">
-        <v>1.584619218416355</v>
+        <v>1.620082023028944</v>
       </c>
       <c r="F2055" t="n">
-        <v>0.7855600696293488</v>
+        <v>0.8369566889573987</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.191357406009</v>
+        <v>4.22219537760583</v>
       </c>
     </row>
     <row r="2056">
@@ -48833,22 +48833,22 @@
         <v>45518</v>
       </c>
       <c r="B2056" t="n">
-        <v>3.699404642256368</v>
+        <v>3.699404642256372</v>
       </c>
       <c r="C2056" t="n">
         <v>3.717314603389025</v>
       </c>
       <c r="D2056" t="n">
-        <v>-5.44453985163107</v>
+        <v>-5.355882840099596</v>
       </c>
       <c r="E2056" t="n">
-        <v>1.539142238422849</v>
+        <v>1.574605043035439</v>
       </c>
       <c r="F2056" t="n">
-        <v>0.6786345217514974</v>
+        <v>0.7300311410795474</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.124495316439925</v>
+        <v>4.155333288036754</v>
       </c>
     </row>
     <row r="2057">
@@ -48856,22 +48856,22 @@
         <v>45519</v>
       </c>
       <c r="B2057" t="n">
-        <v>3.689942600700998</v>
+        <v>3.689942600701002</v>
       </c>
       <c r="C2057" t="n">
         <v>3.71874340553226</v>
       </c>
       <c r="D2057" t="n">
-        <v>-5.589558410138319</v>
+        <v>-5.500901398606845</v>
       </c>
       <c r="E2057" t="n">
-        <v>1.482563617163184</v>
+        <v>1.518026421775774</v>
       </c>
       <c r="F2057" t="n">
-        <v>0.5336159632442489</v>
+        <v>0.5850125825722988</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.038912983478809</v>
+        <v>4.069750955075639</v>
       </c>
     </row>
     <row r="2058">
@@ -48879,22 +48879,22 @@
         <v>45520</v>
       </c>
       <c r="B2058" t="n">
-        <v>3.71185242968701</v>
+        <v>3.711852429687013</v>
       </c>
       <c r="C2058" t="n">
         <v>3.818674644790013</v>
       </c>
       <c r="D2058" t="n">
-        <v>-5.707900175923037</v>
+        <v>-5.619243164391563</v>
       </c>
       <c r="E2058" t="n">
-        <v>1.53515815010705</v>
+        <v>1.57062095471964</v>
       </c>
       <c r="F2058" t="n">
-        <v>0.5443020018071389</v>
+        <v>0.5956986211351889</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.145255845874297</v>
+        <v>4.176093817471126</v>
       </c>
     </row>
     <row r="2059">
@@ -48902,22 +48902,22 @@
         <v>45521</v>
       </c>
       <c r="B2059" t="n">
-        <v>3.7148790517908</v>
+        <v>3.714879051790806</v>
       </c>
       <c r="C2059" t="n">
         <v>3.816460341915952</v>
       </c>
       <c r="D2059" t="n">
-        <v>-5.759310598243744</v>
+        <v>-5.67065358671227</v>
       </c>
       <c r="E2059" t="n">
-        <v>1.512379678304706</v>
+        <v>1.547842482917296</v>
       </c>
       <c r="F2059" t="n">
-        <v>0.5443020018071389</v>
+        <v>0.5956986211351889</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.143041543000235</v>
+        <v>4.173879514597066</v>
       </c>
     </row>
     <row r="2060">
@@ -48925,22 +48925,22 @@
         <v>45522</v>
       </c>
       <c r="B2060" t="n">
-        <v>3.704757949437328</v>
+        <v>3.704757949437335</v>
       </c>
       <c r="C2060" t="n">
         <v>3.816363469990241</v>
       </c>
       <c r="D2060" t="n">
-        <v>-5.838730049451496</v>
+        <v>-5.750073037920022</v>
       </c>
       <c r="E2060" t="n">
-        <v>1.480515025895894</v>
+        <v>1.515977830508484</v>
       </c>
       <c r="F2060" t="n">
-        <v>0.5443020018071389</v>
+        <v>0.5956986211351889</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.142944671074525</v>
+        <v>4.173782642671354</v>
       </c>
     </row>
     <row r="2061">
@@ -48948,22 +48948,22 @@
         <v>45523</v>
       </c>
       <c r="B2061" t="n">
-        <v>3.736804952298394</v>
+        <v>3.736804952298403</v>
       </c>
       <c r="C2061" t="n">
         <v>3.816357363548284</v>
       </c>
       <c r="D2061" t="n">
-        <v>-5.934193047368714</v>
+        <v>-5.84553603583724</v>
       </c>
       <c r="E2061" t="n">
-        <v>1.44232372028705</v>
+        <v>1.47778652489964</v>
       </c>
       <c r="F2061" t="n">
-        <v>0.5443020018071389</v>
+        <v>0.5956986211351889</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.142938564632567</v>
+        <v>4.173776536229398</v>
       </c>
     </row>
     <row r="2062">
@@ -48971,22 +48971,22 @@
         <v>45524</v>
       </c>
       <c r="B2062" t="n">
-        <v>3.715372960217997</v>
+        <v>3.715372960218006</v>
       </c>
       <c r="C2062" t="n">
         <v>3.814453760110895</v>
       </c>
       <c r="D2062" t="n">
-        <v>-5.869817136517999</v>
+        <v>-5.781160124986525</v>
       </c>
       <c r="E2062" t="n">
-        <v>1.466170481189947</v>
+        <v>1.501633285802537</v>
       </c>
       <c r="F2062" t="n">
-        <v>0.6086779126578541</v>
+        <v>0.660074531985904</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.179660507705607</v>
+        <v>4.210498479302437</v>
       </c>
     </row>
     <row r="2063">
@@ -48994,22 +48994,22 @@
         <v>45525</v>
       </c>
       <c r="B2063" t="n">
-        <v>3.736089413353533</v>
+        <v>3.736089413353541</v>
       </c>
       <c r="C2063" t="n">
         <v>3.820187577858621</v>
       </c>
       <c r="D2063" t="n">
-        <v>-5.925186298650193</v>
+        <v>-5.836529287118719</v>
       </c>
       <c r="E2063" t="n">
-        <v>1.449756634084796</v>
+        <v>1.485219438697386</v>
       </c>
       <c r="F2063" t="n">
-        <v>0.6086779126578541</v>
+        <v>0.660074531985904</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.185394325453334</v>
+        <v>4.216232297050164</v>
       </c>
     </row>
     <row r="2064">
@@ -49017,22 +49017,22 @@
         <v>45526</v>
       </c>
       <c r="B2064" t="n">
-        <v>3.736822870113276</v>
+        <v>3.736822870113285</v>
       </c>
       <c r="C2064" t="n">
         <v>3.819725941201554</v>
       </c>
       <c r="D2064" t="n">
-        <v>-5.943404765647801</v>
+        <v>-5.854747754116327</v>
       </c>
       <c r="E2064" t="n">
-        <v>1.442007610628685</v>
+        <v>1.477470415241275</v>
       </c>
       <c r="F2064" t="n">
-        <v>0.5835714754020119</v>
+        <v>0.6349680947300619</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.169868826442761</v>
+        <v>4.200706798039591</v>
       </c>
     </row>
     <row r="2065">
@@ -49040,22 +49040,22 @@
         <v>45527</v>
       </c>
       <c r="B2065" t="n">
-        <v>3.790272500113684</v>
+        <v>3.790272500113693</v>
       </c>
       <c r="C2065" t="n">
         <v>3.839600334051872</v>
       </c>
       <c r="D2065" t="n">
-        <v>-5.904721330303871</v>
+        <v>-5.816064318772397</v>
       </c>
       <c r="E2065" t="n">
-        <v>1.477355377616576</v>
+        <v>1.512818182229166</v>
       </c>
       <c r="F2065" t="n">
-        <v>0.5835714754020119</v>
+        <v>0.6349680947300619</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.18974321929308</v>
+        <v>4.220581190889909</v>
       </c>
     </row>
     <row r="2066">
@@ -49063,22 +49063,22 @@
         <v>45528</v>
       </c>
       <c r="B2066" t="n">
-        <v>3.794486844016436</v>
+        <v>3.794486844016438</v>
       </c>
       <c r="C2066" t="n">
         <v>3.8233010345766</v>
       </c>
       <c r="D2066" t="n">
-        <v>-5.798686335098561</v>
+        <v>-5.710029323567087</v>
       </c>
       <c r="E2066" t="n">
-        <v>1.503470076223428</v>
+        <v>1.538932880836017</v>
       </c>
       <c r="F2066" t="n">
-        <v>0.5835714754020119</v>
+        <v>0.6349680947300619</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.173443919817807</v>
+        <v>4.204281891414637</v>
       </c>
     </row>
     <row r="2067">
@@ -49086,22 +49086,22 @@
         <v>45529</v>
       </c>
       <c r="B2067" t="n">
-        <v>3.794705093307668</v>
+        <v>3.79470509330767</v>
       </c>
       <c r="C2067" t="n">
         <v>3.825731984040646</v>
       </c>
       <c r="D2067" t="n">
-        <v>-5.615474671965466</v>
+        <v>-5.526817660433992</v>
       </c>
       <c r="E2067" t="n">
-        <v>1.579185690940712</v>
+        <v>1.614648495553301</v>
       </c>
       <c r="F2067" t="n">
-        <v>0.5835714754020119</v>
+        <v>0.6349680947300619</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.175874869281854</v>
+        <v>4.206712840878684</v>
       </c>
     </row>
     <row r="2068">
@@ -49109,22 +49109,22 @@
         <v>45530</v>
       </c>
       <c r="B2068" t="n">
-        <v>3.776846557863549</v>
+        <v>3.776846557863551</v>
       </c>
       <c r="C2068" t="n">
         <v>3.808676390120023</v>
       </c>
       <c r="D2068" t="n">
-        <v>-5.543753224951615</v>
+        <v>-5.455096213420141</v>
       </c>
       <c r="E2068" t="n">
-        <v>1.590818675825629</v>
+        <v>1.626281480438219</v>
       </c>
       <c r="F2068" t="n">
-        <v>0.6552929224158626</v>
+        <v>0.7066895417439125</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.201852143569541</v>
+        <v>4.232690115166371</v>
       </c>
     </row>
     <row r="2069">
@@ -49132,22 +49132,22 @@
         <v>45531</v>
       </c>
       <c r="B2069" t="n">
-        <v>3.723789705394109</v>
+        <v>3.723789705394113</v>
       </c>
       <c r="C2069" t="n">
         <v>3.755592136041195</v>
       </c>
       <c r="D2069" t="n">
-        <v>-5.521380199343909</v>
+        <v>-5.432723187812435</v>
       </c>
       <c r="E2069" t="n">
-        <v>1.546683631989883</v>
+        <v>1.582146436602473</v>
       </c>
       <c r="F2069" t="n">
-        <v>0.6665486735287641</v>
+        <v>0.7179452928568141</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.155521340158454</v>
+        <v>4.186359311755283</v>
       </c>
     </row>
     <row r="2070">
@@ -49155,22 +49155,22 @@
         <v>45532</v>
       </c>
       <c r="B2070" t="n">
-        <v>3.715607446456726</v>
+        <v>3.715607446456731</v>
       </c>
       <c r="C2070" t="n">
         <v>3.94079034092655</v>
       </c>
       <c r="D2070" t="n">
-        <v>-5.554396495254654</v>
+        <v>-5.46573948372318</v>
       </c>
       <c r="E2070" t="n">
-        <v>1.71867531851094</v>
+        <v>1.75413812312353</v>
       </c>
       <c r="F2070" t="n">
-        <v>0.5971112968620125</v>
+        <v>0.6485079161900624</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.299057119043757</v>
+        <v>4.329895090640588</v>
       </c>
     </row>
     <row r="2071">
@@ -49178,22 +49178,22 @@
         <v>45533</v>
       </c>
       <c r="B2071" t="n">
-        <v>3.713762536883674</v>
+        <v>3.713762536883682</v>
       </c>
       <c r="C2071" t="n">
         <v>3.932711566754799</v>
       </c>
       <c r="D2071" t="n">
-        <v>-5.542868859605045</v>
+        <v>-5.454211848073571</v>
       </c>
       <c r="E2071" t="n">
-        <v>1.715207598599033</v>
+        <v>1.750670403211622</v>
       </c>
       <c r="F2071" t="n">
-        <v>0.6561119550633749</v>
+        <v>0.7075085743914249</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.326378739792824</v>
+        <v>4.357216711389654</v>
       </c>
     </row>
     <row r="2072">
@@ -49201,22 +49201,22 @@
         <v>45534</v>
       </c>
       <c r="B2072" t="n">
-        <v>3.717150699236295</v>
+        <v>3.717150699236303</v>
       </c>
       <c r="C2072" t="n">
         <v>3.936379679276587</v>
       </c>
       <c r="D2072" t="n">
-        <v>-5.640210360947414</v>
+        <v>-5.55155334941594</v>
       </c>
       <c r="E2072" t="n">
-        <v>1.679939110583874</v>
+        <v>1.715401915196463</v>
       </c>
       <c r="F2072" t="n">
-        <v>0.6116917728978866</v>
+        <v>0.6630883922259365</v>
       </c>
       <c r="G2072" t="n">
-        <v>4.303394743015319</v>
+        <v>4.33423271461215</v>
       </c>
     </row>
     <row r="2073">
@@ -49224,22 +49224,22 @@
         <v>45535</v>
       </c>
       <c r="B2073" t="n">
-        <v>3.705201079427681</v>
+        <v>3.70520107942769</v>
       </c>
       <c r="C2073" t="n">
         <v>3.937630761469426</v>
       </c>
       <c r="D2073" t="n">
-        <v>-5.726066390287381</v>
+        <v>-5.637409378755907</v>
       </c>
       <c r="E2073" t="n">
-        <v>1.646847781040726</v>
+        <v>1.682310585653315</v>
       </c>
       <c r="F2073" t="n">
-        <v>0.5693157036717515</v>
+        <v>0.6207123229998015</v>
       </c>
       <c r="G2073" t="n">
-        <v>4.279220183672477</v>
+        <v>4.310058155269306</v>
       </c>
     </row>
     <row r="2074">
@@ -49247,22 +49247,22 @@
         <v>45536</v>
       </c>
       <c r="B2074" t="n">
-        <v>3.691835499610379</v>
+        <v>3.69183549961038</v>
       </c>
       <c r="C2074" t="n">
         <v>3.920049963289927</v>
       </c>
       <c r="D2074" t="n">
-        <v>-5.7349031877035</v>
+        <v>-5.646246176172026</v>
       </c>
       <c r="E2074" t="n">
-        <v>1.62573226389478</v>
+        <v>1.661195068507369</v>
       </c>
       <c r="F2074" t="n">
-        <v>0.5618735310304008</v>
+        <v>0.6132701503584508</v>
       </c>
       <c r="G2074" t="n">
-        <v>4.257174081908168</v>
+        <v>4.288012053504998</v>
       </c>
     </row>
     <row r="2075">
@@ -49270,22 +49270,22 @@
         <v>45537</v>
       </c>
       <c r="B2075" t="n">
-        <v>3.715544411667452</v>
+        <v>3.715544411667459</v>
       </c>
       <c r="C2075" t="n">
         <v>3.930214474334977</v>
       </c>
       <c r="D2075" t="n">
-        <v>-5.826285750268958</v>
+        <v>-5.737628738737484</v>
       </c>
       <c r="E2075" t="n">
-        <v>1.599343749913646</v>
+        <v>1.634806554526235</v>
       </c>
       <c r="F2075" t="n">
-        <v>0.5253086463110561</v>
+        <v>0.5767052656391061</v>
       </c>
       <c r="G2075" t="n">
-        <v>4.245399662121611</v>
+        <v>4.27623763371844</v>
       </c>
     </row>
     <row r="2076">
@@ -49293,22 +49293,22 @@
         <v>45538</v>
       </c>
       <c r="B2076" t="n">
-        <v>3.673978374889188</v>
+        <v>3.673978374889197</v>
       </c>
       <c r="C2076" t="n">
         <v>4.032342732159245</v>
       </c>
       <c r="D2076" t="n">
-        <v>-5.814579032281952</v>
+        <v>-5.725922020750478</v>
       </c>
       <c r="E2076" t="n">
-        <v>1.706154694932716</v>
+        <v>1.741617499545306</v>
       </c>
       <c r="F2076" t="n">
-        <v>0.5370153642980625</v>
+        <v>0.5884119836261125</v>
       </c>
       <c r="G2076" t="n">
-        <v>4.354551950738083</v>
+        <v>4.385389922334912</v>
       </c>
     </row>
     <row r="2077">
@@ -49316,22 +49316,22 @@
         <v>45539</v>
       </c>
       <c r="B2077" t="n">
-        <v>3.682476099409563</v>
+        <v>3.682476099409572</v>
       </c>
       <c r="C2077" t="n">
         <v>4.03537507089065</v>
       </c>
       <c r="D2077" t="n">
-        <v>-5.885491106024229</v>
+        <v>-5.796834094492755</v>
       </c>
       <c r="E2077" t="n">
-        <v>1.68082220416721</v>
+        <v>1.7162850087798</v>
       </c>
       <c r="F2077" t="n">
-        <v>0.5370153642980625</v>
+        <v>0.5884119836261125</v>
       </c>
       <c r="G2077" t="n">
-        <v>4.357584289469488</v>
+        <v>4.388422261066317</v>
       </c>
     </row>
     <row r="2078">
@@ -49339,22 +49339,22 @@
         <v>45540</v>
       </c>
       <c r="B2078" t="n">
-        <v>3.672895177452569</v>
+        <v>3.67289517745257</v>
       </c>
       <c r="C2078" t="n">
         <v>4.036193896622915</v>
       </c>
       <c r="D2078" t="n">
-        <v>-5.895807204190581</v>
+        <v>-5.807150192659107</v>
       </c>
       <c r="E2078" t="n">
-        <v>1.677514590632934</v>
+        <v>1.712977395245523</v>
       </c>
       <c r="F2078" t="n">
-        <v>0.5370153642980625</v>
+        <v>0.5884119836261125</v>
       </c>
       <c r="G2078" t="n">
-        <v>4.358403115201752</v>
+        <v>4.389241086798582</v>
       </c>
     </row>
     <row r="2079">
@@ -49362,22 +49362,22 @@
         <v>45541</v>
       </c>
       <c r="B2079" t="n">
-        <v>3.623960959762283</v>
+        <v>3.623960959762292</v>
       </c>
       <c r="C2079" t="n">
         <v>4.035372563535004</v>
       </c>
       <c r="D2079" t="n">
-        <v>-5.895713236173209</v>
+        <v>-5.807056224641735</v>
       </c>
       <c r="E2079" t="n">
-        <v>1.676730844751973</v>
+        <v>1.712193649364562</v>
       </c>
       <c r="F2079" t="n">
-        <v>0.5373852256453805</v>
+        <v>0.5887818449734304</v>
       </c>
       <c r="G2079" t="n">
-        <v>4.357803698922233</v>
+        <v>4.388641670519062</v>
       </c>
     </row>
     <row r="2080">
@@ -49385,22 +49385,22 @@
         <v>45542</v>
       </c>
       <c r="B2080" t="n">
-        <v>3.800870306884075</v>
+        <v>3.800870306884084</v>
       </c>
       <c r="C2080" t="n">
         <v>4.029604549479358</v>
       </c>
       <c r="D2080" t="n">
-        <v>-6.039314400196594</v>
+        <v>-5.95065738866512</v>
       </c>
       <c r="E2080" t="n">
-        <v>1.613522365086972</v>
+        <v>1.648985169699562</v>
       </c>
       <c r="F2080" t="n">
-        <v>0.5373852256453805</v>
+        <v>0.5887818449734304</v>
       </c>
       <c r="G2080" t="n">
-        <v>4.352035684866586</v>
+        <v>4.382873656463416</v>
       </c>
     </row>
     <row r="2081">
@@ -49408,22 +49408,22 @@
         <v>45543</v>
       </c>
       <c r="B2081" t="n">
-        <v>3.671015692129645</v>
+        <v>3.671015692129648</v>
       </c>
       <c r="C2081" t="n">
         <v>4.029604549479358</v>
       </c>
       <c r="D2081" t="n">
-        <v>-6.038365977078556</v>
+        <v>-5.949708965547082</v>
       </c>
       <c r="E2081" t="n">
-        <v>1.613901734334187</v>
+        <v>1.649364538946777</v>
       </c>
       <c r="F2081" t="n">
-        <v>0.5373852256453805</v>
+        <v>0.5887818449734304</v>
       </c>
       <c r="G2081" t="n">
-        <v>4.352035684866586</v>
+        <v>4.382873656463416</v>
       </c>
     </row>
     <row r="2082">
@@ -49431,22 +49431,22 @@
         <v>45544</v>
       </c>
       <c r="B2082" t="n">
-        <v>3.904173816052348</v>
+        <v>3.904173816052351</v>
       </c>
       <c r="C2082" t="n">
         <v>4.04233215746045</v>
       </c>
       <c r="D2082" t="n">
-        <v>-6.138635795037576</v>
+        <v>-6.049978783506102</v>
       </c>
       <c r="E2082" t="n">
-        <v>1.586521415131672</v>
+        <v>1.621984219744261</v>
       </c>
       <c r="F2082" t="n">
-        <v>0.5373852256453805</v>
+        <v>0.5887818449734304</v>
       </c>
       <c r="G2082" t="n">
-        <v>4.364763292847678</v>
+        <v>4.395601264444508</v>
       </c>
     </row>
     <row r="2083">
@@ -49454,22 +49454,22 @@
         <v>45545</v>
       </c>
       <c r="B2083" t="n">
-        <v>3.740179607813492</v>
+        <v>3.740179607813495</v>
       </c>
       <c r="C2083" t="n">
         <v>4.044278155884838</v>
       </c>
       <c r="D2083" t="n">
-        <v>-6.132643548248764</v>
+        <v>-6.04398653671729</v>
       </c>
       <c r="E2083" t="n">
-        <v>1.590864312271584</v>
+        <v>1.626327116884173</v>
       </c>
       <c r="F2083" t="n">
-        <v>0.5373852256453805</v>
+        <v>0.5887818449734304</v>
       </c>
       <c r="G2083" t="n">
-        <v>4.366709291272066</v>
+        <v>4.397547262868896</v>
       </c>
     </row>
     <row r="2084">
@@ -49477,22 +49477,22 @@
         <v>45546</v>
       </c>
       <c r="B2084" t="n">
-        <v>3.765050796537942</v>
+        <v>3.765050796537944</v>
       </c>
       <c r="C2084" t="n">
         <v>4.037932291902607</v>
       </c>
       <c r="D2084" t="n">
-        <v>-6.044085587117997</v>
+        <v>-5.955428575586523</v>
       </c>
       <c r="E2084" t="n">
-        <v>1.61994163274166</v>
+        <v>1.65540443735425</v>
       </c>
       <c r="F2084" t="n">
-        <v>0.5373852256453805</v>
+        <v>0.5887818449734304</v>
       </c>
       <c r="G2084" t="n">
-        <v>4.360363427289835</v>
+        <v>4.391201398886665</v>
       </c>
     </row>
     <row r="2085">
@@ -49500,22 +49500,22 @@
         <v>45547</v>
       </c>
       <c r="B2085" t="n">
-        <v>3.758409170771814</v>
+        <v>3.758409170771816</v>
       </c>
       <c r="C2085" t="n">
         <v>4.037240969341602</v>
       </c>
       <c r="D2085" t="n">
-        <v>-6.026326509614923</v>
+        <v>-5.937669498083449</v>
       </c>
       <c r="E2085" t="n">
-        <v>1.626353941181885</v>
+        <v>1.661816745794475</v>
       </c>
       <c r="F2085" t="n">
-        <v>0.5373852256453805</v>
+        <v>0.5887818449734304</v>
       </c>
       <c r="G2085" t="n">
-        <v>4.359672104728831</v>
+        <v>4.39051007632566</v>
       </c>
     </row>
     <row r="2086">
@@ -49523,22 +49523,22 @@
         <v>45548</v>
       </c>
       <c r="B2086" t="n">
-        <v>3.80134059710972</v>
+        <v>3.801340597109721</v>
       </c>
       <c r="C2086" t="n">
         <v>4.050023155250189</v>
       </c>
       <c r="D2086" t="n">
-        <v>-5.926696358565855</v>
+        <v>-5.838039347034381</v>
       </c>
       <c r="E2086" t="n">
-        <v>1.678988187510099</v>
+        <v>1.714450992122689</v>
       </c>
       <c r="F2086" t="n">
-        <v>0.637015376694448</v>
+        <v>0.6884119960224979</v>
       </c>
       <c r="G2086" t="n">
-        <v>4.432232381266858</v>
+        <v>4.463070352863688</v>
       </c>
     </row>
     <row r="2087">
@@ -49546,22 +49546,22 @@
         <v>45549</v>
       </c>
       <c r="B2087" t="n">
-        <v>3.798465546843994</v>
+        <v>3.798465546843996</v>
       </c>
       <c r="C2087" t="n">
         <v>4.239177420748915</v>
       </c>
       <c r="D2087" t="n">
-        <v>-5.976095867254866</v>
+        <v>-5.887438855723392</v>
       </c>
       <c r="E2087" t="n">
-        <v>1.848382649533221</v>
+        <v>1.883845454145811</v>
       </c>
       <c r="F2087" t="n">
-        <v>0.6472742101261927</v>
+        <v>0.6986708294542426</v>
       </c>
       <c r="G2087" t="n">
-        <v>4.627541946824631</v>
+        <v>4.658379918421462</v>
       </c>
     </row>
     <row r="2088">
@@ -49569,22 +49569,22 @@
         <v>45550</v>
       </c>
       <c r="B2088" t="n">
-        <v>3.772186508351855</v>
+        <v>3.77218650835186</v>
       </c>
       <c r="C2088" t="n">
         <v>4.226366093851778</v>
       </c>
       <c r="D2088" t="n">
-        <v>-5.76941139361249</v>
+        <v>-5.680754382081016</v>
       </c>
       <c r="E2088" t="n">
-        <v>1.918245112093034</v>
+        <v>1.953707916705623</v>
       </c>
       <c r="F2088" t="n">
-        <v>0.8539586837685683</v>
+        <v>0.9053553030966183</v>
       </c>
       <c r="G2088" t="n">
-        <v>4.738741304112919</v>
+        <v>4.769579275709749</v>
       </c>
     </row>
     <row r="2089">
@@ -49592,22 +49592,22 @@
         <v>45551</v>
       </c>
       <c r="B2089" t="n">
-        <v>3.763392838551265</v>
+        <v>3.76339283855127</v>
       </c>
       <c r="C2089" t="n">
         <v>4.228367607505882</v>
       </c>
       <c r="D2089" t="n">
-        <v>-5.803568288610016</v>
+        <v>-5.714911277078542</v>
       </c>
       <c r="E2089" t="n">
-        <v>1.906583867748128</v>
+        <v>1.942046672360718</v>
       </c>
       <c r="F2089" t="n">
-        <v>0.7703749142277558</v>
+        <v>0.8217715335558058</v>
       </c>
       <c r="G2089" t="n">
-        <v>4.690592556042536</v>
+        <v>4.721430527639367</v>
       </c>
     </row>
     <row r="2090">
@@ -49615,22 +49615,22 @@
         <v>45552</v>
       </c>
       <c r="B2090" t="n">
-        <v>3.805590565041106</v>
+        <v>3.805590565041111</v>
       </c>
       <c r="C2090" t="n">
         <v>4.58186472149555</v>
       </c>
       <c r="D2090" t="n">
-        <v>-5.71097880954856</v>
+        <v>-5.622321798017086</v>
       </c>
       <c r="E2090" t="n">
-        <v>2.297116773362378</v>
+        <v>2.332579577974968</v>
       </c>
       <c r="F2090" t="n">
-        <v>0.7703749142277558</v>
+        <v>0.8217715335558058</v>
       </c>
       <c r="G2090" t="n">
-        <v>5.044089670032204</v>
+        <v>5.074927641629033</v>
       </c>
     </row>
     <row r="2091">
@@ -49638,22 +49638,22 @@
         <v>45553</v>
       </c>
       <c r="B2091" t="n">
-        <v>3.832164354497396</v>
+        <v>3.832164354497403</v>
       </c>
       <c r="C2091" t="n">
         <v>4.586427833062654</v>
       </c>
       <c r="D2091" t="n">
-        <v>-5.784139413321705</v>
+        <v>-5.695482401790231</v>
       </c>
       <c r="E2091" t="n">
-        <v>2.272415643420224</v>
+        <v>2.307878448032814</v>
       </c>
       <c r="F2091" t="n">
-        <v>0.7423537141935128</v>
+        <v>0.7937503335215628</v>
       </c>
       <c r="G2091" t="n">
-        <v>5.031840061578762</v>
+        <v>5.062678033175592</v>
       </c>
     </row>
     <row r="2092">
@@ -49661,22 +49661,22 @@
         <v>45554</v>
       </c>
       <c r="B2092" t="n">
-        <v>3.858310890492286</v>
+        <v>3.858310890492296</v>
       </c>
       <c r="C2092" t="n">
         <v>4.636257774386181</v>
       </c>
       <c r="D2092" t="n">
-        <v>-5.731923103525363</v>
+        <v>-5.643266091993889</v>
       </c>
       <c r="E2092" t="n">
-        <v>2.343132108662288</v>
+        <v>2.378594913274878</v>
       </c>
       <c r="F2092" t="n">
-        <v>0.7423537141935128</v>
+        <v>0.7937503335215628</v>
       </c>
       <c r="G2092" t="n">
-        <v>5.081670002902289</v>
+        <v>5.11250797449912</v>
       </c>
     </row>
     <row r="2093">
@@ -49684,22 +49684,22 @@
         <v>45555</v>
       </c>
       <c r="B2093" t="n">
-        <v>3.844935596436468</v>
+        <v>3.844935596436478</v>
       </c>
       <c r="C2093" t="n">
         <v>4.645071744596192</v>
       </c>
       <c r="D2093" t="n">
-        <v>-5.679415776014868</v>
+        <v>-5.590758764483394</v>
       </c>
       <c r="E2093" t="n">
-        <v>2.372949009876497</v>
+        <v>2.408411814489087</v>
       </c>
       <c r="F2093" t="n">
-        <v>0.7948610417040077</v>
+        <v>0.8462576610320577</v>
       </c>
       <c r="G2093" t="n">
-        <v>5.121988369618597</v>
+        <v>5.152826341215428</v>
       </c>
     </row>
     <row r="2094">
@@ -49707,22 +49707,22 @@
         <v>45556</v>
       </c>
       <c r="B2094" t="n">
-        <v>3.848376866039477</v>
+        <v>3.848376866039487</v>
       </c>
       <c r="C2094" t="n">
         <v>4.640709328635389</v>
       </c>
       <c r="D2094" t="n">
-        <v>-5.694171100215009</v>
+        <v>-5.605514088683535</v>
       </c>
       <c r="E2094" t="n">
-        <v>2.362684464235638</v>
+        <v>2.398147268848227</v>
       </c>
       <c r="F2094" t="n">
-        <v>0.7948610417040077</v>
+        <v>0.8462576610320577</v>
       </c>
       <c r="G2094" t="n">
-        <v>5.117625953657794</v>
+        <v>5.148463925254624</v>
       </c>
     </row>
     <row r="2095">
@@ -49730,22 +49730,22 @@
         <v>45557</v>
       </c>
       <c r="B2095" t="n">
-        <v>3.868153115524471</v>
+        <v>3.868153115524482</v>
       </c>
       <c r="C2095" t="n">
         <v>4.631633832051669</v>
       </c>
       <c r="D2095" t="n">
-        <v>-5.644706476845097</v>
+        <v>-5.556049465313623</v>
       </c>
       <c r="E2095" t="n">
-        <v>2.373394816999883</v>
+        <v>2.408857621612472</v>
       </c>
       <c r="F2095" t="n">
-        <v>0.8443256650739194</v>
+        <v>0.8957222844019693</v>
       </c>
       <c r="G2095" t="n">
-        <v>5.138229231096021</v>
+        <v>5.169067202692851</v>
       </c>
     </row>
     <row r="2096">
@@ -49753,22 +49753,22 @@
         <v>45558</v>
       </c>
       <c r="B2096" t="n">
-        <v>3.849040239867945</v>
+        <v>3.849040239867955</v>
       </c>
       <c r="C2096" t="n">
         <v>4.628041499766604</v>
       </c>
       <c r="D2096" t="n">
-        <v>-5.481598484691482</v>
+        <v>-5.392941473160008</v>
       </c>
       <c r="E2096" t="n">
-        <v>2.435045681576263</v>
+        <v>2.470508486188853</v>
       </c>
       <c r="F2096" t="n">
-        <v>1.007433657227535</v>
+        <v>1.058830276555585</v>
       </c>
       <c r="G2096" t="n">
-        <v>5.232501694103124</v>
+        <v>5.263339665699955</v>
       </c>
     </row>
     <row r="2097">
@@ -49776,22 +49776,22 @@
         <v>45559</v>
       </c>
       <c r="B2097" t="n">
-        <v>3.870204928232968</v>
+        <v>3.870204928232971</v>
       </c>
       <c r="C2097" t="n">
         <v>4.637088536457732</v>
       </c>
       <c r="D2097" t="n">
-        <v>-5.460955393890254</v>
+        <v>-5.37229838235878</v>
       </c>
       <c r="E2097" t="n">
-        <v>2.452349954587882</v>
+        <v>2.487812759200472</v>
       </c>
       <c r="F2097" t="n">
-        <v>1.007433657227535</v>
+        <v>1.058830276555585</v>
       </c>
       <c r="G2097" t="n">
-        <v>5.241548730794253</v>
+        <v>5.272386702391083</v>
       </c>
     </row>
     <row r="2098">
@@ -49799,22 +49799,22 @@
         <v>45560</v>
       </c>
       <c r="B2098" t="n">
-        <v>3.855534437179672</v>
+        <v>3.855534437179674</v>
       </c>
       <c r="C2098" t="n">
         <v>4.637946001443853</v>
       </c>
       <c r="D2098" t="n">
-        <v>-5.523663310364812</v>
+        <v>-5.435006298833338</v>
       </c>
       <c r="E2098" t="n">
-        <v>2.428124252984181</v>
+        <v>2.46358705759677</v>
       </c>
       <c r="F2098" t="n">
-        <v>0.9447257407529769</v>
+        <v>0.9961223600810269</v>
       </c>
       <c r="G2098" t="n">
-        <v>5.20478144589564</v>
+        <v>5.23561941749247</v>
       </c>
     </row>
     <row r="2099">
@@ -49822,22 +49822,22 @@
         <v>45561</v>
       </c>
       <c r="B2099" t="n">
-        <v>3.884687848967719</v>
+        <v>3.884687848967721</v>
       </c>
       <c r="C2099" t="n">
         <v>4.600855418234206</v>
       </c>
       <c r="D2099" t="n">
-        <v>-5.475655186521119</v>
+        <v>-5.386998174989645</v>
       </c>
       <c r="E2099" t="n">
-        <v>2.41023691931201</v>
+        <v>2.4456997239246</v>
       </c>
       <c r="F2099" t="n">
-        <v>0.9447257407529769</v>
+        <v>0.9961223600810269</v>
       </c>
       <c r="G2099" t="n">
-        <v>5.167690862685992</v>
+        <v>5.198528834282822</v>
       </c>
     </row>
     <row r="2100">
@@ -49845,22 +49845,22 @@
         <v>45562</v>
       </c>
       <c r="B2100" t="n">
-        <v>3.895362357018607</v>
+        <v>3.895362357018612</v>
       </c>
       <c r="C2100" t="n">
         <v>4.604787671792156</v>
       </c>
       <c r="D2100" t="n">
-        <v>-5.325537131299222</v>
+        <v>-5.236880119767748</v>
       </c>
       <c r="E2100" t="n">
-        <v>2.474216394958719</v>
+        <v>2.509679199571309</v>
       </c>
       <c r="F2100" t="n">
-        <v>1.094843795974874</v>
+        <v>1.146240415302924</v>
       </c>
       <c r="G2100" t="n">
-        <v>5.261693949377081</v>
+        <v>5.292531920973911</v>
       </c>
     </row>
     <row r="2101">
@@ -49868,22 +49868,22 @@
         <v>45563</v>
       </c>
       <c r="B2101" t="n">
-        <v>3.89161098107513</v>
+        <v>3.891610981075135</v>
       </c>
       <c r="C2101" t="n">
         <v>4.599686764399193</v>
       </c>
       <c r="D2101" t="n">
-        <v>-5.133602330045348</v>
+        <v>-5.044945318513874</v>
       </c>
       <c r="E2101" t="n">
-        <v>2.545889408067306</v>
+        <v>2.581352212679895</v>
       </c>
       <c r="F2101" t="n">
-        <v>1.094843795974874</v>
+        <v>1.146240415302924</v>
       </c>
       <c r="G2101" t="n">
-        <v>5.256593041984118</v>
+        <v>5.287431013580948</v>
       </c>
     </row>
     <row r="2102">
@@ -49891,22 +49891,22 @@
         <v>45564</v>
       </c>
       <c r="B2102" t="n">
-        <v>3.872432493435436</v>
+        <v>3.872432493435445</v>
       </c>
       <c r="C2102" t="n">
         <v>4.595040673788288</v>
       </c>
       <c r="D2102" t="n">
-        <v>-5.01542895202742</v>
+        <v>-4.926771940495946</v>
       </c>
       <c r="E2102" t="n">
-        <v>2.588512668663572</v>
+        <v>2.623975473276162</v>
       </c>
       <c r="F2102" t="n">
-        <v>1.213017173992801</v>
+        <v>1.264413793320851</v>
       </c>
       <c r="G2102" t="n">
-        <v>5.322850978183969</v>
+        <v>5.353688949780799</v>
       </c>
     </row>
     <row r="2103">
@@ -49914,22 +49914,22 @@
         <v>45565</v>
       </c>
       <c r="B2103" t="n">
-        <v>3.859571723917725</v>
+        <v>3.859571723917734</v>
       </c>
       <c r="C2103" t="n">
         <v>4.624129266651315</v>
       </c>
       <c r="D2103" t="n">
-        <v>-4.926581835167923</v>
+        <v>-4.837924823636449</v>
       </c>
       <c r="E2103" t="n">
-        <v>2.653140108270398</v>
+        <v>2.688602912882987</v>
       </c>
       <c r="F2103" t="n">
-        <v>1.301864290852299</v>
+        <v>1.353260910180349</v>
       </c>
       <c r="G2103" t="n">
-        <v>5.405247841162694</v>
+        <v>5.436085812759525</v>
       </c>
     </row>
     <row r="2104">
@@ -49937,22 +49937,22 @@
         <v>45566</v>
       </c>
       <c r="B2104" t="n">
-        <v>3.828006274013631</v>
+        <v>3.82800627401364</v>
       </c>
       <c r="C2104" t="n">
         <v>4.617689489662492</v>
       </c>
       <c r="D2104" t="n">
-        <v>-4.899532797474669</v>
+        <v>-4.810875785943195</v>
       </c>
       <c r="E2104" t="n">
-        <v>2.657519946358876</v>
+        <v>2.692982750971466</v>
       </c>
       <c r="F2104" t="n">
-        <v>1.328913328545553</v>
+        <v>1.380309947873603</v>
       </c>
       <c r="G2104" t="n">
-        <v>5.415037486789824</v>
+        <v>5.445875458386654</v>
       </c>
     </row>
     <row r="2105">
@@ -49960,22 +49960,22 @@
         <v>45567</v>
       </c>
       <c r="B2105" t="n">
-        <v>3.823987445263768</v>
+        <v>3.82398744526377</v>
       </c>
       <c r="C2105" t="n">
         <v>4.617689489662492</v>
       </c>
       <c r="D2105" t="n">
-        <v>-4.905566077661439</v>
+        <v>-4.816909066129965</v>
       </c>
       <c r="E2105" t="n">
-        <v>2.655106634284168</v>
+        <v>2.690569438896758</v>
       </c>
       <c r="F2105" t="n">
-        <v>1.328913328545553</v>
+        <v>1.380309947873603</v>
       </c>
       <c r="G2105" t="n">
-        <v>5.415037486789824</v>
+        <v>5.445875458386654</v>
       </c>
     </row>
     <row r="2106">
@@ -49983,22 +49983,22 @@
         <v>45568</v>
       </c>
       <c r="B2106" t="n">
-        <v>3.815657203170835</v>
+        <v>3.815657203170844</v>
       </c>
       <c r="C2106" t="n">
         <v>4.621327656804905</v>
       </c>
       <c r="D2106" t="n">
-        <v>-4.924608441760276</v>
+        <v>-4.868760841703127</v>
       </c>
       <c r="E2106" t="n">
-        <v>2.651127855787046</v>
+        <v>2.673466895809906</v>
       </c>
       <c r="F2106" t="n">
-        <v>1.309870964446716</v>
+        <v>1.328458172300441</v>
       </c>
       <c r="G2106" t="n">
-        <v>5.407250235472935</v>
+        <v>5.41840256018517</v>
       </c>
     </row>
     <row r="2107">
@@ -50006,22 +50006,22 @@
         <v>45569</v>
       </c>
       <c r="B2107" t="n">
-        <v>3.830586986431405</v>
+        <v>3.830586986431407</v>
       </c>
       <c r="C2107" t="n">
         <v>4.584819403988742</v>
       </c>
       <c r="D2107" t="n">
-        <v>-4.951665887892102</v>
+        <v>-4.895818287834953</v>
       </c>
       <c r="E2107" t="n">
-        <v>2.603796624518153</v>
+        <v>2.626135664541012</v>
       </c>
       <c r="F2107" t="n">
-        <v>1.309870964446716</v>
+        <v>1.328458172300441</v>
       </c>
       <c r="G2107" t="n">
-        <v>5.370741982656772</v>
+        <v>5.381894307369007</v>
       </c>
     </row>
     <row r="2108">
@@ -50029,22 +50029,22 @@
         <v>45570</v>
       </c>
       <c r="B2108" t="n">
-        <v>3.910581988208739</v>
+        <v>3.91739311730433</v>
       </c>
       <c r="C2108" t="n">
         <v>4.586227353735933</v>
       </c>
       <c r="D2108" t="n">
-        <v>-5.054804165250326</v>
+        <v>-4.969099639688829</v>
       </c>
       <c r="E2108" t="n">
-        <v>2.563949263322054</v>
+        <v>2.598231073546653</v>
       </c>
       <c r="F2108" t="n">
-        <v>1.258672345020671</v>
+        <v>1.31454675016923</v>
       </c>
       <c r="G2108" t="n">
-        <v>5.341430760748336</v>
+        <v>5.374955403837471</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20241006.xlsx
+++ b/tame_output/ON/bt/strategyON_20241006.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>57.3%</t>
+          <t>49.4%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>67.1%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.1%</t>
+          <t>66.1%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>68.2%</t>
+          <t>68.0%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.3%</t>
+          <t>-19.8%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.3%</t>
+          <t>-15.8%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>17.8%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.6%</t>
+          <t>-12.0%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>63.7%</t>
+          <t>35.7%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>84.9%</t>
+          <t>86.3%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-77.8%</t>
+          <t>-78.4%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>107.2%</t>
+          <t>106.8%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>90.1%</t>
+          <t>89.4%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>21.8%</t>
+          <t>21.4%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-73.9%</t>
+          <t>-75.1%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>88.8%</t>
+          <t>88.6%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>421.8%</t>
+          <t>418.9%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-658.5%</t>
+          <t>-676.4%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>31.3%</t>
+          <t>29.7%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>59.4%</t>
+          <t>59.3%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>56.1%</t>
+          <t>56.0%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>14.0%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1160,17 +1160,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>27.0%</t>
+          <t>25.6%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>49.6%</t>
+          <t>49.5%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-4.4%</t>
+          <t>-4.2%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-116.4%</t>
+          <t>-123.6%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-2.2%</t>
+          <t>-3.1%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>74.3%</t>
+          <t>74.2%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.8%</t>
+          <t>10.7%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>4.5%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.8%</t>
+          <t>55.7%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>53.1%</t>
+          <t>44.1%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-365.2%</t>
+          <t>-204.1%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-92.5%</t>
+          <t>-97.7%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>114.2%</t>
+          <t>113.1%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>14.0%</t>
+          <t>14.2%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-20.1%</t>
+          <t>-18.7%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>103.5%</t>
+          <t>103.2%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.5%</t>
+          <t>-16.4%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>36.6%</t>
+          <t>36.7%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>91.5%</t>
+          <t>88.4%</t>
         </is>
       </c>
     </row>
@@ -45872,16 +45872,16 @@
         <v>2.874141992803903</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.65352219721759</v>
+        <v>-4.742179208749064</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.012376689603119</v>
+        <v>0.9769138849905292</v>
       </c>
       <c r="F1927" t="n">
-        <v>0.2578397241163622</v>
+        <v>0.2064431047883115</v>
       </c>
       <c r="G1927" t="n">
-        <v>3.028845827273721</v>
+        <v>2.99800785567689</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.871140064023896</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.530047925904572</v>
+        <v>-4.618704937436046</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.05876446934832</v>
+        <v>1.02330166473573</v>
       </c>
       <c r="F1928" t="n">
-        <v>0.2578397241163622</v>
+        <v>0.2064431047883115</v>
       </c>
       <c r="G1928" t="n">
-        <v>3.025843898493714</v>
+        <v>2.995005926896884</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.872719101034511</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.472112093906357</v>
+        <v>-4.560769105437831</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.08351783915822</v>
+        <v>1.04805503454563</v>
       </c>
       <c r="F1929" t="n">
-        <v>0.2834015987991115</v>
+        <v>0.2320049794710608</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.042760060313978</v>
+        <v>3.011922088717147</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.888613283836334</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.339244404843079</v>
+        <v>-4.427901416374553</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.152559097585354</v>
+        <v>1.117096292972765</v>
       </c>
       <c r="F1930" t="n">
-        <v>0.2834015987991115</v>
+        <v>0.2320049794710608</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.058654243115801</v>
+        <v>3.02781627151897</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.889759128276636</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.21907132147858</v>
+        <v>-4.307728333010054</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.201774175371456</v>
+        <v>1.166311370758866</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.4035746821636105</v>
+        <v>0.3521780628355597</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.131903937574802</v>
+        <v>3.101065965977972</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.899847230838076</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.083817960148603</v>
+        <v>-4.172474971680077</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.265963622464886</v>
+        <v>1.230500817852297</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.5388280434935876</v>
+        <v>0.4874314241655369</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.223144056934228</v>
+        <v>3.192306085337398</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.885884722239501</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.143692787506295</v>
+        <v>-4.232349799037769</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.228051182923235</v>
+        <v>1.192588378310646</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.4789532161358955</v>
+        <v>0.4275565968078447</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.173256651921039</v>
+        <v>3.142418680324209</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.90117389147371</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.023872556595459</v>
+        <v>-4.112529568126932</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.291268444521779</v>
+        <v>1.255805639909189</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.4789532161358955</v>
+        <v>0.4275565968078447</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.188545821155247</v>
+        <v>3.157707849558417</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.808818090796152</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.026342263057265</v>
+        <v>-4.114999274588738</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.197924761259498</v>
+        <v>1.162461956646908</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.4764835096740893</v>
+        <v>0.4250868903460386</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.094708196600605</v>
+        <v>3.063870225003775</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>2.728079952281453</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.094712449381275</v>
+        <v>-4.183369460912749</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.089838548215195</v>
+        <v>1.054375743602606</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.4857592087103043</v>
+        <v>0.4343625893822535</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.019535477507636</v>
+        <v>2.988697505910805</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>2.718516660913344</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.206584729007425</v>
+        <v>-4.295241740538899</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.035526344996626</v>
+        <v>1.000063540384037</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.4857592087103043</v>
+        <v>0.4343625893822535</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.009972186139527</v>
+        <v>2.979134214542697</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.685091185837372</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.190610063521158</v>
+        <v>-4.279267075052632</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.00849073611516</v>
+        <v>0.9730279315025709</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.4857592087103043</v>
+        <v>0.4343625893822535</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.976546711063555</v>
+        <v>2.945708739466724</v>
       </c>
     </row>
     <row r="1939">
@@ -46148,16 +46148,16 @@
         <v>2.689658417829159</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.194704610192155</v>
+        <v>-4.283361621723629</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.011420149438549</v>
+        <v>0.9759573448259597</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.4857592087103043</v>
+        <v>0.4343625893822535</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.981113943055342</v>
+        <v>2.950275971458512</v>
       </c>
     </row>
     <row r="1940">
@@ -46171,16 +46171,16 @@
         <v>2.665400446590366</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.186780235607241</v>
+        <v>-4.275437247138715</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.9903319280337222</v>
+        <v>0.9548691234211324</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.4857592087103043</v>
+        <v>0.4343625893822535</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.956855971816549</v>
+        <v>2.926018000219719</v>
       </c>
     </row>
     <row r="1941">
@@ -46194,16 +46194,16 @@
         <v>2.593938759991816</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.180502033037392</v>
+        <v>-4.269159044568866</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.9213815224631114</v>
+        <v>0.8859187178505219</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.4920374112801533</v>
+        <v>0.4406407919521026</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.889161206759908</v>
+        <v>2.858323235163078</v>
       </c>
     </row>
     <row r="1942">
@@ -46217,16 +46217,16 @@
         <v>2.604111146423949</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.120649413833669</v>
+        <v>-4.209306425365143</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.955494956576733</v>
+        <v>0.9200321519641435</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.4920374112801533</v>
+        <v>0.4406407919521026</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.899333593192041</v>
+        <v>2.86849562159521</v>
       </c>
     </row>
     <row r="1943">
@@ -46240,16 +46240,16 @@
         <v>2.599057416997809</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.034405950807291</v>
+        <v>-4.123062962338765</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.9849386123611445</v>
+        <v>0.9494758077485548</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.4920374112801533</v>
+        <v>0.4406407919521026</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.894279863765901</v>
+        <v>2.863441892169071</v>
       </c>
     </row>
     <row r="1944">
@@ -46263,16 +46263,16 @@
         <v>2.590833192442334</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.079712770206271</v>
+        <v>-4.168369781737745</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.958591660046078</v>
+        <v>0.9231288554334884</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.4512272482709225</v>
+        <v>0.3998306289428718</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.861569541404888</v>
+        <v>2.830731569808058</v>
       </c>
     </row>
     <row r="1945">
@@ -46286,16 +46286,16 @@
         <v>2.591385065475436</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.108745874908572</v>
+        <v>-4.197402886440046</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.9475302911982593</v>
+        <v>0.9120674865856695</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.4512272482709225</v>
+        <v>0.3998306289428718</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.86212141443799</v>
+        <v>2.831283442841159</v>
       </c>
     </row>
     <row r="1946">
@@ -46309,16 +46309,16 @@
         <v>2.520657757366802</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.015935393457712</v>
+        <v>-4.104592404989186</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.9139271756699687</v>
+        <v>0.8784643710573792</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.5440377297217819</v>
+        <v>0.4926411103937312</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.847080395199871</v>
+        <v>2.816242423603041</v>
       </c>
     </row>
     <row r="1947">
@@ -46332,16 +46332,16 @@
         <v>2.522531233291402</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.06032486278714</v>
+        <v>-4.148981874318614</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.8980448638627985</v>
+        <v>0.8625820592502089</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.4996482603923542</v>
+        <v>0.4482516410643035</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.822320189526815</v>
+        <v>2.791482217929985</v>
       </c>
     </row>
     <row r="1948">
@@ -46355,16 +46355,16 @@
         <v>2.517606941803125</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.039821168901643</v>
+        <v>-4.128478180433117</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.9013220499287204</v>
+        <v>0.8658592453161309</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.5201519542778515</v>
+        <v>0.4687553349498008</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.829698114369837</v>
+        <v>2.798860142773006</v>
       </c>
     </row>
     <row r="1949">
@@ -46378,16 +46378,16 @@
         <v>2.523098237633793</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.123493265613975</v>
+        <v>-4.212150277145449</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.8733445070744548</v>
+        <v>0.837881702461865</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.5201519542778515</v>
+        <v>0.4687553349498008</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.835189410200504</v>
+        <v>2.804351438603673</v>
       </c>
     </row>
     <row r="1950">
@@ -46401,16 +46401,16 @@
         <v>2.534595439402332</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.151273663515328</v>
+        <v>-4.239930675046802</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.8737295496824526</v>
+        <v>0.8382667450698631</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.4923715563764985</v>
+        <v>0.4409749370484478</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.830018373228231</v>
+        <v>2.799180401631401</v>
       </c>
     </row>
     <row r="1951">
@@ -46424,16 +46424,16 @@
         <v>2.372951159402985</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.269654336245466</v>
+        <v>-4.35831134777694</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.6647330005910506</v>
+        <v>0.629270195978461</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.4251537042255223</v>
+        <v>0.3737570848974716</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.628043381938299</v>
+        <v>2.597205410341468</v>
       </c>
     </row>
     <row r="1952">
@@ -46447,16 +46447,16 @@
         <v>2.493100820122191</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.378268414688797</v>
+        <v>-4.466925426220271</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.7414370299329238</v>
+        <v>0.7059742253203343</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.4251537042255223</v>
+        <v>0.3737570848974716</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.748193042657504</v>
+        <v>2.717355071060674</v>
       </c>
     </row>
     <row r="1953">
@@ -46470,16 +46470,16 @@
         <v>2.507613846224514</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.342859376440654</v>
+        <v>-4.431516387972128</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.7701136713345038</v>
+        <v>0.7346508667219143</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.4251537042255223</v>
+        <v>0.3737570848974716</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.762706068759827</v>
+        <v>2.731868097162997</v>
       </c>
     </row>
     <row r="1954">
@@ -46493,16 +46493,16 @@
         <v>2.505033287566882</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.351320545096115</v>
+        <v>-4.439977556627589</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.7641486452146884</v>
+        <v>0.7286858406020986</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.4166925355700613</v>
+        <v>0.3652959162420105</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.755048808908919</v>
+        <v>2.724210837312089</v>
       </c>
     </row>
     <row r="1955">
@@ -46516,16 +46516,16 @@
         <v>2.501762316412185</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.174204215060949</v>
+        <v>-4.262861226592423</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.8317242060740571</v>
+        <v>0.7962614014614675</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.4166925355700613</v>
+        <v>0.3652959162420105</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.751777837754222</v>
+        <v>2.720939866157391</v>
       </c>
     </row>
     <row r="1956">
@@ -46539,16 +46539,16 @@
         <v>2.502445708174098</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.219296459894495</v>
+        <v>-4.307953471425969</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.814370699902552</v>
+        <v>0.7789078952899624</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.3547964924006715</v>
+        <v>0.3033998730726207</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.715323603614501</v>
+        <v>2.684485632017671</v>
       </c>
     </row>
     <row r="1957">
@@ -46562,16 +46562,16 @@
         <v>2.496232683480512</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.039921038655727</v>
+        <v>-4.128578050187201</v>
       </c>
       <c r="E1957" t="n">
-        <v>0.8799078437044734</v>
+        <v>0.8444450390918838</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.5115732505713901</v>
+        <v>0.4601766312433394</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.803176633823346</v>
+        <v>2.772338662226516</v>
       </c>
     </row>
     <row r="1958">
@@ -46585,16 +46585,16 @@
         <v>2.477040138812102</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.084935252176333</v>
+        <v>-4.173592263707807</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.8427096136278207</v>
+        <v>0.8072468090152312</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.4812243552567855</v>
+        <v>0.4298277359287348</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.765774751966173</v>
+        <v>2.734936780369343</v>
       </c>
     </row>
     <row r="1959">
@@ -46608,16 +46608,16 @@
         <v>2.482731701151048</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.17294643873503</v>
+        <v>-4.261603450266504</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.8131967013432877</v>
+        <v>0.7777338967306981</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.4157478473976126</v>
+        <v>0.3643512280695618</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.732180409589616</v>
+        <v>2.701342437992785</v>
       </c>
     </row>
     <row r="1960">
@@ -46631,16 +46631,16 @@
         <v>2.481935623047549</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.274144220172203</v>
+        <v>-4.362801231703677</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.77192151066492</v>
+        <v>0.7364587060523304</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.3473390338522934</v>
+        <v>0.2959424145242426</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.690339043358926</v>
+        <v>2.659501071762095</v>
       </c>
     </row>
     <row r="1961">
@@ -46654,16 +46654,16 @@
         <v>2.479535584601866</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.26763325355789</v>
+        <v>-4.356290265089364</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.7721258588649618</v>
+        <v>0.7366630542523722</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.3473390338522934</v>
+        <v>0.2959424145242426</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.687939004913242</v>
+        <v>2.657101033316412</v>
       </c>
     </row>
     <row r="1962">
@@ -46677,16 +46677,16 @@
         <v>2.476060303810111</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.248595125850593</v>
+        <v>-4.337252137382067</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.7762658291561255</v>
+        <v>0.740803024543536</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.2891554225210988</v>
+        <v>0.2377588031930481</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.64955355732277</v>
+        <v>2.61871558572594</v>
       </c>
     </row>
     <row r="1963">
@@ -46700,16 +46700,16 @@
         <v>2.595354705444301</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.301110928125413</v>
+        <v>-4.389767939656887</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.8745539098803878</v>
+        <v>0.8390911052677983</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.2891554225210988</v>
+        <v>0.2377588031930481</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.768847958956961</v>
+        <v>2.73800998736013</v>
       </c>
     </row>
     <row r="1964">
@@ -46723,16 +46723,16 @@
         <v>2.596188034430435</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.304519239559993</v>
+        <v>-4.393176251091467</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.8740239142926893</v>
+        <v>0.8385611096800998</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.3216719915304762</v>
+        <v>0.2702753722024255</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.789191229348721</v>
+        <v>2.75835325775189</v>
       </c>
     </row>
     <row r="1965">
@@ -46746,16 +46746,16 @@
         <v>2.602196564827361</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.285163103666146</v>
+        <v>-4.37382011519762</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.8877748990471543</v>
+        <v>0.8523120944345648</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.3216719915304762</v>
+        <v>0.2702753722024255</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.795199759745647</v>
+        <v>2.764361788148816</v>
       </c>
     </row>
     <row r="1966">
@@ -46769,16 +46769,16 @@
         <v>2.50014678610456</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.358492632404238</v>
+        <v>-4.447149643935712</v>
       </c>
       <c r="E1966" t="n">
-        <v>0.7563933088291168</v>
+        <v>0.7209305042165273</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.3220666539500981</v>
+        <v>0.2706700346220474</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.693386778474619</v>
+        <v>2.662548806877789</v>
       </c>
     </row>
     <row r="1967">
@@ -46792,16 +46792,16 @@
         <v>2.409870503348191</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.442313853678937</v>
+        <v>-4.530970865210411</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.6325885375628686</v>
+        <v>0.597125732950279</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.3220666539500981</v>
+        <v>0.2706700346220474</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.60311049571825</v>
+        <v>2.57227252412142</v>
       </c>
     </row>
     <row r="1968">
@@ -46815,16 +46815,16 @@
         <v>2.41053285173985</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.436161147626152</v>
+        <v>-4.524818159157626</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.6357119683756407</v>
+        <v>0.6002491637630512</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.3282193600028824</v>
+        <v>0.2768227406748317</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.607464467741579</v>
+        <v>2.576626496144749</v>
       </c>
     </row>
     <row r="1969">
@@ -46838,16 +46838,16 @@
         <v>2.40961332847996</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.452970445776654</v>
+        <v>-4.541627457308128</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.6280687258555502</v>
+        <v>0.5926059212429606</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.3114100618523808</v>
+        <v>0.2600134425243301</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.596459365591389</v>
+        <v>2.565621393994558</v>
       </c>
     </row>
     <row r="1970">
@@ -46861,16 +46861,16 @@
         <v>2.475948882276781</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.390672447000532</v>
+        <v>-4.479329458532006</v>
       </c>
       <c r="E1970" t="n">
-        <v>0.71932347916282</v>
+        <v>0.6838606745502305</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.3567043261268228</v>
+        <v>0.3053077067987721</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.689971477952875</v>
+        <v>2.659133506356044</v>
       </c>
     </row>
     <row r="1971">
@@ -46884,16 +46884,16 @@
         <v>2.278240883990908</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.188882249335374</v>
+        <v>-4.277539260866848</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.6023315599430101</v>
+        <v>0.5668687553304206</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.5547225182959772</v>
+        <v>0.5033258989679266</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.611074394968494</v>
+        <v>2.580236423371664</v>
       </c>
     </row>
     <row r="1972">
@@ -46907,16 +46907,16 @@
         <v>2.348531116313083</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.239768962021569</v>
+        <v>-4.328425973553043</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.6522671071907076</v>
+        <v>0.616804302578118</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.5038358056097827</v>
+        <v>0.452439186281732</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.650832599678953</v>
+        <v>2.619994628082122</v>
       </c>
     </row>
     <row r="1973">
@@ -46930,16 +46930,16 @@
         <v>2.363158852429127</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.153158219371762</v>
+        <v>-4.241815230903236</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.701539140366674</v>
+        <v>0.6660763357540844</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.582461536814941</v>
+        <v>0.5310649174868902</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.712635774518092</v>
+        <v>2.681797802921261</v>
       </c>
     </row>
     <row r="1974">
@@ -46953,16 +46953,16 @@
         <v>2.361694833253798</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.213367517377047</v>
+        <v>-4.302024528908521</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.6759914019892317</v>
+        <v>0.6405285973766421</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.5222522388096564</v>
+        <v>0.4708556194816057</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.675046176539592</v>
+        <v>2.644208204942762</v>
       </c>
     </row>
     <row r="1975">
@@ -46976,16 +46976,16 @@
         <v>2.360186451293727</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.164180868692696</v>
+        <v>-4.25283788022417</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.6941576795029007</v>
+        <v>0.6586948748903112</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.5222522388096564</v>
+        <v>0.4708556194816057</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.673537794579521</v>
+        <v>2.642699822982691</v>
       </c>
     </row>
     <row r="1976">
@@ -46999,16 +46999,16 @@
         <v>2.360049318729163</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.119807737054127</v>
+        <v>-4.208464748585601</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.7117697995937644</v>
+        <v>0.6763069949811749</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.566625370448225</v>
+        <v>0.5152287511201743</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.700024540998098</v>
+        <v>2.669186569401268</v>
       </c>
     </row>
     <row r="1977">
@@ -47022,16 +47022,16 @@
         <v>2.354443112867754</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.085076415735626</v>
+        <v>-4.1737334272671</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.7200561222597552</v>
+        <v>0.6845933176471655</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.566625370448225</v>
+        <v>0.5152287511201743</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.694418335136689</v>
+        <v>2.663580363539858</v>
       </c>
     </row>
     <row r="1978">
@@ -47045,16 +47045,16 @@
         <v>2.360824869895558</v>
       </c>
       <c r="D1978" t="n">
-        <v>-4.03742068517457</v>
+        <v>-4.126077696706044</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.7455001715119822</v>
+        <v>0.7100373668993925</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.6142811010092807</v>
+        <v>0.56288448168123</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.729393530501127</v>
+        <v>2.698555558904296</v>
       </c>
     </row>
     <row r="1979">
@@ -47068,16 +47068,16 @@
         <v>2.365717243270283</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.936902526675816</v>
+        <v>-4.02555953820729</v>
       </c>
       <c r="E1979" t="n">
-        <v>0.7905998082862089</v>
+        <v>0.7551370036736191</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.7147992595080352</v>
+        <v>0.6634026401799845</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.794596798975105</v>
+        <v>2.763758827378274</v>
       </c>
     </row>
     <row r="1980">
@@ -47091,16 +47091,16 @@
         <v>2.352471915746155</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.920997197243463</v>
+        <v>-4.009654208774937</v>
       </c>
       <c r="E1980" t="n">
-        <v>0.7837166125350221</v>
+        <v>0.7482538079224326</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.6356865987987963</v>
+        <v>0.5842899794707457</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.733883875025434</v>
+        <v>2.703045903428603</v>
       </c>
     </row>
     <row r="1981">
@@ -47114,16 +47114,16 @@
         <v>2.356569618356784</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.876158795635065</v>
+        <v>-3.964815807166539</v>
       </c>
       <c r="E1981" t="n">
-        <v>0.8057496757890099</v>
+        <v>0.7702868711764204</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.6402300317436658</v>
+        <v>0.5888334124156152</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.740707637402984</v>
+        <v>2.709869665806153</v>
       </c>
     </row>
     <row r="1982">
@@ -47137,16 +47137,16 @@
         <v>2.360730557987862</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.895657251877073</v>
+        <v>-3.984314263408547</v>
       </c>
       <c r="E1982" t="n">
-        <v>0.8021112329232847</v>
+        <v>0.7666484283106949</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.5921453904637615</v>
+        <v>0.5407487711357108</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.716017792266119</v>
+        <v>2.685179820669289</v>
       </c>
     </row>
     <row r="1983">
@@ -47160,16 +47160,16 @@
         <v>2.366610160515699</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.851454414791173</v>
+        <v>-3.940111426322647</v>
       </c>
       <c r="E1983" t="n">
-        <v>0.825671970285482</v>
+        <v>0.7902091656728922</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.6363482275496619</v>
+        <v>0.5849516082216113</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.748419097045496</v>
+        <v>2.717581125448666</v>
       </c>
     </row>
     <row r="1984">
@@ -47183,16 +47183,16 @@
         <v>2.365020160984947</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.85901408062822</v>
+        <v>-3.947671092159694</v>
       </c>
       <c r="E1984" t="n">
-        <v>0.8210581044199108</v>
+        <v>0.785595299807321</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.6911516315594812</v>
+        <v>0.6397550122314306</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.779711139920636</v>
+        <v>2.748873168323805</v>
       </c>
     </row>
     <row r="1985">
@@ -47206,16 +47206,16 @@
         <v>2.416267926167986</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.700722663088948</v>
+        <v>-3.789379674620422</v>
       </c>
       <c r="E1985" t="n">
-        <v>0.9356224366186592</v>
+        <v>0.9001596320060696</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.6911516315594812</v>
+        <v>0.6397550122314306</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.830958905103675</v>
+        <v>2.800120933506845</v>
       </c>
     </row>
     <row r="1986">
@@ -47229,16 +47229,16 @@
         <v>2.414708630762239</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.493080659454471</v>
+        <v>-3.581737670985945</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.017119942666703</v>
+        <v>0.9816571380541133</v>
       </c>
       <c r="F1986" t="n">
-        <v>0.8987936351939574</v>
+        <v>0.8473970158659068</v>
       </c>
       <c r="G1986" t="n">
-        <v>2.953984811878614</v>
+        <v>2.923146840281784</v>
       </c>
     </row>
     <row r="1987">
@@ -47252,16 +47252,16 @@
         <v>2.409656859000509</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.442048566731943</v>
+        <v>-3.530705578263417</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.032481007993984</v>
+        <v>0.9970182033813946</v>
       </c>
       <c r="F1987" t="n">
-        <v>0.9498257279164853</v>
+        <v>0.8984291085884347</v>
       </c>
       <c r="G1987" t="n">
-        <v>2.979552295750401</v>
+        <v>2.94871432415357</v>
       </c>
     </row>
     <row r="1988">
@@ -47275,16 +47275,16 @@
         <v>2.426844263093214</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.376824385604738</v>
+        <v>-3.465481397136212</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.075758084537571</v>
+        <v>1.040295279924982</v>
       </c>
       <c r="F1988" t="n">
-        <v>1.015049909043691</v>
+        <v>0.9636532897156403</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.035874208519429</v>
+        <v>3.005036236922599</v>
       </c>
     </row>
     <row r="1989">
@@ -47298,16 +47298,16 @@
         <v>2.422805235392495</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.339397365533604</v>
+        <v>-3.428054377065078</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.086689864865305</v>
+        <v>1.051227060252716</v>
       </c>
       <c r="F1989" t="n">
-        <v>1.020301447072872</v>
+        <v>0.968904827744822</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.034986103636218</v>
+        <v>3.004148132039388</v>
       </c>
     </row>
     <row r="1990">
@@ -47321,16 +47321,16 @@
         <v>2.424062027723735</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.338039380560058</v>
+        <v>-3.426696392091532</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.088489851185964</v>
+        <v>1.053027046573374</v>
       </c>
       <c r="F1990" t="n">
-        <v>1.094639572610691</v>
+        <v>1.043242953282641</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.08084577129015</v>
+        <v>3.050007799693319</v>
       </c>
     </row>
     <row r="1991">
@@ -47344,16 +47344,16 @@
         <v>2.584619798744946</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.309626117460175</v>
+        <v>-3.398283128991649</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.260412927447128</v>
+        <v>1.224950122834538</v>
       </c>
       <c r="F1991" t="n">
-        <v>1.035664009864262</v>
+        <v>0.9842673905362118</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.206018204663503</v>
+        <v>3.175180233066673</v>
       </c>
     </row>
     <row r="1992">
@@ -47367,16 +47367,16 @@
         <v>2.704732707962763</v>
       </c>
       <c r="D1992" t="n">
-        <v>-3.234843856435162</v>
+        <v>-3.323500867966636</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.41043874107495</v>
+        <v>1.374975936462361</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.110446270889275</v>
+        <v>1.059049651561224</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.371000470496328</v>
+        <v>3.340162498899498</v>
       </c>
     </row>
     <row r="1993">
@@ -47390,16 +47390,16 @@
         <v>2.696440683976622</v>
       </c>
       <c r="D1993" t="n">
-        <v>-3.208759772171354</v>
+        <v>-3.297416783702828</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.412580350794332</v>
+        <v>1.377117546181743</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.110446270889275</v>
+        <v>1.059049651561224</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.362708446510187</v>
+        <v>3.331870474913357</v>
       </c>
     </row>
     <row r="1994">
@@ -47413,16 +47413,16 @@
         <v>2.694633879560401</v>
       </c>
       <c r="D1994" t="n">
-        <v>-3.120881859062234</v>
+        <v>-3.209538870593708</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.44592471162176</v>
+        <v>1.41046190700917</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.226371913312626</v>
+        <v>1.174975293984576</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.430457027547977</v>
+        <v>3.399619055951147</v>
       </c>
     </row>
     <row r="1995">
@@ -47436,16 +47436,16 @@
         <v>2.712188285287193</v>
       </c>
       <c r="D1995" t="n">
-        <v>-3.111989397668951</v>
+        <v>-3.200646409200425</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.467036101905865</v>
+        <v>1.431573297293275</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.226371913312626</v>
+        <v>1.174975293984576</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.448011433274769</v>
+        <v>3.417173461677939</v>
       </c>
     </row>
     <row r="1996">
@@ -47459,16 +47459,16 @@
         <v>2.704043332691777</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.280465514638828</v>
+        <v>-3.369122526170302</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.391500702522497</v>
+        <v>1.356037897909908</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.198424077596045</v>
+        <v>1.147027458267995</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.423097779249404</v>
+        <v>3.392259807652574</v>
       </c>
     </row>
     <row r="1997">
@@ -47482,16 +47482,16 @@
         <v>2.685313029879639</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.834209322009388</v>
+        <v>-2.922866333540862</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.551272876762135</v>
+        <v>1.515810072149546</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.103705407926412</v>
+        <v>1.052308788598362</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.347536274635486</v>
+        <v>3.316698303038656</v>
       </c>
     </row>
     <row r="1998">
@@ -47505,16 +47505,16 @@
         <v>2.675977052376543</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.811488218326236</v>
+        <v>-2.90014522985771</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.551025340732301</v>
+        <v>1.515562536119711</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.103705407926412</v>
+        <v>1.052308788598362</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.338200297132391</v>
+        <v>3.307362325535561</v>
       </c>
     </row>
     <row r="1999">
@@ -47528,16 +47528,16 @@
         <v>2.834883178227712</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.940690031620278</v>
+        <v>-3.029347043151752</v>
       </c>
       <c r="E1999" t="n">
-        <v>1.658250741265853</v>
+        <v>1.622787936653263</v>
       </c>
       <c r="F1999" t="n">
-        <v>0.9745035946323701</v>
+        <v>0.92310697530432</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.419585335007135</v>
+        <v>3.388747363410304</v>
       </c>
     </row>
     <row r="2000">
@@ -47551,16 +47551,16 @@
         <v>2.871961000721359</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.966564430094304</v>
+        <v>-3.055221441625778</v>
       </c>
       <c r="E2000" t="n">
-        <v>1.684978804369889</v>
+        <v>1.649515999757299</v>
       </c>
       <c r="F2000" t="n">
-        <v>1.019415203344111</v>
+        <v>0.9680185840160611</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.483610122727826</v>
+        <v>3.452772151130996</v>
       </c>
     </row>
     <row r="2001">
@@ -47574,16 +47574,16 @@
         <v>2.868636356710904</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.959509739879131</v>
+        <v>-3.048166751410605</v>
       </c>
       <c r="E2001" t="n">
-        <v>1.684476036445504</v>
+        <v>1.649013231832914</v>
       </c>
       <c r="F2001" t="n">
-        <v>1.026469893559285</v>
+        <v>0.9750732742312349</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.484518292846475</v>
+        <v>3.453680321249645</v>
       </c>
     </row>
     <row r="2002">
@@ -47597,16 +47597,16 @@
         <v>2.878642510355645</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.932558515552643</v>
+        <v>-3.021215527084117</v>
       </c>
       <c r="E2002" t="n">
-        <v>1.705262679820841</v>
+        <v>1.669799875208251</v>
       </c>
       <c r="F2002" t="n">
-        <v>1.041350239587004</v>
+        <v>0.9899536202589541</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.503452654107848</v>
+        <v>3.472614682511018</v>
       </c>
     </row>
     <row r="2003">
@@ -47620,16 +47620,16 @@
         <v>3.062745642500605</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.95410274338343</v>
+        <v>-3.042759754914904</v>
       </c>
       <c r="E2003" t="n">
-        <v>1.880748120833485</v>
+        <v>1.845285316220896</v>
       </c>
       <c r="F2003" t="n">
-        <v>1.041350239587004</v>
+        <v>0.9899536202589541</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.687555786252808</v>
+        <v>3.656717814655978</v>
       </c>
     </row>
     <row r="2004">
@@ -47643,16 +47643,16 @@
         <v>3.054862337403598</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.976510861188302</v>
+        <v>-3.065167872719776</v>
       </c>
       <c r="E2004" t="n">
-        <v>1.86390156861453</v>
+        <v>1.82843876400194</v>
       </c>
       <c r="F2004" t="n">
-        <v>1.041350239587004</v>
+        <v>0.9899536202589541</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.679672481155801</v>
+        <v>3.648834509558971</v>
       </c>
     </row>
     <row r="2005">
@@ -47666,16 +47666,16 @@
         <v>3.056916336953236</v>
       </c>
       <c r="D2005" t="n">
-        <v>-3.004735096765902</v>
+        <v>-3.093392108297376</v>
       </c>
       <c r="E2005" t="n">
-        <v>1.854665873933127</v>
+        <v>1.819203069320537</v>
       </c>
       <c r="F2005" t="n">
-        <v>1.059326992038313</v>
+        <v>1.007930372710263</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.692512532176224</v>
+        <v>3.661674560579394</v>
       </c>
     </row>
     <row r="2006">
@@ -47689,16 +47689,16 @@
         <v>3.113170054675083</v>
       </c>
       <c r="D2006" t="n">
-        <v>-3.014176022654432</v>
+        <v>-3.102833034185906</v>
       </c>
       <c r="E2006" t="n">
-        <v>1.907143221299562</v>
+        <v>1.871680416686972</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.181754109581704</v>
+        <v>1.130357490253654</v>
       </c>
       <c r="G2006" t="n">
-        <v>3.822222520424106</v>
+        <v>3.791384548827275</v>
       </c>
     </row>
     <row r="2007">
@@ -47712,16 +47712,16 @@
         <v>3.116061149220384</v>
       </c>
       <c r="D2007" t="n">
-        <v>-3.220414960442866</v>
+        <v>-3.30907197197434</v>
       </c>
       <c r="E2007" t="n">
-        <v>1.82753874072949</v>
+        <v>1.7920759361169</v>
       </c>
       <c r="F2007" t="n">
-        <v>0.9755151717932706</v>
+        <v>0.9241185524652205</v>
       </c>
       <c r="G2007" t="n">
-        <v>3.701370252296346</v>
+        <v>3.670532280699516</v>
       </c>
     </row>
     <row r="2008">
@@ -47735,16 +47735,16 @@
         <v>3.114172962114159</v>
       </c>
       <c r="D2008" t="n">
-        <v>-3.296744938043771</v>
+        <v>-3.385401949575245</v>
       </c>
       <c r="E2008" t="n">
-        <v>1.795118562582902</v>
+        <v>1.759655757970313</v>
       </c>
       <c r="F2008" t="n">
-        <v>0.9755151717932706</v>
+        <v>0.9241185524652205</v>
       </c>
       <c r="G2008" t="n">
-        <v>3.699482065190121</v>
+        <v>3.668644093593291</v>
       </c>
     </row>
     <row r="2009">
@@ -47758,16 +47758,16 @@
         <v>3.108993191717021</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.451701723443901</v>
+        <v>-3.540358734975375</v>
       </c>
       <c r="E2009" t="n">
-        <v>1.727956078025713</v>
+        <v>1.692493273413124</v>
       </c>
       <c r="F2009" t="n">
-        <v>0.8205583863931414</v>
+        <v>0.7691617670650912</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.601328223552906</v>
+        <v>3.570490251956076</v>
       </c>
     </row>
     <row r="2010">
@@ -47781,16 +47781,16 @@
         <v>3.107427201927174</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.613270148971156</v>
+        <v>-3.70192716050263</v>
       </c>
       <c r="E2010" t="n">
-        <v>1.661762718024963</v>
+        <v>1.626299913412374</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.693775462595262</v>
+        <v>0.6423788432672118</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.523692479484331</v>
+        <v>3.492854507887501</v>
       </c>
     </row>
     <row r="2011">
@@ -47804,16 +47804,16 @@
         <v>3.120500608793092</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.721570810841275</v>
+        <v>-3.810227822372749</v>
       </c>
       <c r="E2011" t="n">
-        <v>1.631515860142834</v>
+        <v>1.596053055530245</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.693775462595262</v>
+        <v>0.6423788432672118</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.53676588635025</v>
+        <v>3.505927914753419</v>
       </c>
     </row>
     <row r="2012">
@@ -47827,16 +47827,16 @@
         <v>3.112505805576032</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.881121883604792</v>
+        <v>-3.969778895136266</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.559700627820367</v>
+        <v>1.524237823207778</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.5414977957335105</v>
+        <v>0.4901011764054604</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.437404483016139</v>
+        <v>3.406566511419308</v>
       </c>
     </row>
     <row r="2013">
@@ -47850,16 +47850,16 @@
         <v>3.111029846703034</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.909022670714265</v>
+        <v>-3.997679682245739</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.54706435410358</v>
+        <v>1.51160154949099</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.5069008715905757</v>
+        <v>0.4555042522625256</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.41517036965738</v>
+        <v>3.38433239806055</v>
       </c>
     </row>
     <row r="2014">
@@ -47873,16 +47873,16 @@
         <v>3.107794290680233</v>
       </c>
       <c r="D2014" t="n">
-        <v>-4.031548773417159</v>
+        <v>-4.120205784948633</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.494818356999621</v>
+        <v>1.459355552387032</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.3843747688876819</v>
+        <v>0.3329781495596317</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.338419152012842</v>
+        <v>3.307581180416012</v>
       </c>
     </row>
     <row r="2015">
@@ -47896,16 +47896,16 @@
         <v>3.174500250270737</v>
       </c>
       <c r="D2015" t="n">
-        <v>-4.262063269602748</v>
+        <v>-4.350720281134222</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.46931851811589</v>
+        <v>1.4338557135033</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.1538602727020931</v>
+        <v>0.102463653374043</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.266816413891993</v>
+        <v>3.235978442295163</v>
       </c>
     </row>
     <row r="2016">
@@ -47919,16 +47919,16 @@
         <v>3.314811969272584</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.610808354827191</v>
+        <v>-4.699465366358665</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.470132203027959</v>
+        <v>1.43466939841537</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.04511231878319533</v>
+        <v>-0.006284300544854848</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.341879360542501</v>
+        <v>3.311041388945671</v>
       </c>
     </row>
     <row r="2017">
@@ -47942,16 +47942,16 @@
         <v>3.383792238418224</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.764794772603332</v>
+        <v>-4.853451784134806</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.477517905063143</v>
+        <v>1.442055100450553</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.04511231878319533</v>
+        <v>-0.006284300544854848</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.410859629688141</v>
+        <v>3.380021658091311</v>
       </c>
     </row>
     <row r="2018">
@@ -47965,16 +47965,16 @@
         <v>3.369843440538344</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.96939420746634</v>
+        <v>-5.058051218997814</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.38172933323806</v>
+        <v>1.34626652862547</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.04511231878319533</v>
+        <v>-0.006284300544854848</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.396910831808262</v>
+        <v>3.366072860211432</v>
       </c>
     </row>
     <row r="2019">
@@ -47988,16 +47988,16 @@
         <v>3.381713929593758</v>
       </c>
       <c r="D2019" t="n">
-        <v>-5.221869361474065</v>
+        <v>-5.310526373005539</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.292609760690385</v>
+        <v>1.257146956077795</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.04511231878319533</v>
+        <v>-0.006284300544854848</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.408781320863676</v>
+        <v>3.377943349266846</v>
       </c>
     </row>
     <row r="2020">
@@ -48011,16 +48011,16 @@
         <v>3.382924464112702</v>
       </c>
       <c r="D2020" t="n">
-        <v>-5.514765117953477</v>
+        <v>-5.603422129484951</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.176661992617563</v>
+        <v>1.141199188004974</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.04511231878319533</v>
+        <v>-0.006284300544854848</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.40999185538262</v>
+        <v>3.37915388378579</v>
       </c>
     </row>
     <row r="2021">
@@ -48034,16 +48034,16 @@
         <v>3.387046206340024</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.701429246088285</v>
+        <v>-5.790086257619759</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.106118083590962</v>
+        <v>1.070655278978372</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.01837334795863543</v>
+        <v>-0.03302327136941474</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.398070215115205</v>
+        <v>3.367232243518375</v>
       </c>
     </row>
     <row r="2022">
@@ -48057,16 +48057,16 @@
         <v>3.382124059076213</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.847449933002247</v>
+        <v>-5.936106944533721</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.042787661561566</v>
+        <v>1.007324856948976</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.009290256164778465</v>
+        <v>-0.04210636316327171</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.38769821277508</v>
+        <v>3.35686024117825</v>
       </c>
     </row>
     <row r="2023">
@@ -48080,16 +48080,16 @@
         <v>3.544328115775257</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.939163942111833</v>
+        <v>-6.027820953643307</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.168306114616776</v>
+        <v>1.132843310004186</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.009290256164778465</v>
+        <v>-0.04210636316327171</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.549902269474124</v>
+        <v>3.519064297877294</v>
       </c>
     </row>
     <row r="2024">
@@ -48103,16 +48103,16 @@
         <v>3.539174753739071</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.970815601171802</v>
+        <v>-6.059472612703276</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.150492088956602</v>
+        <v>1.115029284344013</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.00412179892033826</v>
+        <v>-0.04727482040771191</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.541647833091274</v>
+        <v>3.510809861494444</v>
       </c>
     </row>
     <row r="2025">
@@ -48126,16 +48126,16 @@
         <v>3.549404171307562</v>
       </c>
       <c r="D2025" t="n">
-        <v>-6.039881655744739</v>
+        <v>-6.128538667276213</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.133095084695919</v>
+        <v>1.097632280083329</v>
       </c>
       <c r="F2025" t="n">
-        <v>-0.05824907857327177</v>
+        <v>-0.1096456979013219</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.514454724163599</v>
+        <v>3.483616752566769</v>
       </c>
     </row>
     <row r="2026">
@@ -48149,16 +48149,16 @@
         <v>3.558329809763465</v>
       </c>
       <c r="D2026" t="n">
-        <v>-6.141857777993146</v>
+        <v>-6.23051478952462</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.101230274252458</v>
+        <v>1.065767469639868</v>
       </c>
       <c r="F2026" t="n">
-        <v>-0.1602252008216793</v>
+        <v>-0.2116218201497295</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.462194689270457</v>
+        <v>3.431356717673627</v>
       </c>
     </row>
     <row r="2027">
@@ -48172,16 +48172,16 @@
         <v>3.55048269700764</v>
       </c>
       <c r="D2027" t="n">
-        <v>-6.031851494515925</v>
+        <v>-6.120508506047399</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.137385674887522</v>
+        <v>1.101922870274933</v>
       </c>
       <c r="F2027" t="n">
-        <v>-0.1370206289044041</v>
+        <v>-0.1884172482324543</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.468270319664998</v>
+        <v>3.437432348068168</v>
       </c>
     </row>
     <row r="2028">
@@ -48195,16 +48195,16 @@
         <v>3.554732707729614</v>
       </c>
       <c r="D2028" t="n">
-        <v>-6.044381199627804</v>
+        <v>-6.133038211159278</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.136623803564745</v>
+        <v>1.101160998952155</v>
       </c>
       <c r="F2028" t="n">
-        <v>-0.1508471283709272</v>
+        <v>-0.2022437476989773</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.464224430707058</v>
+        <v>3.433386459110229</v>
       </c>
     </row>
     <row r="2029">
@@ -48218,16 +48218,16 @@
         <v>3.56199359061215</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.742934474155966</v>
+        <v>-5.83159148568744</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.264463376636016</v>
+        <v>1.229000572023426</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.1505995971009101</v>
+        <v>0.09920297777285991</v>
       </c>
       <c r="G2029" t="n">
-        <v>3.652353348872697</v>
+        <v>3.621515377275867</v>
       </c>
     </row>
     <row r="2030">
@@ -48241,16 +48241,16 @@
         <v>3.562964768364861</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.76752471839115</v>
+        <v>-5.856181729922624</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.255598456694653</v>
+        <v>1.220135652082063</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.1505995971009101</v>
+        <v>0.09920297777285991</v>
       </c>
       <c r="G2030" t="n">
-        <v>3.653324526625407</v>
+        <v>3.622486555028577</v>
       </c>
     </row>
     <row r="2031">
@@ -48264,16 +48264,16 @@
         <v>3.563807672744617</v>
       </c>
       <c r="D2031" t="n">
-        <v>-5.71648634238463</v>
+        <v>-5.805143353916104</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.276856711477017</v>
+        <v>1.241393906864427</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.1505995971009101</v>
+        <v>0.09920297777285991</v>
       </c>
       <c r="G2031" t="n">
-        <v>3.654167431005163</v>
+        <v>3.623329459408333</v>
       </c>
     </row>
     <row r="2032">
@@ -48287,16 +48287,16 @@
         <v>3.582845771618762</v>
       </c>
       <c r="D2032" t="n">
-        <v>-5.687637665561169</v>
+        <v>-5.776294677092643</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.307434281080546</v>
+        <v>1.271971476467957</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.1794482739243703</v>
+        <v>0.1280516545963202</v>
       </c>
       <c r="G2032" t="n">
-        <v>3.690514735973385</v>
+        <v>3.659676764376554</v>
       </c>
     </row>
     <row r="2033">
@@ -48310,16 +48310,16 @@
         <v>3.399029767742697</v>
       </c>
       <c r="D2033" t="n">
-        <v>-5.591002753542529</v>
+        <v>-5.679659765074003</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.162272242011937</v>
+        <v>1.126809437399347</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.2760831859430103</v>
+        <v>0.2246865666149601</v>
       </c>
       <c r="G2033" t="n">
-        <v>3.564679679308503</v>
+        <v>3.533841707711673</v>
       </c>
     </row>
     <row r="2034">
@@ -48333,16 +48333,16 @@
         <v>3.402531811816661</v>
       </c>
       <c r="D2034" t="n">
-        <v>-5.521964742594061</v>
+        <v>-5.610621754125535</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.193389490465288</v>
+        <v>1.157926685852698</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.3451211968914784</v>
+        <v>0.2937245775634282</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.609604529951548</v>
+        <v>3.578766558354718</v>
       </c>
     </row>
     <row r="2035">
@@ -48356,16 +48356,16 @@
         <v>3.386958630892743</v>
       </c>
       <c r="D2035" t="n">
-        <v>-5.503177642225123</v>
+        <v>-5.591834653756597</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.185331149688946</v>
+        <v>1.149868345076356</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.3639082972604168</v>
+        <v>0.3125116779323667</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.605303609248994</v>
+        <v>3.574465637652164</v>
       </c>
     </row>
     <row r="2036">
@@ -48379,16 +48379,16 @@
         <v>3.386146341329173</v>
       </c>
       <c r="D2036" t="n">
-        <v>-5.42607904068325</v>
+        <v>-5.514736052214724</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.215358300742125</v>
+        <v>1.179895496129535</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.3639082972604168</v>
+        <v>0.3125116779323667</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.604491319685423</v>
+        <v>3.573653348088593</v>
       </c>
     </row>
     <row r="2037">
@@ -48402,16 +48402,16 @@
         <v>3.396015120454245</v>
       </c>
       <c r="D2037" t="n">
-        <v>-5.43646423557314</v>
+        <v>-5.525121247104614</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.221073001911241</v>
+        <v>1.185610197298652</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.3535231023705275</v>
+        <v>0.3021264830424774</v>
       </c>
       <c r="G2037" t="n">
-        <v>3.608128981876562</v>
+        <v>3.577291010279732</v>
       </c>
     </row>
     <row r="2038">
@@ -48425,16 +48425,16 @@
         <v>3.466852126230671</v>
       </c>
       <c r="D2038" t="n">
-        <v>-5.455052394295365</v>
+        <v>-5.543709405826839</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.284474744198777</v>
+        <v>1.249011939586187</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.3349349436483022</v>
+        <v>0.283538324320252</v>
       </c>
       <c r="G2038" t="n">
-        <v>3.667813092419652</v>
+        <v>3.636975120822822</v>
       </c>
     </row>
     <row r="2039">
@@ -48448,16 +48448,16 @@
         <v>3.463721137048969</v>
       </c>
       <c r="D2039" t="n">
-        <v>-5.4553509409914</v>
+        <v>-5.544007952522874</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.281224336338661</v>
+        <v>1.245761531726072</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.3346363969522663</v>
+        <v>0.2832397776242161</v>
       </c>
       <c r="G2039" t="n">
-        <v>3.664502975220329</v>
+        <v>3.633665003623499</v>
       </c>
     </row>
     <row r="2040">
@@ -48471,16 +48471,16 @@
         <v>3.468252031988361</v>
       </c>
       <c r="D2040" t="n">
-        <v>-5.354527807300973</v>
+        <v>-5.443184818832447</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.326084484754223</v>
+        <v>1.290621680141634</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.3471006124366201</v>
+        <v>0.2957039931085699</v>
       </c>
       <c r="G2040" t="n">
-        <v>3.676512399450333</v>
+        <v>3.645674427853503</v>
       </c>
     </row>
     <row r="2041">
@@ -48494,16 +48494,16 @@
         <v>3.468381285466904</v>
       </c>
       <c r="D2041" t="n">
-        <v>-5.163746446548565</v>
+        <v>-5.252403458080039</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.40252628253373</v>
+        <v>1.36706347792114</v>
       </c>
       <c r="F2041" t="n">
-        <v>0.5378819731890274</v>
+        <v>0.4864853538609773</v>
       </c>
       <c r="G2041" t="n">
-        <v>3.791110469380321</v>
+        <v>3.76027249778349</v>
       </c>
     </row>
     <row r="2042">
@@ -48517,16 +48517,16 @@
         <v>3.4482181312045</v>
       </c>
       <c r="D2042" t="n">
-        <v>-5.056783088699143</v>
+        <v>-5.145440100230617</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.425148471411095</v>
+        <v>1.389685666798505</v>
       </c>
       <c r="F2042" t="n">
-        <v>0.5963465811488289</v>
+        <v>0.5449499618207787</v>
       </c>
       <c r="G2042" t="n">
-        <v>3.806026079893798</v>
+        <v>3.775188108296968</v>
       </c>
     </row>
     <row r="2043">
@@ -48540,16 +48540,16 @@
         <v>3.483185067816559</v>
       </c>
       <c r="D2043" t="n">
-        <v>-5.001452500797381</v>
+        <v>-5.090109512328855</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.482247643183858</v>
+        <v>1.446784838571269</v>
       </c>
       <c r="F2043" t="n">
-        <v>0.651677169050591</v>
+        <v>0.6002805497225409</v>
       </c>
       <c r="G2043" t="n">
-        <v>3.874191369246914</v>
+        <v>3.843353397650084</v>
       </c>
     </row>
     <row r="2044">
@@ -48563,16 +48563,16 @@
         <v>3.476871635717997</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.989398373884418</v>
+        <v>-5.078055385415892</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.480755861850481</v>
+        <v>1.445293057237892</v>
       </c>
       <c r="F2044" t="n">
-        <v>0.6637312959635538</v>
+        <v>0.6123346766355037</v>
       </c>
       <c r="G2044" t="n">
-        <v>3.875110413296129</v>
+        <v>3.844272441699299</v>
       </c>
     </row>
     <row r="2045">
@@ -48586,16 +48586,16 @@
         <v>3.478752265902132</v>
       </c>
       <c r="D2045" t="n">
-        <v>-5.066753864012387</v>
+        <v>-5.155410875543861</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.45169429598343</v>
+        <v>1.41623149137084</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.5863758058355845</v>
+        <v>0.5349791865075343</v>
       </c>
       <c r="G2045" t="n">
-        <v>3.830577749403483</v>
+        <v>3.799739777806653</v>
       </c>
     </row>
     <row r="2046">
@@ -48609,16 +48609,16 @@
         <v>3.491603291780015</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.998705301320857</v>
+        <v>-5.087362312852331</v>
       </c>
       <c r="E2046" t="n">
-        <v>1.491764746937924</v>
+        <v>1.456301942325334</v>
       </c>
       <c r="F2046" t="n">
-        <v>0.6544243685271143</v>
+        <v>0.6030277491990641</v>
       </c>
       <c r="G2046" t="n">
-        <v>3.884257912896284</v>
+        <v>3.853419941299454</v>
       </c>
     </row>
     <row r="2047">
@@ -48632,16 +48632,16 @@
         <v>3.511805961953609</v>
       </c>
       <c r="D2047" t="n">
-        <v>-5.230305694490358</v>
+        <v>-5.318962706021832</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.419327259843718</v>
+        <v>1.383864455231128</v>
       </c>
       <c r="F2047" t="n">
-        <v>0.6544243685271143</v>
+        <v>0.6030277491990641</v>
       </c>
       <c r="G2047" t="n">
-        <v>3.904460583069878</v>
+        <v>3.873622611473048</v>
       </c>
     </row>
     <row r="2048">
@@ -48655,16 +48655,16 @@
         <v>3.495412198020491</v>
       </c>
       <c r="D2048" t="n">
-        <v>-5.280357240019578</v>
+        <v>-5.369014251551052</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.382912877698912</v>
+        <v>1.347450073086322</v>
       </c>
       <c r="F2048" t="n">
-        <v>0.6544243685271143</v>
+        <v>0.6030277491990641</v>
       </c>
       <c r="G2048" t="n">
-        <v>3.88806681913676</v>
+        <v>3.85722884753993</v>
       </c>
     </row>
     <row r="2049">
@@ -48678,16 +48678,16 @@
         <v>3.455664111613958</v>
       </c>
       <c r="D2049" t="n">
-        <v>-5.455464072596023</v>
+        <v>-5.544121084127497</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.273122058261801</v>
+        <v>1.237659253649211</v>
       </c>
       <c r="F2049" t="n">
-        <v>0.6544243685271143</v>
+        <v>0.6030277491990641</v>
       </c>
       <c r="G2049" t="n">
-        <v>3.848318732730227</v>
+        <v>3.817480761133397</v>
       </c>
     </row>
     <row r="2050">
@@ -48701,16 +48701,16 @@
         <v>3.462686730610898</v>
       </c>
       <c r="D2050" t="n">
-        <v>-5.2593639191655</v>
+        <v>-5.348020930696974</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.35858473863095</v>
+        <v>1.32312193401836</v>
       </c>
       <c r="F2050" t="n">
-        <v>0.8505245219576372</v>
+        <v>0.799127902629587</v>
       </c>
       <c r="G2050" t="n">
-        <v>3.97300144378548</v>
+        <v>3.94216347218865</v>
       </c>
     </row>
     <row r="2051">
@@ -48724,16 +48724,16 @@
         <v>3.561857730183802</v>
       </c>
       <c r="D2051" t="n">
-        <v>-5.106338527052215</v>
+        <v>-5.194995538583689</v>
       </c>
       <c r="E2051" t="n">
-        <v>1.518965895049168</v>
+        <v>1.483503090436578</v>
       </c>
       <c r="F2051" t="n">
-        <v>1.003549914070921</v>
+        <v>0.9521532947428711</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.163987678626355</v>
+        <v>4.133149707029525</v>
       </c>
     </row>
     <row r="2052">
@@ -48747,16 +48747,16 @@
         <v>3.749323955092095</v>
       </c>
       <c r="D2052" t="n">
-        <v>-5.134645840925486</v>
+        <v>-5.22330285245696</v>
       </c>
       <c r="E2052" t="n">
-        <v>1.695109194408153</v>
+        <v>1.659646389795563</v>
       </c>
       <c r="F2052" t="n">
-        <v>1.003549914070921</v>
+        <v>0.9521532947428711</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.351453903534647</v>
+        <v>4.320615931937818</v>
       </c>
     </row>
     <row r="2053">
@@ -48770,16 +48770,16 @@
         <v>3.718726906446177</v>
       </c>
       <c r="D2053" t="n">
-        <v>-5.301239066039008</v>
+        <v>-5.389896077570482</v>
       </c>
       <c r="E2053" t="n">
-        <v>1.597874855716826</v>
+        <v>1.562412051104237</v>
       </c>
       <c r="F2053" t="n">
-        <v>0.8369566889573987</v>
+        <v>0.7855600696293488</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.220900919820616</v>
+        <v>4.190062948223787</v>
       </c>
     </row>
     <row r="2054">
@@ -48793,16 +48793,16 @@
         <v>3.722403309107895</v>
       </c>
       <c r="D2054" t="n">
-        <v>-5.278203272677442</v>
+        <v>-5.366860284208916</v>
       </c>
       <c r="E2054" t="n">
-        <v>1.61076557572317</v>
+        <v>1.575302771110581</v>
       </c>
       <c r="F2054" t="n">
-        <v>0.8369566889573987</v>
+        <v>0.7855600696293488</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.224577322482334</v>
+        <v>4.193739350885505</v>
       </c>
     </row>
     <row r="2055">
@@ -48816,16 +48816,16 @@
         <v>3.72002136423139</v>
       </c>
       <c r="D2055" t="n">
-        <v>-5.248957292221745</v>
+        <v>-5.337614303753219</v>
       </c>
       <c r="E2055" t="n">
-        <v>1.620082023028944</v>
+        <v>1.584619218416355</v>
       </c>
       <c r="F2055" t="n">
-        <v>0.8369566889573987</v>
+        <v>0.7855600696293488</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.22219537760583</v>
+        <v>4.191357406009</v>
       </c>
     </row>
     <row r="2056">
@@ -48839,16 +48839,16 @@
         <v>3.717314603389025</v>
       </c>
       <c r="D2056" t="n">
-        <v>-5.355882840099596</v>
+        <v>-5.44453985163107</v>
       </c>
       <c r="E2056" t="n">
-        <v>1.574605043035439</v>
+        <v>1.539142238422849</v>
       </c>
       <c r="F2056" t="n">
-        <v>0.7300311410795474</v>
+        <v>0.6786345217514974</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.155333288036754</v>
+        <v>4.124495316439925</v>
       </c>
     </row>
     <row r="2057">
@@ -48862,16 +48862,16 @@
         <v>3.71874340553226</v>
       </c>
       <c r="D2057" t="n">
-        <v>-5.500901398606845</v>
+        <v>-5.589558410138319</v>
       </c>
       <c r="E2057" t="n">
-        <v>1.518026421775774</v>
+        <v>1.482563617163184</v>
       </c>
       <c r="F2057" t="n">
-        <v>0.5850125825722988</v>
+        <v>0.5336159632442489</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.069750955075639</v>
+        <v>4.038912983478809</v>
       </c>
     </row>
     <row r="2058">
@@ -48885,16 +48885,16 @@
         <v>3.818674644790013</v>
       </c>
       <c r="D2058" t="n">
-        <v>-5.619243164391563</v>
+        <v>-5.707900175923037</v>
       </c>
       <c r="E2058" t="n">
-        <v>1.57062095471964</v>
+        <v>1.53515815010705</v>
       </c>
       <c r="F2058" t="n">
-        <v>0.5956986211351889</v>
+        <v>0.5443020018071389</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.176093817471126</v>
+        <v>4.145255845874297</v>
       </c>
     </row>
     <row r="2059">
@@ -48908,16 +48908,16 @@
         <v>3.816460341915952</v>
       </c>
       <c r="D2059" t="n">
-        <v>-5.67065358671227</v>
+        <v>-5.759310598243744</v>
       </c>
       <c r="E2059" t="n">
-        <v>1.547842482917296</v>
+        <v>1.512379678304706</v>
       </c>
       <c r="F2059" t="n">
-        <v>0.5956986211351889</v>
+        <v>0.5443020018071389</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.173879514597066</v>
+        <v>4.143041543000235</v>
       </c>
     </row>
     <row r="2060">
@@ -48931,16 +48931,16 @@
         <v>3.816363469990241</v>
       </c>
       <c r="D2060" t="n">
-        <v>-5.750073037920022</v>
+        <v>-5.838730049451496</v>
       </c>
       <c r="E2060" t="n">
-        <v>1.515977830508484</v>
+        <v>1.480515025895894</v>
       </c>
       <c r="F2060" t="n">
-        <v>0.5956986211351889</v>
+        <v>0.5443020018071389</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.173782642671354</v>
+        <v>4.142944671074525</v>
       </c>
     </row>
     <row r="2061">
@@ -48954,16 +48954,16 @@
         <v>3.816357363548284</v>
       </c>
       <c r="D2061" t="n">
-        <v>-5.84553603583724</v>
+        <v>-5.934193047368714</v>
       </c>
       <c r="E2061" t="n">
-        <v>1.47778652489964</v>
+        <v>1.44232372028705</v>
       </c>
       <c r="F2061" t="n">
-        <v>0.5956986211351889</v>
+        <v>0.5443020018071389</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.173776536229398</v>
+        <v>4.142938564632567</v>
       </c>
     </row>
     <row r="2062">
@@ -48977,16 +48977,16 @@
         <v>3.814453760110895</v>
       </c>
       <c r="D2062" t="n">
-        <v>-5.781160124986525</v>
+        <v>-5.869817136517999</v>
       </c>
       <c r="E2062" t="n">
-        <v>1.501633285802537</v>
+        <v>1.466170481189947</v>
       </c>
       <c r="F2062" t="n">
-        <v>0.660074531985904</v>
+        <v>0.6086779126578541</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.210498479302437</v>
+        <v>4.179660507705607</v>
       </c>
     </row>
     <row r="2063">
@@ -49000,16 +49000,16 @@
         <v>3.820187577858621</v>
       </c>
       <c r="D2063" t="n">
-        <v>-5.836529287118719</v>
+        <v>-5.925186298650193</v>
       </c>
       <c r="E2063" t="n">
-        <v>1.485219438697386</v>
+        <v>1.449756634084796</v>
       </c>
       <c r="F2063" t="n">
-        <v>0.660074531985904</v>
+        <v>0.6086779126578541</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.216232297050164</v>
+        <v>4.185394325453334</v>
       </c>
     </row>
     <row r="2064">
@@ -49023,16 +49023,16 @@
         <v>3.819725941201554</v>
       </c>
       <c r="D2064" t="n">
-        <v>-5.854747754116327</v>
+        <v>-5.943404765647801</v>
       </c>
       <c r="E2064" t="n">
-        <v>1.477470415241275</v>
+        <v>1.442007610628685</v>
       </c>
       <c r="F2064" t="n">
-        <v>0.6349680947300619</v>
+        <v>0.5835714754020119</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.200706798039591</v>
+        <v>4.169868826442761</v>
       </c>
     </row>
     <row r="2065">
@@ -49046,16 +49046,16 @@
         <v>3.839600334051872</v>
       </c>
       <c r="D2065" t="n">
-        <v>-5.816064318772397</v>
+        <v>-5.904721330303871</v>
       </c>
       <c r="E2065" t="n">
-        <v>1.512818182229166</v>
+        <v>1.477355377616576</v>
       </c>
       <c r="F2065" t="n">
-        <v>0.6349680947300619</v>
+        <v>0.5835714754020119</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.220581190889909</v>
+        <v>4.18974321929308</v>
       </c>
     </row>
     <row r="2066">
@@ -49069,16 +49069,16 @@
         <v>3.8233010345766</v>
       </c>
       <c r="D2066" t="n">
-        <v>-5.710029323567087</v>
+        <v>-5.798686335098561</v>
       </c>
       <c r="E2066" t="n">
-        <v>1.538932880836017</v>
+        <v>1.503470076223428</v>
       </c>
       <c r="F2066" t="n">
-        <v>0.6349680947300619</v>
+        <v>0.5835714754020119</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.204281891414637</v>
+        <v>4.173443919817807</v>
       </c>
     </row>
     <row r="2067">
@@ -49092,16 +49092,16 @@
         <v>3.825731984040646</v>
       </c>
       <c r="D2067" t="n">
-        <v>-5.526817660433992</v>
+        <v>-5.615474671965466</v>
       </c>
       <c r="E2067" t="n">
-        <v>1.614648495553301</v>
+        <v>1.579185690940712</v>
       </c>
       <c r="F2067" t="n">
-        <v>0.6349680947300619</v>
+        <v>0.5835714754020119</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.206712840878684</v>
+        <v>4.175874869281854</v>
       </c>
     </row>
     <row r="2068">
@@ -49115,16 +49115,16 @@
         <v>3.808676390120023</v>
       </c>
       <c r="D2068" t="n">
-        <v>-5.455096213420141</v>
+        <v>-5.543753224951615</v>
       </c>
       <c r="E2068" t="n">
-        <v>1.626281480438219</v>
+        <v>1.590818675825629</v>
       </c>
       <c r="F2068" t="n">
-        <v>0.7066895417439125</v>
+        <v>0.6552929224158626</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.232690115166371</v>
+        <v>4.201852143569541</v>
       </c>
     </row>
     <row r="2069">
@@ -49138,16 +49138,16 @@
         <v>3.755592136041195</v>
       </c>
       <c r="D2069" t="n">
-        <v>-5.432723187812435</v>
+        <v>-5.521380199343909</v>
       </c>
       <c r="E2069" t="n">
-        <v>1.582146436602473</v>
+        <v>1.546683631989883</v>
       </c>
       <c r="F2069" t="n">
-        <v>0.7179452928568141</v>
+        <v>0.6665486735287641</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.186359311755283</v>
+        <v>4.155521340158454</v>
       </c>
     </row>
     <row r="2070">
@@ -49161,16 +49161,16 @@
         <v>3.94079034092655</v>
       </c>
       <c r="D2070" t="n">
-        <v>-5.46573948372318</v>
+        <v>-5.554396495254654</v>
       </c>
       <c r="E2070" t="n">
-        <v>1.75413812312353</v>
+        <v>1.71867531851094</v>
       </c>
       <c r="F2070" t="n">
-        <v>0.6485079161900624</v>
+        <v>0.5971112968620125</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.329895090640588</v>
+        <v>4.299057119043757</v>
       </c>
     </row>
     <row r="2071">
@@ -49184,16 +49184,16 @@
         <v>3.932711566754799</v>
       </c>
       <c r="D2071" t="n">
-        <v>-5.454211848073571</v>
+        <v>-5.542868859605045</v>
       </c>
       <c r="E2071" t="n">
-        <v>1.750670403211622</v>
+        <v>1.715207598599033</v>
       </c>
       <c r="F2071" t="n">
-        <v>0.7075085743914249</v>
+        <v>0.6561119550633749</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.357216711389654</v>
+        <v>4.326378739792824</v>
       </c>
     </row>
     <row r="2072">
@@ -49207,16 +49207,16 @@
         <v>3.936379679276587</v>
       </c>
       <c r="D2072" t="n">
-        <v>-5.55155334941594</v>
+        <v>-5.640210360947414</v>
       </c>
       <c r="E2072" t="n">
-        <v>1.715401915196463</v>
+        <v>1.679939110583874</v>
       </c>
       <c r="F2072" t="n">
-        <v>0.6630883922259365</v>
+        <v>0.6116917728978866</v>
       </c>
       <c r="G2072" t="n">
-        <v>4.33423271461215</v>
+        <v>4.303394743015319</v>
       </c>
     </row>
     <row r="2073">
@@ -49230,16 +49230,16 @@
         <v>3.937630761469426</v>
       </c>
       <c r="D2073" t="n">
-        <v>-5.637409378755907</v>
+        <v>-5.726066390287381</v>
       </c>
       <c r="E2073" t="n">
-        <v>1.682310585653315</v>
+        <v>1.646847781040726</v>
       </c>
       <c r="F2073" t="n">
-        <v>0.6207123229998015</v>
+        <v>0.5693157036717515</v>
       </c>
       <c r="G2073" t="n">
-        <v>4.310058155269306</v>
+        <v>4.279220183672477</v>
       </c>
     </row>
     <row r="2074">
@@ -49253,16 +49253,16 @@
         <v>3.920049963289927</v>
       </c>
       <c r="D2074" t="n">
-        <v>-5.646246176172026</v>
+        <v>-5.7349031877035</v>
       </c>
       <c r="E2074" t="n">
-        <v>1.661195068507369</v>
+        <v>1.62573226389478</v>
       </c>
       <c r="F2074" t="n">
-        <v>0.6132701503584508</v>
+        <v>0.5618735310304008</v>
       </c>
       <c r="G2074" t="n">
-        <v>4.288012053504998</v>
+        <v>4.257174081908168</v>
       </c>
     </row>
     <row r="2075">
@@ -49276,16 +49276,16 @@
         <v>3.930214474334977</v>
       </c>
       <c r="D2075" t="n">
-        <v>-5.737628738737484</v>
+        <v>-5.826285750268958</v>
       </c>
       <c r="E2075" t="n">
-        <v>1.634806554526235</v>
+        <v>1.599343749913646</v>
       </c>
       <c r="F2075" t="n">
-        <v>0.5767052656391061</v>
+        <v>0.5253086463110561</v>
       </c>
       <c r="G2075" t="n">
-        <v>4.27623763371844</v>
+        <v>4.245399662121611</v>
       </c>
     </row>
     <row r="2076">
@@ -49299,16 +49299,16 @@
         <v>4.032342732159245</v>
       </c>
       <c r="D2076" t="n">
-        <v>-5.725922020750478</v>
+        <v>-5.814579032281952</v>
       </c>
       <c r="E2076" t="n">
-        <v>1.741617499545306</v>
+        <v>1.706154694932716</v>
       </c>
       <c r="F2076" t="n">
-        <v>0.5884119836261125</v>
+        <v>0.5370153642980625</v>
       </c>
       <c r="G2076" t="n">
-        <v>4.385389922334912</v>
+        <v>4.354551950738083</v>
       </c>
     </row>
     <row r="2077">
@@ -49322,16 +49322,16 @@
         <v>4.03537507089065</v>
       </c>
       <c r="D2077" t="n">
-        <v>-5.796834094492755</v>
+        <v>-5.885491106024229</v>
       </c>
       <c r="E2077" t="n">
-        <v>1.7162850087798</v>
+        <v>1.68082220416721</v>
       </c>
       <c r="F2077" t="n">
-        <v>0.5884119836261125</v>
+        <v>0.5370153642980625</v>
       </c>
       <c r="G2077" t="n">
-        <v>4.388422261066317</v>
+        <v>4.357584289469488</v>
       </c>
     </row>
     <row r="2078">
@@ -49345,16 +49345,16 @@
         <v>4.036193896622915</v>
       </c>
       <c r="D2078" t="n">
-        <v>-5.807150192659107</v>
+        <v>-5.895807204190581</v>
       </c>
       <c r="E2078" t="n">
-        <v>1.712977395245523</v>
+        <v>1.677514590632934</v>
       </c>
       <c r="F2078" t="n">
-        <v>0.5884119836261125</v>
+        <v>0.5370153642980625</v>
       </c>
       <c r="G2078" t="n">
-        <v>4.389241086798582</v>
+        <v>4.358403115201752</v>
       </c>
     </row>
     <row r="2079">
@@ -49368,16 +49368,16 @@
         <v>4.035372563535004</v>
       </c>
       <c r="D2079" t="n">
-        <v>-5.807056224641735</v>
+        <v>-5.895713236173209</v>
       </c>
       <c r="E2079" t="n">
-        <v>1.712193649364562</v>
+        <v>1.676730844751973</v>
       </c>
       <c r="F2079" t="n">
-        <v>0.5887818449734304</v>
+        <v>0.5373852256453805</v>
       </c>
       <c r="G2079" t="n">
-        <v>4.388641670519062</v>
+        <v>4.357803698922233</v>
       </c>
     </row>
     <row r="2080">
@@ -49391,16 +49391,16 @@
         <v>4.029604549479358</v>
       </c>
       <c r="D2080" t="n">
-        <v>-5.95065738866512</v>
+        <v>-6.039314400196594</v>
       </c>
       <c r="E2080" t="n">
-        <v>1.648985169699562</v>
+        <v>1.613522365086972</v>
       </c>
       <c r="F2080" t="n">
-        <v>0.5887818449734304</v>
+        <v>0.5373852256453805</v>
       </c>
       <c r="G2080" t="n">
-        <v>4.382873656463416</v>
+        <v>4.352035684866586</v>
       </c>
     </row>
     <row r="2081">
@@ -49414,16 +49414,16 @@
         <v>4.029604549479358</v>
       </c>
       <c r="D2081" t="n">
-        <v>-5.949708965547082</v>
+        <v>-6.038365977078556</v>
       </c>
       <c r="E2081" t="n">
-        <v>1.649364538946777</v>
+        <v>1.613901734334187</v>
       </c>
       <c r="F2081" t="n">
-        <v>0.5887818449734304</v>
+        <v>0.5373852256453805</v>
       </c>
       <c r="G2081" t="n">
-        <v>4.382873656463416</v>
+        <v>4.352035684866586</v>
       </c>
     </row>
     <row r="2082">
@@ -49437,16 +49437,16 @@
         <v>4.04233215746045</v>
       </c>
       <c r="D2082" t="n">
-        <v>-6.049978783506102</v>
+        <v>-6.138635795037576</v>
       </c>
       <c r="E2082" t="n">
-        <v>1.621984219744261</v>
+        <v>1.586521415131672</v>
       </c>
       <c r="F2082" t="n">
-        <v>0.5887818449734304</v>
+        <v>0.5373852256453805</v>
       </c>
       <c r="G2082" t="n">
-        <v>4.395601264444508</v>
+        <v>4.364763292847678</v>
       </c>
     </row>
     <row r="2083">
@@ -49460,16 +49460,16 @@
         <v>4.044278155884838</v>
       </c>
       <c r="D2083" t="n">
-        <v>-6.04398653671729</v>
+        <v>-6.132643548248764</v>
       </c>
       <c r="E2083" t="n">
-        <v>1.626327116884173</v>
+        <v>1.590864312271584</v>
       </c>
       <c r="F2083" t="n">
-        <v>0.5887818449734304</v>
+        <v>0.5373852256453805</v>
       </c>
       <c r="G2083" t="n">
-        <v>4.397547262868896</v>
+        <v>4.366709291272066</v>
       </c>
     </row>
     <row r="2084">
@@ -49483,16 +49483,16 @@
         <v>4.037932291902607</v>
       </c>
       <c r="D2084" t="n">
-        <v>-5.955428575586523</v>
+        <v>-6.044085587117997</v>
       </c>
       <c r="E2084" t="n">
-        <v>1.65540443735425</v>
+        <v>1.61994163274166</v>
       </c>
       <c r="F2084" t="n">
-        <v>0.5887818449734304</v>
+        <v>0.5373852256453805</v>
       </c>
       <c r="G2084" t="n">
-        <v>4.391201398886665</v>
+        <v>4.360363427289835</v>
       </c>
     </row>
     <row r="2085">
@@ -49506,16 +49506,16 @@
         <v>4.037240969341602</v>
       </c>
       <c r="D2085" t="n">
-        <v>-5.937669498083449</v>
+        <v>-6.026326509614923</v>
       </c>
       <c r="E2085" t="n">
-        <v>1.661816745794475</v>
+        <v>1.626353941181885</v>
       </c>
       <c r="F2085" t="n">
-        <v>0.5887818449734304</v>
+        <v>0.5373852256453805</v>
       </c>
       <c r="G2085" t="n">
-        <v>4.39051007632566</v>
+        <v>4.359672104728831</v>
       </c>
     </row>
     <row r="2086">
@@ -49529,16 +49529,16 @@
         <v>4.050023155250189</v>
       </c>
       <c r="D2086" t="n">
-        <v>-5.838039347034381</v>
+        <v>-5.926696358565855</v>
       </c>
       <c r="E2086" t="n">
-        <v>1.714450992122689</v>
+        <v>1.678988187510099</v>
       </c>
       <c r="F2086" t="n">
-        <v>0.6884119960224979</v>
+        <v>0.637015376694448</v>
       </c>
       <c r="G2086" t="n">
-        <v>4.463070352863688</v>
+        <v>4.432232381266858</v>
       </c>
     </row>
     <row r="2087">
@@ -49552,16 +49552,16 @@
         <v>4.239177420748915</v>
       </c>
       <c r="D2087" t="n">
-        <v>-5.887438855723392</v>
+        <v>-5.976095867254866</v>
       </c>
       <c r="E2087" t="n">
-        <v>1.883845454145811</v>
+        <v>1.848382649533221</v>
       </c>
       <c r="F2087" t="n">
-        <v>0.6986708294542426</v>
+        <v>0.6472742101261927</v>
       </c>
       <c r="G2087" t="n">
-        <v>4.658379918421462</v>
+        <v>4.627541946824631</v>
       </c>
     </row>
     <row r="2088">
@@ -49575,16 +49575,16 @@
         <v>4.226366093851778</v>
       </c>
       <c r="D2088" t="n">
-        <v>-5.680754382081016</v>
+        <v>-5.76941139361249</v>
       </c>
       <c r="E2088" t="n">
-        <v>1.953707916705623</v>
+        <v>1.918245112093034</v>
       </c>
       <c r="F2088" t="n">
-        <v>0.9053553030966183</v>
+        <v>0.8539586837685683</v>
       </c>
       <c r="G2088" t="n">
-        <v>4.769579275709749</v>
+        <v>4.738741304112919</v>
       </c>
     </row>
     <row r="2089">
@@ -49598,16 +49598,16 @@
         <v>4.228367607505882</v>
       </c>
       <c r="D2089" t="n">
-        <v>-5.714911277078542</v>
+        <v>-5.803568288610016</v>
       </c>
       <c r="E2089" t="n">
-        <v>1.942046672360718</v>
+        <v>1.906583867748128</v>
       </c>
       <c r="F2089" t="n">
-        <v>0.8217715335558058</v>
+        <v>0.7703749142277558</v>
       </c>
       <c r="G2089" t="n">
-        <v>4.721430527639367</v>
+        <v>4.690592556042536</v>
       </c>
     </row>
     <row r="2090">
@@ -49621,16 +49621,16 @@
         <v>4.58186472149555</v>
       </c>
       <c r="D2090" t="n">
-        <v>-5.622321798017086</v>
+        <v>-5.71097880954856</v>
       </c>
       <c r="E2090" t="n">
-        <v>2.332579577974968</v>
+        <v>2.297116773362378</v>
       </c>
       <c r="F2090" t="n">
-        <v>0.8217715335558058</v>
+        <v>0.7703749142277558</v>
       </c>
       <c r="G2090" t="n">
-        <v>5.074927641629033</v>
+        <v>5.044089670032204</v>
       </c>
     </row>
     <row r="2091">
@@ -49644,16 +49644,16 @@
         <v>4.586427833062654</v>
       </c>
       <c r="D2091" t="n">
-        <v>-5.695482401790231</v>
+        <v>-5.784139413321705</v>
       </c>
       <c r="E2091" t="n">
-        <v>2.307878448032814</v>
+        <v>2.272415643420224</v>
       </c>
       <c r="F2091" t="n">
-        <v>0.7937503335215628</v>
+        <v>0.7423537141935128</v>
       </c>
       <c r="G2091" t="n">
-        <v>5.062678033175592</v>
+        <v>5.031840061578762</v>
       </c>
     </row>
     <row r="2092">
@@ -49667,16 +49667,16 @@
         <v>4.636257774386181</v>
       </c>
       <c r="D2092" t="n">
-        <v>-5.643266091993889</v>
+        <v>-5.731923103525363</v>
       </c>
       <c r="E2092" t="n">
-        <v>2.378594913274878</v>
+        <v>2.343132108662288</v>
       </c>
       <c r="F2092" t="n">
-        <v>0.7937503335215628</v>
+        <v>0.7423537141935128</v>
       </c>
       <c r="G2092" t="n">
-        <v>5.11250797449912</v>
+        <v>5.081670002902289</v>
       </c>
     </row>
     <row r="2093">
@@ -49690,16 +49690,16 @@
         <v>4.645071744596192</v>
       </c>
       <c r="D2093" t="n">
-        <v>-5.590758764483394</v>
+        <v>-5.679415776014868</v>
       </c>
       <c r="E2093" t="n">
-        <v>2.408411814489087</v>
+        <v>2.372949009876497</v>
       </c>
       <c r="F2093" t="n">
-        <v>0.8462576610320577</v>
+        <v>0.7948610417040077</v>
       </c>
       <c r="G2093" t="n">
-        <v>5.152826341215428</v>
+        <v>5.121988369618597</v>
       </c>
     </row>
     <row r="2094">
@@ -49713,16 +49713,16 @@
         <v>4.640709328635389</v>
       </c>
       <c r="D2094" t="n">
-        <v>-5.605514088683535</v>
+        <v>-5.694171100215009</v>
       </c>
       <c r="E2094" t="n">
-        <v>2.398147268848227</v>
+        <v>2.362684464235638</v>
       </c>
       <c r="F2094" t="n">
-        <v>0.8462576610320577</v>
+        <v>0.7948610417040077</v>
       </c>
       <c r="G2094" t="n">
-        <v>5.148463925254624</v>
+        <v>5.117625953657794</v>
       </c>
     </row>
     <row r="2095">
@@ -49736,16 +49736,16 @@
         <v>4.631633832051669</v>
       </c>
       <c r="D2095" t="n">
-        <v>-5.556049465313623</v>
+        <v>-5.644706476845097</v>
       </c>
       <c r="E2095" t="n">
-        <v>2.408857621612472</v>
+        <v>2.373394816999883</v>
       </c>
       <c r="F2095" t="n">
-        <v>0.8957222844019693</v>
+        <v>0.8443256650739194</v>
       </c>
       <c r="G2095" t="n">
-        <v>5.169067202692851</v>
+        <v>5.138229231096021</v>
       </c>
     </row>
     <row r="2096">
@@ -49759,16 +49759,16 @@
         <v>4.628041499766604</v>
       </c>
       <c r="D2096" t="n">
-        <v>-5.392941473160008</v>
+        <v>-5.481598484691482</v>
       </c>
       <c r="E2096" t="n">
-        <v>2.470508486188853</v>
+        <v>2.435045681576263</v>
       </c>
       <c r="F2096" t="n">
-        <v>1.058830276555585</v>
+        <v>1.007433657227535</v>
       </c>
       <c r="G2096" t="n">
-        <v>5.263339665699955</v>
+        <v>5.232501694103124</v>
       </c>
     </row>
     <row r="2097">
@@ -49782,16 +49782,16 @@
         <v>4.637088536457732</v>
       </c>
       <c r="D2097" t="n">
-        <v>-5.37229838235878</v>
+        <v>-5.460955393890254</v>
       </c>
       <c r="E2097" t="n">
-        <v>2.487812759200472</v>
+        <v>2.452349954587882</v>
       </c>
       <c r="F2097" t="n">
-        <v>1.058830276555585</v>
+        <v>1.007433657227535</v>
       </c>
       <c r="G2097" t="n">
-        <v>5.272386702391083</v>
+        <v>5.241548730794253</v>
       </c>
     </row>
     <row r="2098">
@@ -49805,16 +49805,16 @@
         <v>4.637946001443853</v>
       </c>
       <c r="D2098" t="n">
-        <v>-5.435006298833338</v>
+        <v>-5.523663310364812</v>
       </c>
       <c r="E2098" t="n">
-        <v>2.46358705759677</v>
+        <v>2.428124252984181</v>
       </c>
       <c r="F2098" t="n">
-        <v>0.9961223600810269</v>
+        <v>0.9447257407529769</v>
       </c>
       <c r="G2098" t="n">
-        <v>5.23561941749247</v>
+        <v>5.20478144589564</v>
       </c>
     </row>
     <row r="2099">
@@ -49828,16 +49828,16 @@
         <v>4.600855418234206</v>
       </c>
       <c r="D2099" t="n">
-        <v>-5.386998174989645</v>
+        <v>-5.475655186521119</v>
       </c>
       <c r="E2099" t="n">
-        <v>2.4456997239246</v>
+        <v>2.41023691931201</v>
       </c>
       <c r="F2099" t="n">
-        <v>0.9961223600810269</v>
+        <v>0.9447257407529769</v>
       </c>
       <c r="G2099" t="n">
-        <v>5.198528834282822</v>
+        <v>5.167690862685992</v>
       </c>
     </row>
     <row r="2100">
@@ -49851,16 +49851,16 @@
         <v>4.604787671792156</v>
       </c>
       <c r="D2100" t="n">
-        <v>-5.236880119767748</v>
+        <v>-5.325537131299222</v>
       </c>
       <c r="E2100" t="n">
-        <v>2.509679199571309</v>
+        <v>2.474216394958719</v>
       </c>
       <c r="F2100" t="n">
-        <v>1.146240415302924</v>
+        <v>1.094843795974874</v>
       </c>
       <c r="G2100" t="n">
-        <v>5.292531920973911</v>
+        <v>5.261693949377081</v>
       </c>
     </row>
     <row r="2101">
@@ -49874,16 +49874,16 @@
         <v>4.599686764399193</v>
       </c>
       <c r="D2101" t="n">
-        <v>-5.044945318513874</v>
+        <v>-5.224389299431142</v>
       </c>
       <c r="E2101" t="n">
-        <v>2.581352212679895</v>
+        <v>2.509574620312988</v>
       </c>
       <c r="F2101" t="n">
-        <v>1.146240415302924</v>
+        <v>1.094843795974874</v>
       </c>
       <c r="G2101" t="n">
-        <v>5.287431013580948</v>
+        <v>5.256593041984118</v>
       </c>
     </row>
     <row r="2102">
@@ -49897,16 +49897,16 @@
         <v>4.595040673788288</v>
       </c>
       <c r="D2102" t="n">
-        <v>-4.926771940495946</v>
+        <v>-5.106215921413215</v>
       </c>
       <c r="E2102" t="n">
-        <v>2.623975473276162</v>
+        <v>2.552197880909254</v>
       </c>
       <c r="F2102" t="n">
-        <v>1.264413793320851</v>
+        <v>1.213017173992801</v>
       </c>
       <c r="G2102" t="n">
-        <v>5.353688949780799</v>
+        <v>5.322850978183969</v>
       </c>
     </row>
     <row r="2103">
@@ -49920,16 +49920,16 @@
         <v>4.624129266651315</v>
       </c>
       <c r="D2103" t="n">
-        <v>-4.837924823636449</v>
+        <v>-5.017368804553717</v>
       </c>
       <c r="E2103" t="n">
-        <v>2.688602912882987</v>
+        <v>2.61682532051608</v>
       </c>
       <c r="F2103" t="n">
-        <v>1.353260910180349</v>
+        <v>1.301864290852299</v>
       </c>
       <c r="G2103" t="n">
-        <v>5.436085812759525</v>
+        <v>5.405247841162694</v>
       </c>
     </row>
     <row r="2104">
@@ -49943,16 +49943,16 @@
         <v>4.617689489662492</v>
       </c>
       <c r="D2104" t="n">
-        <v>-4.810875785943195</v>
+        <v>-4.990319766860464</v>
       </c>
       <c r="E2104" t="n">
-        <v>2.692982750971466</v>
+        <v>2.621205158604559</v>
       </c>
       <c r="F2104" t="n">
-        <v>1.380309947873603</v>
+        <v>1.328913328545553</v>
       </c>
       <c r="G2104" t="n">
-        <v>5.445875458386654</v>
+        <v>5.415037486789824</v>
       </c>
     </row>
     <row r="2105">
@@ -49966,16 +49966,16 @@
         <v>4.617689489662492</v>
       </c>
       <c r="D2105" t="n">
-        <v>-4.816909066129965</v>
+        <v>-4.996353047047234</v>
       </c>
       <c r="E2105" t="n">
-        <v>2.690569438896758</v>
+        <v>2.618791846529851</v>
       </c>
       <c r="F2105" t="n">
-        <v>1.380309947873603</v>
+        <v>1.328913328545553</v>
       </c>
       <c r="G2105" t="n">
-        <v>5.445875458386654</v>
+        <v>5.415037486789824</v>
       </c>
     </row>
     <row r="2106">
@@ -49989,16 +49989,16 @@
         <v>4.621327656804905</v>
       </c>
       <c r="D2106" t="n">
-        <v>-4.868760841703127</v>
+        <v>-5.048204822620395</v>
       </c>
       <c r="E2106" t="n">
-        <v>2.673466895809906</v>
+        <v>2.601689303442999</v>
       </c>
       <c r="F2106" t="n">
-        <v>1.328458172300441</v>
+        <v>1.277061552972391</v>
       </c>
       <c r="G2106" t="n">
-        <v>5.41840256018517</v>
+        <v>5.38756458858834</v>
       </c>
     </row>
     <row r="2107">
@@ -50012,16 +50012,16 @@
         <v>4.584819403988742</v>
       </c>
       <c r="D2107" t="n">
-        <v>-4.895818287834953</v>
+        <v>-5.075262268752222</v>
       </c>
       <c r="E2107" t="n">
-        <v>2.626135664541012</v>
+        <v>2.554358072174105</v>
       </c>
       <c r="F2107" t="n">
-        <v>1.328458172300441</v>
+        <v>1.277061552972391</v>
       </c>
       <c r="G2107" t="n">
-        <v>5.381894307369007</v>
+        <v>5.351056335772176</v>
       </c>
     </row>
     <row r="2108">
@@ -50029,22 +50029,22 @@
         <v>45570</v>
       </c>
       <c r="B2108" t="n">
-        <v>3.91739311730433</v>
+        <v>3.637500569392438</v>
       </c>
       <c r="C2108" t="n">
         <v>4.586227353735933</v>
       </c>
       <c r="D2108" t="n">
-        <v>-4.969099639688829</v>
+        <v>-5.148543620606097</v>
       </c>
       <c r="E2108" t="n">
-        <v>2.598231073546653</v>
+        <v>2.526453481179746</v>
       </c>
       <c r="F2108" t="n">
-        <v>1.31454675016923</v>
+        <v>1.26315013084118</v>
       </c>
       <c r="G2108" t="n">
-        <v>5.374955403837471</v>
+        <v>5.344117432240641</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20241006.xlsx
+++ b/tame_output/ON/bt/strategyON_20241006.xlsx
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2105</v>
+        <v>2106</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,7 +628,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-10-05</t>
+          <t>2024-10-06</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -758,7 +758,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>101.9%</t>
+          <t>100.4%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -768,7 +768,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.36</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2105</v>
+        <v>2106</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-10-05</t>
+          <t>2024-10-06</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-9.1%</t>
+          <t>-9.7%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-7.9%</t>
+          <t>-8.1%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>86.3%</t>
+          <t>84.6%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-7.9%</t>
+          <t>-7.8%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>147.0%</t>
+          <t>143.0%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-78.4%</t>
+          <t>-78.1%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>106.8%</t>
+          <t>106.9%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2105</v>
+        <v>2106</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,7 +944,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-10-05</t>
+          <t>2024-10-06</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>89.4%</t>
+          <t>89.6%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-37.8%</t>
+          <t>-37.7%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>21.4%</t>
+          <t>21.6%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-75.1%</t>
+          <t>-74.6%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>88.6%</t>
+          <t>88.7%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>418.9%</t>
+          <t>419.0%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-6.3%</t>
+          <t>-6.2%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-676.4%</t>
+          <t>-668.4%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>29.7%</t>
+          <t>30.4%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2105</v>
+        <v>2106</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-10-05</t>
+          <t>2024-10-06</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1140,7 +1140,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-9.7%</t>
+          <t>-9.6%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>14.0%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1160,17 +1160,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>25.6%</t>
+          <t>26.5%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>49.5%</t>
+          <t>49.6%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-4.2%</t>
+          <t>-4.3%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14.0%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-123.6%</t>
+          <t>-120.4%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-3.1%</t>
+          <t>-2.3%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2105</v>
+        <v>2106</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-10-05</t>
+          <t>2024-10-06</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>74.2%</t>
+          <t>74.3%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.7%</t>
+          <t>10.8%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>3.8%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>44.1%</t>
+          <t>52.1%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-204.1%</t>
+          <t>-365.4%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-97.7%</t>
+          <t>-93.2%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>113.1%</t>
+          <t>57.2%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>57.6%</t>
+          <t>67.1%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2105</v>
+        <v>2106</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-10-05</t>
+          <t>2024-10-06</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>60.2%</t>
+          <t>80.4%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-7.7%</t>
+          <t>-9.5%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>14.2%</t>
+          <t>14.0%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-18.7%</t>
+          <t>-26.5%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>103.2%</t>
+          <t>47.2%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>48.0%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.4%</t>
+          <t>-14.8%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>88.4%</t>
+          <t>7.9%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2108"/>
+  <dimension ref="A1:G2109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191735</v>
+        <v>3.302618194191734</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44463,7 +44463,7 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108636</v>
+        <v>3.305023265108635</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097818</v>
+        <v>3.341378723097817</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094114</v>
+        <v>3.374439043094112</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199281</v>
+        <v>3.40596051119928</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.42463335496959</v>
+        <v>3.424633354969588</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923083</v>
+        <v>3.41997943392308</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297745</v>
+        <v>3.458100091297743</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317614</v>
+        <v>3.447750501317611</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737167</v>
+        <v>3.503515506737166</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.50317028234131</v>
+        <v>3.503170282341309</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937498</v>
+        <v>3.492448711937499</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502790399141701</v>
+        <v>3.502790399141702</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.49685190472989</v>
+        <v>3.496851904729891</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.4900592416086</v>
+        <v>3.490059241608601</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764397</v>
+        <v>3.480692492764398</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390586</v>
+        <v>3.493716014390587</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297397</v>
+        <v>3.492101641297398</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322542</v>
+        <v>3.573674025322543</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600038265158922</v>
+        <v>3.600038265158923</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940719</v>
+        <v>3.69157173394072</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676841549770579</v>
+        <v>3.67684154977058</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615283</v>
+        <v>3.685161381615284</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812103</v>
+        <v>3.684843823812104</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
@@ -45176,7 +45176,7 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.78468452131195</v>
+        <v>3.784684521311949</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
@@ -45199,7 +45199,7 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800829354097244</v>
+        <v>3.800829354097242</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
@@ -45222,7 +45222,7 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017772</v>
+        <v>3.789311112017769</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
@@ -45245,7 +45245,7 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833252747839725</v>
+        <v>3.833252747839722</v>
       </c>
       <c r="C1900" t="n">
         <v>3.151116350215413</v>
@@ -45268,7 +45268,7 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839374447388729</v>
+        <v>3.839374447388725</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
@@ -45291,7 +45291,7 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856161751626475</v>
+        <v>3.856161751626471</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
@@ -45314,7 +45314,7 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787330429291814</v>
+        <v>3.787330429291812</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
@@ -45337,7 +45337,7 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801637122785788</v>
+        <v>3.801637122785786</v>
       </c>
       <c r="C1904" t="n">
         <v>3.155859013848905</v>
@@ -45360,7 +45360,7 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763182248390429</v>
+        <v>3.763182248390427</v>
       </c>
       <c r="C1905" t="n">
         <v>3.057119799856059</v>
@@ -45383,7 +45383,7 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105954</v>
+        <v>3.784718794105952</v>
       </c>
       <c r="C1906" t="n">
         <v>3.059934860543696</v>
@@ -45406,7 +45406,7 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960987</v>
+        <v>3.753882571960985</v>
       </c>
       <c r="C1907" t="n">
         <v>3.072841201767355</v>
@@ -45429,7 +45429,7 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607646</v>
+        <v>3.692931855607644</v>
       </c>
       <c r="C1908" t="n">
         <v>2.944865272168136</v>
@@ -45452,7 +45452,7 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770422583987903</v>
+        <v>3.770422583987902</v>
       </c>
       <c r="C1909" t="n">
         <v>2.993409614045222</v>
@@ -45475,7 +45475,7 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710813</v>
+        <v>3.760333686710811</v>
       </c>
       <c r="C1910" t="n">
         <v>2.876788805406815</v>
@@ -45498,7 +45498,7 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409205</v>
+        <v>3.723566229409204</v>
       </c>
       <c r="C1911" t="n">
         <v>2.868074819153337</v>
@@ -45521,7 +45521,7 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.72996971609811</v>
+        <v>3.729969716098108</v>
       </c>
       <c r="C1912" t="n">
         <v>2.861114207058244</v>
@@ -45544,7 +45544,7 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493421</v>
+        <v>3.782922533493419</v>
       </c>
       <c r="C1913" t="n">
         <v>2.875576561439387</v>
@@ -45567,7 +45567,7 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722819</v>
+        <v>3.828551486722817</v>
       </c>
       <c r="C1914" t="n">
         <v>2.870108681898582</v>
@@ -45590,7 +45590,7 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792047</v>
+        <v>3.828052928792046</v>
       </c>
       <c r="C1915" t="n">
         <v>2.867606775909159</v>
@@ -45613,7 +45613,7 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919907</v>
+        <v>3.812453678919905</v>
       </c>
       <c r="C1916" t="n">
         <v>2.875307754146484</v>
@@ -45636,7 +45636,7 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318092</v>
+        <v>3.74832840831809</v>
       </c>
       <c r="C1917" t="n">
         <v>2.871088462493535</v>
@@ -45659,7 +45659,7 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057527</v>
+        <v>3.824311233057525</v>
       </c>
       <c r="C1918" t="n">
         <v>2.873212776413551</v>
@@ -45682,7 +45682,7 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279186</v>
+        <v>3.826354974279184</v>
       </c>
       <c r="C1919" t="n">
         <v>2.865954851397253</v>
@@ -45705,7 +45705,7 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011499</v>
+        <v>3.835957987011497</v>
       </c>
       <c r="C1920" t="n">
         <v>2.869553974917902</v>
@@ -45728,7 +45728,7 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392988</v>
+        <v>3.780933911392986</v>
       </c>
       <c r="C1921" t="n">
         <v>2.882881480972455</v>
@@ -45751,7 +45751,7 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632782</v>
+        <v>3.773765222632781</v>
       </c>
       <c r="C1922" t="n">
         <v>2.881901958588752</v>
@@ -45774,7 +45774,7 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883074</v>
+        <v>3.764617879883073</v>
       </c>
       <c r="C1923" t="n">
         <v>2.88659675964307</v>
@@ -45797,7 +45797,7 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074784</v>
+        <v>3.798814771074782</v>
       </c>
       <c r="C1924" t="n">
         <v>2.867791018426865</v>
@@ -45820,7 +45820,7 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242294</v>
+        <v>3.797694884242293</v>
       </c>
       <c r="C1925" t="n">
         <v>2.869534095051743</v>
@@ -45843,7 +45843,7 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821593509367686</v>
+        <v>3.821593509367682</v>
       </c>
       <c r="C1926" t="n">
         <v>2.873463408886563</v>
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879966</v>
+        <v>3.822326997879962</v>
       </c>
       <c r="C1927" t="n">
         <v>2.874141992803903</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.742179208749064</v>
+        <v>-4.655499061143624</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.9769138849905292</v>
+        <v>1.011585944032705</v>
       </c>
       <c r="F1927" t="n">
-        <v>0.2064431047883115</v>
+        <v>0.2557333052914421</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.99800785567689</v>
+        <v>3.027581975978769</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.84861662650234</v>
+        <v>3.848616626502333</v>
       </c>
       <c r="C1928" t="n">
         <v>2.871140064023896</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.618704937436046</v>
+        <v>-4.532024789830606</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.02330166473573</v>
+        <v>1.057973723777906</v>
       </c>
       <c r="F1928" t="n">
-        <v>0.2064431047883115</v>
+        <v>0.2557333052914421</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.995005926896884</v>
+        <v>3.024580047198762</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.81866895167594</v>
+        <v>3.818668951675935</v>
       </c>
       <c r="C1929" t="n">
         <v>2.872719101034511</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.560769105437831</v>
+        <v>-4.47408895783239</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.04805503454563</v>
+        <v>1.082727093587806</v>
       </c>
       <c r="F1929" t="n">
-        <v>0.2320049794710608</v>
+        <v>0.2812951799741914</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.011922088717147</v>
+        <v>3.041496209019026</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539952</v>
+        <v>3.843274527539947</v>
       </c>
       <c r="C1930" t="n">
         <v>2.888613283836334</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.427901416374553</v>
+        <v>-4.341221268769113</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.117096292972765</v>
+        <v>1.151768352014941</v>
       </c>
       <c r="F1930" t="n">
-        <v>0.2320049794710608</v>
+        <v>0.2812951799741914</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.02781627151897</v>
+        <v>3.057390391820849</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496263</v>
+        <v>3.845047386496259</v>
       </c>
       <c r="C1931" t="n">
         <v>2.889759128276636</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.307728333010054</v>
+        <v>-4.221048185404614</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.166311370758866</v>
+        <v>1.200983429801042</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.3521780628355597</v>
+        <v>0.4014682633386903</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.101065965977972</v>
+        <v>3.13064008627985</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551577</v>
+        <v>3.791273551576996</v>
       </c>
       <c r="C1932" t="n">
         <v>2.899847230838076</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.172474971680077</v>
+        <v>-4.085794824074637</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.230500817852297</v>
+        <v>1.265172876894473</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.4874314241655369</v>
+        <v>0.5367216246686675</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.192306085337398</v>
+        <v>3.221880205639276</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942106</v>
+        <v>3.735839222942102</v>
       </c>
       <c r="C1933" t="n">
         <v>2.885884722239501</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.232349799037769</v>
+        <v>-4.145669651432329</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.192588378310646</v>
+        <v>1.227260437352822</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.4275565968078447</v>
+        <v>0.4768467973109753</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.142418680324209</v>
+        <v>3.171992800626087</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674515</v>
+        <v>3.762647477674512</v>
       </c>
       <c r="C1934" t="n">
         <v>2.90117389147371</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.112529568126932</v>
+        <v>-4.025849420521492</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.255805639909189</v>
+        <v>1.290477698951365</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.4275565968078447</v>
+        <v>0.4768467973109753</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.157707849558417</v>
+        <v>3.187281969860296</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430697</v>
+        <v>3.729146398430693</v>
       </c>
       <c r="C1935" t="n">
         <v>2.808818090796152</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.114999274588738</v>
+        <v>-4.028319126983298</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.162461956646908</v>
+        <v>1.197134015689084</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.4250868903460386</v>
+        <v>0.4743770908491692</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.063870225003775</v>
+        <v>3.093444345305653</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003604</v>
+        <v>3.7432201960036</v>
       </c>
       <c r="C1936" t="n">
         <v>2.728079952281453</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.183369460912749</v>
+        <v>-4.096689313307309</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.054375743602606</v>
+        <v>1.089047802644782</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.4343625893822535</v>
+        <v>0.4836527898853841</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.988697505910805</v>
+        <v>3.018271626212684</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508372</v>
+        <v>3.714179139508368</v>
       </c>
       <c r="C1937" t="n">
         <v>2.718516660913344</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.295241740538899</v>
+        <v>-4.208561592933459</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.000063540384037</v>
+        <v>1.034735599426213</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.4343625893822535</v>
+        <v>0.4836527898853841</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.979134214542697</v>
+        <v>3.008708334844575</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417706</v>
+        <v>3.710906731417702</v>
       </c>
       <c r="C1938" t="n">
         <v>2.685091185837372</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.279267075052632</v>
+        <v>-4.192586927447191</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.9730279315025709</v>
+        <v>1.007699990544747</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.4343625893822535</v>
+        <v>0.4836527898853841</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.945708739466724</v>
+        <v>2.975282859768603</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205901</v>
+        <v>3.746042526205895</v>
       </c>
       <c r="C1939" t="n">
         <v>2.689658417829159</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.283361621723629</v>
+        <v>-4.196681474118189</v>
       </c>
       <c r="E1939" t="n">
-        <v>0.9759573448259597</v>
+        <v>1.010629403868136</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.4343625893822535</v>
+        <v>0.4836527898853841</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.950275971458512</v>
+        <v>2.97985009176039</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225445</v>
+        <v>3.765024323225438</v>
       </c>
       <c r="C1940" t="n">
         <v>2.665400446590366</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.275437247138715</v>
+        <v>-4.188757099533275</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.9548691234211324</v>
+        <v>0.9895411824633085</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.4343625893822535</v>
+        <v>0.4836527898853841</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.926018000219719</v>
+        <v>2.955592120521597</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111296</v>
+        <v>3.773210297111292</v>
       </c>
       <c r="C1941" t="n">
         <v>2.593938759991816</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.269159044568866</v>
+        <v>-4.182478896963426</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.8859187178505219</v>
+        <v>0.920590776892698</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.4406407919521026</v>
+        <v>0.4899309924552332</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.858323235163078</v>
+        <v>2.887897355464956</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264166</v>
+        <v>3.784343952264162</v>
       </c>
       <c r="C1942" t="n">
         <v>2.604111146423949</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.209306425365143</v>
+        <v>-4.122626277759703</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.9200321519641435</v>
+        <v>0.9547042110063195</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.4406407919521026</v>
+        <v>0.4899309924552332</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.86849562159521</v>
+        <v>2.898069741897089</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742301</v>
+        <v>3.786949957742298</v>
       </c>
       <c r="C1943" t="n">
         <v>2.599057416997809</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.123062962338765</v>
+        <v>-4.036382814733325</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.9494758077485548</v>
+        <v>0.9841478667907309</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.4406407919521026</v>
+        <v>0.4899309924552332</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.863441892169071</v>
+        <v>2.893016012470949</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316048</v>
+        <v>3.752027499316045</v>
       </c>
       <c r="C1944" t="n">
         <v>2.590833192442334</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.168369781737745</v>
+        <v>-4.081689634132305</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.9231288554334884</v>
+        <v>0.9578009144756645</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.3998306289428718</v>
+        <v>0.4491208294460024</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.830731569808058</v>
+        <v>2.860305690109936</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803192</v>
+        <v>3.753571165803189</v>
       </c>
       <c r="C1945" t="n">
         <v>2.591385065475436</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.197402886440046</v>
+        <v>-4.110722738834606</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.9120674865856695</v>
+        <v>0.9467395456278456</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.3998306289428718</v>
+        <v>0.4491208294460024</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.831283442841159</v>
+        <v>2.860857563143038</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809501</v>
+        <v>3.733390600809497</v>
       </c>
       <c r="C1946" t="n">
         <v>2.520657757366802</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.104592404989186</v>
+        <v>-4.017912257383746</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.8784643710573792</v>
+        <v>0.9131364300995553</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.4926411103937312</v>
+        <v>0.5419313108968618</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.816242423603041</v>
+        <v>2.845816543904919</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560427</v>
+        <v>3.748285816560424</v>
       </c>
       <c r="C1947" t="n">
         <v>2.522531233291402</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.148981874318614</v>
+        <v>-4.062301726713174</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.8625820592502089</v>
+        <v>0.897254118292385</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.4482516410643035</v>
+        <v>0.4975418415674341</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.791482217929985</v>
+        <v>2.821056338231863</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472738</v>
+        <v>3.721077195472734</v>
       </c>
       <c r="C1948" t="n">
         <v>2.517606941803125</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.128478180433117</v>
+        <v>-4.041798032827677</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.8658592453161309</v>
+        <v>0.900531304358307</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.4687553349498008</v>
+        <v>0.5180455354529314</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.798860142773006</v>
+        <v>2.828434263074885</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798539</v>
+        <v>3.743047603798535</v>
       </c>
       <c r="C1949" t="n">
         <v>2.523098237633793</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.212150277145449</v>
+        <v>-4.125470129540009</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.837881702461865</v>
+        <v>0.8725537615040411</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.4687553349498008</v>
+        <v>0.5180455354529314</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.804351438603673</v>
+        <v>2.833925558905552</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498865</v>
+        <v>3.689597840498862</v>
       </c>
       <c r="C1950" t="n">
         <v>2.534595439402332</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.239930675046802</v>
+        <v>-4.153250527441362</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.8382667450698631</v>
+        <v>0.8729388041120392</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.4409749370484478</v>
+        <v>0.4902651375515783</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.799180401631401</v>
+        <v>2.828754521933279</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705326</v>
+        <v>3.643069621705322</v>
       </c>
       <c r="C1951" t="n">
         <v>2.372951159402985</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.35831134777694</v>
+        <v>-4.2716312001715</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.629270195978461</v>
+        <v>0.6639422550206371</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.3737570848974716</v>
+        <v>0.4230472854006021</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.597205410341468</v>
+        <v>2.626779530643347</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729271</v>
+        <v>3.682716310729267</v>
       </c>
       <c r="C1952" t="n">
         <v>2.493100820122191</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.466925426220271</v>
+        <v>-4.380245278614831</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.7059742253203343</v>
+        <v>0.7406462843625103</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.3737570848974716</v>
+        <v>0.4230472854006021</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.717355071060674</v>
+        <v>2.746929191362552</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.73301244119077</v>
+        <v>3.733012441190766</v>
       </c>
       <c r="C1953" t="n">
         <v>2.507613846224514</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.431516387972128</v>
+        <v>-4.344836240366688</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.7346508667219143</v>
+        <v>0.7693229257640903</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.3737570848974716</v>
+        <v>0.4230472854006021</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.731868097162997</v>
+        <v>2.761442217464875</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913428</v>
+        <v>3.741174069913424</v>
       </c>
       <c r="C1954" t="n">
         <v>2.505033287566882</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.439977556627589</v>
+        <v>-4.353297409022149</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.7286858406020986</v>
+        <v>0.7633578996442747</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.3652959162420105</v>
+        <v>0.4145861167451411</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.724210837312089</v>
+        <v>2.753784957613967</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532488</v>
+        <v>3.751147197532484</v>
       </c>
       <c r="C1955" t="n">
         <v>2.501762316412185</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.262861226592423</v>
+        <v>-4.176181078986983</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.7962614014614675</v>
+        <v>0.8309334605036436</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.3652959162420105</v>
+        <v>0.4145861167451411</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.720939866157391</v>
+        <v>2.75051398645927</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793904</v>
+        <v>3.741328448793901</v>
       </c>
       <c r="C1956" t="n">
         <v>2.502445708174098</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.307953471425969</v>
+        <v>-4.221273323820529</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.7789078952899624</v>
+        <v>0.8135799543321385</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.3033998730726207</v>
+        <v>0.3526900735757513</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.684485632017671</v>
+        <v>2.714059752319549</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011237</v>
+        <v>3.750729377011231</v>
       </c>
       <c r="C1957" t="n">
         <v>2.496232683480512</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.128578050187201</v>
+        <v>-4.041897902581761</v>
       </c>
       <c r="E1957" t="n">
-        <v>0.8444450390918838</v>
+        <v>0.8791170981340599</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.4601766312433394</v>
+        <v>0.5094668317464699</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.772338662226516</v>
+        <v>2.801912782528394</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.71699171898223</v>
+        <v>3.716991718982224</v>
       </c>
       <c r="C1958" t="n">
         <v>2.477040138812102</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.173592263707807</v>
+        <v>-4.086912116102367</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.8072468090152312</v>
+        <v>0.8419188680574072</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.4298277359287348</v>
+        <v>0.4791179364318653</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.734936780369343</v>
+        <v>2.764510900671221</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509539</v>
+        <v>3.737026608509533</v>
       </c>
       <c r="C1959" t="n">
         <v>2.482731701151048</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.261603450266504</v>
+        <v>-4.174923302661064</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.7777338967306981</v>
+        <v>0.8124059557728742</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.3643512280695618</v>
+        <v>0.4136414285726923</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.701342437992785</v>
+        <v>2.730916558294664</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760813</v>
+        <v>3.702309454760809</v>
       </c>
       <c r="C1960" t="n">
         <v>2.481935623047549</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.362801231703677</v>
+        <v>-4.276121084098237</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.7364587060523304</v>
+        <v>0.7711307650945065</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.2959424145242426</v>
+        <v>0.3452326150273731</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.659501071762095</v>
+        <v>2.689075192063973</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815457</v>
+        <v>3.705571661815453</v>
       </c>
       <c r="C1961" t="n">
         <v>2.479535584601866</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.356290265089364</v>
+        <v>-4.269610117483924</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.7366630542523722</v>
+        <v>0.7713351132945483</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.2959424145242426</v>
+        <v>0.3452326150273731</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.657101033316412</v>
+        <v>2.68667515361829</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378102</v>
+        <v>3.709510443378099</v>
       </c>
       <c r="C1962" t="n">
         <v>2.476060303810111</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.337252137382067</v>
+        <v>-4.250571989776627</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.740803024543536</v>
+        <v>0.775475083585712</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.2377588031930481</v>
+        <v>0.2870490036961786</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.61871558572594</v>
+        <v>2.648289706027818</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.73106447313125</v>
+        <v>3.731064473131246</v>
       </c>
       <c r="C1963" t="n">
         <v>2.595354705444301</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.389767939656887</v>
+        <v>-4.303087792051447</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.8390911052677983</v>
+        <v>0.8737631643099744</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.2377588031930481</v>
+        <v>0.2870490036961786</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.73800998736013</v>
+        <v>2.767584107662008</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067864</v>
+        <v>3.722447362067861</v>
       </c>
       <c r="C1964" t="n">
         <v>2.596188034430435</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.393176251091467</v>
+        <v>-4.306496103486027</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.8385611096800998</v>
+        <v>0.8732331687222759</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.2702753722024255</v>
+        <v>0.319565572705556</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.75835325775189</v>
+        <v>2.787927378053769</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789123</v>
+        <v>3.78742558078912</v>
       </c>
       <c r="C1965" t="n">
         <v>2.602196564827361</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.37382011519762</v>
+        <v>-4.28713996759218</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.8523120944345648</v>
+        <v>0.8869841534767409</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.2702753722024255</v>
+        <v>0.319565572705556</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.764361788148816</v>
+        <v>2.793935908450695</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519908</v>
+        <v>3.781501250519905</v>
       </c>
       <c r="C1966" t="n">
         <v>2.50014678610456</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.447149643935712</v>
+        <v>-4.360469496330272</v>
       </c>
       <c r="E1966" t="n">
-        <v>0.7209305042165273</v>
+        <v>0.7556025632587033</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.2706700346220474</v>
+        <v>0.3199602351251779</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.662548806877789</v>
+        <v>2.692122927179667</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.80224592918117</v>
+        <v>3.802245929181165</v>
       </c>
       <c r="C1967" t="n">
         <v>2.409870503348191</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.530970865210411</v>
+        <v>-4.444290717604971</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.597125732950279</v>
+        <v>0.6317977919924551</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.2706700346220474</v>
+        <v>0.3199602351251779</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.57227252412142</v>
+        <v>2.601846644423298</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394731</v>
+        <v>3.805608985394725</v>
       </c>
       <c r="C1968" t="n">
         <v>2.41053285173985</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.524818159157626</v>
+        <v>-4.438138011552186</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.6002491637630512</v>
+        <v>0.6349212228052272</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.2768227406748317</v>
+        <v>0.3261129411779622</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.576626496144749</v>
+        <v>2.606200616446627</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890613</v>
+        <v>3.798239794890609</v>
       </c>
       <c r="C1969" t="n">
         <v>2.40961332847996</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.541627457308128</v>
+        <v>-4.454947309702688</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.5926059212429606</v>
+        <v>0.6272779802851367</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.2600134425243301</v>
+        <v>0.3093036430274606</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.565621393994558</v>
+        <v>2.595195514296436</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798427</v>
+        <v>3.867362636798424</v>
       </c>
       <c r="C1970" t="n">
         <v>2.475948882276781</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.479329458532006</v>
+        <v>-4.392649310926566</v>
       </c>
       <c r="E1970" t="n">
-        <v>0.6838606745502305</v>
+        <v>0.7185327335924065</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.3053077067987721</v>
+        <v>0.3545979073019026</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.659133506356044</v>
+        <v>2.688707626657922</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992193</v>
+        <v>3.848729139992188</v>
       </c>
       <c r="C1971" t="n">
         <v>2.278240883990908</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.277539260866848</v>
+        <v>-4.190859113261408</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.5668687553304206</v>
+        <v>0.6015408143725967</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.5033258989679266</v>
+        <v>0.5526160994710569</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.580236423371664</v>
+        <v>2.609810543673542</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852424</v>
+        <v>3.841444817852421</v>
       </c>
       <c r="C1972" t="n">
         <v>2.348531116313083</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.328425973553043</v>
+        <v>-4.241745825947603</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.616804302578118</v>
+        <v>0.6514763616202941</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.452439186281732</v>
+        <v>0.5017293867848625</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.619994628082122</v>
+        <v>2.649568748384001</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319546</v>
+        <v>3.81906330031954</v>
       </c>
       <c r="C1973" t="n">
         <v>2.363158852429127</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.241815230903236</v>
+        <v>-4.155135083297796</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.6660763357540844</v>
+        <v>0.7007483947962605</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.5310649174868902</v>
+        <v>0.5803551179900207</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.681797802921261</v>
+        <v>2.711371923223139</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489386</v>
+        <v>3.83181903248938</v>
       </c>
       <c r="C1974" t="n">
         <v>2.361694833253798</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.302024528908521</v>
+        <v>-4.215344381303081</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.6405285973766421</v>
+        <v>0.6752006564188182</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.4708556194816057</v>
+        <v>0.5201458199847362</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.644208204942762</v>
+        <v>2.67378232524464</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397796</v>
+        <v>3.83641167239779</v>
       </c>
       <c r="C1975" t="n">
         <v>2.360186451293727</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.25283788022417</v>
+        <v>-4.166157732618729</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.6586948748903112</v>
+        <v>0.6933669339324873</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.4708556194816057</v>
+        <v>0.5201458199847362</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.642699822982691</v>
+        <v>2.672273943284569</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316252</v>
+        <v>3.833513460316245</v>
       </c>
       <c r="C1976" t="n">
         <v>2.360049318729163</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.208464748585601</v>
+        <v>-4.121784600980161</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.6763069949811749</v>
+        <v>0.7109790540233509</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.5152287511201743</v>
+        <v>0.5645189516233048</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.669186569401268</v>
+        <v>2.698760689703146</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105966</v>
+        <v>3.821562117105962</v>
       </c>
       <c r="C1977" t="n">
         <v>2.354443112867754</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.1737334272671</v>
+        <v>-4.08705327966166</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.6845933176471655</v>
+        <v>0.7192653766893415</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.5152287511201743</v>
+        <v>0.5645189516233048</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.663580363539858</v>
+        <v>2.693154483841737</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190325</v>
+        <v>3.833011148190321</v>
       </c>
       <c r="C1978" t="n">
         <v>2.360824869895558</v>
       </c>
       <c r="D1978" t="n">
-        <v>-4.126077696706044</v>
+        <v>-4.039397549100604</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.7100373668993925</v>
+        <v>0.7447094259415685</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.56288448168123</v>
+        <v>0.6121746821843604</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.698555558904296</v>
+        <v>2.728129679206175</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569618</v>
+        <v>3.822678210569614</v>
       </c>
       <c r="C1979" t="n">
         <v>2.365717243270283</v>
       </c>
       <c r="D1979" t="n">
-        <v>-4.02555953820729</v>
+        <v>-3.93887939060185</v>
       </c>
       <c r="E1979" t="n">
-        <v>0.7551370036736191</v>
+        <v>0.7898090627157952</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.6634026401799845</v>
+        <v>0.712692840683115</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.763758827378274</v>
+        <v>2.793332947680153</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557295</v>
+        <v>3.828808877557291</v>
       </c>
       <c r="C1980" t="n">
         <v>2.352471915746155</v>
       </c>
       <c r="D1980" t="n">
-        <v>-4.009654208774937</v>
+        <v>-3.922974061169497</v>
       </c>
       <c r="E1980" t="n">
-        <v>0.7482538079224326</v>
+        <v>0.7829258669646086</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.5842899794707457</v>
+        <v>0.6335801799738761</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.703045903428603</v>
+        <v>2.732620023730481</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932769</v>
+        <v>3.816837033932766</v>
       </c>
       <c r="C1981" t="n">
         <v>2.356569618356784</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.964815807166539</v>
+        <v>-3.878135659561099</v>
       </c>
       <c r="E1981" t="n">
-        <v>0.7702868711764204</v>
+        <v>0.8049589302185964</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.5888334124156152</v>
+        <v>0.6381236129187455</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.709869665806153</v>
+        <v>2.739443786108032</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917051</v>
+        <v>3.817932354917048</v>
       </c>
       <c r="C1982" t="n">
         <v>2.360730557987862</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.984314263408547</v>
+        <v>-3.897634115803107</v>
       </c>
       <c r="E1982" t="n">
-        <v>0.7666484283106949</v>
+        <v>0.801320487352871</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.5407487711357108</v>
+        <v>0.5900389716388412</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.685179820669289</v>
+        <v>2.714753940971167</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405961</v>
+        <v>3.826684745405958</v>
       </c>
       <c r="C1983" t="n">
         <v>2.366610160515699</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.940111426322647</v>
+        <v>-3.853431278717207</v>
       </c>
       <c r="E1983" t="n">
-        <v>0.7902091656728922</v>
+        <v>0.8248812247150683</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.5849516082216113</v>
+        <v>0.6342418087247417</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.717581125448666</v>
+        <v>2.747155245750544</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265645</v>
+        <v>3.838199629265642</v>
       </c>
       <c r="C1984" t="n">
         <v>2.365020160984947</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.947671092159694</v>
+        <v>-3.860990944554254</v>
       </c>
       <c r="E1984" t="n">
-        <v>0.785595299807321</v>
+        <v>0.8202673588494971</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.6397550122314306</v>
+        <v>0.689045212734561</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.748873168323805</v>
+        <v>2.778447288625683</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.86389508028488</v>
+        <v>3.863895080284877</v>
       </c>
       <c r="C1985" t="n">
         <v>2.416267926167986</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.789379674620422</v>
+        <v>-3.702699527014981</v>
       </c>
       <c r="E1985" t="n">
-        <v>0.9001596320060696</v>
+        <v>0.9348316910482457</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.6397550122314306</v>
+        <v>0.689045212734561</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.800120933506845</v>
+        <v>2.829695053808723</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865338681321023</v>
+        <v>3.86533868132102</v>
       </c>
       <c r="C1986" t="n">
         <v>2.414708630762239</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.581737670985945</v>
+        <v>-3.495057523380505</v>
       </c>
       <c r="E1986" t="n">
-        <v>0.9816571380541133</v>
+        <v>1.016329197096289</v>
       </c>
       <c r="F1986" t="n">
-        <v>0.8473970158659068</v>
+        <v>0.8966872163690371</v>
       </c>
       <c r="G1986" t="n">
-        <v>2.923146840281784</v>
+        <v>2.952720960583662</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475139</v>
+        <v>3.864489842475136</v>
       </c>
       <c r="C1987" t="n">
         <v>2.409656859000509</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.530705578263417</v>
+        <v>-3.444025430657977</v>
       </c>
       <c r="E1987" t="n">
-        <v>0.9970182033813946</v>
+        <v>1.031690262423571</v>
       </c>
       <c r="F1987" t="n">
-        <v>0.8984291085884347</v>
+        <v>0.9477193090915651</v>
       </c>
       <c r="G1987" t="n">
-        <v>2.94871432415357</v>
+        <v>2.978288444455448</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404854</v>
+        <v>3.84254736040485</v>
       </c>
       <c r="C1988" t="n">
         <v>2.426844263093214</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.465481397136212</v>
+        <v>-3.378801249530771</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.040295279924982</v>
+        <v>1.074967338967158</v>
       </c>
       <c r="F1988" t="n">
-        <v>0.9636532897156403</v>
+        <v>1.012943490218771</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.005036236922599</v>
+        <v>3.034610357224477</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882558</v>
+        <v>3.840061186882552</v>
       </c>
       <c r="C1989" t="n">
         <v>2.422805235392495</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.428054377065078</v>
+        <v>-3.341374229459638</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.051227060252716</v>
+        <v>1.085899119294892</v>
       </c>
       <c r="F1989" t="n">
-        <v>0.968904827744822</v>
+        <v>1.018195028247952</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.004148132039388</v>
+        <v>3.033722252341266</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992662</v>
+        <v>3.845169808992655</v>
       </c>
       <c r="C1990" t="n">
         <v>2.424062027723735</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.426696392091532</v>
+        <v>-3.340016244486092</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.053027046573374</v>
+        <v>1.08769910561555</v>
       </c>
       <c r="F1990" t="n">
-        <v>1.043242953282641</v>
+        <v>1.092533153785771</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.050007799693319</v>
+        <v>3.079581919995198</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636287</v>
+        <v>3.828661445636283</v>
       </c>
       <c r="C1991" t="n">
         <v>2.584619798744946</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.398283128991649</v>
+        <v>-3.311602981386208</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.224950122834538</v>
+        <v>1.259622181876714</v>
       </c>
       <c r="F1991" t="n">
-        <v>0.9842673905362118</v>
+        <v>1.033557591039342</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.175180233066673</v>
+        <v>3.204754353368551</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957627</v>
+        <v>3.813222820957621</v>
       </c>
       <c r="C1992" t="n">
         <v>2.704732707962763</v>
       </c>
       <c r="D1992" t="n">
-        <v>-3.323500867966636</v>
+        <v>-3.236820720361196</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.374975936462361</v>
+        <v>1.409647995504537</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.059049651561224</v>
+        <v>1.108339852064355</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.340162498899498</v>
+        <v>3.369736619201376</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998754</v>
+        <v>3.81423072799875</v>
       </c>
       <c r="C1993" t="n">
         <v>2.696440683976622</v>
       </c>
       <c r="D1993" t="n">
-        <v>-3.297416783702828</v>
+        <v>-3.210736636097388</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.377117546181743</v>
+        <v>1.411789605223919</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.059049651561224</v>
+        <v>1.108339852064355</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.331870474913357</v>
+        <v>3.361444595215235</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896929</v>
+        <v>3.803397818896926</v>
       </c>
       <c r="C1994" t="n">
         <v>2.694633879560401</v>
       </c>
       <c r="D1994" t="n">
-        <v>-3.209538870593708</v>
+        <v>-3.122858722988267</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.41046190700917</v>
+        <v>1.445133966051346</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.174975293984576</v>
+        <v>1.224265494487706</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.399619055951147</v>
+        <v>3.429193176253025</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959858</v>
+        <v>3.796264143959855</v>
       </c>
       <c r="C1995" t="n">
         <v>2.712188285287193</v>
       </c>
       <c r="D1995" t="n">
-        <v>-3.200646409200425</v>
+        <v>-3.113966261594984</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.431573297293275</v>
+        <v>1.466245356335451</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.174975293984576</v>
+        <v>1.224265494487706</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.417173461677939</v>
+        <v>3.446747581979817</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945367</v>
+        <v>3.794424941945364</v>
       </c>
       <c r="C1996" t="n">
         <v>2.704043332691777</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.369122526170302</v>
+        <v>-3.282442378564862</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.356037897909908</v>
+        <v>1.390709956952084</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.147027458267995</v>
+        <v>1.196317658771125</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.392259807652574</v>
+        <v>3.421833927954452</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782709</v>
+        <v>3.795574066782706</v>
       </c>
       <c r="C1997" t="n">
         <v>2.685313029879639</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.922866333540862</v>
+        <v>-2.836186185935422</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.515810072149546</v>
+        <v>1.550482131191722</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.052308788598362</v>
+        <v>1.101598989101492</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.316698303038656</v>
+        <v>3.346272423340534</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632637</v>
+        <v>3.784671345632633</v>
       </c>
       <c r="C1998" t="n">
         <v>2.675977052376543</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.90014522985771</v>
+        <v>-2.81346508225227</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.515562536119711</v>
+        <v>1.550234595161887</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.052308788598362</v>
+        <v>1.101598989101492</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.307362325535561</v>
+        <v>3.336936445837439</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777674</v>
+        <v>3.783205696777668</v>
       </c>
       <c r="C1999" t="n">
         <v>2.834883178227712</v>
       </c>
       <c r="D1999" t="n">
-        <v>-3.029347043151752</v>
+        <v>-2.942666895546312</v>
       </c>
       <c r="E1999" t="n">
-        <v>1.622787936653263</v>
+        <v>1.657459995695439</v>
       </c>
       <c r="F1999" t="n">
-        <v>0.92310697530432</v>
+        <v>0.9723971758074501</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.388747363410304</v>
+        <v>3.418321483712182</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644414</v>
+        <v>3.779933725644408</v>
       </c>
       <c r="C2000" t="n">
         <v>2.871961000721359</v>
       </c>
       <c r="D2000" t="n">
-        <v>-3.055221441625778</v>
+        <v>-2.968541294020338</v>
       </c>
       <c r="E2000" t="n">
-        <v>1.649515999757299</v>
+        <v>1.684188058799476</v>
       </c>
       <c r="F2000" t="n">
-        <v>0.9680185840160611</v>
+        <v>1.017308784519191</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.452772151130996</v>
+        <v>3.482346271432874</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799962</v>
+        <v>3.76944361979996</v>
       </c>
       <c r="C2001" t="n">
         <v>2.868636356710904</v>
       </c>
       <c r="D2001" t="n">
-        <v>-3.048166751410605</v>
+        <v>-2.961486603805164</v>
       </c>
       <c r="E2001" t="n">
-        <v>1.649013231832914</v>
+        <v>1.68368529087509</v>
       </c>
       <c r="F2001" t="n">
-        <v>0.9750732742312349</v>
+        <v>1.024363474734365</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.453680321249645</v>
+        <v>3.483254441551523</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331116</v>
+        <v>3.766673496331113</v>
       </c>
       <c r="C2002" t="n">
         <v>2.878642510355645</v>
       </c>
       <c r="D2002" t="n">
-        <v>-3.021215527084117</v>
+        <v>-2.934535379478676</v>
       </c>
       <c r="E2002" t="n">
-        <v>1.669799875208251</v>
+        <v>1.704471934250427</v>
       </c>
       <c r="F2002" t="n">
-        <v>0.9899536202589541</v>
+        <v>1.039243820762084</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.472614682511018</v>
+        <v>3.502188802812896</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784108</v>
+        <v>3.768052067784105</v>
       </c>
       <c r="C2003" t="n">
         <v>3.062745642500605</v>
       </c>
       <c r="D2003" t="n">
-        <v>-3.042759754914904</v>
+        <v>-2.956079607309464</v>
       </c>
       <c r="E2003" t="n">
-        <v>1.845285316220896</v>
+        <v>1.879957375263072</v>
       </c>
       <c r="F2003" t="n">
-        <v>0.9899536202589541</v>
+        <v>1.039243820762084</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.656717814655978</v>
+        <v>3.686291934957856</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714424</v>
+        <v>3.743925505714421</v>
       </c>
       <c r="C2004" t="n">
         <v>3.054862337403598</v>
       </c>
       <c r="D2004" t="n">
-        <v>-3.065167872719776</v>
+        <v>-2.978487725114336</v>
       </c>
       <c r="E2004" t="n">
-        <v>1.82843876400194</v>
+        <v>1.863110823044116</v>
       </c>
       <c r="F2004" t="n">
-        <v>0.9899536202589541</v>
+        <v>1.039243820762084</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.648834509558971</v>
+        <v>3.678408629860849</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155034</v>
+        <v>3.719118627155028</v>
       </c>
       <c r="C2005" t="n">
         <v>3.056916336953236</v>
       </c>
       <c r="D2005" t="n">
-        <v>-3.093392108297376</v>
+        <v>-3.006711960691936</v>
       </c>
       <c r="E2005" t="n">
-        <v>1.819203069320537</v>
+        <v>1.853875128362714</v>
       </c>
       <c r="F2005" t="n">
-        <v>1.007930372710263</v>
+        <v>1.057220573213393</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.661674560579394</v>
+        <v>3.691248680881272</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.72945228516198</v>
+        <v>3.729452285161972</v>
       </c>
       <c r="C2006" t="n">
         <v>3.113170054675083</v>
       </c>
       <c r="D2006" t="n">
-        <v>-3.102833034185906</v>
+        <v>-3.016152886580466</v>
       </c>
       <c r="E2006" t="n">
-        <v>1.871680416686972</v>
+        <v>1.906352475729149</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.130357490253654</v>
+        <v>1.179647690756784</v>
       </c>
       <c r="G2006" t="n">
-        <v>3.791384548827275</v>
+        <v>3.820958669129154</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321637</v>
+        <v>3.714941193321629</v>
       </c>
       <c r="C2007" t="n">
         <v>3.116061149220384</v>
       </c>
       <c r="D2007" t="n">
-        <v>-3.30907197197434</v>
+        <v>-3.222391824368899</v>
       </c>
       <c r="E2007" t="n">
-        <v>1.7920759361169</v>
+        <v>1.826747995159076</v>
       </c>
       <c r="F2007" t="n">
-        <v>0.9241185524652205</v>
+        <v>0.9734087529683506</v>
       </c>
       <c r="G2007" t="n">
-        <v>3.670532280699516</v>
+        <v>3.700106401001395</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347708</v>
+        <v>3.7278981863477</v>
       </c>
       <c r="C2008" t="n">
         <v>3.114172962114159</v>
       </c>
       <c r="D2008" t="n">
-        <v>-3.385401949575245</v>
+        <v>-3.298721801969805</v>
       </c>
       <c r="E2008" t="n">
-        <v>1.759655757970313</v>
+        <v>1.794327817012489</v>
       </c>
       <c r="F2008" t="n">
-        <v>0.9241185524652205</v>
+        <v>0.9734087529683506</v>
       </c>
       <c r="G2008" t="n">
-        <v>3.668644093593291</v>
+        <v>3.69821821389517</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887753</v>
+        <v>3.710654104887745</v>
       </c>
       <c r="C2009" t="n">
         <v>3.108993191717021</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.540358734975375</v>
+        <v>-3.453678587369934</v>
       </c>
       <c r="E2009" t="n">
-        <v>1.692493273413124</v>
+        <v>1.7271653324553</v>
       </c>
       <c r="F2009" t="n">
-        <v>0.7691617670650912</v>
+        <v>0.8184519675682214</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.570490251956076</v>
+        <v>3.600064372257954</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343071</v>
+        <v>3.712897612343062</v>
       </c>
       <c r="C2010" t="n">
         <v>3.107427201927174</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.70192716050263</v>
+        <v>-3.61524701289719</v>
       </c>
       <c r="E2010" t="n">
-        <v>1.626299913412374</v>
+        <v>1.66097197245455</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.6423788432672118</v>
+        <v>0.691669043770342</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.492854507887501</v>
+        <v>3.522428628189379</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754596135389354</v>
+        <v>3.754596135389345</v>
       </c>
       <c r="C2011" t="n">
         <v>3.120500608793092</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.810227822372749</v>
+        <v>-3.723547674767309</v>
       </c>
       <c r="E2011" t="n">
-        <v>1.596053055530245</v>
+        <v>1.630725114572421</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.6423788432672118</v>
+        <v>0.691669043770342</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.505927914753419</v>
+        <v>3.535502035055297</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.74988269137839</v>
+        <v>3.749882691378388</v>
       </c>
       <c r="C2012" t="n">
         <v>3.112505805576032</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.969778895136266</v>
+        <v>-3.883098747530826</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.524237823207778</v>
+        <v>1.558909882249954</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.4901011764054604</v>
+        <v>0.5393913769085905</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.406566511419308</v>
+        <v>3.436140631721187</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715819895006973</v>
+        <v>3.715819895006971</v>
       </c>
       <c r="C2013" t="n">
         <v>3.111029846703034</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.997679682245739</v>
+        <v>-3.910999534640299</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.51160154949099</v>
+        <v>1.546273608533167</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.4555042522625256</v>
+        <v>0.5047944527656557</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.38433239806055</v>
+        <v>3.413906518362428</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684895778787386</v>
+        <v>3.684895778787384</v>
       </c>
       <c r="C2014" t="n">
         <v>3.107794290680233</v>
       </c>
       <c r="D2014" t="n">
-        <v>-4.120205784948633</v>
+        <v>-4.033525637343192</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.459355552387032</v>
+        <v>1.494027611429208</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.3329781495596317</v>
+        <v>0.3822683500627618</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.307581180416012</v>
+        <v>3.33715530071789</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619348081585936</v>
+        <v>3.619348081585934</v>
       </c>
       <c r="C2015" t="n">
         <v>3.174500250270737</v>
       </c>
       <c r="D2015" t="n">
-        <v>-4.350720281134222</v>
+        <v>-4.264040133528781</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.4338557135033</v>
+        <v>1.468527772545476</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.102463653374043</v>
+        <v>0.1517538538771731</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.235978442295163</v>
+        <v>3.265552562597041</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640750087814666</v>
+        <v>3.640750087814664</v>
       </c>
       <c r="C2016" t="n">
         <v>3.314811969272584</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.699465366358665</v>
+        <v>-4.612785218753225</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.43466939841537</v>
+        <v>1.469341457457546</v>
       </c>
       <c r="F2016" t="n">
-        <v>-0.006284300544854848</v>
+        <v>0.04300589995827531</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.311041388945671</v>
+        <v>3.340615509247549</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668289004237095</v>
+        <v>3.668289004237093</v>
       </c>
       <c r="C2017" t="n">
         <v>3.383792238418224</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.853451784134806</v>
+        <v>-4.766771636529366</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.442055100450553</v>
+        <v>1.476727159492729</v>
       </c>
       <c r="F2017" t="n">
-        <v>-0.006284300544854848</v>
+        <v>0.04300589995827531</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.380021658091311</v>
+        <v>3.409595778393189</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619923016423388</v>
+        <v>3.619923016423386</v>
       </c>
       <c r="C2018" t="n">
         <v>3.369843440538344</v>
       </c>
       <c r="D2018" t="n">
-        <v>-5.058051218997814</v>
+        <v>-4.971371071392374</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.34626652862547</v>
+        <v>1.380938587667647</v>
       </c>
       <c r="F2018" t="n">
-        <v>-0.006284300544854848</v>
+        <v>0.04300589995827531</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.366072860211432</v>
+        <v>3.39564698051331</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656332733609753</v>
+        <v>3.656332733609752</v>
       </c>
       <c r="C2019" t="n">
         <v>3.381713929593758</v>
       </c>
       <c r="D2019" t="n">
-        <v>-5.310526373005539</v>
+        <v>-5.223846225400099</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.257146956077795</v>
+        <v>1.291819015119971</v>
       </c>
       <c r="F2019" t="n">
-        <v>-0.006284300544854848</v>
+        <v>0.04300589995827531</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.377943349266846</v>
+        <v>3.407517469568724</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674028535973157</v>
+        <v>3.674028535973155</v>
       </c>
       <c r="C2020" t="n">
         <v>3.382924464112702</v>
       </c>
       <c r="D2020" t="n">
-        <v>-5.603422129484951</v>
+        <v>-5.516741981879511</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.141199188004974</v>
+        <v>1.17587124704715</v>
       </c>
       <c r="F2020" t="n">
-        <v>-0.006284300544854848</v>
+        <v>0.04300589995827531</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.37915388378579</v>
+        <v>3.408728004087668</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663509457251946</v>
+        <v>3.663509457251942</v>
       </c>
       <c r="C2021" t="n">
         <v>3.387046206340024</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.790086257619759</v>
+        <v>-5.703406110014319</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.070655278978372</v>
+        <v>1.105327338020548</v>
       </c>
       <c r="F2021" t="n">
-        <v>-0.03302327136941474</v>
+        <v>0.01626692913371541</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.367232243518375</v>
+        <v>3.396806363820253</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652149152916202</v>
+        <v>3.652149152916197</v>
       </c>
       <c r="C2022" t="n">
         <v>3.382124059076213</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.936106944533721</v>
+        <v>-5.849426796928281</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.007324856948976</v>
+        <v>1.041996915991152</v>
       </c>
       <c r="F2022" t="n">
-        <v>-0.04210636316327171</v>
+        <v>0.007183837339858445</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.35686024117825</v>
+        <v>3.386434361480128</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667962306830328</v>
+        <v>3.667962306830325</v>
       </c>
       <c r="C2023" t="n">
         <v>3.544328115775257</v>
       </c>
       <c r="D2023" t="n">
-        <v>-6.027820953643307</v>
+        <v>-5.941140806037867</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.132843310004186</v>
+        <v>1.167515369046363</v>
       </c>
       <c r="F2023" t="n">
-        <v>-0.04210636316327171</v>
+        <v>0.007183837339858445</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.519064297877294</v>
+        <v>3.548638418179173</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696539468071552</v>
+        <v>3.696539468071547</v>
       </c>
       <c r="C2024" t="n">
         <v>3.539174753739071</v>
       </c>
       <c r="D2024" t="n">
-        <v>-6.059472612703276</v>
+        <v>-5.972792465097836</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.115029284344013</v>
+        <v>1.149701343386189</v>
       </c>
       <c r="F2024" t="n">
-        <v>-0.04727482040771191</v>
+        <v>0.00201538009541824</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.510809861494444</v>
+        <v>3.540383981796322</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750044015868149</v>
+        <v>3.750044015868143</v>
       </c>
       <c r="C2025" t="n">
         <v>3.549404171307562</v>
       </c>
       <c r="D2025" t="n">
-        <v>-6.128538667276213</v>
+        <v>-6.041858519670773</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.097632280083329</v>
+        <v>1.132304339125505</v>
       </c>
       <c r="F2025" t="n">
-        <v>-0.1096456979013219</v>
+        <v>-0.06035549739819179</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.483616752566769</v>
+        <v>3.513190872868647</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783632867332695</v>
+        <v>3.783632867332689</v>
       </c>
       <c r="C2026" t="n">
         <v>3.558329809763465</v>
       </c>
       <c r="D2026" t="n">
-        <v>-6.23051478952462</v>
+        <v>-6.14383464191918</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.065767469639868</v>
+        <v>1.100439528682045</v>
       </c>
       <c r="F2026" t="n">
-        <v>-0.2116218201497295</v>
+        <v>-0.1623316196465994</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.431356717673627</v>
+        <v>3.460930837975505</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798296784231812</v>
+        <v>3.798296784231805</v>
       </c>
       <c r="C2027" t="n">
         <v>3.55048269700764</v>
       </c>
       <c r="D2027" t="n">
-        <v>-6.120508506047399</v>
+        <v>-6.033828358441959</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.101922870274933</v>
+        <v>1.136594929317109</v>
       </c>
       <c r="F2027" t="n">
-        <v>-0.1884172482324543</v>
+        <v>-0.1391270477293242</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.437432348068168</v>
+        <v>3.467006468370046</v>
       </c>
     </row>
     <row r="2028">
@@ -48195,16 +48195,16 @@
         <v>3.554732707729614</v>
       </c>
       <c r="D2028" t="n">
-        <v>-6.133038211159278</v>
+        <v>-6.046358063553837</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.101160998952155</v>
+        <v>1.135833057994331</v>
       </c>
       <c r="F2028" t="n">
-        <v>-0.2022437476989773</v>
+        <v>-0.1529535471958472</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.433386459110229</v>
+        <v>3.462960579412107</v>
       </c>
     </row>
     <row r="2029">
@@ -48218,16 +48218,16 @@
         <v>3.56199359061215</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.83159148568744</v>
+        <v>-5.744911338082</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.229000572023426</v>
+        <v>1.263672631065603</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.09920297777285991</v>
+        <v>0.1484931782759901</v>
       </c>
       <c r="G2029" t="n">
-        <v>3.621515377275867</v>
+        <v>3.651089497577745</v>
       </c>
     </row>
     <row r="2030">
@@ -48241,16 +48241,16 @@
         <v>3.562964768364861</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.856181729922624</v>
+        <v>-5.769501582317184</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.220135652082063</v>
+        <v>1.254807711124239</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.09920297777285991</v>
+        <v>0.1484931782759901</v>
       </c>
       <c r="G2030" t="n">
-        <v>3.622486555028577</v>
+        <v>3.652060675330455</v>
       </c>
     </row>
     <row r="2031">
@@ -48264,16 +48264,16 @@
         <v>3.563807672744617</v>
       </c>
       <c r="D2031" t="n">
-        <v>-5.805143353916104</v>
+        <v>-5.718463206310664</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.241393906864427</v>
+        <v>1.276065965906603</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.09920297777285991</v>
+        <v>0.1484931782759901</v>
       </c>
       <c r="G2031" t="n">
-        <v>3.623329459408333</v>
+        <v>3.652903579710211</v>
       </c>
     </row>
     <row r="2032">
@@ -48281,22 +48281,22 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831734516969543</v>
+        <v>3.831734516969542</v>
       </c>
       <c r="C2032" t="n">
         <v>3.582845771618762</v>
       </c>
       <c r="D2032" t="n">
-        <v>-5.776294677092643</v>
+        <v>-5.689614529487203</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.271971476467957</v>
+        <v>1.306643535510133</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.1280516545963202</v>
+        <v>0.1773418550994503</v>
       </c>
       <c r="G2032" t="n">
-        <v>3.659676764376554</v>
+        <v>3.689250884678433</v>
       </c>
     </row>
     <row r="2033">
@@ -48304,22 +48304,22 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825752932700478</v>
+        <v>3.825752932700476</v>
       </c>
       <c r="C2033" t="n">
         <v>3.399029767742697</v>
       </c>
       <c r="D2033" t="n">
-        <v>-5.679659765074003</v>
+        <v>-5.592979617468563</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.126809437399347</v>
+        <v>1.161481496441523</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.2246865666149601</v>
+        <v>0.2739767671180903</v>
       </c>
       <c r="G2033" t="n">
-        <v>3.533841707711673</v>
+        <v>3.563415828013551</v>
       </c>
     </row>
     <row r="2034">
@@ -48327,22 +48327,22 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.804688961077642</v>
+        <v>3.804688961077638</v>
       </c>
       <c r="C2034" t="n">
         <v>3.402531811816661</v>
       </c>
       <c r="D2034" t="n">
-        <v>-5.610621754125535</v>
+        <v>-5.523941606520095</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.157926685852698</v>
+        <v>1.192598744894874</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.2937245775634282</v>
+        <v>0.3430147780665583</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.578766558354718</v>
+        <v>3.608340678656596</v>
       </c>
     </row>
     <row r="2035">
@@ -48350,22 +48350,22 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775028860833462</v>
+        <v>3.775028860833456</v>
       </c>
       <c r="C2035" t="n">
         <v>3.386958630892743</v>
       </c>
       <c r="D2035" t="n">
-        <v>-5.591834653756597</v>
+        <v>-5.505154506151157</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.149868345076356</v>
+        <v>1.184540404118533</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.3125116779323667</v>
+        <v>0.3618018784354968</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.574465637652164</v>
+        <v>3.604039757954042</v>
       </c>
     </row>
     <row r="2036">
@@ -48373,22 +48373,22 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821030660077627</v>
+        <v>3.821030660077626</v>
       </c>
       <c r="C2036" t="n">
         <v>3.386146341329173</v>
       </c>
       <c r="D2036" t="n">
-        <v>-5.514736052214724</v>
+        <v>-5.428055904609284</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.179895496129535</v>
+        <v>1.214567555171711</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.3125116779323667</v>
+        <v>0.3618018784354968</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.573653348088593</v>
+        <v>3.603227468390471</v>
       </c>
     </row>
     <row r="2037">
@@ -48396,22 +48396,22 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.832307024147909</v>
+        <v>3.832307024147908</v>
       </c>
       <c r="C2037" t="n">
         <v>3.396015120454245</v>
       </c>
       <c r="D2037" t="n">
-        <v>-5.525121247104614</v>
+        <v>-5.438441099499173</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.185610197298652</v>
+        <v>1.220282256340828</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.3021264830424774</v>
+        <v>0.3514166835456075</v>
       </c>
       <c r="G2037" t="n">
-        <v>3.577291010279732</v>
+        <v>3.60686513058161</v>
       </c>
     </row>
     <row r="2038">
@@ -48419,22 +48419,22 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.834415493735285</v>
+        <v>3.834415493735278</v>
       </c>
       <c r="C2038" t="n">
         <v>3.466852126230671</v>
       </c>
       <c r="D2038" t="n">
-        <v>-5.543709405826839</v>
+        <v>-5.457029258221398</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.249011939586187</v>
+        <v>1.283683998628363</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.283538324320252</v>
+        <v>0.3328285248233822</v>
       </c>
       <c r="G2038" t="n">
-        <v>3.636975120822822</v>
+        <v>3.6665492411247</v>
       </c>
     </row>
     <row r="2039">
@@ -48442,22 +48442,22 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.855120535496553</v>
+        <v>3.855120535496552</v>
       </c>
       <c r="C2039" t="n">
         <v>3.463721137048969</v>
       </c>
       <c r="D2039" t="n">
-        <v>-5.544007952522874</v>
+        <v>-5.457327804917434</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.245761531726072</v>
+        <v>1.280433590768248</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.2832397776242161</v>
+        <v>0.3325299781273462</v>
       </c>
       <c r="G2039" t="n">
-        <v>3.633665003623499</v>
+        <v>3.663239123925377</v>
       </c>
     </row>
     <row r="2040">
@@ -48465,22 +48465,22 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.81564321210886</v>
+        <v>3.815643212108854</v>
       </c>
       <c r="C2040" t="n">
         <v>3.468252031988361</v>
       </c>
       <c r="D2040" t="n">
-        <v>-5.443184818832447</v>
+        <v>-5.356504671227007</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.290621680141634</v>
+        <v>1.32529373918381</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.2957039931085699</v>
+        <v>0.3449941936117001</v>
       </c>
       <c r="G2040" t="n">
-        <v>3.645674427853503</v>
+        <v>3.675248548155381</v>
       </c>
     </row>
     <row r="2041">
@@ -48488,22 +48488,22 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.807356168121472</v>
+        <v>3.807356168121464</v>
       </c>
       <c r="C2041" t="n">
         <v>3.468381285466904</v>
       </c>
       <c r="D2041" t="n">
-        <v>-5.252403458080039</v>
+        <v>-5.165723310474599</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.36706347792114</v>
+        <v>1.401735536963316</v>
       </c>
       <c r="F2041" t="n">
-        <v>0.4864853538609773</v>
+        <v>0.5357755543641074</v>
       </c>
       <c r="G2041" t="n">
-        <v>3.76027249778349</v>
+        <v>3.789846618085368</v>
       </c>
     </row>
     <row r="2042">
@@ -48511,22 +48511,22 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.775233033906085</v>
+        <v>3.775233033906077</v>
       </c>
       <c r="C2042" t="n">
         <v>3.4482181312045</v>
       </c>
       <c r="D2042" t="n">
-        <v>-5.145440100230617</v>
+        <v>-5.058759952625177</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.389685666798505</v>
+        <v>1.424357725840681</v>
       </c>
       <c r="F2042" t="n">
-        <v>0.5449499618207787</v>
+        <v>0.5942401623239089</v>
       </c>
       <c r="G2042" t="n">
-        <v>3.775188108296968</v>
+        <v>3.804762228598846</v>
       </c>
     </row>
     <row r="2043">
@@ -48534,22 +48534,22 @@
         <v>45505</v>
       </c>
       <c r="B2043" t="n">
-        <v>3.785761685912989</v>
+        <v>3.785761685912981</v>
       </c>
       <c r="C2043" t="n">
         <v>3.483185067816559</v>
       </c>
       <c r="D2043" t="n">
-        <v>-5.090109512328855</v>
+        <v>-5.003429364723415</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.446784838571269</v>
+        <v>1.481456897613445</v>
       </c>
       <c r="F2043" t="n">
-        <v>0.6002805497225409</v>
+        <v>0.649570750225671</v>
       </c>
       <c r="G2043" t="n">
-        <v>3.843353397650084</v>
+        <v>3.872927517951962</v>
       </c>
     </row>
     <row r="2044">
@@ -48557,22 +48557,22 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.743767956539899</v>
+        <v>3.743767956539891</v>
       </c>
       <c r="C2044" t="n">
         <v>3.476871635717997</v>
       </c>
       <c r="D2044" t="n">
-        <v>-5.078055385415892</v>
+        <v>-4.991375237810452</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.445293057237892</v>
+        <v>1.479965116280068</v>
       </c>
       <c r="F2044" t="n">
-        <v>0.6123346766355037</v>
+        <v>0.6616248771386338</v>
       </c>
       <c r="G2044" t="n">
-        <v>3.844272441699299</v>
+        <v>3.873846562001177</v>
       </c>
     </row>
     <row r="2045">
@@ -48580,22 +48580,22 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.725010844811014</v>
+        <v>3.725010844811005</v>
       </c>
       <c r="C2045" t="n">
         <v>3.478752265902132</v>
       </c>
       <c r="D2045" t="n">
-        <v>-5.155410875543861</v>
+        <v>-5.068730727938421</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.41623149137084</v>
+        <v>1.450903550413016</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.5349791865075343</v>
+        <v>0.5842693870106644</v>
       </c>
       <c r="G2045" t="n">
-        <v>3.799739777806653</v>
+        <v>3.829313898108532</v>
       </c>
     </row>
     <row r="2046">
@@ -48603,22 +48603,22 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.612322444382925</v>
+        <v>3.612322444382916</v>
       </c>
       <c r="C2046" t="n">
         <v>3.491603291780015</v>
       </c>
       <c r="D2046" t="n">
-        <v>-5.087362312852331</v>
+        <v>-5.000682165246891</v>
       </c>
       <c r="E2046" t="n">
-        <v>1.456301942325334</v>
+        <v>1.49097400136751</v>
       </c>
       <c r="F2046" t="n">
-        <v>0.6030277491990641</v>
+        <v>0.6523179497021943</v>
       </c>
       <c r="G2046" t="n">
-        <v>3.853419941299454</v>
+        <v>3.882994061601332</v>
       </c>
     </row>
     <row r="2047">
@@ -48626,22 +48626,22 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.645256780013432</v>
+        <v>3.645256780013423</v>
       </c>
       <c r="C2047" t="n">
         <v>3.511805961953609</v>
       </c>
       <c r="D2047" t="n">
-        <v>-5.318962706021832</v>
+        <v>-5.232282558416392</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.383864455231128</v>
+        <v>1.418536514273304</v>
       </c>
       <c r="F2047" t="n">
-        <v>0.6030277491990641</v>
+        <v>0.6523179497021943</v>
       </c>
       <c r="G2047" t="n">
-        <v>3.873622611473048</v>
+        <v>3.903196731774926</v>
       </c>
     </row>
     <row r="2048">
@@ -48649,22 +48649,22 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666747201498968</v>
+        <v>3.666747201498967</v>
       </c>
       <c r="C2048" t="n">
         <v>3.495412198020491</v>
       </c>
       <c r="D2048" t="n">
-        <v>-5.369014251551052</v>
+        <v>-5.282334103945612</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.347450073086322</v>
+        <v>1.382122132128498</v>
       </c>
       <c r="F2048" t="n">
-        <v>0.6030277491990641</v>
+        <v>0.6523179497021943</v>
       </c>
       <c r="G2048" t="n">
-        <v>3.85722884753993</v>
+        <v>3.886802967841808</v>
       </c>
     </row>
     <row r="2049">
@@ -48672,22 +48672,22 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.670048702800097</v>
+        <v>3.670048702800096</v>
       </c>
       <c r="C2049" t="n">
         <v>3.455664111613958</v>
       </c>
       <c r="D2049" t="n">
-        <v>-5.544121084127497</v>
+        <v>-5.457440936522056</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.237659253649211</v>
+        <v>1.272331312691387</v>
       </c>
       <c r="F2049" t="n">
-        <v>0.6030277491990641</v>
+        <v>0.6523179497021943</v>
       </c>
       <c r="G2049" t="n">
-        <v>3.817480761133397</v>
+        <v>3.847054881435275</v>
       </c>
     </row>
     <row r="2050">
@@ -48695,22 +48695,22 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.745573148660849</v>
+        <v>3.745573148660848</v>
       </c>
       <c r="C2050" t="n">
         <v>3.462686730610898</v>
       </c>
       <c r="D2050" t="n">
-        <v>-5.348020930696974</v>
+        <v>-5.261340783091534</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.32312193401836</v>
+        <v>1.357793993060536</v>
       </c>
       <c r="F2050" t="n">
-        <v>0.799127902629587</v>
+        <v>0.8484181031327171</v>
       </c>
       <c r="G2050" t="n">
-        <v>3.94216347218865</v>
+        <v>3.971737592490529</v>
       </c>
     </row>
     <row r="2051">
@@ -48718,22 +48718,22 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.730570473395087</v>
+        <v>3.730570473395085</v>
       </c>
       <c r="C2051" t="n">
         <v>3.561857730183802</v>
       </c>
       <c r="D2051" t="n">
-        <v>-5.194995538583689</v>
+        <v>-5.108315390978249</v>
       </c>
       <c r="E2051" t="n">
-        <v>1.483503090436578</v>
+        <v>1.518175149478755</v>
       </c>
       <c r="F2051" t="n">
-        <v>0.9521532947428711</v>
+        <v>1.001443495246001</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.133149707029525</v>
+        <v>4.162723827331403</v>
       </c>
     </row>
     <row r="2052">
@@ -48741,22 +48741,22 @@
         <v>45514</v>
       </c>
       <c r="B2052" t="n">
-        <v>3.741278332791149</v>
+        <v>3.741278332791147</v>
       </c>
       <c r="C2052" t="n">
         <v>3.749323955092095</v>
       </c>
       <c r="D2052" t="n">
-        <v>-5.22330285245696</v>
+        <v>-5.136622704851519</v>
       </c>
       <c r="E2052" t="n">
-        <v>1.659646389795563</v>
+        <v>1.694318448837739</v>
       </c>
       <c r="F2052" t="n">
-        <v>0.9521532947428711</v>
+        <v>1.001443495246001</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.320615931937818</v>
+        <v>4.350190052239696</v>
       </c>
     </row>
     <row r="2053">
@@ -48764,22 +48764,22 @@
         <v>45515</v>
       </c>
       <c r="B2053" t="n">
-        <v>3.699115615620435</v>
+        <v>3.699115615620433</v>
       </c>
       <c r="C2053" t="n">
         <v>3.718726906446177</v>
       </c>
       <c r="D2053" t="n">
-        <v>-5.389896077570482</v>
+        <v>-5.303215929965042</v>
       </c>
       <c r="E2053" t="n">
-        <v>1.562412051104237</v>
+        <v>1.597084110146413</v>
       </c>
       <c r="F2053" t="n">
-        <v>0.7855600696293488</v>
+        <v>0.8348502701324787</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.190062948223787</v>
+        <v>4.219637068525665</v>
       </c>
     </row>
     <row r="2054">
@@ -48787,22 +48787,22 @@
         <v>45516</v>
       </c>
       <c r="B2054" t="n">
-        <v>3.708182519285647</v>
+        <v>3.708182519285645</v>
       </c>
       <c r="C2054" t="n">
         <v>3.722403309107895</v>
       </c>
       <c r="D2054" t="n">
-        <v>-5.366860284208916</v>
+        <v>-5.280180136603476</v>
       </c>
       <c r="E2054" t="n">
-        <v>1.575302771110581</v>
+        <v>1.609974830152757</v>
       </c>
       <c r="F2054" t="n">
-        <v>0.7855600696293488</v>
+        <v>0.8348502701324787</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.193739350885505</v>
+        <v>4.223313471187383</v>
       </c>
     </row>
     <row r="2055">
@@ -48810,22 +48810,22 @@
         <v>45517</v>
       </c>
       <c r="B2055" t="n">
-        <v>3.740581401399469</v>
+        <v>3.740581401399467</v>
       </c>
       <c r="C2055" t="n">
         <v>3.72002136423139</v>
       </c>
       <c r="D2055" t="n">
-        <v>-5.337614303753219</v>
+        <v>-5.250934156147779</v>
       </c>
       <c r="E2055" t="n">
-        <v>1.584619218416355</v>
+        <v>1.619291277458531</v>
       </c>
       <c r="F2055" t="n">
-        <v>0.7855600696293488</v>
+        <v>0.8348502701324787</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.191357406009</v>
+        <v>4.220931526310878</v>
       </c>
     </row>
     <row r="2056">
@@ -48833,22 +48833,22 @@
         <v>45518</v>
       </c>
       <c r="B2056" t="n">
-        <v>3.699404642256372</v>
+        <v>3.699404642256368</v>
       </c>
       <c r="C2056" t="n">
         <v>3.717314603389025</v>
       </c>
       <c r="D2056" t="n">
-        <v>-5.44453985163107</v>
+        <v>-5.35785970402563</v>
       </c>
       <c r="E2056" t="n">
-        <v>1.539142238422849</v>
+        <v>1.573814297465026</v>
       </c>
       <c r="F2056" t="n">
-        <v>0.6786345217514974</v>
+        <v>0.7279247222546273</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.124495316439925</v>
+        <v>4.154069436741802</v>
       </c>
     </row>
     <row r="2057">
@@ -48856,22 +48856,22 @@
         <v>45519</v>
       </c>
       <c r="B2057" t="n">
-        <v>3.689942600701002</v>
+        <v>3.689942600700998</v>
       </c>
       <c r="C2057" t="n">
         <v>3.71874340553226</v>
       </c>
       <c r="D2057" t="n">
-        <v>-5.589558410138319</v>
+        <v>-5.502878262532879</v>
       </c>
       <c r="E2057" t="n">
-        <v>1.482563617163184</v>
+        <v>1.51723567620536</v>
       </c>
       <c r="F2057" t="n">
-        <v>0.5336159632442489</v>
+        <v>0.5829061637473788</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.038912983478809</v>
+        <v>4.068487103780687</v>
       </c>
     </row>
     <row r="2058">
@@ -48879,22 +48879,22 @@
         <v>45520</v>
       </c>
       <c r="B2058" t="n">
-        <v>3.711852429687013</v>
+        <v>3.71185242968701</v>
       </c>
       <c r="C2058" t="n">
         <v>3.818674644790013</v>
       </c>
       <c r="D2058" t="n">
-        <v>-5.707900175923037</v>
+        <v>-5.621220028317596</v>
       </c>
       <c r="E2058" t="n">
-        <v>1.53515815010705</v>
+        <v>1.569830209149226</v>
       </c>
       <c r="F2058" t="n">
-        <v>0.5443020018071389</v>
+        <v>0.5935922023102689</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.145255845874297</v>
+        <v>4.174829966176175</v>
       </c>
     </row>
     <row r="2059">
@@ -48902,22 +48902,22 @@
         <v>45521</v>
       </c>
       <c r="B2059" t="n">
-        <v>3.714879051790806</v>
+        <v>3.7148790517908</v>
       </c>
       <c r="C2059" t="n">
         <v>3.816460341915952</v>
       </c>
       <c r="D2059" t="n">
-        <v>-5.759310598243744</v>
+        <v>-5.672630450638304</v>
       </c>
       <c r="E2059" t="n">
-        <v>1.512379678304706</v>
+        <v>1.547051737346882</v>
       </c>
       <c r="F2059" t="n">
-        <v>0.5443020018071389</v>
+        <v>0.5935922023102689</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.143041543000235</v>
+        <v>4.172615663302113</v>
       </c>
     </row>
     <row r="2060">
@@ -48925,22 +48925,22 @@
         <v>45522</v>
       </c>
       <c r="B2060" t="n">
-        <v>3.704757949437335</v>
+        <v>3.704757949437328</v>
       </c>
       <c r="C2060" t="n">
         <v>3.816363469990241</v>
       </c>
       <c r="D2060" t="n">
-        <v>-5.838730049451496</v>
+        <v>-5.752049901846056</v>
       </c>
       <c r="E2060" t="n">
-        <v>1.480515025895894</v>
+        <v>1.51518708493807</v>
       </c>
       <c r="F2060" t="n">
-        <v>0.5443020018071389</v>
+        <v>0.5935922023102689</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.142944671074525</v>
+        <v>4.172518791376403</v>
       </c>
     </row>
     <row r="2061">
@@ -48948,22 +48948,22 @@
         <v>45523</v>
       </c>
       <c r="B2061" t="n">
-        <v>3.736804952298403</v>
+        <v>3.736804952298394</v>
       </c>
       <c r="C2061" t="n">
         <v>3.816357363548284</v>
       </c>
       <c r="D2061" t="n">
-        <v>-5.934193047368714</v>
+        <v>-5.847512899763274</v>
       </c>
       <c r="E2061" t="n">
-        <v>1.44232372028705</v>
+        <v>1.476995779329227</v>
       </c>
       <c r="F2061" t="n">
-        <v>0.5443020018071389</v>
+        <v>0.5935922023102689</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.142938564632567</v>
+        <v>4.172512684934445</v>
       </c>
     </row>
     <row r="2062">
@@ -48971,22 +48971,22 @@
         <v>45524</v>
       </c>
       <c r="B2062" t="n">
-        <v>3.715372960218006</v>
+        <v>3.715372960217997</v>
       </c>
       <c r="C2062" t="n">
         <v>3.814453760110895</v>
       </c>
       <c r="D2062" t="n">
-        <v>-5.869817136517999</v>
+        <v>-5.783136988912559</v>
       </c>
       <c r="E2062" t="n">
-        <v>1.466170481189947</v>
+        <v>1.500842540232123</v>
       </c>
       <c r="F2062" t="n">
-        <v>0.6086779126578541</v>
+        <v>0.657968113160984</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.179660507705607</v>
+        <v>4.209234628007485</v>
       </c>
     </row>
     <row r="2063">
@@ -48994,22 +48994,22 @@
         <v>45525</v>
       </c>
       <c r="B2063" t="n">
-        <v>3.736089413353541</v>
+        <v>3.736089413353533</v>
       </c>
       <c r="C2063" t="n">
         <v>3.820187577858621</v>
       </c>
       <c r="D2063" t="n">
-        <v>-5.925186298650193</v>
+        <v>-5.838506151044752</v>
       </c>
       <c r="E2063" t="n">
-        <v>1.449756634084796</v>
+        <v>1.484428693126972</v>
       </c>
       <c r="F2063" t="n">
-        <v>0.6086779126578541</v>
+        <v>0.657968113160984</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.185394325453334</v>
+        <v>4.214968445755212</v>
       </c>
     </row>
     <row r="2064">
@@ -49017,22 +49017,22 @@
         <v>45526</v>
       </c>
       <c r="B2064" t="n">
-        <v>3.736822870113285</v>
+        <v>3.736822870113276</v>
       </c>
       <c r="C2064" t="n">
         <v>3.819725941201554</v>
       </c>
       <c r="D2064" t="n">
-        <v>-5.943404765647801</v>
+        <v>-5.856724618042361</v>
       </c>
       <c r="E2064" t="n">
-        <v>1.442007610628685</v>
+        <v>1.476679669670861</v>
       </c>
       <c r="F2064" t="n">
-        <v>0.5835714754020119</v>
+        <v>0.6328616759051419</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.169868826442761</v>
+        <v>4.199442946744639</v>
       </c>
     </row>
     <row r="2065">
@@ -49040,22 +49040,22 @@
         <v>45527</v>
       </c>
       <c r="B2065" t="n">
-        <v>3.790272500113693</v>
+        <v>3.790272500113684</v>
       </c>
       <c r="C2065" t="n">
         <v>3.839600334051872</v>
       </c>
       <c r="D2065" t="n">
-        <v>-5.904721330303871</v>
+        <v>-5.818041182698431</v>
       </c>
       <c r="E2065" t="n">
-        <v>1.477355377616576</v>
+        <v>1.512027436658752</v>
       </c>
       <c r="F2065" t="n">
-        <v>0.5835714754020119</v>
+        <v>0.6328616759051419</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.18974321929308</v>
+        <v>4.219317339594958</v>
       </c>
     </row>
     <row r="2066">
@@ -49063,22 +49063,22 @@
         <v>45528</v>
       </c>
       <c r="B2066" t="n">
-        <v>3.794486844016438</v>
+        <v>3.794486844016436</v>
       </c>
       <c r="C2066" t="n">
         <v>3.8233010345766</v>
       </c>
       <c r="D2066" t="n">
-        <v>-5.798686335098561</v>
+        <v>-5.712006187493121</v>
       </c>
       <c r="E2066" t="n">
-        <v>1.503470076223428</v>
+        <v>1.538142135265604</v>
       </c>
       <c r="F2066" t="n">
-        <v>0.5835714754020119</v>
+        <v>0.6328616759051419</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.173443919817807</v>
+        <v>4.203018040119685</v>
       </c>
     </row>
     <row r="2067">
@@ -49086,22 +49086,22 @@
         <v>45529</v>
       </c>
       <c r="B2067" t="n">
-        <v>3.79470509330767</v>
+        <v>3.794705093307668</v>
       </c>
       <c r="C2067" t="n">
         <v>3.825731984040646</v>
       </c>
       <c r="D2067" t="n">
-        <v>-5.615474671965466</v>
+        <v>-5.528794524360026</v>
       </c>
       <c r="E2067" t="n">
-        <v>1.579185690940712</v>
+        <v>1.613857749982888</v>
       </c>
       <c r="F2067" t="n">
-        <v>0.5835714754020119</v>
+        <v>0.6328616759051419</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.175874869281854</v>
+        <v>4.205448989583731</v>
       </c>
     </row>
     <row r="2068">
@@ -49109,22 +49109,22 @@
         <v>45530</v>
       </c>
       <c r="B2068" t="n">
-        <v>3.776846557863551</v>
+        <v>3.776846557863549</v>
       </c>
       <c r="C2068" t="n">
         <v>3.808676390120023</v>
       </c>
       <c r="D2068" t="n">
-        <v>-5.543753224951615</v>
+        <v>-5.457073077346175</v>
       </c>
       <c r="E2068" t="n">
-        <v>1.590818675825629</v>
+        <v>1.625490734867805</v>
       </c>
       <c r="F2068" t="n">
-        <v>0.6552929224158626</v>
+        <v>0.7045831229189925</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.201852143569541</v>
+        <v>4.231426263871419</v>
       </c>
     </row>
     <row r="2069">
@@ -49132,22 +49132,22 @@
         <v>45531</v>
       </c>
       <c r="B2069" t="n">
-        <v>3.723789705394113</v>
+        <v>3.723789705394109</v>
       </c>
       <c r="C2069" t="n">
         <v>3.755592136041195</v>
       </c>
       <c r="D2069" t="n">
-        <v>-5.521380199343909</v>
+        <v>-5.434700051738469</v>
       </c>
       <c r="E2069" t="n">
-        <v>1.546683631989883</v>
+        <v>1.581355691032059</v>
       </c>
       <c r="F2069" t="n">
-        <v>0.6665486735287641</v>
+        <v>0.7158388740318941</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.155521340158454</v>
+        <v>4.185095460460332</v>
       </c>
     </row>
     <row r="2070">
@@ -49155,22 +49155,22 @@
         <v>45532</v>
       </c>
       <c r="B2070" t="n">
-        <v>3.715607446456731</v>
+        <v>3.715607446456726</v>
       </c>
       <c r="C2070" t="n">
         <v>3.94079034092655</v>
       </c>
       <c r="D2070" t="n">
-        <v>-5.554396495254654</v>
+        <v>-5.467716347649214</v>
       </c>
       <c r="E2070" t="n">
-        <v>1.71867531851094</v>
+        <v>1.753347377553117</v>
       </c>
       <c r="F2070" t="n">
-        <v>0.5971112968620125</v>
+        <v>0.6464014973651424</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.299057119043757</v>
+        <v>4.328631239345635</v>
       </c>
     </row>
     <row r="2071">
@@ -49178,22 +49178,22 @@
         <v>45533</v>
       </c>
       <c r="B2071" t="n">
-        <v>3.713762536883682</v>
+        <v>3.713762536883674</v>
       </c>
       <c r="C2071" t="n">
         <v>3.932711566754799</v>
       </c>
       <c r="D2071" t="n">
-        <v>-5.542868859605045</v>
+        <v>-5.456188711999605</v>
       </c>
       <c r="E2071" t="n">
-        <v>1.715207598599033</v>
+        <v>1.749879657641209</v>
       </c>
       <c r="F2071" t="n">
-        <v>0.6561119550633749</v>
+        <v>0.7054021555665049</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.326378739792824</v>
+        <v>4.355952860094702</v>
       </c>
     </row>
     <row r="2072">
@@ -49201,22 +49201,22 @@
         <v>45534</v>
       </c>
       <c r="B2072" t="n">
-        <v>3.717150699236303</v>
+        <v>3.717150699236295</v>
       </c>
       <c r="C2072" t="n">
         <v>3.936379679276587</v>
       </c>
       <c r="D2072" t="n">
-        <v>-5.640210360947414</v>
+        <v>-5.553530213341974</v>
       </c>
       <c r="E2072" t="n">
-        <v>1.679939110583874</v>
+        <v>1.71461116962605</v>
       </c>
       <c r="F2072" t="n">
-        <v>0.6116917728978866</v>
+        <v>0.6609819734010165</v>
       </c>
       <c r="G2072" t="n">
-        <v>4.303394743015319</v>
+        <v>4.332968863317197</v>
       </c>
     </row>
     <row r="2073">
@@ -49224,22 +49224,22 @@
         <v>45535</v>
       </c>
       <c r="B2073" t="n">
-        <v>3.70520107942769</v>
+        <v>3.705201079427681</v>
       </c>
       <c r="C2073" t="n">
         <v>3.937630761469426</v>
       </c>
       <c r="D2073" t="n">
-        <v>-5.726066390287381</v>
+        <v>-5.63938624268194</v>
       </c>
       <c r="E2073" t="n">
-        <v>1.646847781040726</v>
+        <v>1.681519840082902</v>
       </c>
       <c r="F2073" t="n">
-        <v>0.5693157036717515</v>
+        <v>0.6186059041748815</v>
       </c>
       <c r="G2073" t="n">
-        <v>4.279220183672477</v>
+        <v>4.308794303974355</v>
       </c>
     </row>
     <row r="2074">
@@ -49247,22 +49247,22 @@
         <v>45536</v>
       </c>
       <c r="B2074" t="n">
-        <v>3.69183549961038</v>
+        <v>3.691835499610379</v>
       </c>
       <c r="C2074" t="n">
         <v>3.920049963289927</v>
       </c>
       <c r="D2074" t="n">
-        <v>-5.7349031877035</v>
+        <v>-5.64822304009806</v>
       </c>
       <c r="E2074" t="n">
-        <v>1.62573226389478</v>
+        <v>1.660404322936956</v>
       </c>
       <c r="F2074" t="n">
-        <v>0.5618735310304008</v>
+        <v>0.6111637315335308</v>
       </c>
       <c r="G2074" t="n">
-        <v>4.257174081908168</v>
+        <v>4.286748202210046</v>
       </c>
     </row>
     <row r="2075">
@@ -49270,22 +49270,22 @@
         <v>45537</v>
       </c>
       <c r="B2075" t="n">
-        <v>3.715544411667459</v>
+        <v>3.715544411667452</v>
       </c>
       <c r="C2075" t="n">
         <v>3.930214474334977</v>
       </c>
       <c r="D2075" t="n">
-        <v>-5.826285750268958</v>
+        <v>-5.739605602663518</v>
       </c>
       <c r="E2075" t="n">
-        <v>1.599343749913646</v>
+        <v>1.634015808955822</v>
       </c>
       <c r="F2075" t="n">
-        <v>0.5253086463110561</v>
+        <v>0.574598846814186</v>
       </c>
       <c r="G2075" t="n">
-        <v>4.245399662121611</v>
+        <v>4.274973782423489</v>
       </c>
     </row>
     <row r="2076">
@@ -49293,22 +49293,22 @@
         <v>45538</v>
       </c>
       <c r="B2076" t="n">
-        <v>3.673978374889197</v>
+        <v>3.673978374889188</v>
       </c>
       <c r="C2076" t="n">
         <v>4.032342732159245</v>
       </c>
       <c r="D2076" t="n">
-        <v>-5.814579032281952</v>
+        <v>-5.727898884676512</v>
       </c>
       <c r="E2076" t="n">
-        <v>1.706154694932716</v>
+        <v>1.740826753974892</v>
       </c>
       <c r="F2076" t="n">
-        <v>0.5370153642980625</v>
+        <v>0.5863055648011924</v>
       </c>
       <c r="G2076" t="n">
-        <v>4.354551950738083</v>
+        <v>4.384126071039961</v>
       </c>
     </row>
     <row r="2077">
@@ -49316,22 +49316,22 @@
         <v>45539</v>
       </c>
       <c r="B2077" t="n">
-        <v>3.682476099409572</v>
+        <v>3.682476099409563</v>
       </c>
       <c r="C2077" t="n">
         <v>4.03537507089065</v>
       </c>
       <c r="D2077" t="n">
-        <v>-5.885491106024229</v>
+        <v>-5.798810958418789</v>
       </c>
       <c r="E2077" t="n">
-        <v>1.68082220416721</v>
+        <v>1.715494263209386</v>
       </c>
       <c r="F2077" t="n">
-        <v>0.5370153642980625</v>
+        <v>0.5863055648011924</v>
       </c>
       <c r="G2077" t="n">
-        <v>4.357584289469488</v>
+        <v>4.387158409771366</v>
       </c>
     </row>
     <row r="2078">
@@ -49339,22 +49339,22 @@
         <v>45540</v>
       </c>
       <c r="B2078" t="n">
-        <v>3.67289517745257</v>
+        <v>3.672895177452569</v>
       </c>
       <c r="C2078" t="n">
         <v>4.036193896622915</v>
       </c>
       <c r="D2078" t="n">
-        <v>-5.895807204190581</v>
+        <v>-5.809127056585141</v>
       </c>
       <c r="E2078" t="n">
-        <v>1.677514590632934</v>
+        <v>1.71218664967511</v>
       </c>
       <c r="F2078" t="n">
-        <v>0.5370153642980625</v>
+        <v>0.5863055648011924</v>
       </c>
       <c r="G2078" t="n">
-        <v>4.358403115201752</v>
+        <v>4.38797723550363</v>
       </c>
     </row>
     <row r="2079">
@@ -49362,22 +49362,22 @@
         <v>45541</v>
       </c>
       <c r="B2079" t="n">
-        <v>3.623960959762292</v>
+        <v>3.623960959762283</v>
       </c>
       <c r="C2079" t="n">
         <v>4.035372563535004</v>
       </c>
       <c r="D2079" t="n">
-        <v>-5.895713236173209</v>
+        <v>-5.809033088567769</v>
       </c>
       <c r="E2079" t="n">
-        <v>1.676730844751973</v>
+        <v>1.711402903794149</v>
       </c>
       <c r="F2079" t="n">
-        <v>0.5373852256453805</v>
+        <v>0.5866754261485104</v>
       </c>
       <c r="G2079" t="n">
-        <v>4.357803698922233</v>
+        <v>4.387377819224111</v>
       </c>
     </row>
     <row r="2080">
@@ -49385,22 +49385,22 @@
         <v>45542</v>
       </c>
       <c r="B2080" t="n">
-        <v>3.800870306884084</v>
+        <v>3.800870306884075</v>
       </c>
       <c r="C2080" t="n">
         <v>4.029604549479358</v>
       </c>
       <c r="D2080" t="n">
-        <v>-6.039314400196594</v>
+        <v>-5.952634252591154</v>
       </c>
       <c r="E2080" t="n">
-        <v>1.613522365086972</v>
+        <v>1.648194424129148</v>
       </c>
       <c r="F2080" t="n">
-        <v>0.5373852256453805</v>
+        <v>0.5866754261485104</v>
       </c>
       <c r="G2080" t="n">
-        <v>4.352035684866586</v>
+        <v>4.381609805168464</v>
       </c>
     </row>
     <row r="2081">
@@ -49408,22 +49408,22 @@
         <v>45543</v>
       </c>
       <c r="B2081" t="n">
-        <v>3.671015692129648</v>
+        <v>3.671015692129645</v>
       </c>
       <c r="C2081" t="n">
         <v>4.029604549479358</v>
       </c>
       <c r="D2081" t="n">
-        <v>-6.038365977078556</v>
+        <v>-5.951685829473115</v>
       </c>
       <c r="E2081" t="n">
-        <v>1.613901734334187</v>
+        <v>1.648573793376364</v>
       </c>
       <c r="F2081" t="n">
-        <v>0.5373852256453805</v>
+        <v>0.5866754261485104</v>
       </c>
       <c r="G2081" t="n">
-        <v>4.352035684866586</v>
+        <v>4.381609805168464</v>
       </c>
     </row>
     <row r="2082">
@@ -49431,22 +49431,22 @@
         <v>45544</v>
       </c>
       <c r="B2082" t="n">
-        <v>3.904173816052351</v>
+        <v>3.904173816052348</v>
       </c>
       <c r="C2082" t="n">
         <v>4.04233215746045</v>
       </c>
       <c r="D2082" t="n">
-        <v>-6.138635795037576</v>
+        <v>-6.051955647432136</v>
       </c>
       <c r="E2082" t="n">
-        <v>1.586521415131672</v>
+        <v>1.621193474173848</v>
       </c>
       <c r="F2082" t="n">
-        <v>0.5373852256453805</v>
+        <v>0.5866754261485104</v>
       </c>
       <c r="G2082" t="n">
-        <v>4.364763292847678</v>
+        <v>4.394337413149557</v>
       </c>
     </row>
     <row r="2083">
@@ -49454,22 +49454,22 @@
         <v>45545</v>
       </c>
       <c r="B2083" t="n">
-        <v>3.740179607813495</v>
+        <v>3.740179607813492</v>
       </c>
       <c r="C2083" t="n">
         <v>4.044278155884838</v>
       </c>
       <c r="D2083" t="n">
-        <v>-6.132643548248764</v>
+        <v>-6.045963400643324</v>
       </c>
       <c r="E2083" t="n">
-        <v>1.590864312271584</v>
+        <v>1.62553637131376</v>
       </c>
       <c r="F2083" t="n">
-        <v>0.5373852256453805</v>
+        <v>0.5866754261485104</v>
       </c>
       <c r="G2083" t="n">
-        <v>4.366709291272066</v>
+        <v>4.396283411573944</v>
       </c>
     </row>
     <row r="2084">
@@ -49477,22 +49477,22 @@
         <v>45546</v>
       </c>
       <c r="B2084" t="n">
-        <v>3.765050796537944</v>
+        <v>3.765050796537942</v>
       </c>
       <c r="C2084" t="n">
         <v>4.037932291902607</v>
       </c>
       <c r="D2084" t="n">
-        <v>-6.044085587117997</v>
+        <v>-5.957405439512557</v>
       </c>
       <c r="E2084" t="n">
-        <v>1.61994163274166</v>
+        <v>1.654613691783836</v>
       </c>
       <c r="F2084" t="n">
-        <v>0.5373852256453805</v>
+        <v>0.5866754261485104</v>
       </c>
       <c r="G2084" t="n">
-        <v>4.360363427289835</v>
+        <v>4.389937547591713</v>
       </c>
     </row>
     <row r="2085">
@@ -49500,22 +49500,22 @@
         <v>45547</v>
       </c>
       <c r="B2085" t="n">
-        <v>3.758409170771816</v>
+        <v>3.758409170771814</v>
       </c>
       <c r="C2085" t="n">
         <v>4.037240969341602</v>
       </c>
       <c r="D2085" t="n">
-        <v>-6.026326509614923</v>
+        <v>-5.939646362009483</v>
       </c>
       <c r="E2085" t="n">
-        <v>1.626353941181885</v>
+        <v>1.661026000224061</v>
       </c>
       <c r="F2085" t="n">
-        <v>0.5373852256453805</v>
+        <v>0.5866754261485104</v>
       </c>
       <c r="G2085" t="n">
-        <v>4.359672104728831</v>
+        <v>4.389246225030709</v>
       </c>
     </row>
     <row r="2086">
@@ -49523,22 +49523,22 @@
         <v>45548</v>
       </c>
       <c r="B2086" t="n">
-        <v>3.801340597109721</v>
+        <v>3.80134059710972</v>
       </c>
       <c r="C2086" t="n">
         <v>4.050023155250189</v>
       </c>
       <c r="D2086" t="n">
-        <v>-5.926696358565855</v>
+        <v>-5.840016210960415</v>
       </c>
       <c r="E2086" t="n">
-        <v>1.678988187510099</v>
+        <v>1.713660246552275</v>
       </c>
       <c r="F2086" t="n">
-        <v>0.637015376694448</v>
+        <v>0.6863055771975779</v>
       </c>
       <c r="G2086" t="n">
-        <v>4.432232381266858</v>
+        <v>4.461806501568736</v>
       </c>
     </row>
     <row r="2087">
@@ -49546,22 +49546,22 @@
         <v>45549</v>
       </c>
       <c r="B2087" t="n">
-        <v>3.798465546843996</v>
+        <v>3.798465546843994</v>
       </c>
       <c r="C2087" t="n">
         <v>4.239177420748915</v>
       </c>
       <c r="D2087" t="n">
-        <v>-5.976095867254866</v>
+        <v>-5.889415719649426</v>
       </c>
       <c r="E2087" t="n">
-        <v>1.848382649533221</v>
+        <v>1.883054708575397</v>
       </c>
       <c r="F2087" t="n">
-        <v>0.6472742101261927</v>
+        <v>0.6965644106293226</v>
       </c>
       <c r="G2087" t="n">
-        <v>4.627541946824631</v>
+        <v>4.657116067126509</v>
       </c>
     </row>
     <row r="2088">
@@ -49569,22 +49569,22 @@
         <v>45550</v>
       </c>
       <c r="B2088" t="n">
-        <v>3.77218650835186</v>
+        <v>3.772186508351855</v>
       </c>
       <c r="C2088" t="n">
         <v>4.226366093851778</v>
       </c>
       <c r="D2088" t="n">
-        <v>-5.76941139361249</v>
+        <v>-5.68273124600705</v>
       </c>
       <c r="E2088" t="n">
-        <v>1.918245112093034</v>
+        <v>1.95291717113521</v>
       </c>
       <c r="F2088" t="n">
-        <v>0.8539586837685683</v>
+        <v>0.9032488842716982</v>
       </c>
       <c r="G2088" t="n">
-        <v>4.738741304112919</v>
+        <v>4.768315424414797</v>
       </c>
     </row>
     <row r="2089">
@@ -49592,22 +49592,22 @@
         <v>45551</v>
       </c>
       <c r="B2089" t="n">
-        <v>3.76339283855127</v>
+        <v>3.763392838551265</v>
       </c>
       <c r="C2089" t="n">
         <v>4.228367607505882</v>
       </c>
       <c r="D2089" t="n">
-        <v>-5.803568288610016</v>
+        <v>-5.716888141004576</v>
       </c>
       <c r="E2089" t="n">
-        <v>1.906583867748128</v>
+        <v>1.941255926790304</v>
       </c>
       <c r="F2089" t="n">
-        <v>0.7703749142277558</v>
+        <v>0.8196651147308858</v>
       </c>
       <c r="G2089" t="n">
-        <v>4.690592556042536</v>
+        <v>4.720166676344414</v>
       </c>
     </row>
     <row r="2090">
@@ -49615,22 +49615,22 @@
         <v>45552</v>
       </c>
       <c r="B2090" t="n">
-        <v>3.805590565041111</v>
+        <v>3.805590565041106</v>
       </c>
       <c r="C2090" t="n">
         <v>4.58186472149555</v>
       </c>
       <c r="D2090" t="n">
-        <v>-5.71097880954856</v>
+        <v>-5.624298661943119</v>
       </c>
       <c r="E2090" t="n">
-        <v>2.297116773362378</v>
+        <v>2.331788832404554</v>
       </c>
       <c r="F2090" t="n">
-        <v>0.7703749142277558</v>
+        <v>0.8196651147308858</v>
       </c>
       <c r="G2090" t="n">
-        <v>5.044089670032204</v>
+        <v>5.073663790334082</v>
       </c>
     </row>
     <row r="2091">
@@ -49638,22 +49638,22 @@
         <v>45553</v>
       </c>
       <c r="B2091" t="n">
-        <v>3.832164354497403</v>
+        <v>3.832164354497396</v>
       </c>
       <c r="C2091" t="n">
         <v>4.586427833062654</v>
       </c>
       <c r="D2091" t="n">
-        <v>-5.784139413321705</v>
+        <v>-5.697459265716264</v>
       </c>
       <c r="E2091" t="n">
-        <v>2.272415643420224</v>
+        <v>2.3070877024624</v>
       </c>
       <c r="F2091" t="n">
-        <v>0.7423537141935128</v>
+        <v>0.7916439146966427</v>
       </c>
       <c r="G2091" t="n">
-        <v>5.031840061578762</v>
+        <v>5.06141418188064</v>
       </c>
     </row>
     <row r="2092">
@@ -49661,22 +49661,22 @@
         <v>45554</v>
       </c>
       <c r="B2092" t="n">
-        <v>3.858310890492296</v>
+        <v>3.858310890492286</v>
       </c>
       <c r="C2092" t="n">
         <v>4.636257774386181</v>
       </c>
       <c r="D2092" t="n">
-        <v>-5.731923103525363</v>
+        <v>-5.645242955919922</v>
       </c>
       <c r="E2092" t="n">
-        <v>2.343132108662288</v>
+        <v>2.377804167704464</v>
       </c>
       <c r="F2092" t="n">
-        <v>0.7423537141935128</v>
+        <v>0.7916439146966427</v>
       </c>
       <c r="G2092" t="n">
-        <v>5.081670002902289</v>
+        <v>5.111244123204167</v>
       </c>
     </row>
     <row r="2093">
@@ -49684,22 +49684,22 @@
         <v>45555</v>
       </c>
       <c r="B2093" t="n">
-        <v>3.844935596436478</v>
+        <v>3.844935596436468</v>
       </c>
       <c r="C2093" t="n">
         <v>4.645071744596192</v>
       </c>
       <c r="D2093" t="n">
-        <v>-5.679415776014868</v>
+        <v>-5.592735628409428</v>
       </c>
       <c r="E2093" t="n">
-        <v>2.372949009876497</v>
+        <v>2.407621068918673</v>
       </c>
       <c r="F2093" t="n">
-        <v>0.7948610417040077</v>
+        <v>0.8441512422071377</v>
       </c>
       <c r="G2093" t="n">
-        <v>5.121988369618597</v>
+        <v>5.151562489920475</v>
       </c>
     </row>
     <row r="2094">
@@ -49707,22 +49707,22 @@
         <v>45556</v>
       </c>
       <c r="B2094" t="n">
-        <v>3.848376866039487</v>
+        <v>3.848376866039477</v>
       </c>
       <c r="C2094" t="n">
         <v>4.640709328635389</v>
       </c>
       <c r="D2094" t="n">
-        <v>-5.694171100215009</v>
+        <v>-5.607490952609568</v>
       </c>
       <c r="E2094" t="n">
-        <v>2.362684464235638</v>
+        <v>2.397356523277814</v>
       </c>
       <c r="F2094" t="n">
-        <v>0.7948610417040077</v>
+        <v>0.8441512422071377</v>
       </c>
       <c r="G2094" t="n">
-        <v>5.117625953657794</v>
+        <v>5.147200073959672</v>
       </c>
     </row>
     <row r="2095">
@@ -49730,22 +49730,22 @@
         <v>45557</v>
       </c>
       <c r="B2095" t="n">
-        <v>3.868153115524482</v>
+        <v>3.868153115524471</v>
       </c>
       <c r="C2095" t="n">
         <v>4.631633832051669</v>
       </c>
       <c r="D2095" t="n">
-        <v>-5.644706476845097</v>
+        <v>-5.558026329239657</v>
       </c>
       <c r="E2095" t="n">
-        <v>2.373394816999883</v>
+        <v>2.408066876042059</v>
       </c>
       <c r="F2095" t="n">
-        <v>0.8443256650739194</v>
+        <v>0.8936158655770493</v>
       </c>
       <c r="G2095" t="n">
-        <v>5.138229231096021</v>
+        <v>5.167803351397899</v>
       </c>
     </row>
     <row r="2096">
@@ -49753,22 +49753,22 @@
         <v>45558</v>
       </c>
       <c r="B2096" t="n">
-        <v>3.849040239867955</v>
+        <v>3.849040239867945</v>
       </c>
       <c r="C2096" t="n">
         <v>4.628041499766604</v>
       </c>
       <c r="D2096" t="n">
-        <v>-5.481598484691482</v>
+        <v>-5.394918337086041</v>
       </c>
       <c r="E2096" t="n">
-        <v>2.435045681576263</v>
+        <v>2.469717740618439</v>
       </c>
       <c r="F2096" t="n">
-        <v>1.007433657227535</v>
+        <v>1.056723857730665</v>
       </c>
       <c r="G2096" t="n">
-        <v>5.232501694103124</v>
+        <v>5.262075814405002</v>
       </c>
     </row>
     <row r="2097">
@@ -49776,22 +49776,22 @@
         <v>45559</v>
       </c>
       <c r="B2097" t="n">
-        <v>3.870204928232971</v>
+        <v>3.870204928232968</v>
       </c>
       <c r="C2097" t="n">
         <v>4.637088536457732</v>
       </c>
       <c r="D2097" t="n">
-        <v>-5.460955393890254</v>
+        <v>-5.374275246284814</v>
       </c>
       <c r="E2097" t="n">
-        <v>2.452349954587882</v>
+        <v>2.487022013630058</v>
       </c>
       <c r="F2097" t="n">
-        <v>1.007433657227535</v>
+        <v>1.056723857730665</v>
       </c>
       <c r="G2097" t="n">
-        <v>5.241548730794253</v>
+        <v>5.271122851096131</v>
       </c>
     </row>
     <row r="2098">
@@ -49799,22 +49799,22 @@
         <v>45560</v>
       </c>
       <c r="B2098" t="n">
-        <v>3.855534437179674</v>
+        <v>3.855534437179672</v>
       </c>
       <c r="C2098" t="n">
         <v>4.637946001443853</v>
       </c>
       <c r="D2098" t="n">
-        <v>-5.523663310364812</v>
+        <v>-5.436983162759372</v>
       </c>
       <c r="E2098" t="n">
-        <v>2.428124252984181</v>
+        <v>2.462796312026357</v>
       </c>
       <c r="F2098" t="n">
-        <v>0.9447257407529769</v>
+        <v>0.9940159412561069</v>
       </c>
       <c r="G2098" t="n">
-        <v>5.20478144589564</v>
+        <v>5.234355566197518</v>
       </c>
     </row>
     <row r="2099">
@@ -49822,22 +49822,22 @@
         <v>45561</v>
       </c>
       <c r="B2099" t="n">
-        <v>3.884687848967721</v>
+        <v>3.884687848967719</v>
       </c>
       <c r="C2099" t="n">
         <v>4.600855418234206</v>
       </c>
       <c r="D2099" t="n">
-        <v>-5.475655186521119</v>
+        <v>-5.388975038915679</v>
       </c>
       <c r="E2099" t="n">
-        <v>2.41023691931201</v>
+        <v>2.444908978354186</v>
       </c>
       <c r="F2099" t="n">
-        <v>0.9447257407529769</v>
+        <v>0.9940159412561069</v>
       </c>
       <c r="G2099" t="n">
-        <v>5.167690862685992</v>
+        <v>5.19726498298787</v>
       </c>
     </row>
     <row r="2100">
@@ -49845,22 +49845,22 @@
         <v>45562</v>
       </c>
       <c r="B2100" t="n">
-        <v>3.895362357018612</v>
+        <v>3.895362357018607</v>
       </c>
       <c r="C2100" t="n">
         <v>4.604787671792156</v>
       </c>
       <c r="D2100" t="n">
-        <v>-5.325537131299222</v>
+        <v>-5.238856983693782</v>
       </c>
       <c r="E2100" t="n">
-        <v>2.474216394958719</v>
+        <v>2.508888454000895</v>
       </c>
       <c r="F2100" t="n">
-        <v>1.094843795974874</v>
+        <v>1.144133996478004</v>
       </c>
       <c r="G2100" t="n">
-        <v>5.261693949377081</v>
+        <v>5.291268069678958</v>
       </c>
     </row>
     <row r="2101">
@@ -49868,22 +49868,22 @@
         <v>45563</v>
       </c>
       <c r="B2101" t="n">
-        <v>3.891610981075135</v>
+        <v>3.89161098107513</v>
       </c>
       <c r="C2101" t="n">
         <v>4.599686764399193</v>
       </c>
       <c r="D2101" t="n">
-        <v>-5.224389299431142</v>
+        <v>-5.1471442639445</v>
       </c>
       <c r="E2101" t="n">
-        <v>2.509574620312988</v>
+        <v>2.540472634507645</v>
       </c>
       <c r="F2101" t="n">
-        <v>1.094843795974874</v>
+        <v>1.144133996478004</v>
       </c>
       <c r="G2101" t="n">
-        <v>5.256593041984118</v>
+        <v>5.286167162285995</v>
       </c>
     </row>
     <row r="2102">
@@ -49891,22 +49891,22 @@
         <v>45564</v>
       </c>
       <c r="B2102" t="n">
-        <v>3.872432493435445</v>
+        <v>3.872432493435436</v>
       </c>
       <c r="C2102" t="n">
         <v>4.595040673788288</v>
       </c>
       <c r="D2102" t="n">
-        <v>-5.106215921413215</v>
+        <v>-5.028970885926572</v>
       </c>
       <c r="E2102" t="n">
-        <v>2.552197880909254</v>
+        <v>2.583095895103912</v>
       </c>
       <c r="F2102" t="n">
-        <v>1.213017173992801</v>
+        <v>1.262307374495931</v>
       </c>
       <c r="G2102" t="n">
-        <v>5.322850978183969</v>
+        <v>5.352425098485847</v>
       </c>
     </row>
     <row r="2103">
@@ -49914,22 +49914,22 @@
         <v>45565</v>
       </c>
       <c r="B2103" t="n">
-        <v>3.859571723917734</v>
+        <v>3.859571723917725</v>
       </c>
       <c r="C2103" t="n">
         <v>4.624129266651315</v>
       </c>
       <c r="D2103" t="n">
-        <v>-5.017368804553717</v>
+        <v>-4.940123769067075</v>
       </c>
       <c r="E2103" t="n">
-        <v>2.61682532051608</v>
+        <v>2.647723334710737</v>
       </c>
       <c r="F2103" t="n">
-        <v>1.301864290852299</v>
+        <v>1.351154491355429</v>
       </c>
       <c r="G2103" t="n">
-        <v>5.405247841162694</v>
+        <v>5.434821961464573</v>
       </c>
     </row>
     <row r="2104">
@@ -49937,22 +49937,22 @@
         <v>45566</v>
       </c>
       <c r="B2104" t="n">
-        <v>3.82800627401364</v>
+        <v>3.828006274013631</v>
       </c>
       <c r="C2104" t="n">
         <v>4.617689489662492</v>
       </c>
       <c r="D2104" t="n">
-        <v>-4.990319766860464</v>
+        <v>-4.913074731373821</v>
       </c>
       <c r="E2104" t="n">
-        <v>2.621205158604559</v>
+        <v>2.652103172799216</v>
       </c>
       <c r="F2104" t="n">
-        <v>1.328913328545553</v>
+        <v>1.378203529048683</v>
       </c>
       <c r="G2104" t="n">
-        <v>5.415037486789824</v>
+        <v>5.444611607091702</v>
       </c>
     </row>
     <row r="2105">
@@ -49960,22 +49960,22 @@
         <v>45567</v>
       </c>
       <c r="B2105" t="n">
-        <v>3.82398744526377</v>
+        <v>3.823987445263768</v>
       </c>
       <c r="C2105" t="n">
         <v>4.617689489662492</v>
       </c>
       <c r="D2105" t="n">
-        <v>-4.996353047047234</v>
+        <v>-4.919108011560591</v>
       </c>
       <c r="E2105" t="n">
-        <v>2.618791846529851</v>
+        <v>2.649689860724508</v>
       </c>
       <c r="F2105" t="n">
-        <v>1.328913328545553</v>
+        <v>1.378203529048683</v>
       </c>
       <c r="G2105" t="n">
-        <v>5.415037486789824</v>
+        <v>5.444611607091702</v>
       </c>
     </row>
     <row r="2106">
@@ -49983,22 +49983,22 @@
         <v>45568</v>
       </c>
       <c r="B2106" t="n">
-        <v>3.815657203170844</v>
+        <v>3.815657203170835</v>
       </c>
       <c r="C2106" t="n">
         <v>4.621327656804905</v>
       </c>
       <c r="D2106" t="n">
-        <v>-5.048204822620395</v>
+        <v>-4.938150375659427</v>
       </c>
       <c r="E2106" t="n">
-        <v>2.601689303442999</v>
+        <v>2.645711082227386</v>
       </c>
       <c r="F2106" t="n">
-        <v>1.277061552972391</v>
+        <v>1.359161164949847</v>
       </c>
       <c r="G2106" t="n">
-        <v>5.38756458858834</v>
+        <v>5.436824355774813</v>
       </c>
     </row>
     <row r="2107">
@@ -50006,22 +50006,22 @@
         <v>45569</v>
       </c>
       <c r="B2107" t="n">
-        <v>3.830586986431407</v>
+        <v>3.830586986431405</v>
       </c>
       <c r="C2107" t="n">
         <v>4.584819403988742</v>
       </c>
       <c r="D2107" t="n">
-        <v>-5.075262268752222</v>
+        <v>-4.965207821791254</v>
       </c>
       <c r="E2107" t="n">
-        <v>2.554358072174105</v>
+        <v>2.598379850958492</v>
       </c>
       <c r="F2107" t="n">
-        <v>1.277061552972391</v>
+        <v>1.359161164949847</v>
       </c>
       <c r="G2107" t="n">
-        <v>5.351056335772176</v>
+        <v>5.40031610295865</v>
       </c>
     </row>
     <row r="2108">
@@ -50029,22 +50029,45 @@
         <v>45570</v>
       </c>
       <c r="B2108" t="n">
-        <v>3.637500569392438</v>
+        <v>3.830856457232448</v>
       </c>
       <c r="C2108" t="n">
         <v>4.586227353735933</v>
       </c>
       <c r="D2108" t="n">
-        <v>-5.148543620606097</v>
+        <v>-5.068384731369198</v>
       </c>
       <c r="E2108" t="n">
-        <v>2.526453481179746</v>
+        <v>2.558517036874506</v>
       </c>
       <c r="F2108" t="n">
-        <v>1.26315013084118</v>
+        <v>1.307920875567864</v>
       </c>
       <c r="G2108" t="n">
-        <v>5.344117432240641</v>
+        <v>5.370979879076652</v>
+      </c>
+    </row>
+    <row r="2109">
+      <c r="A2109" s="2" t="n">
+        <v>45571</v>
+      </c>
+      <c r="B2109" t="n">
+        <v>3.637552659121755</v>
+      </c>
+      <c r="C2109" t="n">
+        <v>4.546630944171956</v>
+      </c>
+      <c r="D2109" t="n">
+        <v>-5.068384731369198</v>
+      </c>
+      <c r="E2109" t="n">
+        <v>2.558517036874506</v>
+      </c>
+      <c r="F2109" t="n">
+        <v>1.307920875567864</v>
+      </c>
+      <c r="G2109" t="n">
+        <v>4.539694741158324</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20241006.xlsx
+++ b/tame_output/ON/bt/strategyON_20241006.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>49.4%</t>
+          <t>53.8%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>67.1%</t>
+          <t>66.6%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>66.1%</t>
+          <t>65.2%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,12 +666,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.8%</t>
+          <t>-19.3%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.8%</t>
+          <t>-15.3%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.0%</t>
+          <t>-11.5%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>35.7%</t>
+          <t>50.4%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>100.4%</t>
+          <t>102.3%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>43.3%</t>
+          <t>43.2%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>45.8%</t>
+          <t>45.7%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -824,12 +824,12 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-9.7%</t>
+          <t>-9.1%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-2.8%</t>
+          <t>-2.4%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-8.1%</t>
+          <t>-7.8%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>84.6%</t>
+          <t>85.9%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-7.8%</t>
+          <t>-7.9%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>143.0%</t>
+          <t>148.4%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-78.1%</t>
+          <t>-78.0%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>106.9%</t>
+          <t>107.0%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.2%</t>
+          <t>123.1%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>89.6%</t>
+          <t>89.9%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-37.7%</t>
+          <t>-37.8%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>21.6%</t>
+          <t>21.7%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-74.6%</t>
+          <t>-74.3%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>88.7%</t>
+          <t>88.8%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>419.0%</t>
+          <t>420.5%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-6.2%</t>
+          <t>-6.4%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-668.4%</t>
+          <t>-665.2%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>30.4%</t>
+          <t>30.7%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>59.3%</t>
+          <t>59.4%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>56.0%</t>
+          <t>56.1%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-9.6%</t>
+          <t>-9.7%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>-3.9%</t>
+          <t>-3.8%</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -1160,7 +1160,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-4.3%</t>
+          <t>-4.1%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>14.2%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-120.4%</t>
+          <t>-119.1%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-2.3%</t>
+          <t>-3.5%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>74.3%</t>
+          <t>74.2%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.8%</t>
+          <t>10.7%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-24.0%</t>
+          <t>-24.1%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>3.8%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>52.1%</t>
+          <t>43.1%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-365.4%</t>
+          <t>-166.3%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-93.2%</t>
+          <t>-100.3%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>57.2%</t>
+          <t>68.8%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>67.1%</t>
+          <t>65.1%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>80.4%</t>
+          <t>76.4%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>14.0%</t>
+          <t>14.2%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-26.5%</t>
+          <t>-24.0%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>47.2%</t>
+          <t>59.5%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>54.2%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-14.8%</t>
+          <t>-15.0%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>36.7%</t>
+          <t>36.6%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>7.9%</t>
+          <t>13.4%</t>
         </is>
       </c>
     </row>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191734</v>
+        <v>3.302618194191735</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44463,7 +44463,7 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108635</v>
+        <v>3.305023265108636</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097817</v>
+        <v>3.341378723097818</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094112</v>
+        <v>3.374439043094114</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.40596051119928</v>
+        <v>3.405960511199281</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969588</v>
+        <v>3.42463335496959</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.41997943392308</v>
+        <v>3.419979433923083</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297743</v>
+        <v>3.458100091297745</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317611</v>
+        <v>3.447750501317614</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737166</v>
+        <v>3.503515506737167</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341309</v>
+        <v>3.50317028234131</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937499</v>
+        <v>3.492448711937498</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502790399141702</v>
+        <v>3.502790399141701</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496851904729891</v>
+        <v>3.49685190472989</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490059241608601</v>
+        <v>3.4900592416086</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764398</v>
+        <v>3.480692492764397</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390587</v>
+        <v>3.493716014390586</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297398</v>
+        <v>3.492101641297397</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322543</v>
+        <v>3.573674025322542</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600038265158923</v>
+        <v>3.600038265158922</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.69157173394072</v>
+        <v>3.691571733940719</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.67684154977058</v>
+        <v>3.676841549770579</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615284</v>
+        <v>3.685161381615283</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812104</v>
+        <v>3.684843823812103</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
@@ -45176,7 +45176,7 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311949</v>
+        <v>3.78468452131195</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
@@ -45199,7 +45199,7 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800829354097242</v>
+        <v>3.800829354097244</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
@@ -45222,7 +45222,7 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017769</v>
+        <v>3.789311112017772</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
@@ -45245,7 +45245,7 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833252747839722</v>
+        <v>3.833252747839725</v>
       </c>
       <c r="C1900" t="n">
         <v>3.151116350215413</v>
@@ -45268,7 +45268,7 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839374447388725</v>
+        <v>3.839374447388729</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
@@ -45291,7 +45291,7 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856161751626471</v>
+        <v>3.856161751626475</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
@@ -45314,7 +45314,7 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787330429291812</v>
+        <v>3.787330429291814</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
@@ -45337,7 +45337,7 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801637122785786</v>
+        <v>3.801637122785788</v>
       </c>
       <c r="C1904" t="n">
         <v>3.155859013848905</v>
@@ -45360,7 +45360,7 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763182248390427</v>
+        <v>3.763182248390429</v>
       </c>
       <c r="C1905" t="n">
         <v>3.057119799856059</v>
@@ -45383,7 +45383,7 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105952</v>
+        <v>3.784718794105954</v>
       </c>
       <c r="C1906" t="n">
         <v>3.059934860543696</v>
@@ -45406,7 +45406,7 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960985</v>
+        <v>3.753882571960987</v>
       </c>
       <c r="C1907" t="n">
         <v>3.072841201767355</v>
@@ -45429,7 +45429,7 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607644</v>
+        <v>3.692931855607646</v>
       </c>
       <c r="C1908" t="n">
         <v>2.944865272168136</v>
@@ -45452,7 +45452,7 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770422583987902</v>
+        <v>3.770422583987903</v>
       </c>
       <c r="C1909" t="n">
         <v>2.993409614045222</v>
@@ -45475,7 +45475,7 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710811</v>
+        <v>3.760333686710813</v>
       </c>
       <c r="C1910" t="n">
         <v>2.876788805406815</v>
@@ -45498,7 +45498,7 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409204</v>
+        <v>3.723566229409205</v>
       </c>
       <c r="C1911" t="n">
         <v>2.868074819153337</v>
@@ -45521,7 +45521,7 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729969716098108</v>
+        <v>3.72996971609811</v>
       </c>
       <c r="C1912" t="n">
         <v>2.861114207058244</v>
@@ -45544,7 +45544,7 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493419</v>
+        <v>3.782922533493421</v>
       </c>
       <c r="C1913" t="n">
         <v>2.875576561439387</v>
@@ -45567,7 +45567,7 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722817</v>
+        <v>3.828551486722819</v>
       </c>
       <c r="C1914" t="n">
         <v>2.870108681898582</v>
@@ -45590,7 +45590,7 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792046</v>
+        <v>3.828052928792047</v>
       </c>
       <c r="C1915" t="n">
         <v>2.867606775909159</v>
@@ -45613,7 +45613,7 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919905</v>
+        <v>3.812453678919907</v>
       </c>
       <c r="C1916" t="n">
         <v>2.875307754146484</v>
@@ -45636,7 +45636,7 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.74832840831809</v>
+        <v>3.748328408318092</v>
       </c>
       <c r="C1917" t="n">
         <v>2.871088462493535</v>
@@ -45659,7 +45659,7 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057525</v>
+        <v>3.824311233057527</v>
       </c>
       <c r="C1918" t="n">
         <v>2.873212776413551</v>
@@ -45682,7 +45682,7 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279184</v>
+        <v>3.826354974279186</v>
       </c>
       <c r="C1919" t="n">
         <v>2.865954851397253</v>
@@ -45705,7 +45705,7 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011497</v>
+        <v>3.835957987011499</v>
       </c>
       <c r="C1920" t="n">
         <v>2.869553974917902</v>
@@ -45728,7 +45728,7 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392986</v>
+        <v>3.780933911392988</v>
       </c>
       <c r="C1921" t="n">
         <v>2.882881480972455</v>
@@ -45751,7 +45751,7 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632781</v>
+        <v>3.773765222632782</v>
       </c>
       <c r="C1922" t="n">
         <v>2.881901958588752</v>
@@ -45774,7 +45774,7 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883073</v>
+        <v>3.764617879883074</v>
       </c>
       <c r="C1923" t="n">
         <v>2.88659675964307</v>
@@ -45797,7 +45797,7 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074782</v>
+        <v>3.798814771074784</v>
       </c>
       <c r="C1924" t="n">
         <v>2.867791018426865</v>
@@ -45820,7 +45820,7 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242293</v>
+        <v>3.797694884242294</v>
       </c>
       <c r="C1925" t="n">
         <v>2.869534095051743</v>
@@ -45843,7 +45843,7 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821593509367682</v>
+        <v>3.821593509367686</v>
       </c>
       <c r="C1926" t="n">
         <v>2.873463408886563</v>
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879962</v>
+        <v>3.822326997879966</v>
       </c>
       <c r="C1927" t="n">
         <v>2.874141992803903</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.655499061143624</v>
+        <v>-4.742179208749064</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.011585944032705</v>
+        <v>0.9769138849905292</v>
       </c>
       <c r="F1927" t="n">
-        <v>0.2557333052914421</v>
+        <v>0.2064431047883115</v>
       </c>
       <c r="G1927" t="n">
-        <v>3.027581975978769</v>
+        <v>2.99800785567689</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502333</v>
+        <v>3.84861662650234</v>
       </c>
       <c r="C1928" t="n">
         <v>2.871140064023896</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.532024789830606</v>
+        <v>-4.618704937436046</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.057973723777906</v>
+        <v>1.02330166473573</v>
       </c>
       <c r="F1928" t="n">
-        <v>0.2557333052914421</v>
+        <v>0.2064431047883115</v>
       </c>
       <c r="G1928" t="n">
-        <v>3.024580047198762</v>
+        <v>2.995005926896884</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675935</v>
+        <v>3.81866895167594</v>
       </c>
       <c r="C1929" t="n">
         <v>2.872719101034511</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.47408895783239</v>
+        <v>-4.560769105437831</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.082727093587806</v>
+        <v>1.04805503454563</v>
       </c>
       <c r="F1929" t="n">
-        <v>0.2812951799741914</v>
+        <v>0.2320049794710608</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.041496209019026</v>
+        <v>3.011922088717147</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539947</v>
+        <v>3.843274527539952</v>
       </c>
       <c r="C1930" t="n">
         <v>2.888613283836334</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.341221268769113</v>
+        <v>-4.427901416374553</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.151768352014941</v>
+        <v>1.117096292972765</v>
       </c>
       <c r="F1930" t="n">
-        <v>0.2812951799741914</v>
+        <v>0.2320049794710608</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.057390391820849</v>
+        <v>3.02781627151897</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496259</v>
+        <v>3.845047386496263</v>
       </c>
       <c r="C1931" t="n">
         <v>2.889759128276636</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.221048185404614</v>
+        <v>-4.307728333010054</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.200983429801042</v>
+        <v>1.166311370758866</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.4014682633386903</v>
+        <v>0.3521780628355597</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.13064008627985</v>
+        <v>3.101065965977972</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576996</v>
+        <v>3.791273551577</v>
       </c>
       <c r="C1932" t="n">
         <v>2.899847230838076</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.085794824074637</v>
+        <v>-4.172474971680077</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.265172876894473</v>
+        <v>1.230500817852297</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.5367216246686675</v>
+        <v>0.4874314241655369</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.221880205639276</v>
+        <v>3.192306085337398</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942102</v>
+        <v>3.735839222942106</v>
       </c>
       <c r="C1933" t="n">
         <v>2.885884722239501</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.145669651432329</v>
+        <v>-4.232349799037769</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.227260437352822</v>
+        <v>1.192588378310646</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.4768467973109753</v>
+        <v>0.4275565968078447</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.171992800626087</v>
+        <v>3.142418680324209</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674512</v>
+        <v>3.762647477674515</v>
       </c>
       <c r="C1934" t="n">
         <v>2.90117389147371</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.025849420521492</v>
+        <v>-4.112529568126932</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.290477698951365</v>
+        <v>1.255805639909189</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.4768467973109753</v>
+        <v>0.4275565968078447</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.187281969860296</v>
+        <v>3.157707849558417</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430693</v>
+        <v>3.729146398430697</v>
       </c>
       <c r="C1935" t="n">
         <v>2.808818090796152</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.028319126983298</v>
+        <v>-4.114999274588738</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.197134015689084</v>
+        <v>1.162461956646908</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.4743770908491692</v>
+        <v>0.4250868903460386</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.093444345305653</v>
+        <v>3.063870225003775</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.7432201960036</v>
+        <v>3.743220196003604</v>
       </c>
       <c r="C1936" t="n">
         <v>2.728079952281453</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.096689313307309</v>
+        <v>-4.183369460912749</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.089047802644782</v>
+        <v>1.054375743602606</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.4836527898853841</v>
+        <v>0.4343625893822535</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.018271626212684</v>
+        <v>2.988697505910805</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508368</v>
+        <v>3.714179139508372</v>
       </c>
       <c r="C1937" t="n">
         <v>2.718516660913344</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.208561592933459</v>
+        <v>-4.295241740538899</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.034735599426213</v>
+        <v>1.000063540384037</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.4836527898853841</v>
+        <v>0.4343625893822535</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.008708334844575</v>
+        <v>2.979134214542697</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417702</v>
+        <v>3.710906731417706</v>
       </c>
       <c r="C1938" t="n">
         <v>2.685091185837372</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.192586927447191</v>
+        <v>-4.279267075052632</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.007699990544747</v>
+        <v>0.9730279315025709</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.4836527898853841</v>
+        <v>0.4343625893822535</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.975282859768603</v>
+        <v>2.945708739466724</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205895</v>
+        <v>3.746042526205901</v>
       </c>
       <c r="C1939" t="n">
         <v>2.689658417829159</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.196681474118189</v>
+        <v>-4.283361621723629</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.010629403868136</v>
+        <v>0.9759573448259597</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.4836527898853841</v>
+        <v>0.4343625893822535</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.97985009176039</v>
+        <v>2.950275971458512</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225438</v>
+        <v>3.765024323225445</v>
       </c>
       <c r="C1940" t="n">
         <v>2.665400446590366</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.188757099533275</v>
+        <v>-4.275437247138715</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.9895411824633085</v>
+        <v>0.9548691234211324</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.4836527898853841</v>
+        <v>0.4343625893822535</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.955592120521597</v>
+        <v>2.926018000219719</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111292</v>
+        <v>3.773210297111296</v>
       </c>
       <c r="C1941" t="n">
         <v>2.593938759991816</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.182478896963426</v>
+        <v>-4.269159044568866</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.920590776892698</v>
+        <v>0.8859187178505219</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.4899309924552332</v>
+        <v>0.4406407919521026</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.887897355464956</v>
+        <v>2.858323235163078</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264162</v>
+        <v>3.784343952264166</v>
       </c>
       <c r="C1942" t="n">
         <v>2.604111146423949</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.122626277759703</v>
+        <v>-4.209306425365143</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.9547042110063195</v>
+        <v>0.9200321519641435</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.4899309924552332</v>
+        <v>0.4406407919521026</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.898069741897089</v>
+        <v>2.86849562159521</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742298</v>
+        <v>3.786949957742301</v>
       </c>
       <c r="C1943" t="n">
         <v>2.599057416997809</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.036382814733325</v>
+        <v>-4.123062962338765</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.9841478667907309</v>
+        <v>0.9494758077485548</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.4899309924552332</v>
+        <v>0.4406407919521026</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.893016012470949</v>
+        <v>2.863441892169071</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316045</v>
+        <v>3.752027499316048</v>
       </c>
       <c r="C1944" t="n">
         <v>2.590833192442334</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.081689634132305</v>
+        <v>-4.168369781737745</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.9578009144756645</v>
+        <v>0.9231288554334884</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.4491208294460024</v>
+        <v>0.3998306289428718</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.860305690109936</v>
+        <v>2.830731569808058</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803189</v>
+        <v>3.753571165803192</v>
       </c>
       <c r="C1945" t="n">
         <v>2.591385065475436</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.110722738834606</v>
+        <v>-4.197402886440046</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.9467395456278456</v>
+        <v>0.9120674865856695</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.4491208294460024</v>
+        <v>0.3998306289428718</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.860857563143038</v>
+        <v>2.831283442841159</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809497</v>
+        <v>3.733390600809501</v>
       </c>
       <c r="C1946" t="n">
         <v>2.520657757366802</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.017912257383746</v>
+        <v>-4.104592404989186</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.9131364300995553</v>
+        <v>0.8784643710573792</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.5419313108968618</v>
+        <v>0.4926411103937312</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.845816543904919</v>
+        <v>2.816242423603041</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560424</v>
+        <v>3.748285816560427</v>
       </c>
       <c r="C1947" t="n">
         <v>2.522531233291402</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.062301726713174</v>
+        <v>-4.148981874318614</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.897254118292385</v>
+        <v>0.8625820592502089</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.4975418415674341</v>
+        <v>0.4482516410643035</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.821056338231863</v>
+        <v>2.791482217929985</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472734</v>
+        <v>3.721077195472738</v>
       </c>
       <c r="C1948" t="n">
         <v>2.517606941803125</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.041798032827677</v>
+        <v>-4.128478180433117</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.900531304358307</v>
+        <v>0.8658592453161309</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.5180455354529314</v>
+        <v>0.4687553349498008</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.828434263074885</v>
+        <v>2.798860142773006</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798535</v>
+        <v>3.743047603798539</v>
       </c>
       <c r="C1949" t="n">
         <v>2.523098237633793</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.125470129540009</v>
+        <v>-4.212150277145449</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.8725537615040411</v>
+        <v>0.837881702461865</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.5180455354529314</v>
+        <v>0.4687553349498008</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.833925558905552</v>
+        <v>2.804351438603673</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498862</v>
+        <v>3.689597840498865</v>
       </c>
       <c r="C1950" t="n">
         <v>2.534595439402332</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.153250527441362</v>
+        <v>-4.239930675046802</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.8729388041120392</v>
+        <v>0.8382667450698631</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.4902651375515783</v>
+        <v>0.4409749370484478</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.828754521933279</v>
+        <v>2.799180401631401</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705322</v>
+        <v>3.643069621705326</v>
       </c>
       <c r="C1951" t="n">
         <v>2.372951159402985</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.2716312001715</v>
+        <v>-4.35831134777694</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.6639422550206371</v>
+        <v>0.629270195978461</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.4230472854006021</v>
+        <v>0.3737570848974716</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.626779530643347</v>
+        <v>2.597205410341468</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729267</v>
+        <v>3.682716310729271</v>
       </c>
       <c r="C1952" t="n">
         <v>2.493100820122191</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.380245278614831</v>
+        <v>-4.466925426220271</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.7406462843625103</v>
+        <v>0.7059742253203343</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.4230472854006021</v>
+        <v>0.3737570848974716</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.746929191362552</v>
+        <v>2.717355071060674</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190766</v>
+        <v>3.73301244119077</v>
       </c>
       <c r="C1953" t="n">
         <v>2.507613846224514</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.344836240366688</v>
+        <v>-4.431516387972128</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.7693229257640903</v>
+        <v>0.7346508667219143</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.4230472854006021</v>
+        <v>0.3737570848974716</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.761442217464875</v>
+        <v>2.731868097162997</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913424</v>
+        <v>3.741174069913428</v>
       </c>
       <c r="C1954" t="n">
         <v>2.505033287566882</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.353297409022149</v>
+        <v>-4.439977556627589</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.7633578996442747</v>
+        <v>0.7286858406020986</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.4145861167451411</v>
+        <v>0.3652959162420105</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.753784957613967</v>
+        <v>2.724210837312089</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532484</v>
+        <v>3.751147197532488</v>
       </c>
       <c r="C1955" t="n">
         <v>2.501762316412185</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.176181078986983</v>
+        <v>-4.262861226592423</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.8309334605036436</v>
+        <v>0.7962614014614675</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.4145861167451411</v>
+        <v>0.3652959162420105</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.75051398645927</v>
+        <v>2.720939866157391</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793901</v>
+        <v>3.741328448793904</v>
       </c>
       <c r="C1956" t="n">
         <v>2.502445708174098</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.221273323820529</v>
+        <v>-4.307953471425969</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.8135799543321385</v>
+        <v>0.7789078952899624</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.3526900735757513</v>
+        <v>0.3033998730726207</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.714059752319549</v>
+        <v>2.684485632017671</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011231</v>
+        <v>3.750729377011237</v>
       </c>
       <c r="C1957" t="n">
         <v>2.496232683480512</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.041897902581761</v>
+        <v>-4.128578050187201</v>
       </c>
       <c r="E1957" t="n">
-        <v>0.8791170981340599</v>
+        <v>0.8444450390918838</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.5094668317464699</v>
+        <v>0.4601766312433394</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.801912782528394</v>
+        <v>2.772338662226516</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982224</v>
+        <v>3.71699171898223</v>
       </c>
       <c r="C1958" t="n">
         <v>2.477040138812102</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.086912116102367</v>
+        <v>-4.173592263707807</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.8419188680574072</v>
+        <v>0.8072468090152312</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.4791179364318653</v>
+        <v>0.4298277359287348</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.764510900671221</v>
+        <v>2.734936780369343</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509533</v>
+        <v>3.737026608509539</v>
       </c>
       <c r="C1959" t="n">
         <v>2.482731701151048</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.174923302661064</v>
+        <v>-4.261603450266504</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.8124059557728742</v>
+        <v>0.7777338967306981</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.4136414285726923</v>
+        <v>0.3643512280695618</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.730916558294664</v>
+        <v>2.701342437992785</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760809</v>
+        <v>3.702309454760813</v>
       </c>
       <c r="C1960" t="n">
         <v>2.481935623047549</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.276121084098237</v>
+        <v>-4.362801231703677</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.7711307650945065</v>
+        <v>0.7364587060523304</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.3452326150273731</v>
+        <v>0.2959424145242426</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.689075192063973</v>
+        <v>2.659501071762095</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815453</v>
+        <v>3.705571661815457</v>
       </c>
       <c r="C1961" t="n">
         <v>2.479535584601866</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.269610117483924</v>
+        <v>-4.356290265089364</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.7713351132945483</v>
+        <v>0.7366630542523722</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.3452326150273731</v>
+        <v>0.2959424145242426</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.68667515361829</v>
+        <v>2.657101033316412</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378099</v>
+        <v>3.709510443378102</v>
       </c>
       <c r="C1962" t="n">
         <v>2.476060303810111</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.250571989776627</v>
+        <v>-4.337252137382067</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.775475083585712</v>
+        <v>0.740803024543536</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.2870490036961786</v>
+        <v>0.2377588031930481</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.648289706027818</v>
+        <v>2.61871558572594</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131246</v>
+        <v>3.73106447313125</v>
       </c>
       <c r="C1963" t="n">
         <v>2.595354705444301</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.303087792051447</v>
+        <v>-4.389767939656887</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.8737631643099744</v>
+        <v>0.8390911052677983</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.2870490036961786</v>
+        <v>0.2377588031930481</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.767584107662008</v>
+        <v>2.73800998736013</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067861</v>
+        <v>3.722447362067864</v>
       </c>
       <c r="C1964" t="n">
         <v>2.596188034430435</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.306496103486027</v>
+        <v>-4.393176251091467</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.8732331687222759</v>
+        <v>0.8385611096800998</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.319565572705556</v>
+        <v>0.2702753722024255</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.787927378053769</v>
+        <v>2.75835325775189</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.78742558078912</v>
+        <v>3.787425580789123</v>
       </c>
       <c r="C1965" t="n">
         <v>2.602196564827361</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.28713996759218</v>
+        <v>-4.37382011519762</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.8869841534767409</v>
+        <v>0.8523120944345648</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.319565572705556</v>
+        <v>0.2702753722024255</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.793935908450695</v>
+        <v>2.764361788148816</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519905</v>
+        <v>3.781501250519908</v>
       </c>
       <c r="C1966" t="n">
         <v>2.50014678610456</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.360469496330272</v>
+        <v>-4.447149643935712</v>
       </c>
       <c r="E1966" t="n">
-        <v>0.7556025632587033</v>
+        <v>0.7209305042165273</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.3199602351251779</v>
+        <v>0.2706700346220474</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.692122927179667</v>
+        <v>2.662548806877789</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181165</v>
+        <v>3.80224592918117</v>
       </c>
       <c r="C1967" t="n">
         <v>2.409870503348191</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.444290717604971</v>
+        <v>-4.530970865210411</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.6317977919924551</v>
+        <v>0.597125732950279</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.3199602351251779</v>
+        <v>0.2706700346220474</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.601846644423298</v>
+        <v>2.57227252412142</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394725</v>
+        <v>3.805608985394731</v>
       </c>
       <c r="C1968" t="n">
         <v>2.41053285173985</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.438138011552186</v>
+        <v>-4.524818159157626</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.6349212228052272</v>
+        <v>0.6002491637630512</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.3261129411779622</v>
+        <v>0.2768227406748317</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.606200616446627</v>
+        <v>2.576626496144749</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890609</v>
+        <v>3.798239794890613</v>
       </c>
       <c r="C1969" t="n">
         <v>2.40961332847996</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.454947309702688</v>
+        <v>-4.541627457308128</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.6272779802851367</v>
+        <v>0.5926059212429606</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.3093036430274606</v>
+        <v>0.2600134425243301</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.595195514296436</v>
+        <v>2.565621393994558</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798424</v>
+        <v>3.867362636798427</v>
       </c>
       <c r="C1970" t="n">
         <v>2.475948882276781</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.392649310926566</v>
+        <v>-4.479329458532006</v>
       </c>
       <c r="E1970" t="n">
-        <v>0.7185327335924065</v>
+        <v>0.6838606745502305</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.3545979073019026</v>
+        <v>0.3053077067987721</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.688707626657922</v>
+        <v>2.659133506356044</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992188</v>
+        <v>3.848729139992193</v>
       </c>
       <c r="C1971" t="n">
         <v>2.278240883990908</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.190859113261408</v>
+        <v>-4.277539260866848</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.6015408143725967</v>
+        <v>0.5668687553304206</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.5526160994710569</v>
+        <v>0.5033258989679266</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.609810543673542</v>
+        <v>2.580236423371664</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852421</v>
+        <v>3.841444817852424</v>
       </c>
       <c r="C1972" t="n">
         <v>2.348531116313083</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.241745825947603</v>
+        <v>-4.328425973553043</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.6514763616202941</v>
+        <v>0.616804302578118</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.5017293867848625</v>
+        <v>0.452439186281732</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.649568748384001</v>
+        <v>2.619994628082122</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.81906330031954</v>
+        <v>3.819063300319546</v>
       </c>
       <c r="C1973" t="n">
         <v>2.363158852429127</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.155135083297796</v>
+        <v>-4.241815230903236</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.7007483947962605</v>
+        <v>0.6660763357540844</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.5803551179900207</v>
+        <v>0.5310649174868902</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.711371923223139</v>
+        <v>2.681797802921261</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.83181903248938</v>
+        <v>3.831819032489386</v>
       </c>
       <c r="C1974" t="n">
         <v>2.361694833253798</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.215344381303081</v>
+        <v>-4.302024528908521</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.6752006564188182</v>
+        <v>0.6405285973766421</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.5201458199847362</v>
+        <v>0.4708556194816057</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.67378232524464</v>
+        <v>2.644208204942762</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.83641167239779</v>
+        <v>3.836411672397796</v>
       </c>
       <c r="C1975" t="n">
         <v>2.360186451293727</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.166157732618729</v>
+        <v>-4.238583689894325</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.6933669339324873</v>
+        <v>0.6643965510222489</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.5201458199847362</v>
+        <v>0.4708556194816057</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.672273943284569</v>
+        <v>2.642699822982691</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316245</v>
+        <v>3.833513460316252</v>
       </c>
       <c r="C1976" t="n">
         <v>2.360049318729163</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.121784600980161</v>
+        <v>-4.194210558255756</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.7109790540233509</v>
+        <v>0.6820086711131126</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.5645189516233048</v>
+        <v>0.5152287511201743</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.698760689703146</v>
+        <v>2.669186569401268</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105962</v>
+        <v>3.821562117105966</v>
       </c>
       <c r="C1977" t="n">
         <v>2.354443112867754</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.08705327966166</v>
+        <v>-4.159479236937256</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.7192653766893415</v>
+        <v>0.6902949937791034</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.5645189516233048</v>
+        <v>0.5152287511201743</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.693154483841737</v>
+        <v>2.663580363539858</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190321</v>
+        <v>3.833011148190325</v>
       </c>
       <c r="C1978" t="n">
         <v>2.360824869895558</v>
       </c>
       <c r="D1978" t="n">
-        <v>-4.039397549100604</v>
+        <v>-4.1118235063762</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.7447094259415685</v>
+        <v>0.7157390430313304</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.6121746821843604</v>
+        <v>0.56288448168123</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.728129679206175</v>
+        <v>2.698555558904296</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569614</v>
+        <v>3.822678210569618</v>
       </c>
       <c r="C1979" t="n">
         <v>2.365717243270283</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.93887939060185</v>
+        <v>-4.011305347877445</v>
       </c>
       <c r="E1979" t="n">
-        <v>0.7898090627157952</v>
+        <v>0.7608386798055571</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.712692840683115</v>
+        <v>0.6634026401799845</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.793332947680153</v>
+        <v>2.763758827378274</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557291</v>
+        <v>3.828808877557295</v>
       </c>
       <c r="C1980" t="n">
         <v>2.352471915746155</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.922974061169497</v>
+        <v>-3.995400018445093</v>
       </c>
       <c r="E1980" t="n">
-        <v>0.7829258669646086</v>
+        <v>0.7539554840543703</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.6335801799738761</v>
+        <v>0.5842899794707457</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.732620023730481</v>
+        <v>2.703045903428603</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932766</v>
+        <v>3.816837033932769</v>
       </c>
       <c r="C1981" t="n">
         <v>2.356569618356784</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.878135659561099</v>
+        <v>-3.950561616836695</v>
       </c>
       <c r="E1981" t="n">
-        <v>0.8049589302185964</v>
+        <v>0.7759885473083581</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.6381236129187455</v>
+        <v>0.5888334124156152</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.739443786108032</v>
+        <v>2.709869665806153</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917048</v>
+        <v>3.817932354917051</v>
       </c>
       <c r="C1982" t="n">
         <v>2.360730557987862</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.897634115803107</v>
+        <v>-3.970060073078703</v>
       </c>
       <c r="E1982" t="n">
-        <v>0.801320487352871</v>
+        <v>0.7723501044426329</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.5900389716388412</v>
+        <v>0.5407487711357108</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.714753940971167</v>
+        <v>2.685179820669289</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405958</v>
+        <v>3.826684745405961</v>
       </c>
       <c r="C1983" t="n">
         <v>2.366610160515699</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.853431278717207</v>
+        <v>-3.925857235992802</v>
       </c>
       <c r="E1983" t="n">
-        <v>0.8248812247150683</v>
+        <v>0.7959108418048302</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.6342418087247417</v>
+        <v>0.5849516082216113</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.747155245750544</v>
+        <v>2.717581125448666</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265642</v>
+        <v>3.838199629265645</v>
       </c>
       <c r="C1984" t="n">
         <v>2.365020160984947</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.860990944554254</v>
+        <v>-3.933416901829849</v>
       </c>
       <c r="E1984" t="n">
-        <v>0.8202673588494971</v>
+        <v>0.791296975939259</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.689045212734561</v>
+        <v>0.6397550122314306</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.778447288625683</v>
+        <v>2.748873168323805</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284877</v>
+        <v>3.86389508028488</v>
       </c>
       <c r="C1985" t="n">
         <v>2.416267926167986</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.702699527014981</v>
+        <v>-3.775125484290577</v>
       </c>
       <c r="E1985" t="n">
-        <v>0.9348316910482457</v>
+        <v>0.9058613081380074</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.689045212734561</v>
+        <v>0.6397550122314306</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.829695053808723</v>
+        <v>2.800120933506845</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.86533868132102</v>
+        <v>3.865338681321023</v>
       </c>
       <c r="C1986" t="n">
         <v>2.414708630762239</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.495057523380505</v>
+        <v>-3.567483480656101</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.016329197096289</v>
+        <v>0.987358814186051</v>
       </c>
       <c r="F1986" t="n">
-        <v>0.8966872163690371</v>
+        <v>0.8473970158659068</v>
       </c>
       <c r="G1986" t="n">
-        <v>2.952720960583662</v>
+        <v>2.923146840281784</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475136</v>
+        <v>3.864489842475139</v>
       </c>
       <c r="C1987" t="n">
         <v>2.409656859000509</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.444025430657977</v>
+        <v>-3.516451387933573</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.031690262423571</v>
+        <v>1.002719879513332</v>
       </c>
       <c r="F1987" t="n">
-        <v>0.9477193090915651</v>
+        <v>0.8984291085884347</v>
       </c>
       <c r="G1987" t="n">
-        <v>2.978288444455448</v>
+        <v>2.94871432415357</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.84254736040485</v>
+        <v>3.842547360404854</v>
       </c>
       <c r="C1988" t="n">
         <v>2.426844263093214</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.378801249530771</v>
+        <v>-3.451227206806367</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.074967338967158</v>
+        <v>1.04599695605692</v>
       </c>
       <c r="F1988" t="n">
-        <v>1.012943490218771</v>
+        <v>0.9636532897156403</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.034610357224477</v>
+        <v>3.005036236922599</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882552</v>
+        <v>3.840061186882558</v>
       </c>
       <c r="C1989" t="n">
         <v>2.422805235392495</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.341374229459638</v>
+        <v>-3.413800186735233</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.085899119294892</v>
+        <v>1.056928736384653</v>
       </c>
       <c r="F1989" t="n">
-        <v>1.018195028247952</v>
+        <v>0.968904827744822</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.033722252341266</v>
+        <v>3.004148132039388</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992655</v>
+        <v>3.845169808992662</v>
       </c>
       <c r="C1990" t="n">
         <v>2.424062027723735</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.340016244486092</v>
+        <v>-3.412442201761688</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.08769910561555</v>
+        <v>1.058728722705312</v>
       </c>
       <c r="F1990" t="n">
-        <v>1.092533153785771</v>
+        <v>1.043242953282641</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.079581919995198</v>
+        <v>3.050007799693319</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636283</v>
+        <v>3.828661445636287</v>
       </c>
       <c r="C1991" t="n">
         <v>2.584619798744946</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.311602981386208</v>
+        <v>-3.384028938661804</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.259622181876714</v>
+        <v>1.230651798966476</v>
       </c>
       <c r="F1991" t="n">
-        <v>1.033557591039342</v>
+        <v>0.9842673905362118</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.204754353368551</v>
+        <v>3.175180233066673</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957621</v>
+        <v>3.813222820957627</v>
       </c>
       <c r="C1992" t="n">
         <v>2.704732707962763</v>
       </c>
       <c r="D1992" t="n">
-        <v>-3.236820720361196</v>
+        <v>-3.309246677636791</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.409647995504537</v>
+        <v>1.380677612594298</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.108339852064355</v>
+        <v>1.059049651561224</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.369736619201376</v>
+        <v>3.340162498899498</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.81423072799875</v>
+        <v>3.814230727998754</v>
       </c>
       <c r="C1993" t="n">
         <v>2.696440683976622</v>
       </c>
       <c r="D1993" t="n">
-        <v>-3.210736636097388</v>
+        <v>-3.283162593372984</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.411789605223919</v>
+        <v>1.382819222313681</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.108339852064355</v>
+        <v>1.059049651561224</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.361444595215235</v>
+        <v>3.331870474913357</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896926</v>
+        <v>3.803397818896929</v>
       </c>
       <c r="C1994" t="n">
         <v>2.694633879560401</v>
       </c>
       <c r="D1994" t="n">
-        <v>-3.122858722988267</v>
+        <v>-3.195284680263863</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.445133966051346</v>
+        <v>1.416163583141108</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.224265494487706</v>
+        <v>1.174975293984576</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.429193176253025</v>
+        <v>3.399619055951147</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959855</v>
+        <v>3.796264143959858</v>
       </c>
       <c r="C1995" t="n">
         <v>2.712188285287193</v>
       </c>
       <c r="D1995" t="n">
-        <v>-3.113966261594984</v>
+        <v>-3.18639221887058</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.466245356335451</v>
+        <v>1.437274973425213</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.224265494487706</v>
+        <v>1.174975293984576</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.446747581979817</v>
+        <v>3.417173461677939</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945364</v>
+        <v>3.794424941945367</v>
       </c>
       <c r="C1996" t="n">
         <v>2.704043332691777</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.282442378564862</v>
+        <v>-3.354868335840458</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.390709956952084</v>
+        <v>1.361739574041846</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.196317658771125</v>
+        <v>1.147027458267995</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.421833927954452</v>
+        <v>3.392259807652574</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782706</v>
+        <v>3.795574066782709</v>
       </c>
       <c r="C1997" t="n">
         <v>2.685313029879639</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.836186185935422</v>
+        <v>-2.908612143211018</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.550482131191722</v>
+        <v>1.521511748281484</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.101598989101492</v>
+        <v>1.052308788598362</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.346272423340534</v>
+        <v>3.316698303038656</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632633</v>
+        <v>3.784671345632637</v>
       </c>
       <c r="C1998" t="n">
         <v>2.675977052376543</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.81346508225227</v>
+        <v>-2.885891039527865</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.550234595161887</v>
+        <v>1.521264212251649</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.101598989101492</v>
+        <v>1.052308788598362</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.336936445837439</v>
+        <v>3.307362325535561</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777668</v>
+        <v>3.783205696777674</v>
       </c>
       <c r="C1999" t="n">
         <v>2.834883178227712</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.942666895546312</v>
+        <v>-3.015092852821908</v>
       </c>
       <c r="E1999" t="n">
-        <v>1.657459995695439</v>
+        <v>1.628489612785201</v>
       </c>
       <c r="F1999" t="n">
-        <v>0.9723971758074501</v>
+        <v>0.92310697530432</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.418321483712182</v>
+        <v>3.388747363410304</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644408</v>
+        <v>3.779933725644414</v>
       </c>
       <c r="C2000" t="n">
         <v>2.871961000721359</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.968541294020338</v>
+        <v>-3.040967251295934</v>
       </c>
       <c r="E2000" t="n">
-        <v>1.684188058799476</v>
+        <v>1.655217675889237</v>
       </c>
       <c r="F2000" t="n">
-        <v>1.017308784519191</v>
+        <v>0.9680185840160611</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.482346271432874</v>
+        <v>3.452772151130996</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.76944361979996</v>
+        <v>3.769443619799962</v>
       </c>
       <c r="C2001" t="n">
         <v>2.868636356710904</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.961486603805164</v>
+        <v>-3.03391256108076</v>
       </c>
       <c r="E2001" t="n">
-        <v>1.68368529087509</v>
+        <v>1.654714907964852</v>
       </c>
       <c r="F2001" t="n">
-        <v>1.024363474734365</v>
+        <v>0.9750732742312349</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.483254441551523</v>
+        <v>3.453680321249645</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331113</v>
+        <v>3.766673496331116</v>
       </c>
       <c r="C2002" t="n">
         <v>2.878642510355645</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.934535379478676</v>
+        <v>-3.006961336754272</v>
       </c>
       <c r="E2002" t="n">
-        <v>1.704471934250427</v>
+        <v>1.675501551340189</v>
       </c>
       <c r="F2002" t="n">
-        <v>1.039243820762084</v>
+        <v>0.9899536202589541</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.502188802812896</v>
+        <v>3.472614682511018</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784105</v>
+        <v>3.768052067784108</v>
       </c>
       <c r="C2003" t="n">
         <v>3.062745642500605</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.956079607309464</v>
+        <v>-3.028505564585059</v>
       </c>
       <c r="E2003" t="n">
-        <v>1.879957375263072</v>
+        <v>1.850986992352833</v>
       </c>
       <c r="F2003" t="n">
-        <v>1.039243820762084</v>
+        <v>0.9899536202589541</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.686291934957856</v>
+        <v>3.656717814655978</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714421</v>
+        <v>3.743925505714424</v>
       </c>
       <c r="C2004" t="n">
         <v>3.054862337403598</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.978487725114336</v>
+        <v>-3.050913682389931</v>
       </c>
       <c r="E2004" t="n">
-        <v>1.863110823044116</v>
+        <v>1.834140440133878</v>
       </c>
       <c r="F2004" t="n">
-        <v>1.039243820762084</v>
+        <v>0.9899536202589541</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.678408629860849</v>
+        <v>3.648834509558971</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155028</v>
+        <v>3.719118627155034</v>
       </c>
       <c r="C2005" t="n">
         <v>3.056916336953236</v>
       </c>
       <c r="D2005" t="n">
-        <v>-3.006711960691936</v>
+        <v>-3.079137917967532</v>
       </c>
       <c r="E2005" t="n">
-        <v>1.853875128362714</v>
+        <v>1.824904745452475</v>
       </c>
       <c r="F2005" t="n">
-        <v>1.057220573213393</v>
+        <v>1.007930372710263</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.691248680881272</v>
+        <v>3.661674560579394</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161972</v>
+        <v>3.72945228516198</v>
       </c>
       <c r="C2006" t="n">
         <v>3.113170054675083</v>
       </c>
       <c r="D2006" t="n">
-        <v>-3.016152886580466</v>
+        <v>-3.088578843856062</v>
       </c>
       <c r="E2006" t="n">
-        <v>1.906352475729149</v>
+        <v>1.87738209281891</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.179647690756784</v>
+        <v>1.130357490253654</v>
       </c>
       <c r="G2006" t="n">
-        <v>3.820958669129154</v>
+        <v>3.791384548827275</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321629</v>
+        <v>3.714941193321637</v>
       </c>
       <c r="C2007" t="n">
         <v>3.116061149220384</v>
       </c>
       <c r="D2007" t="n">
-        <v>-3.222391824368899</v>
+        <v>-3.294817781644495</v>
       </c>
       <c r="E2007" t="n">
-        <v>1.826747995159076</v>
+        <v>1.797777612248838</v>
       </c>
       <c r="F2007" t="n">
-        <v>0.9734087529683506</v>
+        <v>0.9241185524652205</v>
       </c>
       <c r="G2007" t="n">
-        <v>3.700106401001395</v>
+        <v>3.670532280699516</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.7278981863477</v>
+        <v>3.727898186347708</v>
       </c>
       <c r="C2008" t="n">
         <v>3.114172962114159</v>
       </c>
       <c r="D2008" t="n">
-        <v>-3.298721801969805</v>
+        <v>-3.371147759245401</v>
       </c>
       <c r="E2008" t="n">
-        <v>1.794327817012489</v>
+        <v>1.765357434102251</v>
       </c>
       <c r="F2008" t="n">
-        <v>0.9734087529683506</v>
+        <v>0.9241185524652205</v>
       </c>
       <c r="G2008" t="n">
-        <v>3.69821821389517</v>
+        <v>3.668644093593291</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887745</v>
+        <v>3.710654104887753</v>
       </c>
       <c r="C2009" t="n">
         <v>3.108993191717021</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.453678587369934</v>
+        <v>-3.52610454464553</v>
       </c>
       <c r="E2009" t="n">
-        <v>1.7271653324553</v>
+        <v>1.698194949545061</v>
       </c>
       <c r="F2009" t="n">
-        <v>0.8184519675682214</v>
+        <v>0.7691617670650912</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.600064372257954</v>
+        <v>3.570490251956076</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343062</v>
+        <v>3.712897612343071</v>
       </c>
       <c r="C2010" t="n">
         <v>3.107427201927174</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.61524701289719</v>
+        <v>-3.687672970172785</v>
       </c>
       <c r="E2010" t="n">
-        <v>1.66097197245455</v>
+        <v>1.632001589544311</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.691669043770342</v>
+        <v>0.6423788432672118</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.522428628189379</v>
+        <v>3.492854507887501</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754596135389345</v>
+        <v>3.754596135389354</v>
       </c>
       <c r="C2011" t="n">
         <v>3.120500608793092</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.723547674767309</v>
+        <v>-3.795973632042905</v>
       </c>
       <c r="E2011" t="n">
-        <v>1.630725114572421</v>
+        <v>1.601754731662182</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.691669043770342</v>
+        <v>0.6423788432672118</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.535502035055297</v>
+        <v>3.505927914753419</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749882691378388</v>
+        <v>3.74988269137839</v>
       </c>
       <c r="C2012" t="n">
         <v>3.112505805576032</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.883098747530826</v>
+        <v>-3.955524704806422</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.558909882249954</v>
+        <v>1.529939499339716</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.5393913769085905</v>
+        <v>0.4901011764054604</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.436140631721187</v>
+        <v>3.406566511419308</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715819895006971</v>
+        <v>3.715819895006973</v>
       </c>
       <c r="C2013" t="n">
         <v>3.111029846703034</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.910999534640299</v>
+        <v>-3.983425491915895</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.546273608533167</v>
+        <v>1.517303225622928</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.5047944527656557</v>
+        <v>0.4555042522625256</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.413906518362428</v>
+        <v>3.38433239806055</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684895778787384</v>
+        <v>3.684895778787386</v>
       </c>
       <c r="C2014" t="n">
         <v>3.107794290680233</v>
       </c>
       <c r="D2014" t="n">
-        <v>-4.033525637343192</v>
+        <v>-4.105951594618789</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.494027611429208</v>
+        <v>1.465057228518969</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.3822683500627618</v>
+        <v>0.3329781495596317</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.33715530071789</v>
+        <v>3.307581180416012</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619348081585934</v>
+        <v>3.619348081585936</v>
       </c>
       <c r="C2015" t="n">
         <v>3.174500250270737</v>
       </c>
       <c r="D2015" t="n">
-        <v>-4.264040133528781</v>
+        <v>-4.336466090804378</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.468527772545476</v>
+        <v>1.439557389635238</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.1517538538771731</v>
+        <v>0.102463653374043</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.265552562597041</v>
+        <v>3.235978442295163</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640750087814664</v>
+        <v>3.640750087814666</v>
       </c>
       <c r="C2016" t="n">
         <v>3.314811969272584</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.612785218753225</v>
+        <v>-4.685211176028822</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.469341457457546</v>
+        <v>1.440371074547307</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.04300589995827531</v>
+        <v>-0.006284300544854848</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.340615509247549</v>
+        <v>3.311041388945671</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668289004237093</v>
+        <v>3.668289004237095</v>
       </c>
       <c r="C2017" t="n">
         <v>3.383792238418224</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.766771636529366</v>
+        <v>-4.839197593804962</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.476727159492729</v>
+        <v>1.447756776582491</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.04300589995827531</v>
+        <v>-0.006284300544854848</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.409595778393189</v>
+        <v>3.380021658091311</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619923016423386</v>
+        <v>3.619923016423388</v>
       </c>
       <c r="C2018" t="n">
         <v>3.369843440538344</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.971371071392374</v>
+        <v>-5.043797028667971</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.380938587667647</v>
+        <v>1.351968204757408</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.04300589995827531</v>
+        <v>-0.006284300544854848</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.39564698051331</v>
+        <v>3.366072860211432</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656332733609752</v>
+        <v>3.656332733609753</v>
       </c>
       <c r="C2019" t="n">
         <v>3.381713929593758</v>
       </c>
       <c r="D2019" t="n">
-        <v>-5.223846225400099</v>
+        <v>-5.296272182675695</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.291819015119971</v>
+        <v>1.262848632209733</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.04300589995827531</v>
+        <v>-0.006284300544854848</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.407517469568724</v>
+        <v>3.377943349266846</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674028535973155</v>
+        <v>3.674028535973157</v>
       </c>
       <c r="C2020" t="n">
         <v>3.382924464112702</v>
       </c>
       <c r="D2020" t="n">
-        <v>-5.516741981879511</v>
+        <v>-5.589167939155107</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.17587124704715</v>
+        <v>1.146900864136911</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.04300589995827531</v>
+        <v>-0.006284300544854848</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.408728004087668</v>
+        <v>3.37915388378579</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663509457251942</v>
+        <v>3.663509457251946</v>
       </c>
       <c r="C2021" t="n">
         <v>3.387046206340024</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.703406110014319</v>
+        <v>-5.775832067289915</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.105327338020548</v>
+        <v>1.07635695511031</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.01626692913371541</v>
+        <v>-0.03302327136941474</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.396806363820253</v>
+        <v>3.367232243518375</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652149152916197</v>
+        <v>3.652149152916202</v>
       </c>
       <c r="C2022" t="n">
         <v>3.382124059076213</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.849426796928281</v>
+        <v>-5.921852754203877</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.041996915991152</v>
+        <v>1.013026533080914</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.007183837339858445</v>
+        <v>-0.04210636316327171</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.386434361480128</v>
+        <v>3.35686024117825</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667962306830325</v>
+        <v>3.667962306830328</v>
       </c>
       <c r="C2023" t="n">
         <v>3.544328115775257</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.941140806037867</v>
+        <v>-6.013566763313463</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.167515369046363</v>
+        <v>1.138544986136124</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.007183837339858445</v>
+        <v>-0.04210636316327171</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.548638418179173</v>
+        <v>3.519064297877294</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696539468071547</v>
+        <v>3.696539468071552</v>
       </c>
       <c r="C2024" t="n">
         <v>3.539174753739071</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.972792465097836</v>
+        <v>-6.038356454893608</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.149701343386189</v>
+        <v>1.12347574746788</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.00201538009541824</v>
+        <v>-0.07357933481011636</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.540383981796322</v>
+        <v>3.495027152853002</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750044015868143</v>
+        <v>3.750044015868149</v>
       </c>
       <c r="C2025" t="n">
         <v>3.549404171307562</v>
       </c>
       <c r="D2025" t="n">
-        <v>-6.041858519670773</v>
+        <v>-6.107422509466545</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.132304339125505</v>
+        <v>1.106078743207196</v>
       </c>
       <c r="F2025" t="n">
-        <v>-0.06035549739819179</v>
+        <v>-0.1359502123037264</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.513190872868647</v>
+        <v>3.467834043925327</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783632867332689</v>
+        <v>3.783632867332695</v>
       </c>
       <c r="C2026" t="n">
         <v>3.558329809763465</v>
       </c>
       <c r="D2026" t="n">
-        <v>-6.14383464191918</v>
+        <v>-6.209398631714953</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.100439528682045</v>
+        <v>1.074213932763736</v>
       </c>
       <c r="F2026" t="n">
-        <v>-0.1623316196465994</v>
+        <v>-0.237926334552134</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.460930837975505</v>
+        <v>3.415574009032185</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798296784231805</v>
+        <v>3.798296784231812</v>
       </c>
       <c r="C2027" t="n">
         <v>3.55048269700764</v>
       </c>
       <c r="D2027" t="n">
-        <v>-6.033828358441959</v>
+        <v>-6.099392348237731</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.136594929317109</v>
+        <v>1.1103693333988</v>
       </c>
       <c r="F2027" t="n">
-        <v>-0.1391270477293242</v>
+        <v>-0.2147217626348588</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.467006468370046</v>
+        <v>3.421649639426725</v>
       </c>
     </row>
     <row r="2028">
@@ -48195,16 +48195,16 @@
         <v>3.554732707729614</v>
       </c>
       <c r="D2028" t="n">
-        <v>-6.046358063553837</v>
+        <v>-6.11192205334961</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.135833057994331</v>
+        <v>1.109607462076022</v>
       </c>
       <c r="F2028" t="n">
-        <v>-0.1529535471958472</v>
+        <v>-0.2285482621013818</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.462960579412107</v>
+        <v>3.417603750468786</v>
       </c>
     </row>
     <row r="2029">
@@ -48218,16 +48218,16 @@
         <v>3.56199359061215</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.744911338082</v>
+        <v>-5.810475327877772</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.263672631065603</v>
+        <v>1.237447035147293</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.1484931782759901</v>
+        <v>0.07289846337045547</v>
       </c>
       <c r="G2029" t="n">
-        <v>3.651089497577745</v>
+        <v>3.605732668634424</v>
       </c>
     </row>
     <row r="2030">
@@ -48241,16 +48241,16 @@
         <v>3.562964768364861</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.769501582317184</v>
+        <v>-5.835065572112956</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.254807711124239</v>
+        <v>1.22858211520593</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.1484931782759901</v>
+        <v>0.07289846337045547</v>
       </c>
       <c r="G2030" t="n">
-        <v>3.652060675330455</v>
+        <v>3.606703846387135</v>
       </c>
     </row>
     <row r="2031">
@@ -48264,16 +48264,16 @@
         <v>3.563807672744617</v>
       </c>
       <c r="D2031" t="n">
-        <v>-5.718463206310664</v>
+        <v>-5.784027196106436</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.276065965906603</v>
+        <v>1.249840369988294</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.1484931782759901</v>
+        <v>0.07289846337045547</v>
       </c>
       <c r="G2031" t="n">
-        <v>3.652903579710211</v>
+        <v>3.60754675076689</v>
       </c>
     </row>
     <row r="2032">
@@ -48281,22 +48281,22 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831734516969542</v>
+        <v>3.831734516969543</v>
       </c>
       <c r="C2032" t="n">
         <v>3.582845771618762</v>
       </c>
       <c r="D2032" t="n">
-        <v>-5.689614529487203</v>
+        <v>-5.755178519282976</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.306643535510133</v>
+        <v>1.280417939591824</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.1773418550994503</v>
+        <v>0.1017471401939157</v>
       </c>
       <c r="G2032" t="n">
-        <v>3.689250884678433</v>
+        <v>3.643894055735112</v>
       </c>
     </row>
     <row r="2033">
@@ -48304,22 +48304,22 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825752932700476</v>
+        <v>3.825752932700478</v>
       </c>
       <c r="C2033" t="n">
         <v>3.399029767742697</v>
       </c>
       <c r="D2033" t="n">
-        <v>-5.592979617468563</v>
+        <v>-5.658543607264336</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.161481496441523</v>
+        <v>1.135255900523215</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.2739767671180903</v>
+        <v>0.1983820522125557</v>
       </c>
       <c r="G2033" t="n">
-        <v>3.563415828013551</v>
+        <v>3.51805899907023</v>
       </c>
     </row>
     <row r="2034">
@@ -48327,22 +48327,22 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.804688961077638</v>
+        <v>3.804688961077642</v>
       </c>
       <c r="C2034" t="n">
         <v>3.402531811816661</v>
       </c>
       <c r="D2034" t="n">
-        <v>-5.523941606520095</v>
+        <v>-5.589505596315868</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.192598744894874</v>
+        <v>1.166373148976566</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.3430147780665583</v>
+        <v>0.2674200631610237</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.608340678656596</v>
+        <v>3.562983849713275</v>
       </c>
     </row>
     <row r="2035">
@@ -48350,22 +48350,22 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775028860833456</v>
+        <v>3.775028860833462</v>
       </c>
       <c r="C2035" t="n">
         <v>3.386958630892743</v>
       </c>
       <c r="D2035" t="n">
-        <v>-5.505154506151157</v>
+        <v>-5.570718495946929</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.184540404118533</v>
+        <v>1.158314808200223</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.3618018784354968</v>
+        <v>0.2862071635299622</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.604039757954042</v>
+        <v>3.558682929010721</v>
       </c>
     </row>
     <row r="2036">
@@ -48373,22 +48373,22 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821030660077626</v>
+        <v>3.821030660077627</v>
       </c>
       <c r="C2036" t="n">
         <v>3.386146341329173</v>
       </c>
       <c r="D2036" t="n">
-        <v>-5.428055904609284</v>
+        <v>-5.493619894405056</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.214567555171711</v>
+        <v>1.188341959253402</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.3618018784354968</v>
+        <v>0.2862071635299622</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.603227468390471</v>
+        <v>3.557870639447151</v>
       </c>
     </row>
     <row r="2037">
@@ -48396,22 +48396,22 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.832307024147908</v>
+        <v>3.832307024147909</v>
       </c>
       <c r="C2037" t="n">
         <v>3.396015120454245</v>
       </c>
       <c r="D2037" t="n">
-        <v>-5.438441099499173</v>
+        <v>-5.504005089294946</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.220282256340828</v>
+        <v>1.194056660422519</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.3514166835456075</v>
+        <v>0.2758219686400729</v>
       </c>
       <c r="G2037" t="n">
-        <v>3.60686513058161</v>
+        <v>3.561508301638289</v>
       </c>
     </row>
     <row r="2038">
@@ -48419,22 +48419,22 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.834415493735278</v>
+        <v>3.834415493735285</v>
       </c>
       <c r="C2038" t="n">
         <v>3.466852126230671</v>
       </c>
       <c r="D2038" t="n">
-        <v>-5.457029258221398</v>
+        <v>-5.522593248017171</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.283683998628363</v>
+        <v>1.257458402710054</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.3328285248233822</v>
+        <v>0.2572338099178476</v>
       </c>
       <c r="G2038" t="n">
-        <v>3.6665492411247</v>
+        <v>3.621192412181379</v>
       </c>
     </row>
     <row r="2039">
@@ -48442,22 +48442,22 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.855120535496552</v>
+        <v>3.855120535496553</v>
       </c>
       <c r="C2039" t="n">
         <v>3.463721137048969</v>
       </c>
       <c r="D2039" t="n">
-        <v>-5.457327804917434</v>
+        <v>-5.522891794713207</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.280433590768248</v>
+        <v>1.254207994849939</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.3325299781273462</v>
+        <v>0.2569352632218116</v>
       </c>
       <c r="G2039" t="n">
-        <v>3.663239123925377</v>
+        <v>3.617882294982056</v>
       </c>
     </row>
     <row r="2040">
@@ -48465,22 +48465,22 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.815643212108854</v>
+        <v>3.81564321210886</v>
       </c>
       <c r="C2040" t="n">
         <v>3.468252031988361</v>
       </c>
       <c r="D2040" t="n">
-        <v>-5.356504671227007</v>
+        <v>-5.422068661022779</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.32529373918381</v>
+        <v>1.299068143265501</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.3449941936117001</v>
+        <v>0.2693994787061655</v>
       </c>
       <c r="G2040" t="n">
-        <v>3.675248548155381</v>
+        <v>3.62989171921206</v>
       </c>
     </row>
     <row r="2041">
@@ -48488,22 +48488,22 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.807356168121464</v>
+        <v>3.807356168121472</v>
       </c>
       <c r="C2041" t="n">
         <v>3.468381285466904</v>
       </c>
       <c r="D2041" t="n">
-        <v>-5.165723310474599</v>
+        <v>-5.231287300270372</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.401735536963316</v>
+        <v>1.375509941045007</v>
       </c>
       <c r="F2041" t="n">
-        <v>0.5357755543641074</v>
+        <v>0.4601808394585729</v>
       </c>
       <c r="G2041" t="n">
-        <v>3.789846618085368</v>
+        <v>3.744489789142048</v>
       </c>
     </row>
     <row r="2042">
@@ -48511,22 +48511,22 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.775233033906077</v>
+        <v>3.775233033906085</v>
       </c>
       <c r="C2042" t="n">
         <v>3.4482181312045</v>
       </c>
       <c r="D2042" t="n">
-        <v>-5.058759952625177</v>
+        <v>-5.124323942420951</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.424357725840681</v>
+        <v>1.398132129922372</v>
       </c>
       <c r="F2042" t="n">
-        <v>0.5942401623239089</v>
+        <v>0.5186454474183744</v>
       </c>
       <c r="G2042" t="n">
-        <v>3.804762228598846</v>
+        <v>3.759405399655525</v>
       </c>
     </row>
     <row r="2043">
@@ -48534,22 +48534,22 @@
         <v>45505</v>
       </c>
       <c r="B2043" t="n">
-        <v>3.785761685912981</v>
+        <v>3.785761685912989</v>
       </c>
       <c r="C2043" t="n">
         <v>3.483185067816559</v>
       </c>
       <c r="D2043" t="n">
-        <v>-5.003429364723415</v>
+        <v>-5.068993354519188</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.481456897613445</v>
+        <v>1.455231301695135</v>
       </c>
       <c r="F2043" t="n">
-        <v>0.649570750225671</v>
+        <v>0.5739760353201365</v>
       </c>
       <c r="G2043" t="n">
-        <v>3.872927517951962</v>
+        <v>3.827570689008641</v>
       </c>
     </row>
     <row r="2044">
@@ -48557,22 +48557,22 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.743767956539891</v>
+        <v>3.743767956539899</v>
       </c>
       <c r="C2044" t="n">
         <v>3.476871635717997</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.991375237810452</v>
+        <v>-5.056939227606225</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.479965116280068</v>
+        <v>1.453739520361758</v>
       </c>
       <c r="F2044" t="n">
-        <v>0.6616248771386338</v>
+        <v>0.5860301622330993</v>
       </c>
       <c r="G2044" t="n">
-        <v>3.873846562001177</v>
+        <v>3.828489733057856</v>
       </c>
     </row>
     <row r="2045">
@@ -48580,22 +48580,22 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.725010844811005</v>
+        <v>3.725010844811014</v>
       </c>
       <c r="C2045" t="n">
         <v>3.478752265902132</v>
       </c>
       <c r="D2045" t="n">
-        <v>-5.068730727938421</v>
+        <v>-5.134294717734194</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.450903550413016</v>
+        <v>1.424677954494707</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.5842693870106644</v>
+        <v>0.50867467210513</v>
       </c>
       <c r="G2045" t="n">
-        <v>3.829313898108532</v>
+        <v>3.78395706916521</v>
       </c>
     </row>
     <row r="2046">
@@ -48603,22 +48603,22 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.612322444382916</v>
+        <v>3.612322444382925</v>
       </c>
       <c r="C2046" t="n">
         <v>3.491603291780015</v>
       </c>
       <c r="D2046" t="n">
-        <v>-5.000682165246891</v>
+        <v>-5.066246155042665</v>
       </c>
       <c r="E2046" t="n">
-        <v>1.49097400136751</v>
+        <v>1.464748405449201</v>
       </c>
       <c r="F2046" t="n">
-        <v>0.6523179497021943</v>
+        <v>0.5767232347966598</v>
       </c>
       <c r="G2046" t="n">
-        <v>3.882994061601332</v>
+        <v>3.837637232658011</v>
       </c>
     </row>
     <row r="2047">
@@ -48626,22 +48626,22 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.645256780013423</v>
+        <v>3.645256780013432</v>
       </c>
       <c r="C2047" t="n">
         <v>3.511805961953609</v>
       </c>
       <c r="D2047" t="n">
-        <v>-5.232282558416392</v>
+        <v>-5.297846548212165</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.418536514273304</v>
+        <v>1.392310918354995</v>
       </c>
       <c r="F2047" t="n">
-        <v>0.6523179497021943</v>
+        <v>0.5767232347966598</v>
       </c>
       <c r="G2047" t="n">
-        <v>3.903196731774926</v>
+        <v>3.857839902831605</v>
       </c>
     </row>
     <row r="2048">
@@ -48649,22 +48649,22 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666747201498967</v>
+        <v>3.666747201498968</v>
       </c>
       <c r="C2048" t="n">
         <v>3.495412198020491</v>
       </c>
       <c r="D2048" t="n">
-        <v>-5.282334103945612</v>
+        <v>-5.347898093741385</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.382122132128498</v>
+        <v>1.355896536210189</v>
       </c>
       <c r="F2048" t="n">
-        <v>0.6523179497021943</v>
+        <v>0.5767232347966598</v>
       </c>
       <c r="G2048" t="n">
-        <v>3.886802967841808</v>
+        <v>3.841446138898487</v>
       </c>
     </row>
     <row r="2049">
@@ -48672,22 +48672,22 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.670048702800096</v>
+        <v>3.670048702800097</v>
       </c>
       <c r="C2049" t="n">
         <v>3.455664111613958</v>
       </c>
       <c r="D2049" t="n">
-        <v>-5.457440936522056</v>
+        <v>-5.52300492631783</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.272331312691387</v>
+        <v>1.246105716773078</v>
       </c>
       <c r="F2049" t="n">
-        <v>0.6523179497021943</v>
+        <v>0.5767232347966598</v>
       </c>
       <c r="G2049" t="n">
-        <v>3.847054881435275</v>
+        <v>3.801698052491954</v>
       </c>
     </row>
     <row r="2050">
@@ -48695,22 +48695,22 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.745573148660848</v>
+        <v>3.745573148660849</v>
       </c>
       <c r="C2050" t="n">
         <v>3.462686730610898</v>
       </c>
       <c r="D2050" t="n">
-        <v>-5.261340783091534</v>
+        <v>-5.326904772887307</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.357793993060536</v>
+        <v>1.331568397142227</v>
       </c>
       <c r="F2050" t="n">
-        <v>0.8484181031327171</v>
+        <v>0.7728233882271827</v>
       </c>
       <c r="G2050" t="n">
-        <v>3.971737592490529</v>
+        <v>3.926380763547208</v>
       </c>
     </row>
     <row r="2051">
@@ -48718,22 +48718,22 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.730570473395085</v>
+        <v>3.730570473395087</v>
       </c>
       <c r="C2051" t="n">
         <v>3.561857730183802</v>
       </c>
       <c r="D2051" t="n">
-        <v>-5.108315390978249</v>
+        <v>-5.173879380774022</v>
       </c>
       <c r="E2051" t="n">
-        <v>1.518175149478755</v>
+        <v>1.491949553560445</v>
       </c>
       <c r="F2051" t="n">
-        <v>1.001443495246001</v>
+        <v>0.9258487803404668</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.162723827331403</v>
+        <v>4.117366998388082</v>
       </c>
     </row>
     <row r="2052">
@@ -48741,22 +48741,22 @@
         <v>45514</v>
       </c>
       <c r="B2052" t="n">
-        <v>3.741278332791147</v>
+        <v>3.741278332791149</v>
       </c>
       <c r="C2052" t="n">
         <v>3.749323955092095</v>
       </c>
       <c r="D2052" t="n">
-        <v>-5.136622704851519</v>
+        <v>-5.202186694647293</v>
       </c>
       <c r="E2052" t="n">
-        <v>1.694318448837739</v>
+        <v>1.668092852919429</v>
       </c>
       <c r="F2052" t="n">
-        <v>1.001443495246001</v>
+        <v>0.9258487803404668</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.350190052239696</v>
+        <v>4.304833223296376</v>
       </c>
     </row>
     <row r="2053">
@@ -48764,22 +48764,22 @@
         <v>45515</v>
       </c>
       <c r="B2053" t="n">
-        <v>3.699115615620433</v>
+        <v>3.699115615620435</v>
       </c>
       <c r="C2053" t="n">
         <v>3.718726906446177</v>
       </c>
       <c r="D2053" t="n">
-        <v>-5.303215929965042</v>
+        <v>-5.368779919760815</v>
       </c>
       <c r="E2053" t="n">
-        <v>1.597084110146413</v>
+        <v>1.570858514228104</v>
       </c>
       <c r="F2053" t="n">
-        <v>0.8348502701324787</v>
+        <v>0.7592555552269444</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.219637068525665</v>
+        <v>4.174280239582345</v>
       </c>
     </row>
     <row r="2054">
@@ -48787,22 +48787,22 @@
         <v>45516</v>
       </c>
       <c r="B2054" t="n">
-        <v>3.708182519285645</v>
+        <v>3.708182519285647</v>
       </c>
       <c r="C2054" t="n">
         <v>3.722403309107895</v>
       </c>
       <c r="D2054" t="n">
-        <v>-5.280180136603476</v>
+        <v>-5.345744126399249</v>
       </c>
       <c r="E2054" t="n">
-        <v>1.609974830152757</v>
+        <v>1.583749234234447</v>
       </c>
       <c r="F2054" t="n">
-        <v>0.8348502701324787</v>
+        <v>0.7592555552269444</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.223313471187383</v>
+        <v>4.177956642244062</v>
       </c>
     </row>
     <row r="2055">
@@ -48810,22 +48810,22 @@
         <v>45517</v>
       </c>
       <c r="B2055" t="n">
-        <v>3.740581401399467</v>
+        <v>3.740581401399469</v>
       </c>
       <c r="C2055" t="n">
         <v>3.72002136423139</v>
       </c>
       <c r="D2055" t="n">
-        <v>-5.250934156147779</v>
+        <v>-5.316498145943553</v>
       </c>
       <c r="E2055" t="n">
-        <v>1.619291277458531</v>
+        <v>1.593065681540221</v>
       </c>
       <c r="F2055" t="n">
-        <v>0.8348502701324787</v>
+        <v>0.7592555552269444</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.220931526310878</v>
+        <v>4.175574697367558</v>
       </c>
     </row>
     <row r="2056">
@@ -48833,22 +48833,22 @@
         <v>45518</v>
       </c>
       <c r="B2056" t="n">
-        <v>3.699404642256368</v>
+        <v>3.699404642256372</v>
       </c>
       <c r="C2056" t="n">
         <v>3.717314603389025</v>
       </c>
       <c r="D2056" t="n">
-        <v>-5.35785970402563</v>
+        <v>-5.423423693821404</v>
       </c>
       <c r="E2056" t="n">
-        <v>1.573814297465026</v>
+        <v>1.547588701546716</v>
       </c>
       <c r="F2056" t="n">
-        <v>0.7279247222546273</v>
+        <v>0.6523300073490931</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.154069436741802</v>
+        <v>4.108712607798481</v>
       </c>
     </row>
     <row r="2057">
@@ -48856,22 +48856,22 @@
         <v>45519</v>
       </c>
       <c r="B2057" t="n">
-        <v>3.689942600700998</v>
+        <v>3.689942600701002</v>
       </c>
       <c r="C2057" t="n">
         <v>3.71874340553226</v>
       </c>
       <c r="D2057" t="n">
-        <v>-5.502878262532879</v>
+        <v>-5.568442252328652</v>
       </c>
       <c r="E2057" t="n">
-        <v>1.51723567620536</v>
+        <v>1.491010080287051</v>
       </c>
       <c r="F2057" t="n">
-        <v>0.5829061637473788</v>
+        <v>0.5073114488418445</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.068487103780687</v>
+        <v>4.023130274837366</v>
       </c>
     </row>
     <row r="2058">
@@ -48879,22 +48879,22 @@
         <v>45520</v>
       </c>
       <c r="B2058" t="n">
-        <v>3.71185242968701</v>
+        <v>3.711852429687013</v>
       </c>
       <c r="C2058" t="n">
         <v>3.818674644790013</v>
       </c>
       <c r="D2058" t="n">
-        <v>-5.621220028317596</v>
+        <v>-5.68678401811337</v>
       </c>
       <c r="E2058" t="n">
-        <v>1.569830209149226</v>
+        <v>1.543604613230917</v>
       </c>
       <c r="F2058" t="n">
-        <v>0.5935922023102689</v>
+        <v>0.5179974874047346</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.174829966176175</v>
+        <v>4.129473137232853</v>
       </c>
     </row>
     <row r="2059">
@@ -48902,22 +48902,22 @@
         <v>45521</v>
       </c>
       <c r="B2059" t="n">
-        <v>3.7148790517908</v>
+        <v>3.714879051790806</v>
       </c>
       <c r="C2059" t="n">
         <v>3.816460341915952</v>
       </c>
       <c r="D2059" t="n">
-        <v>-5.672630450638304</v>
+        <v>-5.738194440434078</v>
       </c>
       <c r="E2059" t="n">
-        <v>1.547051737346882</v>
+        <v>1.520826141428573</v>
       </c>
       <c r="F2059" t="n">
-        <v>0.5935922023102689</v>
+        <v>0.5179974874047346</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.172615663302113</v>
+        <v>4.127258834358793</v>
       </c>
     </row>
     <row r="2060">
@@ -48925,22 +48925,22 @@
         <v>45522</v>
       </c>
       <c r="B2060" t="n">
-        <v>3.704757949437328</v>
+        <v>3.704757949437335</v>
       </c>
       <c r="C2060" t="n">
         <v>3.816363469990241</v>
       </c>
       <c r="D2060" t="n">
-        <v>-5.752049901846056</v>
+        <v>-5.817613891641829</v>
       </c>
       <c r="E2060" t="n">
-        <v>1.51518708493807</v>
+        <v>1.488961489019761</v>
       </c>
       <c r="F2060" t="n">
-        <v>0.5935922023102689</v>
+        <v>0.5179974874047346</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.172518791376403</v>
+        <v>4.127161962433082</v>
       </c>
     </row>
     <row r="2061">
@@ -48948,22 +48948,22 @@
         <v>45523</v>
       </c>
       <c r="B2061" t="n">
-        <v>3.736804952298394</v>
+        <v>3.736804952298403</v>
       </c>
       <c r="C2061" t="n">
         <v>3.816357363548284</v>
       </c>
       <c r="D2061" t="n">
-        <v>-5.847512899763274</v>
+        <v>-5.913076889559047</v>
       </c>
       <c r="E2061" t="n">
-        <v>1.476995779329227</v>
+        <v>1.450770183410917</v>
       </c>
       <c r="F2061" t="n">
-        <v>0.5935922023102689</v>
+        <v>0.5179974874047346</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.172512684934445</v>
+        <v>4.127155855991125</v>
       </c>
     </row>
     <row r="2062">
@@ -48971,22 +48971,22 @@
         <v>45524</v>
       </c>
       <c r="B2062" t="n">
-        <v>3.715372960217997</v>
+        <v>3.715372960218006</v>
       </c>
       <c r="C2062" t="n">
         <v>3.814453760110895</v>
       </c>
       <c r="D2062" t="n">
-        <v>-5.783136988912559</v>
+        <v>-5.848700978708332</v>
       </c>
       <c r="E2062" t="n">
-        <v>1.500842540232123</v>
+        <v>1.474616944313814</v>
       </c>
       <c r="F2062" t="n">
-        <v>0.657968113160984</v>
+        <v>0.5823733982554498</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.209234628007485</v>
+        <v>4.163877799064164</v>
       </c>
     </row>
     <row r="2063">
@@ -48994,22 +48994,22 @@
         <v>45525</v>
       </c>
       <c r="B2063" t="n">
-        <v>3.736089413353533</v>
+        <v>3.736089413353541</v>
       </c>
       <c r="C2063" t="n">
         <v>3.820187577858621</v>
       </c>
       <c r="D2063" t="n">
-        <v>-5.838506151044752</v>
+        <v>-5.904070140840526</v>
       </c>
       <c r="E2063" t="n">
-        <v>1.484428693126972</v>
+        <v>1.458203097208663</v>
       </c>
       <c r="F2063" t="n">
-        <v>0.657968113160984</v>
+        <v>0.5823733982554498</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.214968445755212</v>
+        <v>4.169611616811891</v>
       </c>
     </row>
     <row r="2064">
@@ -49017,22 +49017,22 @@
         <v>45526</v>
       </c>
       <c r="B2064" t="n">
-        <v>3.736822870113276</v>
+        <v>3.736822870113285</v>
       </c>
       <c r="C2064" t="n">
         <v>3.819725941201554</v>
       </c>
       <c r="D2064" t="n">
-        <v>-5.856724618042361</v>
+        <v>-5.922288607838134</v>
       </c>
       <c r="E2064" t="n">
-        <v>1.476679669670861</v>
+        <v>1.450454073752552</v>
       </c>
       <c r="F2064" t="n">
-        <v>0.6328616759051419</v>
+        <v>0.5572669609996076</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.199442946744639</v>
+        <v>4.154086117801318</v>
       </c>
     </row>
     <row r="2065">
@@ -49040,22 +49040,22 @@
         <v>45527</v>
       </c>
       <c r="B2065" t="n">
-        <v>3.790272500113684</v>
+        <v>3.790272500113693</v>
       </c>
       <c r="C2065" t="n">
         <v>3.839600334051872</v>
       </c>
       <c r="D2065" t="n">
-        <v>-5.818041182698431</v>
+        <v>-5.883605172494204</v>
       </c>
       <c r="E2065" t="n">
-        <v>1.512027436658752</v>
+        <v>1.485801840740443</v>
       </c>
       <c r="F2065" t="n">
-        <v>0.6328616759051419</v>
+        <v>0.5572669609996076</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.219317339594958</v>
+        <v>4.173960510651638</v>
       </c>
     </row>
     <row r="2066">
@@ -49063,22 +49063,22 @@
         <v>45528</v>
       </c>
       <c r="B2066" t="n">
-        <v>3.794486844016436</v>
+        <v>3.794486844016438</v>
       </c>
       <c r="C2066" t="n">
         <v>3.8233010345766</v>
       </c>
       <c r="D2066" t="n">
-        <v>-5.712006187493121</v>
+        <v>-5.777570177288895</v>
       </c>
       <c r="E2066" t="n">
-        <v>1.538142135265604</v>
+        <v>1.511916539347294</v>
       </c>
       <c r="F2066" t="n">
-        <v>0.6328616759051419</v>
+        <v>0.5572669609996076</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.203018040119685</v>
+        <v>4.157661211176364</v>
       </c>
     </row>
     <row r="2067">
@@ -49086,22 +49086,22 @@
         <v>45529</v>
       </c>
       <c r="B2067" t="n">
-        <v>3.794705093307668</v>
+        <v>3.79470509330767</v>
       </c>
       <c r="C2067" t="n">
         <v>3.825731984040646</v>
       </c>
       <c r="D2067" t="n">
-        <v>-5.528794524360026</v>
+        <v>-5.594358514155799</v>
       </c>
       <c r="E2067" t="n">
-        <v>1.613857749982888</v>
+        <v>1.587632154064578</v>
       </c>
       <c r="F2067" t="n">
-        <v>0.6328616759051419</v>
+        <v>0.5572669609996076</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.205448989583731</v>
+        <v>4.160092160640411</v>
       </c>
     </row>
     <row r="2068">
@@ -49109,22 +49109,22 @@
         <v>45530</v>
       </c>
       <c r="B2068" t="n">
-        <v>3.776846557863549</v>
+        <v>3.776846557863551</v>
       </c>
       <c r="C2068" t="n">
         <v>3.808676390120023</v>
       </c>
       <c r="D2068" t="n">
-        <v>-5.457073077346175</v>
+        <v>-5.522637067141948</v>
       </c>
       <c r="E2068" t="n">
-        <v>1.625490734867805</v>
+        <v>1.599265138949496</v>
       </c>
       <c r="F2068" t="n">
-        <v>0.7045831229189925</v>
+        <v>0.6289884080134582</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.231426263871419</v>
+        <v>4.186069434928099</v>
       </c>
     </row>
     <row r="2069">
@@ -49132,22 +49132,22 @@
         <v>45531</v>
       </c>
       <c r="B2069" t="n">
-        <v>3.723789705394109</v>
+        <v>3.723789705394113</v>
       </c>
       <c r="C2069" t="n">
         <v>3.755592136041195</v>
       </c>
       <c r="D2069" t="n">
-        <v>-5.434700051738469</v>
+        <v>-5.500264041534242</v>
       </c>
       <c r="E2069" t="n">
-        <v>1.581355691032059</v>
+        <v>1.55513009511375</v>
       </c>
       <c r="F2069" t="n">
-        <v>0.7158388740318941</v>
+        <v>0.6402441591263598</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.185095460460332</v>
+        <v>4.139738631517011</v>
       </c>
     </row>
     <row r="2070">
@@ -49155,22 +49155,22 @@
         <v>45532</v>
       </c>
       <c r="B2070" t="n">
-        <v>3.715607446456726</v>
+        <v>3.715607446456731</v>
       </c>
       <c r="C2070" t="n">
         <v>3.94079034092655</v>
       </c>
       <c r="D2070" t="n">
-        <v>-5.467716347649214</v>
+        <v>-5.533280337444987</v>
       </c>
       <c r="E2070" t="n">
-        <v>1.753347377553117</v>
+        <v>1.727121781634807</v>
       </c>
       <c r="F2070" t="n">
-        <v>0.6464014973651424</v>
+        <v>0.5708067824596081</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.328631239345635</v>
+        <v>4.283274410402315</v>
       </c>
     </row>
     <row r="2071">
@@ -49178,22 +49178,22 @@
         <v>45533</v>
       </c>
       <c r="B2071" t="n">
-        <v>3.713762536883674</v>
+        <v>3.713762536883682</v>
       </c>
       <c r="C2071" t="n">
         <v>3.932711566754799</v>
       </c>
       <c r="D2071" t="n">
-        <v>-5.456188711999605</v>
+        <v>-5.521752701795378</v>
       </c>
       <c r="E2071" t="n">
-        <v>1.749879657641209</v>
+        <v>1.723654061722899</v>
       </c>
       <c r="F2071" t="n">
-        <v>0.7054021555665049</v>
+        <v>0.6298074406609706</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.355952860094702</v>
+        <v>4.310596031151381</v>
       </c>
     </row>
     <row r="2072">
@@ -49201,22 +49201,22 @@
         <v>45534</v>
       </c>
       <c r="B2072" t="n">
-        <v>3.717150699236295</v>
+        <v>3.717150699236303</v>
       </c>
       <c r="C2072" t="n">
         <v>3.936379679276587</v>
       </c>
       <c r="D2072" t="n">
-        <v>-5.553530213341974</v>
+        <v>-5.619094203137747</v>
       </c>
       <c r="E2072" t="n">
-        <v>1.71461116962605</v>
+        <v>1.688385573707741</v>
       </c>
       <c r="F2072" t="n">
-        <v>0.6609819734010165</v>
+        <v>0.5853872584954822</v>
       </c>
       <c r="G2072" t="n">
-        <v>4.332968863317197</v>
+        <v>4.287612034373877</v>
       </c>
     </row>
     <row r="2073">
@@ -49224,22 +49224,22 @@
         <v>45535</v>
       </c>
       <c r="B2073" t="n">
-        <v>3.705201079427681</v>
+        <v>3.70520107942769</v>
       </c>
       <c r="C2073" t="n">
         <v>3.937630761469426</v>
       </c>
       <c r="D2073" t="n">
-        <v>-5.63938624268194</v>
+        <v>-5.704950232477714</v>
       </c>
       <c r="E2073" t="n">
-        <v>1.681519840082902</v>
+        <v>1.655294244164592</v>
       </c>
       <c r="F2073" t="n">
-        <v>0.6186059041748815</v>
+        <v>0.5430111892693472</v>
       </c>
       <c r="G2073" t="n">
-        <v>4.308794303974355</v>
+        <v>4.263437475031035</v>
       </c>
     </row>
     <row r="2074">
@@ -49247,22 +49247,22 @@
         <v>45536</v>
       </c>
       <c r="B2074" t="n">
-        <v>3.691835499610379</v>
+        <v>3.69183549961038</v>
       </c>
       <c r="C2074" t="n">
         <v>3.920049963289927</v>
       </c>
       <c r="D2074" t="n">
-        <v>-5.64822304009806</v>
+        <v>-5.713787029893833</v>
       </c>
       <c r="E2074" t="n">
-        <v>1.660404322936956</v>
+        <v>1.634178727018646</v>
       </c>
       <c r="F2074" t="n">
-        <v>0.6111637315335308</v>
+        <v>0.5355690166279965</v>
       </c>
       <c r="G2074" t="n">
-        <v>4.286748202210046</v>
+        <v>4.241391373266726</v>
       </c>
     </row>
     <row r="2075">
@@ -49270,22 +49270,22 @@
         <v>45537</v>
       </c>
       <c r="B2075" t="n">
-        <v>3.715544411667452</v>
+        <v>3.715544411667459</v>
       </c>
       <c r="C2075" t="n">
         <v>3.930214474334977</v>
       </c>
       <c r="D2075" t="n">
-        <v>-5.739605602663518</v>
+        <v>-5.805169592459292</v>
       </c>
       <c r="E2075" t="n">
-        <v>1.634015808955822</v>
+        <v>1.607790213037512</v>
       </c>
       <c r="F2075" t="n">
-        <v>0.574598846814186</v>
+        <v>0.4990041319086518</v>
       </c>
       <c r="G2075" t="n">
-        <v>4.274973782423489</v>
+        <v>4.229616953480169</v>
       </c>
     </row>
     <row r="2076">
@@ -49293,22 +49293,22 @@
         <v>45538</v>
       </c>
       <c r="B2076" t="n">
-        <v>3.673978374889188</v>
+        <v>3.673978374889197</v>
       </c>
       <c r="C2076" t="n">
         <v>4.032342732159245</v>
       </c>
       <c r="D2076" t="n">
-        <v>-5.727898884676512</v>
+        <v>-5.793462874472286</v>
       </c>
       <c r="E2076" t="n">
-        <v>1.740826753974892</v>
+        <v>1.714601158056583</v>
       </c>
       <c r="F2076" t="n">
-        <v>0.5863055648011924</v>
+        <v>0.5107108498956582</v>
       </c>
       <c r="G2076" t="n">
-        <v>4.384126071039961</v>
+        <v>4.338769242096641</v>
       </c>
     </row>
     <row r="2077">
@@ -49316,22 +49316,22 @@
         <v>45539</v>
       </c>
       <c r="B2077" t="n">
-        <v>3.682476099409563</v>
+        <v>3.682476099409572</v>
       </c>
       <c r="C2077" t="n">
         <v>4.03537507089065</v>
       </c>
       <c r="D2077" t="n">
-        <v>-5.798810958418789</v>
+        <v>-5.864374948214563</v>
       </c>
       <c r="E2077" t="n">
-        <v>1.715494263209386</v>
+        <v>1.689268667291077</v>
       </c>
       <c r="F2077" t="n">
-        <v>0.5863055648011924</v>
+        <v>0.5107108498956582</v>
       </c>
       <c r="G2077" t="n">
-        <v>4.387158409771366</v>
+        <v>4.341801580828045</v>
       </c>
     </row>
     <row r="2078">
@@ -49339,22 +49339,22 @@
         <v>45540</v>
       </c>
       <c r="B2078" t="n">
-        <v>3.672895177452569</v>
+        <v>3.67289517745257</v>
       </c>
       <c r="C2078" t="n">
         <v>4.036193896622915</v>
       </c>
       <c r="D2078" t="n">
-        <v>-5.809127056585141</v>
+        <v>-5.874691046380915</v>
       </c>
       <c r="E2078" t="n">
-        <v>1.71218664967511</v>
+        <v>1.685961053756801</v>
       </c>
       <c r="F2078" t="n">
-        <v>0.5863055648011924</v>
+        <v>0.5107108498956582</v>
       </c>
       <c r="G2078" t="n">
-        <v>4.38797723550363</v>
+        <v>4.34262040656031</v>
       </c>
     </row>
     <row r="2079">
@@ -49362,22 +49362,22 @@
         <v>45541</v>
       </c>
       <c r="B2079" t="n">
-        <v>3.623960959762283</v>
+        <v>3.623960959762292</v>
       </c>
       <c r="C2079" t="n">
         <v>4.035372563535004</v>
       </c>
       <c r="D2079" t="n">
-        <v>-5.809033088567769</v>
+        <v>-5.874597078363542</v>
       </c>
       <c r="E2079" t="n">
-        <v>1.711402903794149</v>
+        <v>1.685177307875839</v>
       </c>
       <c r="F2079" t="n">
-        <v>0.5866754261485104</v>
+        <v>0.5110807112429762</v>
       </c>
       <c r="G2079" t="n">
-        <v>4.387377819224111</v>
+        <v>4.34202099028079</v>
       </c>
     </row>
     <row r="2080">
@@ -49385,22 +49385,22 @@
         <v>45542</v>
       </c>
       <c r="B2080" t="n">
-        <v>3.800870306884075</v>
+        <v>3.800870306884084</v>
       </c>
       <c r="C2080" t="n">
         <v>4.029604549479358</v>
       </c>
       <c r="D2080" t="n">
-        <v>-5.952634252591154</v>
+        <v>-6.018198242386927</v>
       </c>
       <c r="E2080" t="n">
-        <v>1.648194424129148</v>
+        <v>1.621968828210839</v>
       </c>
       <c r="F2080" t="n">
-        <v>0.5866754261485104</v>
+        <v>0.5110807112429762</v>
       </c>
       <c r="G2080" t="n">
-        <v>4.381609805168464</v>
+        <v>4.336252976225144</v>
       </c>
     </row>
     <row r="2081">
@@ -49408,22 +49408,22 @@
         <v>45543</v>
       </c>
       <c r="B2081" t="n">
-        <v>3.671015692129645</v>
+        <v>3.671015692129648</v>
       </c>
       <c r="C2081" t="n">
         <v>4.029604549479358</v>
       </c>
       <c r="D2081" t="n">
-        <v>-5.951685829473115</v>
+        <v>-6.017249819268889</v>
       </c>
       <c r="E2081" t="n">
-        <v>1.648573793376364</v>
+        <v>1.622348197458054</v>
       </c>
       <c r="F2081" t="n">
-        <v>0.5866754261485104</v>
+        <v>0.5110807112429762</v>
       </c>
       <c r="G2081" t="n">
-        <v>4.381609805168464</v>
+        <v>4.336252976225144</v>
       </c>
     </row>
     <row r="2082">
@@ -49431,22 +49431,22 @@
         <v>45544</v>
       </c>
       <c r="B2082" t="n">
-        <v>3.904173816052348</v>
+        <v>3.904173816052351</v>
       </c>
       <c r="C2082" t="n">
         <v>4.04233215746045</v>
       </c>
       <c r="D2082" t="n">
-        <v>-6.051955647432136</v>
+        <v>-6.117519637227909</v>
       </c>
       <c r="E2082" t="n">
-        <v>1.621193474173848</v>
+        <v>1.594967878255538</v>
       </c>
       <c r="F2082" t="n">
-        <v>0.5866754261485104</v>
+        <v>0.5110807112429762</v>
       </c>
       <c r="G2082" t="n">
-        <v>4.394337413149557</v>
+        <v>4.348980584206236</v>
       </c>
     </row>
     <row r="2083">
@@ -49454,22 +49454,22 @@
         <v>45545</v>
       </c>
       <c r="B2083" t="n">
-        <v>3.740179607813492</v>
+        <v>3.740179607813495</v>
       </c>
       <c r="C2083" t="n">
         <v>4.044278155884838</v>
       </c>
       <c r="D2083" t="n">
-        <v>-6.045963400643324</v>
+        <v>-6.111527390439098</v>
       </c>
       <c r="E2083" t="n">
-        <v>1.62553637131376</v>
+        <v>1.599310775395451</v>
       </c>
       <c r="F2083" t="n">
-        <v>0.5866754261485104</v>
+        <v>0.5110807112429762</v>
       </c>
       <c r="G2083" t="n">
-        <v>4.396283411573944</v>
+        <v>4.350926582630624</v>
       </c>
     </row>
     <row r="2084">
@@ -49477,22 +49477,22 @@
         <v>45546</v>
       </c>
       <c r="B2084" t="n">
-        <v>3.765050796537942</v>
+        <v>3.765050796537944</v>
       </c>
       <c r="C2084" t="n">
         <v>4.037932291902607</v>
       </c>
       <c r="D2084" t="n">
-        <v>-5.957405439512557</v>
+        <v>-6.02296942930833</v>
       </c>
       <c r="E2084" t="n">
-        <v>1.654613691783836</v>
+        <v>1.628388095865526</v>
       </c>
       <c r="F2084" t="n">
-        <v>0.5866754261485104</v>
+        <v>0.5110807112429762</v>
       </c>
       <c r="G2084" t="n">
-        <v>4.389937547591713</v>
+        <v>4.344580718648393</v>
       </c>
     </row>
     <row r="2085">
@@ -49500,22 +49500,22 @@
         <v>45547</v>
       </c>
       <c r="B2085" t="n">
-        <v>3.758409170771814</v>
+        <v>3.758409170771816</v>
       </c>
       <c r="C2085" t="n">
         <v>4.037240969341602</v>
       </c>
       <c r="D2085" t="n">
-        <v>-5.939646362009483</v>
+        <v>-6.005210351805256</v>
       </c>
       <c r="E2085" t="n">
-        <v>1.661026000224061</v>
+        <v>1.634800404305752</v>
       </c>
       <c r="F2085" t="n">
-        <v>0.5866754261485104</v>
+        <v>0.5110807112429762</v>
       </c>
       <c r="G2085" t="n">
-        <v>4.389246225030709</v>
+        <v>4.343889396087389</v>
       </c>
     </row>
     <row r="2086">
@@ -49523,22 +49523,22 @@
         <v>45548</v>
       </c>
       <c r="B2086" t="n">
-        <v>3.80134059710972</v>
+        <v>3.801340597109721</v>
       </c>
       <c r="C2086" t="n">
         <v>4.050023155250189</v>
       </c>
       <c r="D2086" t="n">
-        <v>-5.840016210960415</v>
+        <v>-5.905580200756188</v>
       </c>
       <c r="E2086" t="n">
-        <v>1.713660246552275</v>
+        <v>1.687434650633966</v>
       </c>
       <c r="F2086" t="n">
-        <v>0.6863055771975779</v>
+        <v>0.6107108622920436</v>
       </c>
       <c r="G2086" t="n">
-        <v>4.461806501568736</v>
+        <v>4.416449672625416</v>
       </c>
     </row>
     <row r="2087">
@@ -49546,22 +49546,22 @@
         <v>45549</v>
       </c>
       <c r="B2087" t="n">
-        <v>3.798465546843994</v>
+        <v>3.798465546843996</v>
       </c>
       <c r="C2087" t="n">
         <v>4.239177420748915</v>
       </c>
       <c r="D2087" t="n">
-        <v>-5.889415719649426</v>
+        <v>-5.954979709445199</v>
       </c>
       <c r="E2087" t="n">
-        <v>1.883054708575397</v>
+        <v>1.856829112657088</v>
       </c>
       <c r="F2087" t="n">
-        <v>0.6965644106293226</v>
+        <v>0.6209696957237884</v>
       </c>
       <c r="G2087" t="n">
-        <v>4.657116067126509</v>
+        <v>4.611759238183189</v>
       </c>
     </row>
     <row r="2088">
@@ -49569,22 +49569,22 @@
         <v>45550</v>
       </c>
       <c r="B2088" t="n">
-        <v>3.772186508351855</v>
+        <v>3.77218650835186</v>
       </c>
       <c r="C2088" t="n">
         <v>4.226366093851778</v>
       </c>
       <c r="D2088" t="n">
-        <v>-5.68273124600705</v>
+        <v>-5.748295235802823</v>
       </c>
       <c r="E2088" t="n">
-        <v>1.95291717113521</v>
+        <v>1.9266915752169</v>
       </c>
       <c r="F2088" t="n">
-        <v>0.9032488842716982</v>
+        <v>0.827654169366164</v>
       </c>
       <c r="G2088" t="n">
-        <v>4.768315424414797</v>
+        <v>4.722958595471476</v>
       </c>
     </row>
     <row r="2089">
@@ -49592,22 +49592,22 @@
         <v>45551</v>
       </c>
       <c r="B2089" t="n">
-        <v>3.763392838551265</v>
+        <v>3.76339283855127</v>
       </c>
       <c r="C2089" t="n">
         <v>4.228367607505882</v>
       </c>
       <c r="D2089" t="n">
-        <v>-5.716888141004576</v>
+        <v>-5.782452130800349</v>
       </c>
       <c r="E2089" t="n">
-        <v>1.941255926790304</v>
+        <v>1.915030330871995</v>
       </c>
       <c r="F2089" t="n">
-        <v>0.8196651147308858</v>
+        <v>0.7440703998253515</v>
       </c>
       <c r="G2089" t="n">
-        <v>4.720166676344414</v>
+        <v>4.674809847401094</v>
       </c>
     </row>
     <row r="2090">
@@ -49615,22 +49615,22 @@
         <v>45552</v>
       </c>
       <c r="B2090" t="n">
-        <v>3.805590565041106</v>
+        <v>3.805590565041111</v>
       </c>
       <c r="C2090" t="n">
         <v>4.58186472149555</v>
       </c>
       <c r="D2090" t="n">
-        <v>-5.624298661943119</v>
+        <v>-5.689862651738893</v>
       </c>
       <c r="E2090" t="n">
-        <v>2.331788832404554</v>
+        <v>2.305563236486245</v>
       </c>
       <c r="F2090" t="n">
-        <v>0.8196651147308858</v>
+        <v>0.7440703998253515</v>
       </c>
       <c r="G2090" t="n">
-        <v>5.073663790334082</v>
+        <v>5.028306961390761</v>
       </c>
     </row>
     <row r="2091">
@@ -49638,22 +49638,22 @@
         <v>45553</v>
       </c>
       <c r="B2091" t="n">
-        <v>3.832164354497396</v>
+        <v>3.832164354497403</v>
       </c>
       <c r="C2091" t="n">
         <v>4.586427833062654</v>
       </c>
       <c r="D2091" t="n">
-        <v>-5.697459265716264</v>
+        <v>-5.763023255512038</v>
       </c>
       <c r="E2091" t="n">
-        <v>2.3070877024624</v>
+        <v>2.280862106544091</v>
       </c>
       <c r="F2091" t="n">
-        <v>0.7916439146966427</v>
+        <v>0.7160491997911085</v>
       </c>
       <c r="G2091" t="n">
-        <v>5.06141418188064</v>
+        <v>5.016057352937319</v>
       </c>
     </row>
     <row r="2092">
@@ -49661,22 +49661,22 @@
         <v>45554</v>
       </c>
       <c r="B2092" t="n">
-        <v>3.858310890492286</v>
+        <v>3.858310890492296</v>
       </c>
       <c r="C2092" t="n">
         <v>4.636257774386181</v>
       </c>
       <c r="D2092" t="n">
-        <v>-5.645242955919922</v>
+        <v>-5.710806945715696</v>
       </c>
       <c r="E2092" t="n">
-        <v>2.377804167704464</v>
+        <v>2.351578571786155</v>
       </c>
       <c r="F2092" t="n">
-        <v>0.7916439146966427</v>
+        <v>0.7160491997911085</v>
       </c>
       <c r="G2092" t="n">
-        <v>5.111244123204167</v>
+        <v>5.065887294260847</v>
       </c>
     </row>
     <row r="2093">
@@ -49684,22 +49684,22 @@
         <v>45555</v>
       </c>
       <c r="B2093" t="n">
-        <v>3.844935596436468</v>
+        <v>3.844935596436478</v>
       </c>
       <c r="C2093" t="n">
         <v>4.645071744596192</v>
       </c>
       <c r="D2093" t="n">
-        <v>-5.592735628409428</v>
+        <v>-5.658299618205201</v>
       </c>
       <c r="E2093" t="n">
-        <v>2.407621068918673</v>
+        <v>2.381395473000364</v>
       </c>
       <c r="F2093" t="n">
-        <v>0.8441512422071377</v>
+        <v>0.7685565273016034</v>
       </c>
       <c r="G2093" t="n">
-        <v>5.151562489920475</v>
+        <v>5.106205660977155</v>
       </c>
     </row>
     <row r="2094">
@@ -49707,22 +49707,22 @@
         <v>45556</v>
       </c>
       <c r="B2094" t="n">
-        <v>3.848376866039477</v>
+        <v>3.848376866039487</v>
       </c>
       <c r="C2094" t="n">
         <v>4.640709328635389</v>
       </c>
       <c r="D2094" t="n">
-        <v>-5.607490952609568</v>
+        <v>-5.673054942405342</v>
       </c>
       <c r="E2094" t="n">
-        <v>2.397356523277814</v>
+        <v>2.371130927359505</v>
       </c>
       <c r="F2094" t="n">
-        <v>0.8441512422071377</v>
+        <v>0.7685565273016034</v>
       </c>
       <c r="G2094" t="n">
-        <v>5.147200073959672</v>
+        <v>5.101843245016352</v>
       </c>
     </row>
     <row r="2095">
@@ -49730,22 +49730,22 @@
         <v>45557</v>
       </c>
       <c r="B2095" t="n">
-        <v>3.868153115524471</v>
+        <v>3.868153115524482</v>
       </c>
       <c r="C2095" t="n">
         <v>4.631633832051669</v>
       </c>
       <c r="D2095" t="n">
-        <v>-5.558026329239657</v>
+        <v>-5.62359031903543</v>
       </c>
       <c r="E2095" t="n">
-        <v>2.408066876042059</v>
+        <v>2.381841280123749</v>
       </c>
       <c r="F2095" t="n">
-        <v>0.8936158655770493</v>
+        <v>0.818021150671515</v>
       </c>
       <c r="G2095" t="n">
-        <v>5.167803351397899</v>
+        <v>5.122446522454578</v>
       </c>
     </row>
     <row r="2096">
@@ -49753,22 +49753,22 @@
         <v>45558</v>
       </c>
       <c r="B2096" t="n">
-        <v>3.849040239867945</v>
+        <v>3.849040239867955</v>
       </c>
       <c r="C2096" t="n">
         <v>4.628041499766604</v>
       </c>
       <c r="D2096" t="n">
-        <v>-5.394918337086041</v>
+        <v>-5.460482326881815</v>
       </c>
       <c r="E2096" t="n">
-        <v>2.469717740618439</v>
+        <v>2.44349214470013</v>
       </c>
       <c r="F2096" t="n">
-        <v>1.056723857730665</v>
+        <v>0.9811291428251303</v>
       </c>
       <c r="G2096" t="n">
-        <v>5.262075814405002</v>
+        <v>5.216718985461682</v>
       </c>
     </row>
     <row r="2097">
@@ -49776,22 +49776,22 @@
         <v>45559</v>
       </c>
       <c r="B2097" t="n">
-        <v>3.870204928232968</v>
+        <v>3.870204928232971</v>
       </c>
       <c r="C2097" t="n">
         <v>4.637088536457732</v>
       </c>
       <c r="D2097" t="n">
-        <v>-5.374275246284814</v>
+        <v>-5.439839236080587</v>
       </c>
       <c r="E2097" t="n">
-        <v>2.487022013630058</v>
+        <v>2.460796417711749</v>
       </c>
       <c r="F2097" t="n">
-        <v>1.056723857730665</v>
+        <v>0.9811291428251303</v>
       </c>
       <c r="G2097" t="n">
-        <v>5.271122851096131</v>
+        <v>5.22576602215281</v>
       </c>
     </row>
     <row r="2098">
@@ -49799,22 +49799,22 @@
         <v>45560</v>
       </c>
       <c r="B2098" t="n">
-        <v>3.855534437179672</v>
+        <v>3.855534437179674</v>
       </c>
       <c r="C2098" t="n">
         <v>4.637946001443853</v>
       </c>
       <c r="D2098" t="n">
-        <v>-5.436983162759372</v>
+        <v>-5.502547152555145</v>
       </c>
       <c r="E2098" t="n">
-        <v>2.462796312026357</v>
+        <v>2.436570716108047</v>
       </c>
       <c r="F2098" t="n">
-        <v>0.9940159412561069</v>
+        <v>0.9184212263505726</v>
       </c>
       <c r="G2098" t="n">
-        <v>5.234355566197518</v>
+        <v>5.188998737254197</v>
       </c>
     </row>
     <row r="2099">
@@ -49822,22 +49822,22 @@
         <v>45561</v>
       </c>
       <c r="B2099" t="n">
-        <v>3.884687848967719</v>
+        <v>3.884687848967721</v>
       </c>
       <c r="C2099" t="n">
         <v>4.600855418234206</v>
       </c>
       <c r="D2099" t="n">
-        <v>-5.388975038915679</v>
+        <v>-5.454539028711452</v>
       </c>
       <c r="E2099" t="n">
-        <v>2.444908978354186</v>
+        <v>2.418683382435877</v>
       </c>
       <c r="F2099" t="n">
-        <v>0.9940159412561069</v>
+        <v>0.9184212263505726</v>
       </c>
       <c r="G2099" t="n">
-        <v>5.19726498298787</v>
+        <v>5.151908154044549</v>
       </c>
     </row>
     <row r="2100">
@@ -49845,22 +49845,22 @@
         <v>45562</v>
       </c>
       <c r="B2100" t="n">
-        <v>3.895362357018607</v>
+        <v>3.895362357018612</v>
       </c>
       <c r="C2100" t="n">
         <v>4.604787671792156</v>
       </c>
       <c r="D2100" t="n">
-        <v>-5.238856983693782</v>
+        <v>-5.304420973489555</v>
       </c>
       <c r="E2100" t="n">
-        <v>2.508888454000895</v>
+        <v>2.482662858082586</v>
       </c>
       <c r="F2100" t="n">
-        <v>1.144133996478004</v>
+        <v>1.06853928157247</v>
       </c>
       <c r="G2100" t="n">
-        <v>5.291268069678958</v>
+        <v>5.245911240735638</v>
       </c>
     </row>
     <row r="2101">
@@ -49868,22 +49868,22 @@
         <v>45563</v>
       </c>
       <c r="B2101" t="n">
-        <v>3.89161098107513</v>
+        <v>3.891610981075135</v>
       </c>
       <c r="C2101" t="n">
         <v>4.599686764399193</v>
       </c>
       <c r="D2101" t="n">
-        <v>-5.1471442639445</v>
+        <v>-5.112486172235681</v>
       </c>
       <c r="E2101" t="n">
-        <v>2.540472634507645</v>
+        <v>2.554335871191173</v>
       </c>
       <c r="F2101" t="n">
-        <v>1.144133996478004</v>
+        <v>1.06853928157247</v>
       </c>
       <c r="G2101" t="n">
-        <v>5.286167162285995</v>
+        <v>5.240810333342675</v>
       </c>
     </row>
     <row r="2102">
@@ -49891,22 +49891,22 @@
         <v>45564</v>
       </c>
       <c r="B2102" t="n">
-        <v>3.872432493435436</v>
+        <v>3.872432493435445</v>
       </c>
       <c r="C2102" t="n">
         <v>4.595040673788288</v>
       </c>
       <c r="D2102" t="n">
-        <v>-5.028970885926572</v>
+        <v>-4.994312794217754</v>
       </c>
       <c r="E2102" t="n">
-        <v>2.583095895103912</v>
+        <v>2.596959131787439</v>
       </c>
       <c r="F2102" t="n">
-        <v>1.262307374495931</v>
+        <v>1.186712659590397</v>
       </c>
       <c r="G2102" t="n">
-        <v>5.352425098485847</v>
+        <v>5.307068269542527</v>
       </c>
     </row>
     <row r="2103">
@@ -49914,22 +49914,22 @@
         <v>45565</v>
       </c>
       <c r="B2103" t="n">
-        <v>3.859571723917725</v>
+        <v>3.859571723917734</v>
       </c>
       <c r="C2103" t="n">
         <v>4.624129266651315</v>
       </c>
       <c r="D2103" t="n">
-        <v>-4.940123769067075</v>
+        <v>-4.905465677358256</v>
       </c>
       <c r="E2103" t="n">
-        <v>2.647723334710737</v>
+        <v>2.661586571394265</v>
       </c>
       <c r="F2103" t="n">
-        <v>1.351154491355429</v>
+        <v>1.275559776449894</v>
       </c>
       <c r="G2103" t="n">
-        <v>5.434821961464573</v>
+        <v>5.389465132521252</v>
       </c>
     </row>
     <row r="2104">
@@ -49937,22 +49937,22 @@
         <v>45566</v>
       </c>
       <c r="B2104" t="n">
-        <v>3.828006274013631</v>
+        <v>3.82800627401364</v>
       </c>
       <c r="C2104" t="n">
         <v>4.617689489662492</v>
       </c>
       <c r="D2104" t="n">
-        <v>-4.913074731373821</v>
+        <v>-4.878416639665002</v>
       </c>
       <c r="E2104" t="n">
-        <v>2.652103172799216</v>
+        <v>2.665966409482743</v>
       </c>
       <c r="F2104" t="n">
-        <v>1.378203529048683</v>
+        <v>1.302608814143148</v>
       </c>
       <c r="G2104" t="n">
-        <v>5.444611607091702</v>
+        <v>5.399254778148381</v>
       </c>
     </row>
     <row r="2105">
@@ -49960,22 +49960,22 @@
         <v>45567</v>
       </c>
       <c r="B2105" t="n">
-        <v>3.823987445263768</v>
+        <v>3.82398744526377</v>
       </c>
       <c r="C2105" t="n">
         <v>4.617689489662492</v>
       </c>
       <c r="D2105" t="n">
-        <v>-4.919108011560591</v>
+        <v>-4.884449919851773</v>
       </c>
       <c r="E2105" t="n">
-        <v>2.649689860724508</v>
+        <v>2.663553097408035</v>
       </c>
       <c r="F2105" t="n">
-        <v>1.378203529048683</v>
+        <v>1.302608814143148</v>
       </c>
       <c r="G2105" t="n">
-        <v>5.444611607091702</v>
+        <v>5.399254778148381</v>
       </c>
     </row>
     <row r="2106">
@@ -49983,22 +49983,22 @@
         <v>45568</v>
       </c>
       <c r="B2106" t="n">
-        <v>3.815657203170835</v>
+        <v>3.815657203170844</v>
       </c>
       <c r="C2106" t="n">
         <v>4.621327656804905</v>
       </c>
       <c r="D2106" t="n">
-        <v>-4.938150375659427</v>
+        <v>-4.936301695424934</v>
       </c>
       <c r="E2106" t="n">
-        <v>2.645711082227386</v>
+        <v>2.646450554321183</v>
       </c>
       <c r="F2106" t="n">
-        <v>1.359161164949847</v>
+        <v>1.250757038569987</v>
       </c>
       <c r="G2106" t="n">
-        <v>5.436824355774813</v>
+        <v>5.371781879946897</v>
       </c>
     </row>
     <row r="2107">
@@ -50006,22 +50006,22 @@
         <v>45569</v>
       </c>
       <c r="B2107" t="n">
-        <v>3.830586986431405</v>
+        <v>3.830586986431407</v>
       </c>
       <c r="C2107" t="n">
         <v>4.584819403988742</v>
       </c>
       <c r="D2107" t="n">
-        <v>-4.965207821791254</v>
+        <v>-4.963359141556761</v>
       </c>
       <c r="E2107" t="n">
-        <v>2.598379850958492</v>
+        <v>2.599119323052289</v>
       </c>
       <c r="F2107" t="n">
-        <v>1.359161164949847</v>
+        <v>1.250757038569987</v>
       </c>
       <c r="G2107" t="n">
-        <v>5.40031610295865</v>
+        <v>5.335273627130734</v>
       </c>
     </row>
     <row r="2108">
@@ -50029,22 +50029,22 @@
         <v>45570</v>
       </c>
       <c r="B2108" t="n">
-        <v>3.830856457232448</v>
+        <v>3.830856457232453</v>
       </c>
       <c r="C2108" t="n">
         <v>4.586227353735933</v>
       </c>
       <c r="D2108" t="n">
-        <v>-5.068384731369198</v>
+        <v>-5.036640493410636</v>
       </c>
       <c r="E2108" t="n">
-        <v>2.558517036874506</v>
+        <v>2.571214732057931</v>
       </c>
       <c r="F2108" t="n">
-        <v>1.307920875567864</v>
+        <v>1.236845616438775</v>
       </c>
       <c r="G2108" t="n">
-        <v>5.370979879076652</v>
+        <v>5.328334723599198</v>
       </c>
     </row>
     <row r="2109">
@@ -50052,22 +50052,22 @@
         <v>45571</v>
       </c>
       <c r="B2109" t="n">
-        <v>3.637552659121755</v>
+        <v>3.784899418085193</v>
       </c>
       <c r="C2109" t="n">
-        <v>4.546630944171956</v>
+        <v>4.600747436321408</v>
       </c>
       <c r="D2109" t="n">
-        <v>-5.068384731369198</v>
+        <v>-5.036640493410636</v>
       </c>
       <c r="E2109" t="n">
-        <v>2.558517036874506</v>
+        <v>2.571214732057931</v>
       </c>
       <c r="F2109" t="n">
-        <v>1.307920875567864</v>
+        <v>1.236845616438775</v>
       </c>
       <c r="G2109" t="n">
-        <v>4.539694741158324</v>
+        <v>4.593811233307775</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20241006.xlsx
+++ b/tame_output/ON/bt/strategyON_20241006.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>53.8%</t>
+          <t>57.1%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.6%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.2%</t>
+          <t>65.1%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>68.0%</t>
+          <t>68.1%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>17.7%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.5%</t>
+          <t>-11.6%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>50.4%</t>
+          <t>62.7%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>102.3%</t>
+          <t>107.9%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>43.2%</t>
+          <t>43.9%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>45.7%</t>
+          <t>46.9%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,12 +834,12 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>10.5%</t>
+          <t>10.6%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-7.8%</t>
+          <t>-8.2%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>85.9%</t>
+          <t>89.8%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>35.4%</t>
+          <t>35.9%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.6%</t>
+          <t>39.9%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>148.4%</t>
+          <t>165.8%</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-78.0%</t>
+          <t>-77.6%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>89.9%</t>
+          <t>89.8%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>21.7%</t>
+          <t>21.6%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-48.0%</t>
+          <t>-47.7%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-74.3%</t>
+          <t>-73.9%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>88.8%</t>
+          <t>88.7%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>420.5%</t>
+          <t>421.6%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-6.4%</t>
+          <t>-6.5%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-665.2%</t>
+          <t>-656.9%</t>
         </is>
       </c>
     </row>
@@ -1074,22 +1074,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>30.7%</t>
+          <t>31.4%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>59.4%</t>
+          <t>59.3%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>57.2%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>-3.8%</t>
+          <t>-3.9%</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-31.1%</t>
+          <t>-30.8%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>26.5%</t>
+          <t>27.1%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-4.1%</t>
+          <t>-4.2%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-119.1%</t>
+          <t>-115.8%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-3.5%</t>
+          <t>-1.2%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.9%</t>
+          <t>66.8%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.8%</t>
+          <t>54.9%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>62.8%</t>
+          <t>62.6%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1298,22 +1298,22 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>-5.5%</t>
+          <t>-4.1%</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>-3.2%</t>
+          <t>-3.1%</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.7%</t>
+          <t>10.5%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-24.1%</t>
+          <t>-24.8%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>5.3%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.7%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>43.1%</t>
+          <t>48.0%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-166.3%</t>
+          <t>-216.2%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-100.3%</t>
+          <t>-87.6%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>68.8%</t>
+          <t>80.6%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>65.1%</t>
+          <t>63.3%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>76.4%</t>
+          <t>72.7%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1447,7 +1447,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>14.2%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-24.0%</t>
+          <t>-23.3%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>59.5%</t>
+          <t>73.3%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>54.2%</t>
+          <t>52.9%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.0%</t>
+          <t>-16.4%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>36.6%</t>
+          <t>35.9%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>13.4%</t>
+          <t>30.7%</t>
         </is>
       </c>
     </row>
@@ -46976,10 +46976,10 @@
         <v>2.360186451293727</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.238583689894325</v>
+        <v>-4.25283788022417</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.6643965510222489</v>
+        <v>0.6586948748903112</v>
       </c>
       <c r="F1975" t="n">
         <v>0.4708556194816057</v>
@@ -46999,10 +46999,10 @@
         <v>2.360049318729163</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.194210558255756</v>
+        <v>-4.208464748585601</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.6820086711131126</v>
+        <v>0.6763069949811749</v>
       </c>
       <c r="F1976" t="n">
         <v>0.5152287511201743</v>
@@ -47022,10 +47022,10 @@
         <v>2.354443112867754</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.159479236937256</v>
+        <v>-4.1737334272671</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.6902949937791034</v>
+        <v>0.6845933176471655</v>
       </c>
       <c r="F1977" t="n">
         <v>0.5152287511201743</v>
@@ -47045,10 +47045,10 @@
         <v>2.360824869895558</v>
       </c>
       <c r="D1978" t="n">
-        <v>-4.1118235063762</v>
+        <v>-4.126077696706044</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.7157390430313304</v>
+        <v>0.7100373668993925</v>
       </c>
       <c r="F1978" t="n">
         <v>0.56288448168123</v>
@@ -47068,10 +47068,10 @@
         <v>2.365717243270283</v>
       </c>
       <c r="D1979" t="n">
-        <v>-4.011305347877445</v>
+        <v>-4.02555953820729</v>
       </c>
       <c r="E1979" t="n">
-        <v>0.7608386798055571</v>
+        <v>0.7551370036736191</v>
       </c>
       <c r="F1979" t="n">
         <v>0.6634026401799845</v>
@@ -47091,10 +47091,10 @@
         <v>2.352471915746155</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.995400018445093</v>
+        <v>-4.009654208774937</v>
       </c>
       <c r="E1980" t="n">
-        <v>0.7539554840543703</v>
+        <v>0.7482538079224326</v>
       </c>
       <c r="F1980" t="n">
         <v>0.5842899794707457</v>
@@ -47114,10 +47114,10 @@
         <v>2.356569618356784</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.950561616836695</v>
+        <v>-3.964815807166539</v>
       </c>
       <c r="E1981" t="n">
-        <v>0.7759885473083581</v>
+        <v>0.7702868711764204</v>
       </c>
       <c r="F1981" t="n">
         <v>0.5888334124156152</v>
@@ -47137,10 +47137,10 @@
         <v>2.360730557987862</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.970060073078703</v>
+        <v>-3.984314263408547</v>
       </c>
       <c r="E1982" t="n">
-        <v>0.7723501044426329</v>
+        <v>0.7666484283106949</v>
       </c>
       <c r="F1982" t="n">
         <v>0.5407487711357108</v>
@@ -47160,10 +47160,10 @@
         <v>2.366610160515699</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.925857235992802</v>
+        <v>-3.940111426322647</v>
       </c>
       <c r="E1983" t="n">
-        <v>0.7959108418048302</v>
+        <v>0.7902091656728922</v>
       </c>
       <c r="F1983" t="n">
         <v>0.5849516082216113</v>
@@ -47183,10 +47183,10 @@
         <v>2.365020160984947</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.933416901829849</v>
+        <v>-3.947671092159694</v>
       </c>
       <c r="E1984" t="n">
-        <v>0.791296975939259</v>
+        <v>0.785595299807321</v>
       </c>
       <c r="F1984" t="n">
         <v>0.6397550122314306</v>
@@ -47206,10 +47206,10 @@
         <v>2.416267926167986</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.775125484290577</v>
+        <v>-3.789379674620422</v>
       </c>
       <c r="E1985" t="n">
-        <v>0.9058613081380074</v>
+        <v>0.9001596320060696</v>
       </c>
       <c r="F1985" t="n">
         <v>0.6397550122314306</v>
@@ -47229,10 +47229,10 @@
         <v>2.414708630762239</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.567483480656101</v>
+        <v>-3.581737670985945</v>
       </c>
       <c r="E1986" t="n">
-        <v>0.987358814186051</v>
+        <v>0.9816571380541133</v>
       </c>
       <c r="F1986" t="n">
         <v>0.8473970158659068</v>
@@ -47252,10 +47252,10 @@
         <v>2.409656859000509</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.516451387933573</v>
+        <v>-3.530705578263417</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.002719879513332</v>
+        <v>0.9970182033813946</v>
       </c>
       <c r="F1987" t="n">
         <v>0.8984291085884347</v>
@@ -47275,10 +47275,10 @@
         <v>2.426844263093214</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.451227206806367</v>
+        <v>-3.465481397136212</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.04599695605692</v>
+        <v>1.040295279924982</v>
       </c>
       <c r="F1988" t="n">
         <v>0.9636532897156403</v>
@@ -47298,10 +47298,10 @@
         <v>2.422805235392495</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.413800186735233</v>
+        <v>-3.428054377065078</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.056928736384653</v>
+        <v>1.051227060252716</v>
       </c>
       <c r="F1989" t="n">
         <v>0.968904827744822</v>
@@ -47321,10 +47321,10 @@
         <v>2.424062027723735</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.412442201761688</v>
+        <v>-3.426696392091532</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.058728722705312</v>
+        <v>1.053027046573374</v>
       </c>
       <c r="F1990" t="n">
         <v>1.043242953282641</v>
@@ -47344,10 +47344,10 @@
         <v>2.584619798744946</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.384028938661804</v>
+        <v>-3.398283128991649</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.230651798966476</v>
+        <v>1.224950122834538</v>
       </c>
       <c r="F1991" t="n">
         <v>0.9842673905362118</v>
@@ -47367,10 +47367,10 @@
         <v>2.704732707962763</v>
       </c>
       <c r="D1992" t="n">
-        <v>-3.309246677636791</v>
+        <v>-3.323500867966636</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.380677612594298</v>
+        <v>1.374975936462361</v>
       </c>
       <c r="F1992" t="n">
         <v>1.059049651561224</v>
@@ -47390,10 +47390,10 @@
         <v>2.696440683976622</v>
       </c>
       <c r="D1993" t="n">
-        <v>-3.283162593372984</v>
+        <v>-3.297416783702828</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.382819222313681</v>
+        <v>1.377117546181743</v>
       </c>
       <c r="F1993" t="n">
         <v>1.059049651561224</v>
@@ -47413,10 +47413,10 @@
         <v>2.694633879560401</v>
       </c>
       <c r="D1994" t="n">
-        <v>-3.195284680263863</v>
+        <v>-3.209538870593708</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.416163583141108</v>
+        <v>1.41046190700917</v>
       </c>
       <c r="F1994" t="n">
         <v>1.174975293984576</v>
@@ -47436,10 +47436,10 @@
         <v>2.712188285287193</v>
       </c>
       <c r="D1995" t="n">
-        <v>-3.18639221887058</v>
+        <v>-3.200646409200425</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.437274973425213</v>
+        <v>1.431573297293275</v>
       </c>
       <c r="F1995" t="n">
         <v>1.174975293984576</v>
@@ -47459,10 +47459,10 @@
         <v>2.704043332691777</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.354868335840458</v>
+        <v>-3.369122526170302</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.361739574041846</v>
+        <v>1.356037897909908</v>
       </c>
       <c r="F1996" t="n">
         <v>1.147027458267995</v>
@@ -47482,10 +47482,10 @@
         <v>2.685313029879639</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.908612143211018</v>
+        <v>-2.922866333540862</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.521511748281484</v>
+        <v>1.515810072149546</v>
       </c>
       <c r="F1997" t="n">
         <v>1.052308788598362</v>
@@ -47505,10 +47505,10 @@
         <v>2.675977052376543</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.885891039527865</v>
+        <v>-2.90014522985771</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.521264212251649</v>
+        <v>1.515562536119711</v>
       </c>
       <c r="F1998" t="n">
         <v>1.052308788598362</v>
@@ -47528,10 +47528,10 @@
         <v>2.834883178227712</v>
       </c>
       <c r="D1999" t="n">
-        <v>-3.015092852821908</v>
+        <v>-3.029347043151752</v>
       </c>
       <c r="E1999" t="n">
-        <v>1.628489612785201</v>
+        <v>1.622787936653263</v>
       </c>
       <c r="F1999" t="n">
         <v>0.92310697530432</v>
@@ -47551,10 +47551,10 @@
         <v>2.871961000721359</v>
       </c>
       <c r="D2000" t="n">
-        <v>-3.040967251295934</v>
+        <v>-3.055221441625778</v>
       </c>
       <c r="E2000" t="n">
-        <v>1.655217675889237</v>
+        <v>1.649515999757299</v>
       </c>
       <c r="F2000" t="n">
         <v>0.9680185840160611</v>
@@ -47574,10 +47574,10 @@
         <v>2.868636356710904</v>
       </c>
       <c r="D2001" t="n">
-        <v>-3.03391256108076</v>
+        <v>-3.048166751410605</v>
       </c>
       <c r="E2001" t="n">
-        <v>1.654714907964852</v>
+        <v>1.649013231832914</v>
       </c>
       <c r="F2001" t="n">
         <v>0.9750732742312349</v>
@@ -47597,10 +47597,10 @@
         <v>2.878642510355645</v>
       </c>
       <c r="D2002" t="n">
-        <v>-3.006961336754272</v>
+        <v>-3.021215527084117</v>
       </c>
       <c r="E2002" t="n">
-        <v>1.675501551340189</v>
+        <v>1.669799875208251</v>
       </c>
       <c r="F2002" t="n">
         <v>0.9899536202589541</v>
@@ -47620,10 +47620,10 @@
         <v>3.062745642500605</v>
       </c>
       <c r="D2003" t="n">
-        <v>-3.028505564585059</v>
+        <v>-3.042759754914904</v>
       </c>
       <c r="E2003" t="n">
-        <v>1.850986992352833</v>
+        <v>1.845285316220896</v>
       </c>
       <c r="F2003" t="n">
         <v>0.9899536202589541</v>
@@ -47643,10 +47643,10 @@
         <v>3.054862337403598</v>
       </c>
       <c r="D2004" t="n">
-        <v>-3.050913682389931</v>
+        <v>-3.065167872719776</v>
       </c>
       <c r="E2004" t="n">
-        <v>1.834140440133878</v>
+        <v>1.82843876400194</v>
       </c>
       <c r="F2004" t="n">
         <v>0.9899536202589541</v>
@@ -47666,10 +47666,10 @@
         <v>3.056916336953236</v>
       </c>
       <c r="D2005" t="n">
-        <v>-3.079137917967532</v>
+        <v>-3.093392108297376</v>
       </c>
       <c r="E2005" t="n">
-        <v>1.824904745452475</v>
+        <v>1.819203069320537</v>
       </c>
       <c r="F2005" t="n">
         <v>1.007930372710263</v>
@@ -47689,10 +47689,10 @@
         <v>3.113170054675083</v>
       </c>
       <c r="D2006" t="n">
-        <v>-3.088578843856062</v>
+        <v>-3.102833034185906</v>
       </c>
       <c r="E2006" t="n">
-        <v>1.87738209281891</v>
+        <v>1.871680416686972</v>
       </c>
       <c r="F2006" t="n">
         <v>1.130357490253654</v>
@@ -47712,10 +47712,10 @@
         <v>3.116061149220384</v>
       </c>
       <c r="D2007" t="n">
-        <v>-3.294817781644495</v>
+        <v>-3.30907197197434</v>
       </c>
       <c r="E2007" t="n">
-        <v>1.797777612248838</v>
+        <v>1.7920759361169</v>
       </c>
       <c r="F2007" t="n">
         <v>0.9241185524652205</v>
@@ -47735,10 +47735,10 @@
         <v>3.114172962114159</v>
       </c>
       <c r="D2008" t="n">
-        <v>-3.371147759245401</v>
+        <v>-3.385401949575245</v>
       </c>
       <c r="E2008" t="n">
-        <v>1.765357434102251</v>
+        <v>1.759655757970313</v>
       </c>
       <c r="F2008" t="n">
         <v>0.9241185524652205</v>
@@ -47758,10 +47758,10 @@
         <v>3.108993191717021</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.52610454464553</v>
+        <v>-3.540358734975375</v>
       </c>
       <c r="E2009" t="n">
-        <v>1.698194949545061</v>
+        <v>1.692493273413124</v>
       </c>
       <c r="F2009" t="n">
         <v>0.7691617670650912</v>
@@ -47775,16 +47775,16 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343071</v>
+        <v>3.71289761234307</v>
       </c>
       <c r="C2010" t="n">
         <v>3.107427201927174</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.687672970172785</v>
+        <v>-3.70192716050263</v>
       </c>
       <c r="E2010" t="n">
-        <v>1.632001589544311</v>
+        <v>1.626299913412374</v>
       </c>
       <c r="F2010" t="n">
         <v>0.6423788432672118</v>
@@ -47804,10 +47804,10 @@
         <v>3.120500608793092</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.795973632042905</v>
+        <v>-3.810227822372749</v>
       </c>
       <c r="E2011" t="n">
-        <v>1.601754731662182</v>
+        <v>1.596053055530245</v>
       </c>
       <c r="F2011" t="n">
         <v>0.6423788432672118</v>
@@ -47827,10 +47827,10 @@
         <v>3.112505805576032</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.955524704806422</v>
+        <v>-3.969778895136266</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.529939499339716</v>
+        <v>1.524237823207778</v>
       </c>
       <c r="F2012" t="n">
         <v>0.4901011764054604</v>
@@ -47850,10 +47850,10 @@
         <v>3.111029846703034</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.983425491915895</v>
+        <v>-3.997679682245739</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.517303225622928</v>
+        <v>1.51160154949099</v>
       </c>
       <c r="F2013" t="n">
         <v>0.4555042522625256</v>
@@ -47873,10 +47873,10 @@
         <v>3.107794290680233</v>
       </c>
       <c r="D2014" t="n">
-        <v>-4.105951594618789</v>
+        <v>-4.120205784948633</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.465057228518969</v>
+        <v>1.459355552387032</v>
       </c>
       <c r="F2014" t="n">
         <v>0.3329781495596317</v>
@@ -47896,10 +47896,10 @@
         <v>3.174500250270737</v>
       </c>
       <c r="D2015" t="n">
-        <v>-4.336466090804378</v>
+        <v>-4.350720281134222</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.439557389635238</v>
+        <v>1.4338557135033</v>
       </c>
       <c r="F2015" t="n">
         <v>0.102463653374043</v>
@@ -47919,10 +47919,10 @@
         <v>3.314811969272584</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.685211176028822</v>
+        <v>-4.699465366358665</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.440371074547307</v>
+        <v>1.43466939841537</v>
       </c>
       <c r="F2016" t="n">
         <v>-0.006284300544854848</v>
@@ -47942,10 +47942,10 @@
         <v>3.383792238418224</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.839197593804962</v>
+        <v>-4.853451784134806</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.447756776582491</v>
+        <v>1.442055100450553</v>
       </c>
       <c r="F2017" t="n">
         <v>-0.006284300544854848</v>
@@ -47965,10 +47965,10 @@
         <v>3.369843440538344</v>
       </c>
       <c r="D2018" t="n">
-        <v>-5.043797028667971</v>
+        <v>-5.058051218997814</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.351968204757408</v>
+        <v>1.34626652862547</v>
       </c>
       <c r="F2018" t="n">
         <v>-0.006284300544854848</v>
@@ -47988,10 +47988,10 @@
         <v>3.381713929593758</v>
       </c>
       <c r="D2019" t="n">
-        <v>-5.296272182675695</v>
+        <v>-5.310526373005539</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.262848632209733</v>
+        <v>1.257146956077795</v>
       </c>
       <c r="F2019" t="n">
         <v>-0.006284300544854848</v>
@@ -48011,10 +48011,10 @@
         <v>3.382924464112702</v>
       </c>
       <c r="D2020" t="n">
-        <v>-5.589167939155107</v>
+        <v>-5.603422129484951</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.146900864136911</v>
+        <v>1.141199188004974</v>
       </c>
       <c r="F2020" t="n">
         <v>-0.006284300544854848</v>
@@ -48034,10 +48034,10 @@
         <v>3.387046206340024</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.775832067289915</v>
+        <v>-5.790086257619759</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.07635695511031</v>
+        <v>1.070655278978372</v>
       </c>
       <c r="F2021" t="n">
         <v>-0.03302327136941474</v>
@@ -48057,10 +48057,10 @@
         <v>3.382124059076213</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.921852754203877</v>
+        <v>-5.936106944533721</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.013026533080914</v>
+        <v>1.007324856948976</v>
       </c>
       <c r="F2022" t="n">
         <v>-0.04210636316327171</v>
@@ -48080,10 +48080,10 @@
         <v>3.544328115775257</v>
       </c>
       <c r="D2023" t="n">
-        <v>-6.013566763313463</v>
+        <v>-6.027820953643307</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.138544986136124</v>
+        <v>1.132843310004186</v>
       </c>
       <c r="F2023" t="n">
         <v>-0.04210636316327171</v>
@@ -48103,16 +48103,16 @@
         <v>3.539174753739071</v>
       </c>
       <c r="D2024" t="n">
-        <v>-6.038356454893608</v>
+        <v>-6.059472612703276</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.12347574746788</v>
+        <v>1.115029284344013</v>
       </c>
       <c r="F2024" t="n">
-        <v>-0.07357933481011636</v>
+        <v>-0.04727482040771191</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.495027152853002</v>
+        <v>3.510809861494444</v>
       </c>
     </row>
     <row r="2025">
@@ -48126,16 +48126,16 @@
         <v>3.549404171307562</v>
       </c>
       <c r="D2025" t="n">
-        <v>-6.107422509466545</v>
+        <v>-6.128538667276213</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.106078743207196</v>
+        <v>1.097632280083329</v>
       </c>
       <c r="F2025" t="n">
-        <v>-0.1359502123037264</v>
+        <v>-0.1096456979013219</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.467834043925327</v>
+        <v>3.483616752566769</v>
       </c>
     </row>
     <row r="2026">
@@ -48149,16 +48149,16 @@
         <v>3.558329809763465</v>
       </c>
       <c r="D2026" t="n">
-        <v>-6.209398631714953</v>
+        <v>-6.126031610773144</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.074213932763736</v>
+        <v>1.107560741140459</v>
       </c>
       <c r="F2026" t="n">
-        <v>-0.237926334552134</v>
+        <v>-0.1071386413982535</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.415574009032185</v>
+        <v>3.494046624924513</v>
       </c>
     </row>
     <row r="2027">
@@ -48172,16 +48172,16 @@
         <v>3.55048269700764</v>
       </c>
       <c r="D2027" t="n">
-        <v>-6.099392348237731</v>
+        <v>-6.016025327295923</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.1103693333988</v>
+        <v>1.143716141775523</v>
       </c>
       <c r="F2027" t="n">
-        <v>-0.2147217626348588</v>
+        <v>-0.08393406948097831</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.421649639426725</v>
+        <v>3.500122255319054</v>
       </c>
     </row>
     <row r="2028">
@@ -48195,16 +48195,16 @@
         <v>3.554732707729614</v>
       </c>
       <c r="D2028" t="n">
-        <v>-6.11192205334961</v>
+        <v>-6.028555032407802</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.109607462076022</v>
+        <v>1.142954270452746</v>
       </c>
       <c r="F2028" t="n">
-        <v>-0.2285482621013818</v>
+        <v>-0.09776056894750135</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.417603750468786</v>
+        <v>3.496076366361114</v>
       </c>
     </row>
     <row r="2029">
@@ -48218,16 +48218,16 @@
         <v>3.56199359061215</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.810475327877772</v>
+        <v>-5.727108306935964</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.237447035147293</v>
+        <v>1.270793843524017</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.07289846337045547</v>
+        <v>0.2036861565243359</v>
       </c>
       <c r="G2029" t="n">
-        <v>3.605732668634424</v>
+        <v>3.684205284526752</v>
       </c>
     </row>
     <row r="2030">
@@ -48241,16 +48241,16 @@
         <v>3.562964768364861</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.835065572112956</v>
+        <v>-5.751698551171148</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.22858211520593</v>
+        <v>1.261928923582654</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.07289846337045547</v>
+        <v>0.2036861565243359</v>
       </c>
       <c r="G2030" t="n">
-        <v>3.606703846387135</v>
+        <v>3.685176462279463</v>
       </c>
     </row>
     <row r="2031">
@@ -48264,16 +48264,16 @@
         <v>3.563807672744617</v>
       </c>
       <c r="D2031" t="n">
-        <v>-5.784027196106436</v>
+        <v>-5.700660175164628</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.249840369988294</v>
+        <v>1.283187178365018</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.07289846337045547</v>
+        <v>0.2036861565243359</v>
       </c>
       <c r="G2031" t="n">
-        <v>3.60754675076689</v>
+        <v>3.686019366659218</v>
       </c>
     </row>
     <row r="2032">
@@ -48287,16 +48287,16 @@
         <v>3.582845771618762</v>
       </c>
       <c r="D2032" t="n">
-        <v>-5.755178519282976</v>
+        <v>-5.671811498341167</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.280417939591824</v>
+        <v>1.313764747968547</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.1017471401939157</v>
+        <v>0.2325348333477962</v>
       </c>
       <c r="G2032" t="n">
-        <v>3.643894055735112</v>
+        <v>3.72236667162744</v>
       </c>
     </row>
     <row r="2033">
@@ -48310,16 +48310,16 @@
         <v>3.399029767742697</v>
       </c>
       <c r="D2033" t="n">
-        <v>-5.658543607264336</v>
+        <v>-5.575176586322527</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.135255900523215</v>
+        <v>1.168602708899938</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.1983820522125557</v>
+        <v>0.3291697453664361</v>
       </c>
       <c r="G2033" t="n">
-        <v>3.51805899907023</v>
+        <v>3.596531614962558</v>
       </c>
     </row>
     <row r="2034">
@@ -48333,16 +48333,16 @@
         <v>3.402531811816661</v>
       </c>
       <c r="D2034" t="n">
-        <v>-5.589505596315868</v>
+        <v>-5.506138575374059</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.166373148976566</v>
+        <v>1.199719957353289</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.2674200631610237</v>
+        <v>0.3982077563149042</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.562983849713275</v>
+        <v>3.641456465605604</v>
       </c>
     </row>
     <row r="2035">
@@ -48356,16 +48356,16 @@
         <v>3.386958630892743</v>
       </c>
       <c r="D2035" t="n">
-        <v>-5.570718495946929</v>
+        <v>-5.487351475005121</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.158314808200223</v>
+        <v>1.191661616576947</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.2862071635299622</v>
+        <v>0.4169948566838427</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.558682929010721</v>
+        <v>3.637155544903049</v>
       </c>
     </row>
     <row r="2036">
@@ -48379,16 +48379,16 @@
         <v>3.386146341329173</v>
       </c>
       <c r="D2036" t="n">
-        <v>-5.493619894405056</v>
+        <v>-5.410252873463248</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.188341959253402</v>
+        <v>1.221688767630126</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.2862071635299622</v>
+        <v>0.4169948566838427</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.557870639447151</v>
+        <v>3.636343255339479</v>
       </c>
     </row>
     <row r="2037">
@@ -48402,16 +48402,16 @@
         <v>3.396015120454245</v>
       </c>
       <c r="D2037" t="n">
-        <v>-5.504005089294946</v>
+        <v>-5.420638068353138</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.194056660422519</v>
+        <v>1.227403468799242</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.2758219686400729</v>
+        <v>0.4066096617939534</v>
       </c>
       <c r="G2037" t="n">
-        <v>3.561508301638289</v>
+        <v>3.639980917530618</v>
       </c>
     </row>
     <row r="2038">
@@ -48425,16 +48425,16 @@
         <v>3.466852126230671</v>
       </c>
       <c r="D2038" t="n">
-        <v>-5.522593248017171</v>
+        <v>-5.439226227075363</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.257458402710054</v>
+        <v>1.290805211086778</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.2572338099178476</v>
+        <v>0.388021503071728</v>
       </c>
       <c r="G2038" t="n">
-        <v>3.621192412181379</v>
+        <v>3.699665028073708</v>
       </c>
     </row>
     <row r="2039">
@@ -48448,16 +48448,16 @@
         <v>3.463721137048969</v>
       </c>
       <c r="D2039" t="n">
-        <v>-5.522891794713207</v>
+        <v>-5.439524773771399</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.254207994849939</v>
+        <v>1.287554803226662</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.2569352632218116</v>
+        <v>0.3877229563756921</v>
       </c>
       <c r="G2039" t="n">
-        <v>3.617882294982056</v>
+        <v>3.696354910874385</v>
       </c>
     </row>
     <row r="2040">
@@ -48471,16 +48471,16 @@
         <v>3.468252031988361</v>
       </c>
       <c r="D2040" t="n">
-        <v>-5.422068661022779</v>
+        <v>-5.338701640080971</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.299068143265501</v>
+        <v>1.332414951642224</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.2693994787061655</v>
+        <v>0.4001871718600459</v>
       </c>
       <c r="G2040" t="n">
-        <v>3.62989171921206</v>
+        <v>3.708364335104388</v>
       </c>
     </row>
     <row r="2041">
@@ -48494,16 +48494,16 @@
         <v>3.468381285466904</v>
       </c>
       <c r="D2041" t="n">
-        <v>-5.231287300270372</v>
+        <v>-5.147920279328563</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.375509941045007</v>
+        <v>1.408856749421731</v>
       </c>
       <c r="F2041" t="n">
-        <v>0.4601808394585729</v>
+        <v>0.5909685326124533</v>
       </c>
       <c r="G2041" t="n">
-        <v>3.744489789142048</v>
+        <v>3.822962405034376</v>
       </c>
     </row>
     <row r="2042">
@@ -48517,16 +48517,16 @@
         <v>3.4482181312045</v>
       </c>
       <c r="D2042" t="n">
-        <v>-5.124323942420951</v>
+        <v>-5.040956921479141</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.398132129922372</v>
+        <v>1.431478938299096</v>
       </c>
       <c r="F2042" t="n">
-        <v>0.5186454474183744</v>
+        <v>0.6494331405722548</v>
       </c>
       <c r="G2042" t="n">
-        <v>3.759405399655525</v>
+        <v>3.837878015547854</v>
       </c>
     </row>
     <row r="2043">
@@ -48540,16 +48540,16 @@
         <v>3.483185067816559</v>
       </c>
       <c r="D2043" t="n">
-        <v>-5.068993354519188</v>
+        <v>-4.985626333577379</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.455231301695135</v>
+        <v>1.488578110071859</v>
       </c>
       <c r="F2043" t="n">
-        <v>0.5739760353201365</v>
+        <v>0.7047637284740169</v>
       </c>
       <c r="G2043" t="n">
-        <v>3.827570689008641</v>
+        <v>3.906043304900969</v>
       </c>
     </row>
     <row r="2044">
@@ -48563,16 +48563,16 @@
         <v>3.476871635717997</v>
       </c>
       <c r="D2044" t="n">
-        <v>-5.056939227606225</v>
+        <v>-4.973572206664416</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.453739520361758</v>
+        <v>1.487086328738482</v>
       </c>
       <c r="F2044" t="n">
-        <v>0.5860301622330993</v>
+        <v>0.7168178553869797</v>
       </c>
       <c r="G2044" t="n">
-        <v>3.828489733057856</v>
+        <v>3.906962348950185</v>
       </c>
     </row>
     <row r="2045">
@@ -48586,16 +48586,16 @@
         <v>3.478752265902132</v>
       </c>
       <c r="D2045" t="n">
-        <v>-5.134294717734194</v>
+        <v>-5.050927696792385</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.424677954494707</v>
+        <v>1.45802476287143</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.50867467210513</v>
+        <v>0.6394623652590103</v>
       </c>
       <c r="G2045" t="n">
-        <v>3.78395706916521</v>
+        <v>3.862429685057539</v>
       </c>
     </row>
     <row r="2046">
@@ -48609,16 +48609,16 @@
         <v>3.491603291780015</v>
       </c>
       <c r="D2046" t="n">
-        <v>-5.066246155042665</v>
+        <v>-4.982879134100855</v>
       </c>
       <c r="E2046" t="n">
-        <v>1.464748405449201</v>
+        <v>1.498095213825925</v>
       </c>
       <c r="F2046" t="n">
-        <v>0.5767232347966598</v>
+        <v>0.7075109279505402</v>
       </c>
       <c r="G2046" t="n">
-        <v>3.837637232658011</v>
+        <v>3.916109848550339</v>
       </c>
     </row>
     <row r="2047">
@@ -48632,16 +48632,16 @@
         <v>3.511805961953609</v>
       </c>
       <c r="D2047" t="n">
-        <v>-5.297846548212165</v>
+        <v>-5.214479527270356</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.392310918354995</v>
+        <v>1.425657726731719</v>
       </c>
       <c r="F2047" t="n">
-        <v>0.5767232347966598</v>
+        <v>0.7075109279505402</v>
       </c>
       <c r="G2047" t="n">
-        <v>3.857839902831605</v>
+        <v>3.936312518723933</v>
       </c>
     </row>
     <row r="2048">
@@ -48655,16 +48655,16 @@
         <v>3.495412198020491</v>
       </c>
       <c r="D2048" t="n">
-        <v>-5.347898093741385</v>
+        <v>-5.264531072799576</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.355896536210189</v>
+        <v>1.389243344586913</v>
       </c>
       <c r="F2048" t="n">
-        <v>0.5767232347966598</v>
+        <v>0.7075109279505402</v>
       </c>
       <c r="G2048" t="n">
-        <v>3.841446138898487</v>
+        <v>3.919918754790816</v>
       </c>
     </row>
     <row r="2049">
@@ -48678,16 +48678,16 @@
         <v>3.455664111613958</v>
       </c>
       <c r="D2049" t="n">
-        <v>-5.52300492631783</v>
+        <v>-5.439637905376021</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.246105716773078</v>
+        <v>1.279452525149801</v>
       </c>
       <c r="F2049" t="n">
-        <v>0.5767232347966598</v>
+        <v>0.7075109279505402</v>
       </c>
       <c r="G2049" t="n">
-        <v>3.801698052491954</v>
+        <v>3.880170668384282</v>
       </c>
     </row>
     <row r="2050">
@@ -48701,16 +48701,16 @@
         <v>3.462686730610898</v>
       </c>
       <c r="D2050" t="n">
-        <v>-5.326904772887307</v>
+        <v>-5.243537751945498</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.331568397142227</v>
+        <v>1.364915205518951</v>
       </c>
       <c r="F2050" t="n">
-        <v>0.7728233882271827</v>
+        <v>0.9036110813810631</v>
       </c>
       <c r="G2050" t="n">
-        <v>3.926380763547208</v>
+        <v>4.004853379439536</v>
       </c>
     </row>
     <row r="2051">
@@ -48724,16 +48724,16 @@
         <v>3.561857730183802</v>
       </c>
       <c r="D2051" t="n">
-        <v>-5.173879380774022</v>
+        <v>-5.090512359832213</v>
       </c>
       <c r="E2051" t="n">
-        <v>1.491949553560445</v>
+        <v>1.525296361937169</v>
       </c>
       <c r="F2051" t="n">
-        <v>0.9258487803404668</v>
+        <v>1.056636473494347</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.117366998388082</v>
+        <v>4.195839614280411</v>
       </c>
     </row>
     <row r="2052">
@@ -48747,16 +48747,16 @@
         <v>3.749323955092095</v>
       </c>
       <c r="D2052" t="n">
-        <v>-5.202186694647293</v>
+        <v>-5.118819673705484</v>
       </c>
       <c r="E2052" t="n">
-        <v>1.668092852919429</v>
+        <v>1.701439661296153</v>
       </c>
       <c r="F2052" t="n">
-        <v>0.9258487803404668</v>
+        <v>1.056636473494347</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.304833223296376</v>
+        <v>4.383305839188703</v>
       </c>
     </row>
     <row r="2053">
@@ -48770,16 +48770,16 @@
         <v>3.718726906446177</v>
       </c>
       <c r="D2053" t="n">
-        <v>-5.368779919760815</v>
+        <v>-5.285412898819006</v>
       </c>
       <c r="E2053" t="n">
-        <v>1.570858514228104</v>
+        <v>1.604205322604827</v>
       </c>
       <c r="F2053" t="n">
-        <v>0.7592555552269444</v>
+        <v>0.8900432483808247</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.174280239582345</v>
+        <v>4.252752855474673</v>
       </c>
     </row>
     <row r="2054">
@@ -48793,16 +48793,16 @@
         <v>3.722403309107895</v>
       </c>
       <c r="D2054" t="n">
-        <v>-5.345744126399249</v>
+        <v>-5.26237710545744</v>
       </c>
       <c r="E2054" t="n">
-        <v>1.583749234234447</v>
+        <v>1.617096042611171</v>
       </c>
       <c r="F2054" t="n">
-        <v>0.7592555552269444</v>
+        <v>0.8900432483808247</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.177956642244062</v>
+        <v>4.25642925813639</v>
       </c>
     </row>
     <row r="2055">
@@ -48816,16 +48816,16 @@
         <v>3.72002136423139</v>
       </c>
       <c r="D2055" t="n">
-        <v>-5.316498145943553</v>
+        <v>-5.233131125001743</v>
       </c>
       <c r="E2055" t="n">
-        <v>1.593065681540221</v>
+        <v>1.626412489916945</v>
       </c>
       <c r="F2055" t="n">
-        <v>0.7592555552269444</v>
+        <v>0.8900432483808247</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.175574697367558</v>
+        <v>4.254047313259885</v>
       </c>
     </row>
     <row r="2056">
@@ -48839,16 +48839,16 @@
         <v>3.717314603389025</v>
       </c>
       <c r="D2056" t="n">
-        <v>-5.423423693821404</v>
+        <v>-5.340056672879594</v>
       </c>
       <c r="E2056" t="n">
-        <v>1.547588701546716</v>
+        <v>1.58093550992344</v>
       </c>
       <c r="F2056" t="n">
-        <v>0.6523300073490931</v>
+        <v>0.7831177005029734</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.108712607798481</v>
+        <v>4.187185223690809</v>
       </c>
     </row>
     <row r="2057">
@@ -48862,16 +48862,16 @@
         <v>3.71874340553226</v>
       </c>
       <c r="D2057" t="n">
-        <v>-5.568442252328652</v>
+        <v>-5.485075231386843</v>
       </c>
       <c r="E2057" t="n">
-        <v>1.491010080287051</v>
+        <v>1.524356888663775</v>
       </c>
       <c r="F2057" t="n">
-        <v>0.5073114488418445</v>
+        <v>0.6380991419957248</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.023130274837366</v>
+        <v>4.101602890729695</v>
       </c>
     </row>
     <row r="2058">
@@ -48885,16 +48885,16 @@
         <v>3.818674644790013</v>
       </c>
       <c r="D2058" t="n">
-        <v>-5.68678401811337</v>
+        <v>-5.603416997171561</v>
       </c>
       <c r="E2058" t="n">
-        <v>1.543604613230917</v>
+        <v>1.576951421607641</v>
       </c>
       <c r="F2058" t="n">
-        <v>0.5179974874047346</v>
+        <v>0.6487851805586149</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.129473137232853</v>
+        <v>4.207945753125182</v>
       </c>
     </row>
     <row r="2059">
@@ -48908,16 +48908,16 @@
         <v>3.816460341915952</v>
       </c>
       <c r="D2059" t="n">
-        <v>-5.738194440434078</v>
+        <v>-5.654827419492269</v>
       </c>
       <c r="E2059" t="n">
-        <v>1.520826141428573</v>
+        <v>1.554172949805297</v>
       </c>
       <c r="F2059" t="n">
-        <v>0.5179974874047346</v>
+        <v>0.6487851805586149</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.127258834358793</v>
+        <v>4.205731450251121</v>
       </c>
     </row>
     <row r="2060">
@@ -48931,16 +48931,16 @@
         <v>3.816363469990241</v>
       </c>
       <c r="D2060" t="n">
-        <v>-5.817613891641829</v>
+        <v>-5.73424687070002</v>
       </c>
       <c r="E2060" t="n">
-        <v>1.488961489019761</v>
+        <v>1.522308297396485</v>
       </c>
       <c r="F2060" t="n">
-        <v>0.5179974874047346</v>
+        <v>0.6487851805586149</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.127161962433082</v>
+        <v>4.205634578325411</v>
       </c>
     </row>
     <row r="2061">
@@ -48954,16 +48954,16 @@
         <v>3.816357363548284</v>
       </c>
       <c r="D2061" t="n">
-        <v>-5.913076889559047</v>
+        <v>-5.829709868617238</v>
       </c>
       <c r="E2061" t="n">
-        <v>1.450770183410917</v>
+        <v>1.484116991787641</v>
       </c>
       <c r="F2061" t="n">
-        <v>0.5179974874047346</v>
+        <v>0.6487851805586149</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.127155855991125</v>
+        <v>4.205628471883453</v>
       </c>
     </row>
     <row r="2062">
@@ -48977,16 +48977,16 @@
         <v>3.814453760110895</v>
       </c>
       <c r="D2062" t="n">
-        <v>-5.848700978708332</v>
+        <v>-5.765333957766523</v>
       </c>
       <c r="E2062" t="n">
-        <v>1.474616944313814</v>
+        <v>1.507963752690537</v>
       </c>
       <c r="F2062" t="n">
-        <v>0.5823733982554498</v>
+        <v>0.71316109140933</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.163877799064164</v>
+        <v>4.242350414956493</v>
       </c>
     </row>
     <row r="2063">
@@ -49000,16 +49000,16 @@
         <v>3.820187577858621</v>
       </c>
       <c r="D2063" t="n">
-        <v>-5.904070140840526</v>
+        <v>-5.820703119898717</v>
       </c>
       <c r="E2063" t="n">
-        <v>1.458203097208663</v>
+        <v>1.491549905585387</v>
       </c>
       <c r="F2063" t="n">
-        <v>0.5823733982554498</v>
+        <v>0.71316109140933</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.169611616811891</v>
+        <v>4.24808423270422</v>
       </c>
     </row>
     <row r="2064">
@@ -49023,16 +49023,16 @@
         <v>3.819725941201554</v>
       </c>
       <c r="D2064" t="n">
-        <v>-5.922288607838134</v>
+        <v>-5.838921586896325</v>
       </c>
       <c r="E2064" t="n">
-        <v>1.450454073752552</v>
+        <v>1.483800882129275</v>
       </c>
       <c r="F2064" t="n">
-        <v>0.5572669609996076</v>
+        <v>0.6880546541534879</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.154086117801318</v>
+        <v>4.232558733693646</v>
       </c>
     </row>
     <row r="2065">
@@ -49046,16 +49046,16 @@
         <v>3.839600334051872</v>
       </c>
       <c r="D2065" t="n">
-        <v>-5.883605172494204</v>
+        <v>-5.800238151552395</v>
       </c>
       <c r="E2065" t="n">
-        <v>1.485801840740443</v>
+        <v>1.519148649117166</v>
       </c>
       <c r="F2065" t="n">
-        <v>0.5572669609996076</v>
+        <v>0.6880546541534879</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.173960510651638</v>
+        <v>4.252433126543965</v>
       </c>
     </row>
     <row r="2066">
@@ -49069,16 +49069,16 @@
         <v>3.8233010345766</v>
       </c>
       <c r="D2066" t="n">
-        <v>-5.777570177288895</v>
+        <v>-5.694203156347085</v>
       </c>
       <c r="E2066" t="n">
-        <v>1.511916539347294</v>
+        <v>1.545263347724018</v>
       </c>
       <c r="F2066" t="n">
-        <v>0.5572669609996076</v>
+        <v>0.6880546541534879</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.157661211176364</v>
+        <v>4.236133827068693</v>
       </c>
     </row>
     <row r="2067">
@@ -49092,16 +49092,16 @@
         <v>3.825731984040646</v>
       </c>
       <c r="D2067" t="n">
-        <v>-5.594358514155799</v>
+        <v>-5.51099149321399</v>
       </c>
       <c r="E2067" t="n">
-        <v>1.587632154064578</v>
+        <v>1.620978962441302</v>
       </c>
       <c r="F2067" t="n">
-        <v>0.5572669609996076</v>
+        <v>0.6880546541534879</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.160092160640411</v>
+        <v>4.238564776532739</v>
       </c>
     </row>
     <row r="2068">
@@ -49115,16 +49115,16 @@
         <v>3.808676390120023</v>
       </c>
       <c r="D2068" t="n">
-        <v>-5.522637067141948</v>
+        <v>-5.439270046200139</v>
       </c>
       <c r="E2068" t="n">
-        <v>1.599265138949496</v>
+        <v>1.63261194732622</v>
       </c>
       <c r="F2068" t="n">
-        <v>0.6289884080134582</v>
+        <v>0.7597761011673385</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.186069434928099</v>
+        <v>4.264542050820427</v>
       </c>
     </row>
     <row r="2069">
@@ -49138,16 +49138,16 @@
         <v>3.755592136041195</v>
       </c>
       <c r="D2069" t="n">
-        <v>-5.500264041534242</v>
+        <v>-5.416897020592433</v>
       </c>
       <c r="E2069" t="n">
-        <v>1.55513009511375</v>
+        <v>1.588476903490474</v>
       </c>
       <c r="F2069" t="n">
-        <v>0.6402441591263598</v>
+        <v>0.7710318522802401</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.139738631517011</v>
+        <v>4.218211247409339</v>
       </c>
     </row>
     <row r="2070">
@@ -49161,16 +49161,16 @@
         <v>3.94079034092655</v>
       </c>
       <c r="D2070" t="n">
-        <v>-5.533280337444987</v>
+        <v>-5.449913316503178</v>
       </c>
       <c r="E2070" t="n">
-        <v>1.727121781634807</v>
+        <v>1.760468590011531</v>
       </c>
       <c r="F2070" t="n">
-        <v>0.5708067824596081</v>
+        <v>0.7015944756134884</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.283274410402315</v>
+        <v>4.361747026294643</v>
       </c>
     </row>
     <row r="2071">
@@ -49184,16 +49184,16 @@
         <v>3.932711566754799</v>
       </c>
       <c r="D2071" t="n">
-        <v>-5.521752701795378</v>
+        <v>-5.438385680853569</v>
       </c>
       <c r="E2071" t="n">
-        <v>1.723654061722899</v>
+        <v>1.757000870099623</v>
       </c>
       <c r="F2071" t="n">
-        <v>0.6298074406609706</v>
+        <v>0.7605951338148509</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.310596031151381</v>
+        <v>4.389068647043709</v>
       </c>
     </row>
     <row r="2072">
@@ -49207,16 +49207,16 @@
         <v>3.936379679276587</v>
       </c>
       <c r="D2072" t="n">
-        <v>-5.619094203137747</v>
+        <v>-5.535727182195938</v>
       </c>
       <c r="E2072" t="n">
-        <v>1.688385573707741</v>
+        <v>1.721732382084464</v>
       </c>
       <c r="F2072" t="n">
-        <v>0.5853872584954822</v>
+        <v>0.7161749516493625</v>
       </c>
       <c r="G2072" t="n">
-        <v>4.287612034373877</v>
+        <v>4.366084650266205</v>
       </c>
     </row>
     <row r="2073">
@@ -49230,16 +49230,16 @@
         <v>3.937630761469426</v>
       </c>
       <c r="D2073" t="n">
-        <v>-5.704950232477714</v>
+        <v>-5.621583211535905</v>
       </c>
       <c r="E2073" t="n">
-        <v>1.655294244164592</v>
+        <v>1.688641052541316</v>
       </c>
       <c r="F2073" t="n">
-        <v>0.5430111892693472</v>
+        <v>0.6737988824232275</v>
       </c>
       <c r="G2073" t="n">
-        <v>4.263437475031035</v>
+        <v>4.341910090923363</v>
       </c>
     </row>
     <row r="2074">
@@ -49253,16 +49253,16 @@
         <v>3.920049963289927</v>
       </c>
       <c r="D2074" t="n">
-        <v>-5.713787029893833</v>
+        <v>-5.630420008952024</v>
       </c>
       <c r="E2074" t="n">
-        <v>1.634178727018646</v>
+        <v>1.66752553539537</v>
       </c>
       <c r="F2074" t="n">
-        <v>0.5355690166279965</v>
+        <v>0.6663567097818768</v>
       </c>
       <c r="G2074" t="n">
-        <v>4.241391373266726</v>
+        <v>4.319863989159054</v>
       </c>
     </row>
     <row r="2075">
@@ -49276,16 +49276,16 @@
         <v>3.930214474334977</v>
       </c>
       <c r="D2075" t="n">
-        <v>-5.805169592459292</v>
+        <v>-5.721802571517483</v>
       </c>
       <c r="E2075" t="n">
-        <v>1.607790213037512</v>
+        <v>1.641137021414236</v>
       </c>
       <c r="F2075" t="n">
-        <v>0.4990041319086518</v>
+        <v>0.6297918250625321</v>
       </c>
       <c r="G2075" t="n">
-        <v>4.229616953480169</v>
+        <v>4.308089569372497</v>
       </c>
     </row>
     <row r="2076">
@@ -49299,16 +49299,16 @@
         <v>4.032342732159245</v>
       </c>
       <c r="D2076" t="n">
-        <v>-5.793462874472286</v>
+        <v>-5.710095853530476</v>
       </c>
       <c r="E2076" t="n">
-        <v>1.714601158056583</v>
+        <v>1.747947966433307</v>
       </c>
       <c r="F2076" t="n">
-        <v>0.5107108498956582</v>
+        <v>0.6414985430495385</v>
       </c>
       <c r="G2076" t="n">
-        <v>4.338769242096641</v>
+        <v>4.417241857988969</v>
       </c>
     </row>
     <row r="2077">
@@ -49322,16 +49322,16 @@
         <v>4.03537507089065</v>
       </c>
       <c r="D2077" t="n">
-        <v>-5.864374948214563</v>
+        <v>-5.781007927272753</v>
       </c>
       <c r="E2077" t="n">
-        <v>1.689268667291077</v>
+        <v>1.7226154756678</v>
       </c>
       <c r="F2077" t="n">
-        <v>0.5107108498956582</v>
+        <v>0.6414985430495385</v>
       </c>
       <c r="G2077" t="n">
-        <v>4.341801580828045</v>
+        <v>4.420274196720373</v>
       </c>
     </row>
     <row r="2078">
@@ -49345,16 +49345,16 @@
         <v>4.036193896622915</v>
       </c>
       <c r="D2078" t="n">
-        <v>-5.874691046380915</v>
+        <v>-5.791324025439105</v>
       </c>
       <c r="E2078" t="n">
-        <v>1.685961053756801</v>
+        <v>1.719307862133524</v>
       </c>
       <c r="F2078" t="n">
-        <v>0.5107108498956582</v>
+        <v>0.6382608623766438</v>
       </c>
       <c r="G2078" t="n">
-        <v>4.34262040656031</v>
+        <v>4.419150414048901</v>
       </c>
     </row>
     <row r="2079">
@@ -49368,16 +49368,16 @@
         <v>4.035372563535004</v>
       </c>
       <c r="D2079" t="n">
-        <v>-5.874597078363542</v>
+        <v>-5.791230057421733</v>
       </c>
       <c r="E2079" t="n">
-        <v>1.685177307875839</v>
+        <v>1.718524116252563</v>
       </c>
       <c r="F2079" t="n">
-        <v>0.5110807112429762</v>
+        <v>0.6386307237239618</v>
       </c>
       <c r="G2079" t="n">
-        <v>4.34202099028079</v>
+        <v>4.418550997769382</v>
       </c>
     </row>
     <row r="2080">
@@ -49391,16 +49391,16 @@
         <v>4.029604549479358</v>
       </c>
       <c r="D2080" t="n">
-        <v>-6.018198242386927</v>
+        <v>-5.934831221445118</v>
       </c>
       <c r="E2080" t="n">
-        <v>1.621968828210839</v>
+        <v>1.655315636587563</v>
       </c>
       <c r="F2080" t="n">
-        <v>0.5110807112429762</v>
+        <v>0.6386307237239618</v>
       </c>
       <c r="G2080" t="n">
-        <v>4.336252976225144</v>
+        <v>4.412782983713735</v>
       </c>
     </row>
     <row r="2081">
@@ -49414,16 +49414,16 @@
         <v>4.029604549479358</v>
       </c>
       <c r="D2081" t="n">
-        <v>-6.017249819268889</v>
+        <v>-5.93388279832708</v>
       </c>
       <c r="E2081" t="n">
-        <v>1.622348197458054</v>
+        <v>1.655695005834778</v>
       </c>
       <c r="F2081" t="n">
-        <v>0.5110807112429762</v>
+        <v>0.6386307237239618</v>
       </c>
       <c r="G2081" t="n">
-        <v>4.336252976225144</v>
+        <v>4.412782983713735</v>
       </c>
     </row>
     <row r="2082">
@@ -49437,16 +49437,16 @@
         <v>4.04233215746045</v>
       </c>
       <c r="D2082" t="n">
-        <v>-6.117519637227909</v>
+        <v>-6.0341526162861</v>
       </c>
       <c r="E2082" t="n">
-        <v>1.594967878255538</v>
+        <v>1.628314686632262</v>
       </c>
       <c r="F2082" t="n">
-        <v>0.5110807112429762</v>
+        <v>0.6386307237239618</v>
       </c>
       <c r="G2082" t="n">
-        <v>4.348980584206236</v>
+        <v>4.425510591694827</v>
       </c>
     </row>
     <row r="2083">
@@ -49460,16 +49460,16 @@
         <v>4.044278155884838</v>
       </c>
       <c r="D2083" t="n">
-        <v>-6.111527390439098</v>
+        <v>-6.028160369497289</v>
       </c>
       <c r="E2083" t="n">
-        <v>1.599310775395451</v>
+        <v>1.632657583772174</v>
       </c>
       <c r="F2083" t="n">
-        <v>0.5110807112429762</v>
+        <v>0.6386307237239618</v>
       </c>
       <c r="G2083" t="n">
-        <v>4.350926582630624</v>
+        <v>4.427456590119215</v>
       </c>
     </row>
     <row r="2084">
@@ -49483,16 +49483,16 @@
         <v>4.037932291902607</v>
       </c>
       <c r="D2084" t="n">
-        <v>-6.02296942930833</v>
+        <v>-5.939602408366521</v>
       </c>
       <c r="E2084" t="n">
-        <v>1.628388095865526</v>
+        <v>1.66173490424225</v>
       </c>
       <c r="F2084" t="n">
-        <v>0.5110807112429762</v>
+        <v>0.6386307237239618</v>
       </c>
       <c r="G2084" t="n">
-        <v>4.344580718648393</v>
+        <v>4.421110726136984</v>
       </c>
     </row>
     <row r="2085">
@@ -49506,16 +49506,16 @@
         <v>4.037240969341602</v>
       </c>
       <c r="D2085" t="n">
-        <v>-6.005210351805256</v>
+        <v>-5.921843330863447</v>
       </c>
       <c r="E2085" t="n">
-        <v>1.634800404305752</v>
+        <v>1.668147212682475</v>
       </c>
       <c r="F2085" t="n">
-        <v>0.5110807112429762</v>
+        <v>0.6386307237239618</v>
       </c>
       <c r="G2085" t="n">
-        <v>4.343889396087389</v>
+        <v>4.42041940357598</v>
       </c>
     </row>
     <row r="2086">
@@ -49529,16 +49529,16 @@
         <v>4.050023155250189</v>
       </c>
       <c r="D2086" t="n">
-        <v>-5.905580200756188</v>
+        <v>-5.822213179814379</v>
       </c>
       <c r="E2086" t="n">
-        <v>1.687434650633966</v>
+        <v>1.72078145901069</v>
       </c>
       <c r="F2086" t="n">
-        <v>0.6107108622920436</v>
+        <v>0.7382608747730293</v>
       </c>
       <c r="G2086" t="n">
-        <v>4.416449672625416</v>
+        <v>4.492979680114007</v>
       </c>
     </row>
     <row r="2087">
@@ -49552,16 +49552,16 @@
         <v>4.239177420748915</v>
       </c>
       <c r="D2087" t="n">
-        <v>-5.954979709445199</v>
+        <v>-5.87161268850339</v>
       </c>
       <c r="E2087" t="n">
-        <v>1.856829112657088</v>
+        <v>1.890175921033812</v>
       </c>
       <c r="F2087" t="n">
-        <v>0.6209696957237884</v>
+        <v>0.748519708204774</v>
       </c>
       <c r="G2087" t="n">
-        <v>4.611759238183189</v>
+        <v>4.68828924567178</v>
       </c>
     </row>
     <row r="2088">
@@ -49575,16 +49575,16 @@
         <v>4.226366093851778</v>
       </c>
       <c r="D2088" t="n">
-        <v>-5.748295235802823</v>
+        <v>-5.664928214861014</v>
       </c>
       <c r="E2088" t="n">
-        <v>1.9266915752169</v>
+        <v>1.960038383593624</v>
       </c>
       <c r="F2088" t="n">
-        <v>0.827654169366164</v>
+        <v>0.9552041818471496</v>
       </c>
       <c r="G2088" t="n">
-        <v>4.722958595471476</v>
+        <v>4.799488602960068</v>
       </c>
     </row>
     <row r="2089">
@@ -49598,16 +49598,16 @@
         <v>4.228367607505882</v>
       </c>
       <c r="D2089" t="n">
-        <v>-5.782452130800349</v>
+        <v>-5.69908510985854</v>
       </c>
       <c r="E2089" t="n">
-        <v>1.915030330871995</v>
+        <v>1.948377139248719</v>
       </c>
       <c r="F2089" t="n">
-        <v>0.7440703998253515</v>
+        <v>0.8716204123063371</v>
       </c>
       <c r="G2089" t="n">
-        <v>4.674809847401094</v>
+        <v>4.751339854889685</v>
       </c>
     </row>
     <row r="2090">
@@ -49621,16 +49621,16 @@
         <v>4.58186472149555</v>
       </c>
       <c r="D2090" t="n">
-        <v>-5.689862651738893</v>
+        <v>-5.606495630797084</v>
       </c>
       <c r="E2090" t="n">
-        <v>2.305563236486245</v>
+        <v>2.338910044862968</v>
       </c>
       <c r="F2090" t="n">
-        <v>0.7440703998253515</v>
+        <v>0.8716204123063371</v>
       </c>
       <c r="G2090" t="n">
-        <v>5.028306961390761</v>
+        <v>5.104836968879352</v>
       </c>
     </row>
     <row r="2091">
@@ -49644,16 +49644,16 @@
         <v>4.586427833062654</v>
       </c>
       <c r="D2091" t="n">
-        <v>-5.763023255512038</v>
+        <v>-5.679656234570229</v>
       </c>
       <c r="E2091" t="n">
-        <v>2.280862106544091</v>
+        <v>2.314208914920814</v>
       </c>
       <c r="F2091" t="n">
-        <v>0.7160491997911085</v>
+        <v>0.8435992122720941</v>
       </c>
       <c r="G2091" t="n">
-        <v>5.016057352937319</v>
+        <v>5.09258736042591</v>
       </c>
     </row>
     <row r="2092">
@@ -49667,16 +49667,16 @@
         <v>4.636257774386181</v>
       </c>
       <c r="D2092" t="n">
-        <v>-5.710806945715696</v>
+        <v>-5.627439924773887</v>
       </c>
       <c r="E2092" t="n">
-        <v>2.351578571786155</v>
+        <v>2.384925380162879</v>
       </c>
       <c r="F2092" t="n">
-        <v>0.7160491997911085</v>
+        <v>0.8435992122720941</v>
       </c>
       <c r="G2092" t="n">
-        <v>5.065887294260847</v>
+        <v>5.142417301749438</v>
       </c>
     </row>
     <row r="2093">
@@ -49690,16 +49690,16 @@
         <v>4.645071744596192</v>
       </c>
       <c r="D2093" t="n">
-        <v>-5.658299618205201</v>
+        <v>-5.574932597263392</v>
       </c>
       <c r="E2093" t="n">
-        <v>2.381395473000364</v>
+        <v>2.414742281377088</v>
       </c>
       <c r="F2093" t="n">
-        <v>0.7685565273016034</v>
+        <v>0.896106539782589</v>
       </c>
       <c r="G2093" t="n">
-        <v>5.106205660977155</v>
+        <v>5.182735668465746</v>
       </c>
     </row>
     <row r="2094">
@@ -49713,16 +49713,16 @@
         <v>4.640709328635389</v>
       </c>
       <c r="D2094" t="n">
-        <v>-5.673054942405342</v>
+        <v>-5.589687921463533</v>
       </c>
       <c r="E2094" t="n">
-        <v>2.371130927359505</v>
+        <v>2.404477735736228</v>
       </c>
       <c r="F2094" t="n">
-        <v>0.7685565273016034</v>
+        <v>0.896106539782589</v>
       </c>
       <c r="G2094" t="n">
-        <v>5.101843245016352</v>
+        <v>5.178373252504943</v>
       </c>
     </row>
     <row r="2095">
@@ -49736,16 +49736,16 @@
         <v>4.631633832051669</v>
       </c>
       <c r="D2095" t="n">
-        <v>-5.62359031903543</v>
+        <v>-5.540223298093621</v>
       </c>
       <c r="E2095" t="n">
-        <v>2.381841280123749</v>
+        <v>2.415188088500473</v>
       </c>
       <c r="F2095" t="n">
-        <v>0.818021150671515</v>
+        <v>0.9455711631525007</v>
       </c>
       <c r="G2095" t="n">
-        <v>5.122446522454578</v>
+        <v>5.19897652994317</v>
       </c>
     </row>
     <row r="2096">
@@ -49759,16 +49759,16 @@
         <v>4.628041499766604</v>
       </c>
       <c r="D2096" t="n">
-        <v>-5.460482326881815</v>
+        <v>-5.377115305940006</v>
       </c>
       <c r="E2096" t="n">
-        <v>2.44349214470013</v>
+        <v>2.476838953076853</v>
       </c>
       <c r="F2096" t="n">
-        <v>0.9811291428251303</v>
+        <v>1.108679155306116</v>
       </c>
       <c r="G2096" t="n">
-        <v>5.216718985461682</v>
+        <v>5.293248992950273</v>
       </c>
     </row>
     <row r="2097">
@@ -49782,16 +49782,16 @@
         <v>4.637088536457732</v>
       </c>
       <c r="D2097" t="n">
-        <v>-5.439839236080587</v>
+        <v>-5.356472215138778</v>
       </c>
       <c r="E2097" t="n">
-        <v>2.460796417711749</v>
+        <v>2.494143226088473</v>
       </c>
       <c r="F2097" t="n">
-        <v>0.9811291428251303</v>
+        <v>1.108679155306116</v>
       </c>
       <c r="G2097" t="n">
-        <v>5.22576602215281</v>
+        <v>5.302296029641401</v>
       </c>
     </row>
     <row r="2098">
@@ -49805,16 +49805,16 @@
         <v>4.637946001443853</v>
       </c>
       <c r="D2098" t="n">
-        <v>-5.502547152555145</v>
+        <v>-5.419180131613336</v>
       </c>
       <c r="E2098" t="n">
-        <v>2.436570716108047</v>
+        <v>2.469917524484771</v>
       </c>
       <c r="F2098" t="n">
-        <v>0.9184212263505726</v>
+        <v>1.045971238831558</v>
       </c>
       <c r="G2098" t="n">
-        <v>5.188998737254197</v>
+        <v>5.265528744742789</v>
       </c>
     </row>
     <row r="2099">
@@ -49828,16 +49828,16 @@
         <v>4.600855418234206</v>
       </c>
       <c r="D2099" t="n">
-        <v>-5.454539028711452</v>
+        <v>-5.371172007769643</v>
       </c>
       <c r="E2099" t="n">
-        <v>2.418683382435877</v>
+        <v>2.452030190812601</v>
       </c>
       <c r="F2099" t="n">
-        <v>0.9184212263505726</v>
+        <v>1.045971238831558</v>
       </c>
       <c r="G2099" t="n">
-        <v>5.151908154044549</v>
+        <v>5.228438161533141</v>
       </c>
     </row>
     <row r="2100">
@@ -49851,16 +49851,16 @@
         <v>4.604787671792156</v>
       </c>
       <c r="D2100" t="n">
-        <v>-5.304420973489555</v>
+        <v>-5.221053952547746</v>
       </c>
       <c r="E2100" t="n">
-        <v>2.482662858082586</v>
+        <v>2.51600966645931</v>
       </c>
       <c r="F2100" t="n">
-        <v>1.06853928157247</v>
+        <v>1.196089294053455</v>
       </c>
       <c r="G2100" t="n">
-        <v>5.245911240735638</v>
+        <v>5.322441248224229</v>
       </c>
     </row>
     <row r="2101">
@@ -49874,16 +49874,16 @@
         <v>4.599686764399193</v>
       </c>
       <c r="D2101" t="n">
-        <v>-5.112486172235681</v>
+        <v>-5.029119151293872</v>
       </c>
       <c r="E2101" t="n">
-        <v>2.554335871191173</v>
+        <v>2.587682679567896</v>
       </c>
       <c r="F2101" t="n">
-        <v>1.06853928157247</v>
+        <v>1.196089294053455</v>
       </c>
       <c r="G2101" t="n">
-        <v>5.240810333342675</v>
+        <v>5.317340340831266</v>
       </c>
     </row>
     <row r="2102">
@@ -49897,16 +49897,16 @@
         <v>4.595040673788288</v>
       </c>
       <c r="D2102" t="n">
-        <v>-4.994312794217754</v>
+        <v>-4.910945773275945</v>
       </c>
       <c r="E2102" t="n">
-        <v>2.596959131787439</v>
+        <v>2.630305940164162</v>
       </c>
       <c r="F2102" t="n">
-        <v>1.186712659590397</v>
+        <v>1.314262672071383</v>
       </c>
       <c r="G2102" t="n">
-        <v>5.307068269542527</v>
+        <v>5.383598277031118</v>
       </c>
     </row>
     <row r="2103">
@@ -49920,16 +49920,16 @@
         <v>4.624129266651315</v>
       </c>
       <c r="D2103" t="n">
-        <v>-4.905465677358256</v>
+        <v>-4.822098656416447</v>
       </c>
       <c r="E2103" t="n">
-        <v>2.661586571394265</v>
+        <v>2.694933379770989</v>
       </c>
       <c r="F2103" t="n">
-        <v>1.275559776449894</v>
+        <v>1.40310978893088</v>
       </c>
       <c r="G2103" t="n">
-        <v>5.389465132521252</v>
+        <v>5.465995140009843</v>
       </c>
     </row>
     <row r="2104">
@@ -49943,16 +49943,16 @@
         <v>4.617689489662492</v>
       </c>
       <c r="D2104" t="n">
-        <v>-4.878416639665002</v>
+        <v>-4.795049618723193</v>
       </c>
       <c r="E2104" t="n">
-        <v>2.665966409482743</v>
+        <v>2.699313217859467</v>
       </c>
       <c r="F2104" t="n">
-        <v>1.302608814143148</v>
+        <v>1.430158826624134</v>
       </c>
       <c r="G2104" t="n">
-        <v>5.399254778148381</v>
+        <v>5.475784785636973</v>
       </c>
     </row>
     <row r="2105">
@@ -49966,16 +49966,16 @@
         <v>4.617689489662492</v>
       </c>
       <c r="D2105" t="n">
-        <v>-4.884449919851773</v>
+        <v>-4.801082898909963</v>
       </c>
       <c r="E2105" t="n">
-        <v>2.663553097408035</v>
+        <v>2.696899905784759</v>
       </c>
       <c r="F2105" t="n">
-        <v>1.302608814143148</v>
+        <v>1.430158826624134</v>
       </c>
       <c r="G2105" t="n">
-        <v>5.399254778148381</v>
+        <v>5.475784785636973</v>
       </c>
     </row>
     <row r="2106">
@@ -49989,16 +49989,16 @@
         <v>4.621327656804905</v>
       </c>
       <c r="D2106" t="n">
-        <v>-4.936301695424934</v>
+        <v>-4.852934674483125</v>
       </c>
       <c r="E2106" t="n">
-        <v>2.646450554321183</v>
+        <v>2.679797362697907</v>
       </c>
       <c r="F2106" t="n">
-        <v>1.250757038569987</v>
+        <v>1.378307051050973</v>
       </c>
       <c r="G2106" t="n">
-        <v>5.371781879946897</v>
+        <v>5.448311887435489</v>
       </c>
     </row>
     <row r="2107">
@@ -50012,16 +50012,16 @@
         <v>4.584819403988742</v>
       </c>
       <c r="D2107" t="n">
-        <v>-4.963359141556761</v>
+        <v>-4.879992120614951</v>
       </c>
       <c r="E2107" t="n">
-        <v>2.599119323052289</v>
+        <v>2.632466131429013</v>
       </c>
       <c r="F2107" t="n">
-        <v>1.250757038569987</v>
+        <v>1.378307051050973</v>
       </c>
       <c r="G2107" t="n">
-        <v>5.335273627130734</v>
+        <v>5.411803634619325</v>
       </c>
     </row>
     <row r="2108">
@@ -50029,22 +50029,22 @@
         <v>45570</v>
       </c>
       <c r="B2108" t="n">
-        <v>3.830856457232453</v>
+        <v>3.830856457232457</v>
       </c>
       <c r="C2108" t="n">
         <v>4.586227353735933</v>
       </c>
       <c r="D2108" t="n">
-        <v>-5.036640493410636</v>
+        <v>-4.953273472468827</v>
       </c>
       <c r="E2108" t="n">
-        <v>2.571214732057931</v>
+        <v>2.604561540434654</v>
       </c>
       <c r="F2108" t="n">
-        <v>1.236845616438775</v>
+        <v>1.364395628919761</v>
       </c>
       <c r="G2108" t="n">
-        <v>5.328334723599198</v>
+        <v>5.40486473108779</v>
       </c>
     </row>
     <row r="2109">
@@ -50052,22 +50052,22 @@
         <v>45571</v>
       </c>
       <c r="B2109" t="n">
-        <v>3.784899418085193</v>
+        <v>3.907285875710493</v>
       </c>
       <c r="C2109" t="n">
-        <v>4.600747436321408</v>
+        <v>4.774161771843032</v>
       </c>
       <c r="D2109" t="n">
-        <v>-5.036640493410636</v>
+        <v>-4.953273472468827</v>
       </c>
       <c r="E2109" t="n">
-        <v>2.571214732057931</v>
+        <v>2.604561540434654</v>
       </c>
       <c r="F2109" t="n">
-        <v>1.236845616438775</v>
+        <v>1.364395628919761</v>
       </c>
       <c r="G2109" t="n">
-        <v>4.593811233307775</v>
+        <v>4.7672255688294</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20241006.xlsx
+++ b/tame_output/ON/bt/strategyON_20241006.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>53.8%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>66.6%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.1%</t>
+          <t>65.2%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>68.1%</t>
+          <t>68.0%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>17.7%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.6%</t>
+          <t>-11.5%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>62.7%</t>
+          <t>50.6%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>107.9%</t>
+          <t>102.3%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>43.9%</t>
+          <t>43.2%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>2.36</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>46.9%</t>
+          <t>45.7%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -829,17 +829,17 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-2.4%</t>
+          <t>-2.5%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>10.6%</t>
+          <t>10.5%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-8.2%</t>
+          <t>-7.8%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>89.8%</t>
+          <t>85.8%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>35.9%</t>
+          <t>35.4%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.9%</t>
+          <t>39.6%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>165.8%</t>
+          <t>148.3%</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-77.6%</t>
+          <t>-77.9%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.1%</t>
+          <t>123.2%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>89.8%</t>
+          <t>89.9%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -982,12 +982,12 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-37.8%</t>
+          <t>-37.6%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>-9.6%</t>
+          <t>-9.5%</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-47.7%</t>
+          <t>-47.9%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-73.9%</t>
+          <t>-74.3%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>421.6%</t>
+          <t>420.6%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-6.5%</t>
+          <t>-6.4%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-656.9%</t>
+          <t>-663.6%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>31.4%</t>
+          <t>30.8%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.2%</t>
+          <t>57.1%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1140,7 +1140,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-9.7%</t>
+          <t>-9.5%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-30.8%</t>
+          <t>-31.0%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>27.1%</t>
+          <t>26.7%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14.2%</t>
+          <t>14.1%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-115.8%</t>
+          <t>-118.5%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-1.2%</t>
+          <t>-2.3%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.8%</t>
+          <t>67.0%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.9%</t>
+          <t>54.8%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>62.6%</t>
+          <t>62.8%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>74.2%</t>
+          <t>74.5%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1298,22 +1298,22 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>-4.1%</t>
+          <t>-4.6%</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>-3.1%</t>
+          <t>-3.2%</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.5%</t>
+          <t>10.7%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-24.8%</t>
+          <t>-23.7%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>5.3%</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>55.8%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>48.0%</t>
+          <t>42.4%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-216.2%</t>
+          <t>-204.7%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-87.6%</t>
+          <t>-92.7%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>80.6%</t>
+          <t>64.5%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>63.3%</t>
+          <t>66.1%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>72.7%</t>
+          <t>78.3%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1447,7 +1447,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1471,7 +1471,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-23.3%</t>
+          <t>-24.3%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>73.3%</t>
+          <t>55.5%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>52.9%</t>
+          <t>55.0%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.4%</t>
+          <t>-15.0%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>35.9%</t>
+          <t>36.7%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>30.7%</t>
+          <t>13.2%</t>
         </is>
       </c>
     </row>
@@ -47775,7 +47775,7 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.71289761234307</v>
+        <v>3.712897612343071</v>
       </c>
       <c r="C2010" t="n">
         <v>3.107427201927174</v>
@@ -48149,16 +48149,16 @@
         <v>3.558329809763465</v>
       </c>
       <c r="D2026" t="n">
-        <v>-6.126031610773144</v>
+        <v>-6.23051478952462</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.107560741140459</v>
+        <v>1.065767469639868</v>
       </c>
       <c r="F2026" t="n">
-        <v>-0.1071386413982535</v>
+        <v>-0.2116218201497295</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.494046624924513</v>
+        <v>3.431356717673627</v>
       </c>
     </row>
     <row r="2027">
@@ -48172,16 +48172,16 @@
         <v>3.55048269700764</v>
       </c>
       <c r="D2027" t="n">
-        <v>-6.016025327295923</v>
+        <v>-6.120508506047399</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.143716141775523</v>
+        <v>1.101922870274933</v>
       </c>
       <c r="F2027" t="n">
-        <v>-0.08393406948097831</v>
+        <v>-0.1884172482324543</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.500122255319054</v>
+        <v>3.437432348068168</v>
       </c>
     </row>
     <row r="2028">
@@ -48195,16 +48195,16 @@
         <v>3.554732707729614</v>
       </c>
       <c r="D2028" t="n">
-        <v>-6.028555032407802</v>
+        <v>-6.133038211159278</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.142954270452746</v>
+        <v>1.101160998952155</v>
       </c>
       <c r="F2028" t="n">
-        <v>-0.09776056894750135</v>
+        <v>-0.2022437476989773</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.496076366361114</v>
+        <v>3.433386459110229</v>
       </c>
     </row>
     <row r="2029">
@@ -48218,16 +48218,16 @@
         <v>3.56199359061215</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.727108306935964</v>
+        <v>-5.83159148568744</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.270793843524017</v>
+        <v>1.229000572023426</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.2036861565243359</v>
+        <v>0.09920297777285991</v>
       </c>
       <c r="G2029" t="n">
-        <v>3.684205284526752</v>
+        <v>3.621515377275867</v>
       </c>
     </row>
     <row r="2030">
@@ -48241,16 +48241,16 @@
         <v>3.562964768364861</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.751698551171148</v>
+        <v>-5.856181729922624</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.261928923582654</v>
+        <v>1.220135652082063</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.2036861565243359</v>
+        <v>0.09920297777285991</v>
       </c>
       <c r="G2030" t="n">
-        <v>3.685176462279463</v>
+        <v>3.622486555028577</v>
       </c>
     </row>
     <row r="2031">
@@ -48264,16 +48264,16 @@
         <v>3.563807672744617</v>
       </c>
       <c r="D2031" t="n">
-        <v>-5.700660175164628</v>
+        <v>-5.805143353916104</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.283187178365018</v>
+        <v>1.241393906864427</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.2036861565243359</v>
+        <v>0.09920297777285991</v>
       </c>
       <c r="G2031" t="n">
-        <v>3.686019366659218</v>
+        <v>3.623329459408333</v>
       </c>
     </row>
     <row r="2032">
@@ -48287,16 +48287,16 @@
         <v>3.582845771618762</v>
       </c>
       <c r="D2032" t="n">
-        <v>-5.671811498341167</v>
+        <v>-5.776294677092643</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.313764747968547</v>
+        <v>1.271971476467957</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.2325348333477962</v>
+        <v>0.1280516545963202</v>
       </c>
       <c r="G2032" t="n">
-        <v>3.72236667162744</v>
+        <v>3.659676764376554</v>
       </c>
     </row>
     <row r="2033">
@@ -48310,16 +48310,16 @@
         <v>3.399029767742697</v>
       </c>
       <c r="D2033" t="n">
-        <v>-5.575176586322527</v>
+        <v>-5.679659765074003</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.168602708899938</v>
+        <v>1.126809437399347</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.3291697453664361</v>
+        <v>0.2246865666149601</v>
       </c>
       <c r="G2033" t="n">
-        <v>3.596531614962558</v>
+        <v>3.533841707711673</v>
       </c>
     </row>
     <row r="2034">
@@ -48333,16 +48333,16 @@
         <v>3.402531811816661</v>
       </c>
       <c r="D2034" t="n">
-        <v>-5.506138575374059</v>
+        <v>-5.610621754125535</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.199719957353289</v>
+        <v>1.157926685852698</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.3982077563149042</v>
+        <v>0.2937245775634282</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.641456465605604</v>
+        <v>3.578766558354718</v>
       </c>
     </row>
     <row r="2035">
@@ -48356,16 +48356,16 @@
         <v>3.386958630892743</v>
       </c>
       <c r="D2035" t="n">
-        <v>-5.487351475005121</v>
+        <v>-5.591834653756597</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.191661616576947</v>
+        <v>1.149868345076356</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.4169948566838427</v>
+        <v>0.3125116779323667</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.637155544903049</v>
+        <v>3.574465637652164</v>
       </c>
     </row>
     <row r="2036">
@@ -48379,16 +48379,16 @@
         <v>3.386146341329173</v>
       </c>
       <c r="D2036" t="n">
-        <v>-5.410252873463248</v>
+        <v>-5.514736052214724</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.221688767630126</v>
+        <v>1.179895496129535</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.4169948566838427</v>
+        <v>0.3125116779323667</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.636343255339479</v>
+        <v>3.573653348088593</v>
       </c>
     </row>
     <row r="2037">
@@ -48402,16 +48402,16 @@
         <v>3.396015120454245</v>
       </c>
       <c r="D2037" t="n">
-        <v>-5.420638068353138</v>
+        <v>-5.525121247104614</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.227403468799242</v>
+        <v>1.185610197298652</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.4066096617939534</v>
+        <v>0.3021264830424774</v>
       </c>
       <c r="G2037" t="n">
-        <v>3.639980917530618</v>
+        <v>3.577291010279732</v>
       </c>
     </row>
     <row r="2038">
@@ -48425,16 +48425,16 @@
         <v>3.466852126230671</v>
       </c>
       <c r="D2038" t="n">
-        <v>-5.439226227075363</v>
+        <v>-5.543709405826839</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.290805211086778</v>
+        <v>1.249011939586187</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.388021503071728</v>
+        <v>0.283538324320252</v>
       </c>
       <c r="G2038" t="n">
-        <v>3.699665028073708</v>
+        <v>3.636975120822822</v>
       </c>
     </row>
     <row r="2039">
@@ -48448,16 +48448,16 @@
         <v>3.463721137048969</v>
       </c>
       <c r="D2039" t="n">
-        <v>-5.439524773771399</v>
+        <v>-5.544007952522874</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.287554803226662</v>
+        <v>1.245761531726072</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.3877229563756921</v>
+        <v>0.2832397776242161</v>
       </c>
       <c r="G2039" t="n">
-        <v>3.696354910874385</v>
+        <v>3.633665003623499</v>
       </c>
     </row>
     <row r="2040">
@@ -48471,16 +48471,16 @@
         <v>3.468252031988361</v>
       </c>
       <c r="D2040" t="n">
-        <v>-5.338701640080971</v>
+        <v>-5.443184818832447</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.332414951642224</v>
+        <v>1.290621680141634</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.4001871718600459</v>
+        <v>0.2957039931085699</v>
       </c>
       <c r="G2040" t="n">
-        <v>3.708364335104388</v>
+        <v>3.645674427853503</v>
       </c>
     </row>
     <row r="2041">
@@ -48494,16 +48494,16 @@
         <v>3.468381285466904</v>
       </c>
       <c r="D2041" t="n">
-        <v>-5.147920279328563</v>
+        <v>-5.252403458080039</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.408856749421731</v>
+        <v>1.36706347792114</v>
       </c>
       <c r="F2041" t="n">
-        <v>0.5909685326124533</v>
+        <v>0.4864853538609773</v>
       </c>
       <c r="G2041" t="n">
-        <v>3.822962405034376</v>
+        <v>3.76027249778349</v>
       </c>
     </row>
     <row r="2042">
@@ -48511,22 +48511,22 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.775233033906085</v>
+        <v>3.775233033906084</v>
       </c>
       <c r="C2042" t="n">
         <v>3.4482181312045</v>
       </c>
       <c r="D2042" t="n">
-        <v>-5.040956921479141</v>
+        <v>-5.144195086847026</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.431478938299096</v>
+        <v>1.390183672151942</v>
       </c>
       <c r="F2042" t="n">
-        <v>0.6494331405722548</v>
+        <v>0.5946937250939899</v>
       </c>
       <c r="G2042" t="n">
-        <v>3.837878015547854</v>
+        <v>3.805034366260895</v>
       </c>
     </row>
     <row r="2043">
@@ -48540,16 +48540,16 @@
         <v>3.483185067816559</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.985626333577379</v>
+        <v>-5.088864498945264</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.488578110071859</v>
+        <v>1.447282843924705</v>
       </c>
       <c r="F2043" t="n">
-        <v>0.7047637284740169</v>
+        <v>0.650024312995752</v>
       </c>
       <c r="G2043" t="n">
-        <v>3.906043304900969</v>
+        <v>3.87319965561401</v>
       </c>
     </row>
     <row r="2044">
@@ -48557,22 +48557,22 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.743767956539899</v>
+        <v>3.743767956539898</v>
       </c>
       <c r="C2044" t="n">
         <v>3.476871635717997</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.973572206664416</v>
+        <v>-5.076810372032301</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.487086328738482</v>
+        <v>1.445791062591328</v>
       </c>
       <c r="F2044" t="n">
-        <v>0.7168178553869797</v>
+        <v>0.6620784399087148</v>
       </c>
       <c r="G2044" t="n">
-        <v>3.906962348950185</v>
+        <v>3.874118699663226</v>
       </c>
     </row>
     <row r="2045">
@@ -48580,22 +48580,22 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.725010844811014</v>
+        <v>3.725010844811013</v>
       </c>
       <c r="C2045" t="n">
         <v>3.478752265902132</v>
       </c>
       <c r="D2045" t="n">
-        <v>-5.050927696792385</v>
+        <v>-5.15416586216027</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.45802476287143</v>
+        <v>1.416729496724277</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.6394623652590103</v>
+        <v>0.5847229497807455</v>
       </c>
       <c r="G2045" t="n">
-        <v>3.862429685057539</v>
+        <v>3.82958603577058</v>
       </c>
     </row>
     <row r="2046">
@@ -48603,22 +48603,22 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.612322444382925</v>
+        <v>3.612322444382924</v>
       </c>
       <c r="C2046" t="n">
         <v>3.491603291780015</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.982879134100855</v>
+        <v>-5.08611729946874</v>
       </c>
       <c r="E2046" t="n">
-        <v>1.498095213825925</v>
+        <v>1.456799947678771</v>
       </c>
       <c r="F2046" t="n">
-        <v>0.7075109279505402</v>
+        <v>0.6527715124722753</v>
       </c>
       <c r="G2046" t="n">
-        <v>3.916109848550339</v>
+        <v>3.88326619926338</v>
       </c>
     </row>
     <row r="2047">
@@ -48626,22 +48626,22 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.645256780013432</v>
+        <v>3.645256780013431</v>
       </c>
       <c r="C2047" t="n">
         <v>3.511805961953609</v>
       </c>
       <c r="D2047" t="n">
-        <v>-5.214479527270356</v>
+        <v>-5.317717692638241</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.425657726731719</v>
+        <v>1.384362460584565</v>
       </c>
       <c r="F2047" t="n">
-        <v>0.7075109279505402</v>
+        <v>0.6527715124722753</v>
       </c>
       <c r="G2047" t="n">
-        <v>3.936312518723933</v>
+        <v>3.903468869436975</v>
       </c>
     </row>
     <row r="2048">
@@ -48655,16 +48655,16 @@
         <v>3.495412198020491</v>
       </c>
       <c r="D2048" t="n">
-        <v>-5.264531072799576</v>
+        <v>-5.36776923816746</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.389243344586913</v>
+        <v>1.347948078439759</v>
       </c>
       <c r="F2048" t="n">
-        <v>0.7075109279505402</v>
+        <v>0.6527715124722753</v>
       </c>
       <c r="G2048" t="n">
-        <v>3.919918754790816</v>
+        <v>3.887075105503857</v>
       </c>
     </row>
     <row r="2049">
@@ -48672,22 +48672,22 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.670048702800097</v>
+        <v>3.670048702800098</v>
       </c>
       <c r="C2049" t="n">
         <v>3.455664111613958</v>
       </c>
       <c r="D2049" t="n">
-        <v>-5.439637905376021</v>
+        <v>-5.542876070743905</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.279452525149801</v>
+        <v>1.238157259002648</v>
       </c>
       <c r="F2049" t="n">
-        <v>0.7075109279505402</v>
+        <v>0.6527715124722753</v>
       </c>
       <c r="G2049" t="n">
-        <v>3.880170668384282</v>
+        <v>3.847327019097323</v>
       </c>
     </row>
     <row r="2050">
@@ -48695,22 +48695,22 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.745573148660849</v>
+        <v>3.74557314866085</v>
       </c>
       <c r="C2050" t="n">
         <v>3.462686730610898</v>
       </c>
       <c r="D2050" t="n">
-        <v>-5.243537751945498</v>
+        <v>-5.346775917313382</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.364915205518951</v>
+        <v>1.323619939371797</v>
       </c>
       <c r="F2050" t="n">
-        <v>0.9036110813810631</v>
+        <v>0.8488716659027982</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.004853379439536</v>
+        <v>3.972009730152577</v>
       </c>
     </row>
     <row r="2051">
@@ -48724,16 +48724,16 @@
         <v>3.561857730183802</v>
       </c>
       <c r="D2051" t="n">
-        <v>-5.090512359832213</v>
+        <v>-5.193750525200097</v>
       </c>
       <c r="E2051" t="n">
-        <v>1.525296361937169</v>
+        <v>1.484001095790015</v>
       </c>
       <c r="F2051" t="n">
-        <v>1.056636473494347</v>
+        <v>1.001897058016082</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.195839614280411</v>
+        <v>4.162995964993452</v>
       </c>
     </row>
     <row r="2052">
@@ -48747,16 +48747,16 @@
         <v>3.749323955092095</v>
       </c>
       <c r="D2052" t="n">
-        <v>-5.118819673705484</v>
+        <v>-5.222057839073368</v>
       </c>
       <c r="E2052" t="n">
-        <v>1.701439661296153</v>
+        <v>1.660144395149</v>
       </c>
       <c r="F2052" t="n">
-        <v>1.056636473494347</v>
+        <v>1.001897058016082</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.383305839188703</v>
+        <v>4.350462189901744</v>
       </c>
     </row>
     <row r="2053">
@@ -48770,16 +48770,16 @@
         <v>3.718726906446177</v>
       </c>
       <c r="D2053" t="n">
-        <v>-5.285412898819006</v>
+        <v>-5.38865106418689</v>
       </c>
       <c r="E2053" t="n">
-        <v>1.604205322604827</v>
+        <v>1.562910056457674</v>
       </c>
       <c r="F2053" t="n">
-        <v>0.8900432483808247</v>
+        <v>0.8353038329025597</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.252752855474673</v>
+        <v>4.219909206187713</v>
       </c>
     </row>
     <row r="2054">
@@ -48793,16 +48793,16 @@
         <v>3.722403309107895</v>
       </c>
       <c r="D2054" t="n">
-        <v>-5.26237710545744</v>
+        <v>-5.365615270825324</v>
       </c>
       <c r="E2054" t="n">
-        <v>1.617096042611171</v>
+        <v>1.575800776464018</v>
       </c>
       <c r="F2054" t="n">
-        <v>0.8900432483808247</v>
+        <v>0.8353038329025597</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.25642925813639</v>
+        <v>4.223585608849431</v>
       </c>
     </row>
     <row r="2055">
@@ -48816,16 +48816,16 @@
         <v>3.72002136423139</v>
       </c>
       <c r="D2055" t="n">
-        <v>-5.233131125001743</v>
+        <v>-5.336369290369627</v>
       </c>
       <c r="E2055" t="n">
-        <v>1.626412489916945</v>
+        <v>1.585117223769791</v>
       </c>
       <c r="F2055" t="n">
-        <v>0.8900432483808247</v>
+        <v>0.8353038329025597</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.254047313259885</v>
+        <v>4.221203663972926</v>
       </c>
     </row>
     <row r="2056">
@@ -48839,16 +48839,16 @@
         <v>3.717314603389025</v>
       </c>
       <c r="D2056" t="n">
-        <v>-5.340056672879594</v>
+        <v>-5.443294838247478</v>
       </c>
       <c r="E2056" t="n">
-        <v>1.58093550992344</v>
+        <v>1.539640243776286</v>
       </c>
       <c r="F2056" t="n">
-        <v>0.7831177005029734</v>
+        <v>0.7283782850247084</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.187185223690809</v>
+        <v>4.15434157440385</v>
       </c>
     </row>
     <row r="2057">
@@ -48862,16 +48862,16 @@
         <v>3.71874340553226</v>
       </c>
       <c r="D2057" t="n">
-        <v>-5.485075231386843</v>
+        <v>-5.588313396754727</v>
       </c>
       <c r="E2057" t="n">
-        <v>1.524356888663775</v>
+        <v>1.483061622516621</v>
       </c>
       <c r="F2057" t="n">
-        <v>0.6380991419957248</v>
+        <v>0.5833597265174598</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.101602890729695</v>
+        <v>4.068759241442736</v>
       </c>
     </row>
     <row r="2058">
@@ -48885,16 +48885,16 @@
         <v>3.818674644790013</v>
       </c>
       <c r="D2058" t="n">
-        <v>-5.603416997171561</v>
+        <v>-5.706655162539445</v>
       </c>
       <c r="E2058" t="n">
-        <v>1.576951421607641</v>
+        <v>1.535656155460487</v>
       </c>
       <c r="F2058" t="n">
-        <v>0.6487851805586149</v>
+        <v>0.5940457650803499</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.207945753125182</v>
+        <v>4.175102103838223</v>
       </c>
     </row>
     <row r="2059">
@@ -48908,16 +48908,16 @@
         <v>3.816460341915952</v>
       </c>
       <c r="D2059" t="n">
-        <v>-5.654827419492269</v>
+        <v>-5.758065584860153</v>
       </c>
       <c r="E2059" t="n">
-        <v>1.554172949805297</v>
+        <v>1.512877683658143</v>
       </c>
       <c r="F2059" t="n">
-        <v>0.6487851805586149</v>
+        <v>0.5940457650803499</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.205731450251121</v>
+        <v>4.172887800964162</v>
       </c>
     </row>
     <row r="2060">
@@ -48931,16 +48931,16 @@
         <v>3.816363469990241</v>
       </c>
       <c r="D2060" t="n">
-        <v>-5.73424687070002</v>
+        <v>-5.837485036067904</v>
       </c>
       <c r="E2060" t="n">
-        <v>1.522308297396485</v>
+        <v>1.481013031249331</v>
       </c>
       <c r="F2060" t="n">
-        <v>0.6487851805586149</v>
+        <v>0.5940457650803499</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.205634578325411</v>
+        <v>4.172790929038452</v>
       </c>
     </row>
     <row r="2061">
@@ -48954,16 +48954,16 @@
         <v>3.816357363548284</v>
       </c>
       <c r="D2061" t="n">
-        <v>-5.829709868617238</v>
+        <v>-5.932948033985122</v>
       </c>
       <c r="E2061" t="n">
-        <v>1.484116991787641</v>
+        <v>1.442821725640487</v>
       </c>
       <c r="F2061" t="n">
-        <v>0.6487851805586149</v>
+        <v>0.5940457650803499</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.205628471883453</v>
+        <v>4.172784822596494</v>
       </c>
     </row>
     <row r="2062">
@@ -48977,16 +48977,16 @@
         <v>3.814453760110895</v>
       </c>
       <c r="D2062" t="n">
-        <v>-5.765333957766523</v>
+        <v>-5.868572123134407</v>
       </c>
       <c r="E2062" t="n">
-        <v>1.507963752690537</v>
+        <v>1.466668486543384</v>
       </c>
       <c r="F2062" t="n">
-        <v>0.71316109140933</v>
+        <v>0.658421675931065</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.242350414956493</v>
+        <v>4.209506765669534</v>
       </c>
     </row>
     <row r="2063">
@@ -49000,16 +49000,16 @@
         <v>3.820187577858621</v>
       </c>
       <c r="D2063" t="n">
-        <v>-5.820703119898717</v>
+        <v>-5.923941285266601</v>
       </c>
       <c r="E2063" t="n">
-        <v>1.491549905585387</v>
+        <v>1.450254639438233</v>
       </c>
       <c r="F2063" t="n">
-        <v>0.71316109140933</v>
+        <v>0.658421675931065</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.24808423270422</v>
+        <v>4.215240583417261</v>
       </c>
     </row>
     <row r="2064">
@@ -49023,16 +49023,16 @@
         <v>3.819725941201554</v>
       </c>
       <c r="D2064" t="n">
-        <v>-5.838921586896325</v>
+        <v>-5.942159752264209</v>
       </c>
       <c r="E2064" t="n">
-        <v>1.483800882129275</v>
+        <v>1.442505615982122</v>
       </c>
       <c r="F2064" t="n">
-        <v>0.6880546541534879</v>
+        <v>0.6333152386752229</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.232558733693646</v>
+        <v>4.199715084406687</v>
       </c>
     </row>
     <row r="2065">
@@ -49046,16 +49046,16 @@
         <v>3.839600334051872</v>
       </c>
       <c r="D2065" t="n">
-        <v>-5.800238151552395</v>
+        <v>-5.903476316920279</v>
       </c>
       <c r="E2065" t="n">
-        <v>1.519148649117166</v>
+        <v>1.477853382970013</v>
       </c>
       <c r="F2065" t="n">
-        <v>0.6880546541534879</v>
+        <v>0.6333152386752229</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.252433126543965</v>
+        <v>4.219589477257006</v>
       </c>
     </row>
     <row r="2066">
@@ -49069,16 +49069,16 @@
         <v>3.8233010345766</v>
       </c>
       <c r="D2066" t="n">
-        <v>-5.694203156347085</v>
+        <v>-5.797441321714969</v>
       </c>
       <c r="E2066" t="n">
-        <v>1.545263347724018</v>
+        <v>1.503968081576864</v>
       </c>
       <c r="F2066" t="n">
-        <v>0.6880546541534879</v>
+        <v>0.6333152386752229</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.236133827068693</v>
+        <v>4.203290177781734</v>
       </c>
     </row>
     <row r="2067">
@@ -49092,16 +49092,16 @@
         <v>3.825731984040646</v>
       </c>
       <c r="D2067" t="n">
-        <v>-5.51099149321399</v>
+        <v>-5.614229658581874</v>
       </c>
       <c r="E2067" t="n">
-        <v>1.620978962441302</v>
+        <v>1.579683696294148</v>
       </c>
       <c r="F2067" t="n">
-        <v>0.6880546541534879</v>
+        <v>0.6333152386752229</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.238564776532739</v>
+        <v>4.20572112724578</v>
       </c>
     </row>
     <row r="2068">
@@ -49115,16 +49115,16 @@
         <v>3.808676390120023</v>
       </c>
       <c r="D2068" t="n">
-        <v>-5.439270046200139</v>
+        <v>-5.542508211568023</v>
       </c>
       <c r="E2068" t="n">
-        <v>1.63261194732622</v>
+        <v>1.591316681179066</v>
       </c>
       <c r="F2068" t="n">
-        <v>0.7597761011673385</v>
+        <v>0.7050366856890735</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.264542050820427</v>
+        <v>4.231698401533468</v>
       </c>
     </row>
     <row r="2069">
@@ -49138,16 +49138,16 @@
         <v>3.755592136041195</v>
       </c>
       <c r="D2069" t="n">
-        <v>-5.416897020592433</v>
+        <v>-5.520135185960317</v>
       </c>
       <c r="E2069" t="n">
-        <v>1.588476903490474</v>
+        <v>1.54718163734332</v>
       </c>
       <c r="F2069" t="n">
-        <v>0.7710318522802401</v>
+        <v>0.7162924368019751</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.218211247409339</v>
+        <v>4.18536759812238</v>
       </c>
     </row>
     <row r="2070">
@@ -49161,16 +49161,16 @@
         <v>3.94079034092655</v>
       </c>
       <c r="D2070" t="n">
-        <v>-5.449913316503178</v>
+        <v>-5.553151481871062</v>
       </c>
       <c r="E2070" t="n">
-        <v>1.760468590011531</v>
+        <v>1.719173323864377</v>
       </c>
       <c r="F2070" t="n">
-        <v>0.7015944756134884</v>
+        <v>0.6468550601352234</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.361747026294643</v>
+        <v>4.328903377007684</v>
       </c>
     </row>
     <row r="2071">
@@ -49184,16 +49184,16 @@
         <v>3.932711566754799</v>
       </c>
       <c r="D2071" t="n">
-        <v>-5.438385680853569</v>
+        <v>-5.541623846221453</v>
       </c>
       <c r="E2071" t="n">
-        <v>1.757000870099623</v>
+        <v>1.71570560395247</v>
       </c>
       <c r="F2071" t="n">
-        <v>0.7605951338148509</v>
+        <v>0.7058557183365859</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.389068647043709</v>
+        <v>4.356224997756751</v>
       </c>
     </row>
     <row r="2072">
@@ -49207,16 +49207,16 @@
         <v>3.936379679276587</v>
       </c>
       <c r="D2072" t="n">
-        <v>-5.535727182195938</v>
+        <v>-5.638965347563822</v>
       </c>
       <c r="E2072" t="n">
-        <v>1.721732382084464</v>
+        <v>1.680437115937311</v>
       </c>
       <c r="F2072" t="n">
-        <v>0.7161749516493625</v>
+        <v>0.6614355361710975</v>
       </c>
       <c r="G2072" t="n">
-        <v>4.366084650266205</v>
+        <v>4.333241000979246</v>
       </c>
     </row>
     <row r="2073">
@@ -49230,16 +49230,16 @@
         <v>3.937630761469426</v>
       </c>
       <c r="D2073" t="n">
-        <v>-5.621583211535905</v>
+        <v>-5.724821376903789</v>
       </c>
       <c r="E2073" t="n">
-        <v>1.688641052541316</v>
+        <v>1.647345786394162</v>
       </c>
       <c r="F2073" t="n">
-        <v>0.6737988824232275</v>
+        <v>0.6190594669449625</v>
       </c>
       <c r="G2073" t="n">
-        <v>4.341910090923363</v>
+        <v>4.309066441636404</v>
       </c>
     </row>
     <row r="2074">
@@ -49247,22 +49247,22 @@
         <v>45536</v>
       </c>
       <c r="B2074" t="n">
-        <v>3.69183549961038</v>
+        <v>3.691835499610381</v>
       </c>
       <c r="C2074" t="n">
         <v>3.920049963289927</v>
       </c>
       <c r="D2074" t="n">
-        <v>-5.630420008952024</v>
+        <v>-5.733658174319908</v>
       </c>
       <c r="E2074" t="n">
-        <v>1.66752553539537</v>
+        <v>1.626230269248216</v>
       </c>
       <c r="F2074" t="n">
-        <v>0.6663567097818768</v>
+        <v>0.6116172943036118</v>
       </c>
       <c r="G2074" t="n">
-        <v>4.319863989159054</v>
+        <v>4.287020339872095</v>
       </c>
     </row>
     <row r="2075">
@@ -49270,22 +49270,22 @@
         <v>45537</v>
       </c>
       <c r="B2075" t="n">
-        <v>3.715544411667459</v>
+        <v>3.71554441166746</v>
       </c>
       <c r="C2075" t="n">
         <v>3.930214474334977</v>
       </c>
       <c r="D2075" t="n">
-        <v>-5.721802571517483</v>
+        <v>-5.825040736885366</v>
       </c>
       <c r="E2075" t="n">
-        <v>1.641137021414236</v>
+        <v>1.599841755267082</v>
       </c>
       <c r="F2075" t="n">
-        <v>0.6297918250625321</v>
+        <v>0.5750524095842671</v>
       </c>
       <c r="G2075" t="n">
-        <v>4.308089569372497</v>
+        <v>4.275245920085537</v>
       </c>
     </row>
     <row r="2076">
@@ -49299,16 +49299,16 @@
         <v>4.032342732159245</v>
       </c>
       <c r="D2076" t="n">
-        <v>-5.710095853530476</v>
+        <v>-5.81333401889836</v>
       </c>
       <c r="E2076" t="n">
-        <v>1.747947966433307</v>
+        <v>1.706652700286153</v>
       </c>
       <c r="F2076" t="n">
-        <v>0.6414985430495385</v>
+        <v>0.5867591275712735</v>
       </c>
       <c r="G2076" t="n">
-        <v>4.417241857988969</v>
+        <v>4.384398208702009</v>
       </c>
     </row>
     <row r="2077">
@@ -49316,22 +49316,22 @@
         <v>45539</v>
       </c>
       <c r="B2077" t="n">
-        <v>3.682476099409572</v>
+        <v>3.682476099409573</v>
       </c>
       <c r="C2077" t="n">
         <v>4.03537507089065</v>
       </c>
       <c r="D2077" t="n">
-        <v>-5.781007927272753</v>
+        <v>-5.884246092640637</v>
       </c>
       <c r="E2077" t="n">
-        <v>1.7226154756678</v>
+        <v>1.681320209520647</v>
       </c>
       <c r="F2077" t="n">
-        <v>0.6414985430495385</v>
+        <v>0.5867591275712735</v>
       </c>
       <c r="G2077" t="n">
-        <v>4.420274196720373</v>
+        <v>4.387430547433414</v>
       </c>
     </row>
     <row r="2078">
@@ -49339,22 +49339,22 @@
         <v>45540</v>
       </c>
       <c r="B2078" t="n">
-        <v>3.67289517745257</v>
+        <v>3.672895177452572</v>
       </c>
       <c r="C2078" t="n">
         <v>4.036193896622915</v>
       </c>
       <c r="D2078" t="n">
-        <v>-5.791324025439105</v>
+        <v>-5.894562190806989</v>
       </c>
       <c r="E2078" t="n">
-        <v>1.719307862133524</v>
+        <v>1.678012595986371</v>
       </c>
       <c r="F2078" t="n">
-        <v>0.6382608623766438</v>
+        <v>0.5867591275712735</v>
       </c>
       <c r="G2078" t="n">
-        <v>4.419150414048901</v>
+        <v>4.388249373165679</v>
       </c>
     </row>
     <row r="2079">
@@ -49362,22 +49362,22 @@
         <v>45541</v>
       </c>
       <c r="B2079" t="n">
-        <v>3.623960959762292</v>
+        <v>3.623960959762293</v>
       </c>
       <c r="C2079" t="n">
         <v>4.035372563535004</v>
       </c>
       <c r="D2079" t="n">
-        <v>-5.791230057421733</v>
+        <v>-5.894468222789617</v>
       </c>
       <c r="E2079" t="n">
-        <v>1.718524116252563</v>
+        <v>1.67722885010541</v>
       </c>
       <c r="F2079" t="n">
-        <v>0.6386307237239618</v>
+        <v>0.5871289889185914</v>
       </c>
       <c r="G2079" t="n">
-        <v>4.418550997769382</v>
+        <v>4.387649956886159</v>
       </c>
     </row>
     <row r="2080">
@@ -49385,22 +49385,22 @@
         <v>45542</v>
       </c>
       <c r="B2080" t="n">
-        <v>3.800870306884084</v>
+        <v>3.800870306884086</v>
       </c>
       <c r="C2080" t="n">
         <v>4.029604549479358</v>
       </c>
       <c r="D2080" t="n">
-        <v>-5.934831221445118</v>
+        <v>-6.038069386813002</v>
       </c>
       <c r="E2080" t="n">
-        <v>1.655315636587563</v>
+        <v>1.614020370440409</v>
       </c>
       <c r="F2080" t="n">
-        <v>0.6386307237239618</v>
+        <v>0.5871289889185914</v>
       </c>
       <c r="G2080" t="n">
-        <v>4.412782983713735</v>
+        <v>4.381881942830513</v>
       </c>
     </row>
     <row r="2081">
@@ -49408,22 +49408,22 @@
         <v>45543</v>
       </c>
       <c r="B2081" t="n">
-        <v>3.671015692129648</v>
+        <v>3.67101569212965</v>
       </c>
       <c r="C2081" t="n">
         <v>4.029604549479358</v>
       </c>
       <c r="D2081" t="n">
-        <v>-5.93388279832708</v>
+        <v>-6.037120963694964</v>
       </c>
       <c r="E2081" t="n">
-        <v>1.655695005834778</v>
+        <v>1.614399739687625</v>
       </c>
       <c r="F2081" t="n">
-        <v>0.6386307237239618</v>
+        <v>0.5871289889185914</v>
       </c>
       <c r="G2081" t="n">
-        <v>4.412782983713735</v>
+        <v>4.381881942830513</v>
       </c>
     </row>
     <row r="2082">
@@ -49431,22 +49431,22 @@
         <v>45544</v>
       </c>
       <c r="B2082" t="n">
-        <v>3.904173816052351</v>
+        <v>3.904173816052353</v>
       </c>
       <c r="C2082" t="n">
         <v>4.04233215746045</v>
       </c>
       <c r="D2082" t="n">
-        <v>-6.0341526162861</v>
+        <v>-6.137390781653984</v>
       </c>
       <c r="E2082" t="n">
-        <v>1.628314686632262</v>
+        <v>1.587019420485108</v>
       </c>
       <c r="F2082" t="n">
-        <v>0.6386307237239618</v>
+        <v>0.5871289889185914</v>
       </c>
       <c r="G2082" t="n">
-        <v>4.425510591694827</v>
+        <v>4.394609550811605</v>
       </c>
     </row>
     <row r="2083">
@@ -49454,22 +49454,22 @@
         <v>45545</v>
       </c>
       <c r="B2083" t="n">
-        <v>3.740179607813495</v>
+        <v>3.740179607813497</v>
       </c>
       <c r="C2083" t="n">
         <v>4.044278155884838</v>
       </c>
       <c r="D2083" t="n">
-        <v>-6.028160369497289</v>
+        <v>-6.131398534865173</v>
       </c>
       <c r="E2083" t="n">
-        <v>1.632657583772174</v>
+        <v>1.591362317625021</v>
       </c>
       <c r="F2083" t="n">
-        <v>0.6386307237239618</v>
+        <v>0.5871289889185914</v>
       </c>
       <c r="G2083" t="n">
-        <v>4.427456590119215</v>
+        <v>4.396555549235993</v>
       </c>
     </row>
     <row r="2084">
@@ -49477,22 +49477,22 @@
         <v>45546</v>
       </c>
       <c r="B2084" t="n">
-        <v>3.765050796537944</v>
+        <v>3.765050796537945</v>
       </c>
       <c r="C2084" t="n">
         <v>4.037932291902607</v>
       </c>
       <c r="D2084" t="n">
-        <v>-5.939602408366521</v>
+        <v>-6.042840573734405</v>
       </c>
       <c r="E2084" t="n">
-        <v>1.66173490424225</v>
+        <v>1.620439638095097</v>
       </c>
       <c r="F2084" t="n">
-        <v>0.6386307237239618</v>
+        <v>0.5871289889185914</v>
       </c>
       <c r="G2084" t="n">
-        <v>4.421110726136984</v>
+        <v>4.390209685253762</v>
       </c>
     </row>
     <row r="2085">
@@ -49500,22 +49500,22 @@
         <v>45547</v>
       </c>
       <c r="B2085" t="n">
-        <v>3.758409170771816</v>
+        <v>3.758409170771817</v>
       </c>
       <c r="C2085" t="n">
         <v>4.037240969341602</v>
       </c>
       <c r="D2085" t="n">
-        <v>-5.921843330863447</v>
+        <v>-6.025081496231331</v>
       </c>
       <c r="E2085" t="n">
-        <v>1.668147212682475</v>
+        <v>1.626851946535322</v>
       </c>
       <c r="F2085" t="n">
-        <v>0.6386307237239618</v>
+        <v>0.5871289889185914</v>
       </c>
       <c r="G2085" t="n">
-        <v>4.42041940357598</v>
+        <v>4.389518362692757</v>
       </c>
     </row>
     <row r="2086">
@@ -49523,22 +49523,22 @@
         <v>45548</v>
       </c>
       <c r="B2086" t="n">
-        <v>3.801340597109721</v>
+        <v>3.801340597109723</v>
       </c>
       <c r="C2086" t="n">
         <v>4.050023155250189</v>
       </c>
       <c r="D2086" t="n">
-        <v>-5.822213179814379</v>
+        <v>-5.925451345182263</v>
       </c>
       <c r="E2086" t="n">
-        <v>1.72078145901069</v>
+        <v>1.679486192863536</v>
       </c>
       <c r="F2086" t="n">
-        <v>0.7382608747730293</v>
+        <v>0.6867591399676589</v>
       </c>
       <c r="G2086" t="n">
-        <v>4.492979680114007</v>
+        <v>4.462078639230785</v>
       </c>
     </row>
     <row r="2087">
@@ -49546,22 +49546,22 @@
         <v>45549</v>
       </c>
       <c r="B2087" t="n">
-        <v>3.798465546843996</v>
+        <v>3.798465546843998</v>
       </c>
       <c r="C2087" t="n">
         <v>4.239177420748915</v>
       </c>
       <c r="D2087" t="n">
-        <v>-5.87161268850339</v>
+        <v>-5.974850853871274</v>
       </c>
       <c r="E2087" t="n">
-        <v>1.890175921033812</v>
+        <v>1.848880654886658</v>
       </c>
       <c r="F2087" t="n">
-        <v>0.748519708204774</v>
+        <v>0.6970179733994036</v>
       </c>
       <c r="G2087" t="n">
-        <v>4.68828924567178</v>
+        <v>4.657388204788558</v>
       </c>
     </row>
     <row r="2088">
@@ -49569,22 +49569,22 @@
         <v>45550</v>
       </c>
       <c r="B2088" t="n">
-        <v>3.77218650835186</v>
+        <v>3.772186508351862</v>
       </c>
       <c r="C2088" t="n">
         <v>4.226366093851778</v>
       </c>
       <c r="D2088" t="n">
-        <v>-5.664928214861014</v>
+        <v>-5.768166380228898</v>
       </c>
       <c r="E2088" t="n">
-        <v>1.960038383593624</v>
+        <v>1.91874311744647</v>
       </c>
       <c r="F2088" t="n">
-        <v>0.9552041818471496</v>
+        <v>0.9037024470417793</v>
       </c>
       <c r="G2088" t="n">
-        <v>4.799488602960068</v>
+        <v>4.768587562076846</v>
       </c>
     </row>
     <row r="2089">
@@ -49592,22 +49592,22 @@
         <v>45551</v>
       </c>
       <c r="B2089" t="n">
-        <v>3.76339283855127</v>
+        <v>3.763392838551272</v>
       </c>
       <c r="C2089" t="n">
         <v>4.228367607505882</v>
       </c>
       <c r="D2089" t="n">
-        <v>-5.69908510985854</v>
+        <v>-5.802323275226424</v>
       </c>
       <c r="E2089" t="n">
-        <v>1.948377139248719</v>
+        <v>1.907081873101565</v>
       </c>
       <c r="F2089" t="n">
-        <v>0.8716204123063371</v>
+        <v>0.8201186775009668</v>
       </c>
       <c r="G2089" t="n">
-        <v>4.751339854889685</v>
+        <v>4.720438814006463</v>
       </c>
     </row>
     <row r="2090">
@@ -49615,22 +49615,22 @@
         <v>45552</v>
       </c>
       <c r="B2090" t="n">
-        <v>3.805590565041111</v>
+        <v>3.805590565041113</v>
       </c>
       <c r="C2090" t="n">
         <v>4.58186472149555</v>
       </c>
       <c r="D2090" t="n">
-        <v>-5.606495630797084</v>
+        <v>-5.709733796164968</v>
       </c>
       <c r="E2090" t="n">
-        <v>2.338910044862968</v>
+        <v>2.297614778715815</v>
       </c>
       <c r="F2090" t="n">
-        <v>0.8716204123063371</v>
+        <v>0.8201186775009668</v>
       </c>
       <c r="G2090" t="n">
-        <v>5.104836968879352</v>
+        <v>5.07393592799613</v>
       </c>
     </row>
     <row r="2091">
@@ -49638,22 +49638,22 @@
         <v>45553</v>
       </c>
       <c r="B2091" t="n">
-        <v>3.832164354497403</v>
+        <v>3.832164354497404</v>
       </c>
       <c r="C2091" t="n">
         <v>4.586427833062654</v>
       </c>
       <c r="D2091" t="n">
-        <v>-5.679656234570229</v>
+        <v>-5.782894399938113</v>
       </c>
       <c r="E2091" t="n">
-        <v>2.314208914920814</v>
+        <v>2.272913648773661</v>
       </c>
       <c r="F2091" t="n">
-        <v>0.8435992122720941</v>
+        <v>0.7920974774667238</v>
       </c>
       <c r="G2091" t="n">
-        <v>5.09258736042591</v>
+        <v>5.061686319542688</v>
       </c>
     </row>
     <row r="2092">
@@ -49661,22 +49661,22 @@
         <v>45554</v>
       </c>
       <c r="B2092" t="n">
-        <v>3.858310890492296</v>
+        <v>3.858310890492298</v>
       </c>
       <c r="C2092" t="n">
         <v>4.636257774386181</v>
       </c>
       <c r="D2092" t="n">
-        <v>-5.627439924773887</v>
+        <v>-5.730678090141771</v>
       </c>
       <c r="E2092" t="n">
-        <v>2.384925380162879</v>
+        <v>2.343630114015725</v>
       </c>
       <c r="F2092" t="n">
-        <v>0.8435992122720941</v>
+        <v>0.7920974774667238</v>
       </c>
       <c r="G2092" t="n">
-        <v>5.142417301749438</v>
+        <v>5.111516260866216</v>
       </c>
     </row>
     <row r="2093">
@@ -49690,16 +49690,16 @@
         <v>4.645071744596192</v>
       </c>
       <c r="D2093" t="n">
-        <v>-5.574932597263392</v>
+        <v>-5.678170762631276</v>
       </c>
       <c r="E2093" t="n">
-        <v>2.414742281377088</v>
+        <v>2.373447015229934</v>
       </c>
       <c r="F2093" t="n">
-        <v>0.896106539782589</v>
+        <v>0.8446048049772187</v>
       </c>
       <c r="G2093" t="n">
-        <v>5.182735668465746</v>
+        <v>5.151834627582524</v>
       </c>
     </row>
     <row r="2094">
@@ -49707,22 +49707,22 @@
         <v>45556</v>
       </c>
       <c r="B2094" t="n">
-        <v>3.848376866039487</v>
+        <v>3.848376866039488</v>
       </c>
       <c r="C2094" t="n">
         <v>4.640709328635389</v>
       </c>
       <c r="D2094" t="n">
-        <v>-5.589687921463533</v>
+        <v>-5.692926086831417</v>
       </c>
       <c r="E2094" t="n">
-        <v>2.404477735736228</v>
+        <v>2.363182469589075</v>
       </c>
       <c r="F2094" t="n">
-        <v>0.896106539782589</v>
+        <v>0.8446048049772187</v>
       </c>
       <c r="G2094" t="n">
-        <v>5.178373252504943</v>
+        <v>5.147472211621721</v>
       </c>
     </row>
     <row r="2095">
@@ -49730,22 +49730,22 @@
         <v>45557</v>
       </c>
       <c r="B2095" t="n">
-        <v>3.868153115524482</v>
+        <v>3.868153115524483</v>
       </c>
       <c r="C2095" t="n">
         <v>4.631633832051669</v>
       </c>
       <c r="D2095" t="n">
-        <v>-5.540223298093621</v>
+        <v>-5.643461463461505</v>
       </c>
       <c r="E2095" t="n">
-        <v>2.415188088500473</v>
+        <v>2.373892822353319</v>
       </c>
       <c r="F2095" t="n">
-        <v>0.9455711631525007</v>
+        <v>0.8940694283471303</v>
       </c>
       <c r="G2095" t="n">
-        <v>5.19897652994317</v>
+        <v>5.168075489059948</v>
       </c>
     </row>
     <row r="2096">
@@ -49753,22 +49753,22 @@
         <v>45558</v>
       </c>
       <c r="B2096" t="n">
-        <v>3.849040239867955</v>
+        <v>3.849040239867957</v>
       </c>
       <c r="C2096" t="n">
         <v>4.628041499766604</v>
       </c>
       <c r="D2096" t="n">
-        <v>-5.377115305940006</v>
+        <v>-5.48035347130789</v>
       </c>
       <c r="E2096" t="n">
-        <v>2.476838953076853</v>
+        <v>2.4355436869297</v>
       </c>
       <c r="F2096" t="n">
-        <v>1.108679155306116</v>
+        <v>1.057177420500746</v>
       </c>
       <c r="G2096" t="n">
-        <v>5.293248992950273</v>
+        <v>5.262347952067051</v>
       </c>
     </row>
     <row r="2097">
@@ -49776,22 +49776,22 @@
         <v>45559</v>
       </c>
       <c r="B2097" t="n">
-        <v>3.870204928232971</v>
+        <v>3.870204928232973</v>
       </c>
       <c r="C2097" t="n">
         <v>4.637088536457732</v>
       </c>
       <c r="D2097" t="n">
-        <v>-5.356472215138778</v>
+        <v>-5.459710380506662</v>
       </c>
       <c r="E2097" t="n">
-        <v>2.494143226088473</v>
+        <v>2.452847959941319</v>
       </c>
       <c r="F2097" t="n">
-        <v>1.108679155306116</v>
+        <v>1.057177420500746</v>
       </c>
       <c r="G2097" t="n">
-        <v>5.302296029641401</v>
+        <v>5.271394988758179</v>
       </c>
     </row>
     <row r="2098">
@@ -49799,22 +49799,22 @@
         <v>45560</v>
       </c>
       <c r="B2098" t="n">
-        <v>3.855534437179674</v>
+        <v>3.855534437179677</v>
       </c>
       <c r="C2098" t="n">
         <v>4.637946001443853</v>
       </c>
       <c r="D2098" t="n">
-        <v>-5.419180131613336</v>
+        <v>-5.52241829698122</v>
       </c>
       <c r="E2098" t="n">
-        <v>2.469917524484771</v>
+        <v>2.428622258337617</v>
       </c>
       <c r="F2098" t="n">
-        <v>1.045971238831558</v>
+        <v>0.9944695040261879</v>
       </c>
       <c r="G2098" t="n">
-        <v>5.265528744742789</v>
+        <v>5.234627703859567</v>
       </c>
     </row>
     <row r="2099">
@@ -49822,22 +49822,22 @@
         <v>45561</v>
       </c>
       <c r="B2099" t="n">
-        <v>3.884687848967721</v>
+        <v>3.884687848967724</v>
       </c>
       <c r="C2099" t="n">
         <v>4.600855418234206</v>
       </c>
       <c r="D2099" t="n">
-        <v>-5.371172007769643</v>
+        <v>-5.474410173137527</v>
       </c>
       <c r="E2099" t="n">
-        <v>2.452030190812601</v>
+        <v>2.410734924665447</v>
       </c>
       <c r="F2099" t="n">
-        <v>1.045971238831558</v>
+        <v>0.9944695040261879</v>
       </c>
       <c r="G2099" t="n">
-        <v>5.228438161533141</v>
+        <v>5.197537120649919</v>
       </c>
     </row>
     <row r="2100">
@@ -49845,22 +49845,22 @@
         <v>45562</v>
       </c>
       <c r="B2100" t="n">
-        <v>3.895362357018612</v>
+        <v>3.895362357018615</v>
       </c>
       <c r="C2100" t="n">
         <v>4.604787671792156</v>
       </c>
       <c r="D2100" t="n">
-        <v>-5.221053952547746</v>
+        <v>-5.32429211791563</v>
       </c>
       <c r="E2100" t="n">
-        <v>2.51600966645931</v>
+        <v>2.474714400312156</v>
       </c>
       <c r="F2100" t="n">
-        <v>1.196089294053455</v>
+        <v>1.144587559248085</v>
       </c>
       <c r="G2100" t="n">
-        <v>5.322441248224229</v>
+        <v>5.291540207341007</v>
       </c>
     </row>
     <row r="2101">
@@ -49868,22 +49868,22 @@
         <v>45563</v>
       </c>
       <c r="B2101" t="n">
-        <v>3.891610981075135</v>
+        <v>3.891610981075138</v>
       </c>
       <c r="C2101" t="n">
         <v>4.599686764399193</v>
       </c>
       <c r="D2101" t="n">
-        <v>-5.029119151293872</v>
+        <v>-5.132357316661756</v>
       </c>
       <c r="E2101" t="n">
-        <v>2.587682679567896</v>
+        <v>2.546387413420743</v>
       </c>
       <c r="F2101" t="n">
-        <v>1.196089294053455</v>
+        <v>1.144587559248085</v>
       </c>
       <c r="G2101" t="n">
-        <v>5.317340340831266</v>
+        <v>5.286439299948044</v>
       </c>
     </row>
     <row r="2102">
@@ -49891,22 +49891,22 @@
         <v>45564</v>
       </c>
       <c r="B2102" t="n">
-        <v>3.872432493435445</v>
+        <v>3.872432493435449</v>
       </c>
       <c r="C2102" t="n">
         <v>4.595040673788288</v>
       </c>
       <c r="D2102" t="n">
-        <v>-4.910945773275945</v>
+        <v>-5.014183938643828</v>
       </c>
       <c r="E2102" t="n">
-        <v>2.630305940164162</v>
+        <v>2.589010674017009</v>
       </c>
       <c r="F2102" t="n">
-        <v>1.314262672071383</v>
+        <v>1.262760937266012</v>
       </c>
       <c r="G2102" t="n">
-        <v>5.383598277031118</v>
+        <v>5.352697236147896</v>
       </c>
     </row>
     <row r="2103">
@@ -49914,22 +49914,22 @@
         <v>45565</v>
       </c>
       <c r="B2103" t="n">
-        <v>3.859571723917734</v>
+        <v>3.859571723917736</v>
       </c>
       <c r="C2103" t="n">
         <v>4.624129266651315</v>
       </c>
       <c r="D2103" t="n">
-        <v>-4.822098656416447</v>
+        <v>-4.925336821784331</v>
       </c>
       <c r="E2103" t="n">
-        <v>2.694933379770989</v>
+        <v>2.653638113623835</v>
       </c>
       <c r="F2103" t="n">
-        <v>1.40310978893088</v>
+        <v>1.35160805412551</v>
       </c>
       <c r="G2103" t="n">
-        <v>5.465995140009843</v>
+        <v>5.435094099126621</v>
       </c>
     </row>
     <row r="2104">
@@ -49937,22 +49937,22 @@
         <v>45566</v>
       </c>
       <c r="B2104" t="n">
-        <v>3.82800627401364</v>
+        <v>3.828006274013642</v>
       </c>
       <c r="C2104" t="n">
         <v>4.617689489662492</v>
       </c>
       <c r="D2104" t="n">
-        <v>-4.795049618723193</v>
+        <v>-4.898287784091077</v>
       </c>
       <c r="E2104" t="n">
-        <v>2.699313217859467</v>
+        <v>2.658017951712313</v>
       </c>
       <c r="F2104" t="n">
-        <v>1.430158826624134</v>
+        <v>1.378657091818764</v>
       </c>
       <c r="G2104" t="n">
-        <v>5.475784785636973</v>
+        <v>5.444883744753751</v>
       </c>
     </row>
     <row r="2105">
@@ -49960,22 +49960,22 @@
         <v>45567</v>
       </c>
       <c r="B2105" t="n">
-        <v>3.82398744526377</v>
+        <v>3.823987445263773</v>
       </c>
       <c r="C2105" t="n">
         <v>4.617689489662492</v>
       </c>
       <c r="D2105" t="n">
-        <v>-4.801082898909963</v>
+        <v>-4.904321064277847</v>
       </c>
       <c r="E2105" t="n">
-        <v>2.696899905784759</v>
+        <v>2.655604639637605</v>
       </c>
       <c r="F2105" t="n">
-        <v>1.430158826624134</v>
+        <v>1.378657091818764</v>
       </c>
       <c r="G2105" t="n">
-        <v>5.475784785636973</v>
+        <v>5.444883744753751</v>
       </c>
     </row>
     <row r="2106">
@@ -49983,22 +49983,22 @@
         <v>45568</v>
       </c>
       <c r="B2106" t="n">
-        <v>3.815657203170844</v>
+        <v>3.815657203170847</v>
       </c>
       <c r="C2106" t="n">
         <v>4.621327656804905</v>
       </c>
       <c r="D2106" t="n">
-        <v>-4.852934674483125</v>
+        <v>-4.956172839851009</v>
       </c>
       <c r="E2106" t="n">
-        <v>2.679797362697907</v>
+        <v>2.638502096550753</v>
       </c>
       <c r="F2106" t="n">
-        <v>1.378307051050973</v>
+        <v>1.326805316245602</v>
       </c>
       <c r="G2106" t="n">
-        <v>5.448311887435489</v>
+        <v>5.417410846552267</v>
       </c>
     </row>
     <row r="2107">
@@ -50006,22 +50006,22 @@
         <v>45569</v>
       </c>
       <c r="B2107" t="n">
-        <v>3.830586986431407</v>
+        <v>3.830586986431411</v>
       </c>
       <c r="C2107" t="n">
         <v>4.584819403988742</v>
       </c>
       <c r="D2107" t="n">
-        <v>-4.879992120614951</v>
+        <v>-4.947330653560489</v>
       </c>
       <c r="E2107" t="n">
-        <v>2.632466131429013</v>
+        <v>2.605530718250798</v>
       </c>
       <c r="F2107" t="n">
-        <v>1.378307051050973</v>
+        <v>1.326805316245602</v>
       </c>
       <c r="G2107" t="n">
-        <v>5.411803634619325</v>
+        <v>5.380902593736103</v>
       </c>
     </row>
     <row r="2108">
@@ -50029,22 +50029,22 @@
         <v>45570</v>
       </c>
       <c r="B2108" t="n">
-        <v>3.830856457232457</v>
+        <v>3.830856457232461</v>
       </c>
       <c r="C2108" t="n">
         <v>4.586227353735933</v>
       </c>
       <c r="D2108" t="n">
-        <v>-4.953273472468827</v>
+        <v>-5.020612005414365</v>
       </c>
       <c r="E2108" t="n">
-        <v>2.604561540434654</v>
+        <v>2.577626127256439</v>
       </c>
       <c r="F2108" t="n">
-        <v>1.364395628919761</v>
+        <v>1.312893894114391</v>
       </c>
       <c r="G2108" t="n">
-        <v>5.40486473108779</v>
+        <v>5.373963690204568</v>
       </c>
     </row>
     <row r="2109">
@@ -50052,22 +50052,22 @@
         <v>45571</v>
       </c>
       <c r="B2109" t="n">
-        <v>3.907285875710493</v>
+        <v>3.786339171305453</v>
       </c>
       <c r="C2109" t="n">
-        <v>4.774161771843032</v>
+        <v>4.599336815855964</v>
       </c>
       <c r="D2109" t="n">
-        <v>-4.953273472468827</v>
+        <v>-5.020612005414365</v>
       </c>
       <c r="E2109" t="n">
-        <v>2.604561540434654</v>
+        <v>2.577626127256439</v>
       </c>
       <c r="F2109" t="n">
-        <v>1.364395628919761</v>
+        <v>1.312893894114391</v>
       </c>
       <c r="G2109" t="n">
-        <v>4.7672255688294</v>
+        <v>4.592400612842332</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20241006.xlsx
+++ b/tame_output/ON/bt/strategyON_20241006.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>53.8%</t>
+          <t>54.9%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.2%</t>
+          <t>65.1%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.5%</t>
+          <t>-11.3%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>50.6%</t>
+          <t>54.4%</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>102.3%</t>
+          <t>101.7%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -768,7 +768,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.36</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,12 +791,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>39.9%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>45.7%</t>
+          <t>45.8%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -829,7 +829,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-2.5%</t>
+          <t>-2.8%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-7.8%</t>
+          <t>-7.9%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>85.8%</t>
+          <t>85.0%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>148.3%</t>
+          <t>146.5%</t>
         </is>
       </c>
     </row>
@@ -921,7 +921,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>107.0%</t>
+          <t>107.1%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.2%</t>
+          <t>52.1%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>89.9%</t>
+          <t>90.1%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -982,12 +982,12 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-37.6%</t>
+          <t>-34.7%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>-9.5%</t>
+          <t>-9.6%</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-47.9%</t>
+          <t>-47.8%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-74.3%</t>
+          <t>-74.2%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>88.7%</t>
+          <t>88.8%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>420.6%</t>
+          <t>421.1%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-663.6%</t>
+          <t>-662.0%</t>
         </is>
       </c>
     </row>
@@ -1079,7 +1079,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>59.3%</t>
+          <t>59.4%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>57.2%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>56.1%</t>
+          <t>56.2%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1140,7 +1140,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-9.5%</t>
+          <t>-10.2%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-31.0%</t>
+          <t>-31.2%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>26.7%</t>
+          <t>26.6%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-4.2%</t>
+          <t>-4.4%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14.1%</t>
+          <t>14.0%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-118.5%</t>
+          <t>-118.3%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-2.3%</t>
+          <t>-1.8%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.8%</t>
+          <t>54.9%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1298,22 +1298,22 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>-4.6%</t>
+          <t>-5.5%</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>-3.2%</t>
+          <t>-3.1%</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.7%</t>
+          <t>10.9%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-23.7%</t>
+          <t>-23.9%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>4.8%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>42.4%</t>
+          <t>41.5%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-204.7%</t>
+          <t>-205.0%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-92.7%</t>
+          <t>-89.6%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>64.5%</t>
+          <t>114.6%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>66.1%</t>
+          <t>57.6%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>78.3%</t>
+          <t>60.2%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>56.0%</t>
+          <t>56.1%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-9.5%</t>
+          <t>-7.6%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-24.3%</t>
+          <t>-18.7%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>55.5%</t>
+          <t>104.0%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>55.0%</t>
+          <t>48.0%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.0%</t>
+          <t>-16.6%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>36.7%</t>
+          <t>36.6%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>92.8%</t>
         </is>
       </c>
     </row>
@@ -48511,22 +48511,22 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.775233033906084</v>
+        <v>3.775233033906085</v>
       </c>
       <c r="C2042" t="n">
         <v>3.4482181312045</v>
       </c>
       <c r="D2042" t="n">
-        <v>-5.144195086847026</v>
+        <v>-5.145440100230617</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.390183672151942</v>
+        <v>1.389685666798505</v>
       </c>
       <c r="F2042" t="n">
-        <v>0.5946937250939899</v>
+        <v>0.5449499618207787</v>
       </c>
       <c r="G2042" t="n">
-        <v>3.805034366260895</v>
+        <v>3.775188108296968</v>
       </c>
     </row>
     <row r="2043">
@@ -48540,16 +48540,16 @@
         <v>3.483185067816559</v>
       </c>
       <c r="D2043" t="n">
-        <v>-5.088864498945264</v>
+        <v>-5.036469644204036</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.447282843924705</v>
+        <v>1.468240785821196</v>
       </c>
       <c r="F2043" t="n">
-        <v>0.650024312995752</v>
+        <v>0.6539204178473598</v>
       </c>
       <c r="G2043" t="n">
-        <v>3.87319965561401</v>
+        <v>3.875537318524975</v>
       </c>
     </row>
     <row r="2044">
@@ -48563,16 +48563,16 @@
         <v>3.476871635717997</v>
       </c>
       <c r="D2044" t="n">
-        <v>-5.076810372032301</v>
+        <v>-5.005276696352669</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.445791062591328</v>
+        <v>1.474404532863181</v>
       </c>
       <c r="F2044" t="n">
-        <v>0.6620784399087148</v>
+        <v>0.6851133656987265</v>
       </c>
       <c r="G2044" t="n">
-        <v>3.874118699663226</v>
+        <v>3.887939655137233</v>
       </c>
     </row>
     <row r="2045">
@@ -48586,16 +48586,16 @@
         <v>3.478752265902132</v>
       </c>
       <c r="D2045" t="n">
-        <v>-5.15416586216027</v>
+        <v>-5.082632186480638</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.416729496724277</v>
+        <v>1.445342966996129</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.5847229497807455</v>
+        <v>0.6077578755707571</v>
       </c>
       <c r="G2045" t="n">
-        <v>3.82958603577058</v>
+        <v>3.843406991244587</v>
       </c>
     </row>
     <row r="2046">
@@ -48609,16 +48609,16 @@
         <v>3.491603291780015</v>
       </c>
       <c r="D2046" t="n">
-        <v>-5.08611729946874</v>
+        <v>-5.014583623789108</v>
       </c>
       <c r="E2046" t="n">
-        <v>1.456799947678771</v>
+        <v>1.485413417950623</v>
       </c>
       <c r="F2046" t="n">
-        <v>0.6527715124722753</v>
+        <v>0.6758064382622869</v>
       </c>
       <c r="G2046" t="n">
-        <v>3.88326619926338</v>
+        <v>3.897087154737387</v>
       </c>
     </row>
     <row r="2047">
@@ -48632,16 +48632,16 @@
         <v>3.511805961953609</v>
       </c>
       <c r="D2047" t="n">
-        <v>-5.317717692638241</v>
+        <v>-5.246184016958609</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.384362460584565</v>
+        <v>1.412975930856418</v>
       </c>
       <c r="F2047" t="n">
-        <v>0.6527715124722753</v>
+        <v>0.6758064382622869</v>
       </c>
       <c r="G2047" t="n">
-        <v>3.903468869436975</v>
+        <v>3.917289824910982</v>
       </c>
     </row>
     <row r="2048">
@@ -48655,16 +48655,16 @@
         <v>3.495412198020491</v>
       </c>
       <c r="D2048" t="n">
-        <v>-5.36776923816746</v>
+        <v>-5.296235562487828</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.347948078439759</v>
+        <v>1.376561548711612</v>
       </c>
       <c r="F2048" t="n">
-        <v>0.6527715124722753</v>
+        <v>0.6758064382622869</v>
       </c>
       <c r="G2048" t="n">
-        <v>3.887075105503857</v>
+        <v>3.900896060977864</v>
       </c>
     </row>
     <row r="2049">
@@ -48672,22 +48672,22 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.670048702800098</v>
+        <v>3.670048702800097</v>
       </c>
       <c r="C2049" t="n">
         <v>3.455664111613958</v>
       </c>
       <c r="D2049" t="n">
-        <v>-5.542876070743905</v>
+        <v>-5.471342395064273</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.238157259002648</v>
+        <v>1.266770729274501</v>
       </c>
       <c r="F2049" t="n">
-        <v>0.6527715124722753</v>
+        <v>0.6758064382622869</v>
       </c>
       <c r="G2049" t="n">
-        <v>3.847327019097323</v>
+        <v>3.86114797457133</v>
       </c>
     </row>
     <row r="2050">
@@ -48695,22 +48695,22 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.74557314866085</v>
+        <v>3.745573148660849</v>
       </c>
       <c r="C2050" t="n">
         <v>3.462686730610898</v>
       </c>
       <c r="D2050" t="n">
-        <v>-5.346775917313382</v>
+        <v>-5.27524224163375</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.323619939371797</v>
+        <v>1.35223340964365</v>
       </c>
       <c r="F2050" t="n">
-        <v>0.8488716659027982</v>
+        <v>0.8719065916928098</v>
       </c>
       <c r="G2050" t="n">
-        <v>3.972009730152577</v>
+        <v>3.985830685626584</v>
       </c>
     </row>
     <row r="2051">
@@ -48724,16 +48724,16 @@
         <v>3.561857730183802</v>
       </c>
       <c r="D2051" t="n">
-        <v>-5.193750525200097</v>
+        <v>-5.122216849520465</v>
       </c>
       <c r="E2051" t="n">
-        <v>1.484001095790015</v>
+        <v>1.512614566061868</v>
       </c>
       <c r="F2051" t="n">
-        <v>1.001897058016082</v>
+        <v>1.024931983806094</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.162995964993452</v>
+        <v>4.176816920467459</v>
       </c>
     </row>
     <row r="2052">
@@ -48747,16 +48747,16 @@
         <v>3.749323955092095</v>
       </c>
       <c r="D2052" t="n">
-        <v>-5.222057839073368</v>
+        <v>-5.150524163393736</v>
       </c>
       <c r="E2052" t="n">
-        <v>1.660144395149</v>
+        <v>1.688757865420853</v>
       </c>
       <c r="F2052" t="n">
-        <v>1.001897058016082</v>
+        <v>1.024931983806094</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.350462189901744</v>
+        <v>4.364283145375751</v>
       </c>
     </row>
     <row r="2053">
@@ -48770,16 +48770,16 @@
         <v>3.718726906446177</v>
       </c>
       <c r="D2053" t="n">
-        <v>-5.38865106418689</v>
+        <v>-5.317117388507258</v>
       </c>
       <c r="E2053" t="n">
-        <v>1.562910056457674</v>
+        <v>1.591523526729526</v>
       </c>
       <c r="F2053" t="n">
-        <v>0.8353038329025597</v>
+        <v>0.8583387586925715</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.219909206187713</v>
+        <v>4.233730161661721</v>
       </c>
     </row>
     <row r="2054">
@@ -48793,16 +48793,16 @@
         <v>3.722403309107895</v>
       </c>
       <c r="D2054" t="n">
-        <v>-5.365615270825324</v>
+        <v>-5.294081595145692</v>
       </c>
       <c r="E2054" t="n">
-        <v>1.575800776464018</v>
+        <v>1.60441424673587</v>
       </c>
       <c r="F2054" t="n">
-        <v>0.8353038329025597</v>
+        <v>0.8583387586925715</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.223585608849431</v>
+        <v>4.237406564323439</v>
       </c>
     </row>
     <row r="2055">
@@ -48816,16 +48816,16 @@
         <v>3.72002136423139</v>
       </c>
       <c r="D2055" t="n">
-        <v>-5.336369290369627</v>
+        <v>-5.264835614689996</v>
       </c>
       <c r="E2055" t="n">
-        <v>1.585117223769791</v>
+        <v>1.613730694041644</v>
       </c>
       <c r="F2055" t="n">
-        <v>0.8353038329025597</v>
+        <v>0.8583387586925715</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.221203663972926</v>
+        <v>4.235024619446934</v>
       </c>
     </row>
     <row r="2056">
@@ -48839,16 +48839,16 @@
         <v>3.717314603389025</v>
       </c>
       <c r="D2056" t="n">
-        <v>-5.443294838247478</v>
+        <v>-5.371761162567847</v>
       </c>
       <c r="E2056" t="n">
-        <v>1.539640243776286</v>
+        <v>1.568253714048139</v>
       </c>
       <c r="F2056" t="n">
-        <v>0.7283782850247084</v>
+        <v>0.7514132108147201</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.15434157440385</v>
+        <v>4.168162529877858</v>
       </c>
     </row>
     <row r="2057">
@@ -48862,16 +48862,16 @@
         <v>3.71874340553226</v>
       </c>
       <c r="D2057" t="n">
-        <v>-5.588313396754727</v>
+        <v>-5.516779721075095</v>
       </c>
       <c r="E2057" t="n">
-        <v>1.483061622516621</v>
+        <v>1.511675092788474</v>
       </c>
       <c r="F2057" t="n">
-        <v>0.5833597265174598</v>
+        <v>0.6063946523074716</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.068759241442736</v>
+        <v>4.082580196916743</v>
       </c>
     </row>
     <row r="2058">
@@ -48885,16 +48885,16 @@
         <v>3.818674644790013</v>
       </c>
       <c r="D2058" t="n">
-        <v>-5.706655162539445</v>
+        <v>-5.635121486859813</v>
       </c>
       <c r="E2058" t="n">
-        <v>1.535656155460487</v>
+        <v>1.56426962573234</v>
       </c>
       <c r="F2058" t="n">
-        <v>0.5940457650803499</v>
+        <v>0.6170806908703617</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.175102103838223</v>
+        <v>4.18892305931223</v>
       </c>
     </row>
     <row r="2059">
@@ -48908,16 +48908,16 @@
         <v>3.816460341915952</v>
       </c>
       <c r="D2059" t="n">
-        <v>-5.758065584860153</v>
+        <v>-5.686531909180521</v>
       </c>
       <c r="E2059" t="n">
-        <v>1.512877683658143</v>
+        <v>1.541491153929996</v>
       </c>
       <c r="F2059" t="n">
-        <v>0.5940457650803499</v>
+        <v>0.6170806908703617</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.172887800964162</v>
+        <v>4.186708756438169</v>
       </c>
     </row>
     <row r="2060">
@@ -48931,16 +48931,16 @@
         <v>3.816363469990241</v>
       </c>
       <c r="D2060" t="n">
-        <v>-5.837485036067904</v>
+        <v>-5.765951360388272</v>
       </c>
       <c r="E2060" t="n">
-        <v>1.481013031249331</v>
+        <v>1.509626501521184</v>
       </c>
       <c r="F2060" t="n">
-        <v>0.5940457650803499</v>
+        <v>0.6170806908703617</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.172790929038452</v>
+        <v>4.186611884512458</v>
       </c>
     </row>
     <row r="2061">
@@ -48954,16 +48954,16 @@
         <v>3.816357363548284</v>
       </c>
       <c r="D2061" t="n">
-        <v>-5.932948033985122</v>
+        <v>-5.86141435830549</v>
       </c>
       <c r="E2061" t="n">
-        <v>1.442821725640487</v>
+        <v>1.47143519591234</v>
       </c>
       <c r="F2061" t="n">
-        <v>0.5940457650803499</v>
+        <v>0.6170806908703617</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.172784822596494</v>
+        <v>4.186605778070501</v>
       </c>
     </row>
     <row r="2062">
@@ -48977,16 +48977,16 @@
         <v>3.814453760110895</v>
       </c>
       <c r="D2062" t="n">
-        <v>-5.868572123134407</v>
+        <v>-5.797038447454775</v>
       </c>
       <c r="E2062" t="n">
-        <v>1.466668486543384</v>
+        <v>1.495281956815237</v>
       </c>
       <c r="F2062" t="n">
-        <v>0.658421675931065</v>
+        <v>0.6814566017210768</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.209506765669534</v>
+        <v>4.223327721143541</v>
       </c>
     </row>
     <row r="2063">
@@ -49000,16 +49000,16 @@
         <v>3.820187577858621</v>
       </c>
       <c r="D2063" t="n">
-        <v>-5.923941285266601</v>
+        <v>-5.852407609586969</v>
       </c>
       <c r="E2063" t="n">
-        <v>1.450254639438233</v>
+        <v>1.478868109710086</v>
       </c>
       <c r="F2063" t="n">
-        <v>0.658421675931065</v>
+        <v>0.6814566017210768</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.215240583417261</v>
+        <v>4.229061538891267</v>
       </c>
     </row>
     <row r="2064">
@@ -49023,16 +49023,16 @@
         <v>3.819725941201554</v>
       </c>
       <c r="D2064" t="n">
-        <v>-5.942159752264209</v>
+        <v>-5.870626076584577</v>
       </c>
       <c r="E2064" t="n">
-        <v>1.442505615982122</v>
+        <v>1.471119086253974</v>
       </c>
       <c r="F2064" t="n">
-        <v>0.6333152386752229</v>
+        <v>0.6563501644652346</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.199715084406687</v>
+        <v>4.213536039880695</v>
       </c>
     </row>
     <row r="2065">
@@ -49046,16 +49046,16 @@
         <v>3.839600334051872</v>
       </c>
       <c r="D2065" t="n">
-        <v>-5.903476316920279</v>
+        <v>-5.831942641240647</v>
       </c>
       <c r="E2065" t="n">
-        <v>1.477853382970013</v>
+        <v>1.506466853241866</v>
       </c>
       <c r="F2065" t="n">
-        <v>0.6333152386752229</v>
+        <v>0.6563501644652346</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.219589477257006</v>
+        <v>4.233410432731013</v>
       </c>
     </row>
     <row r="2066">
@@ -49069,16 +49069,16 @@
         <v>3.8233010345766</v>
       </c>
       <c r="D2066" t="n">
-        <v>-5.797441321714969</v>
+        <v>-5.725907646035338</v>
       </c>
       <c r="E2066" t="n">
-        <v>1.503968081576864</v>
+        <v>1.532581551848717</v>
       </c>
       <c r="F2066" t="n">
-        <v>0.6333152386752229</v>
+        <v>0.6563501644652346</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.203290177781734</v>
+        <v>4.217111133255741</v>
       </c>
     </row>
     <row r="2067">
@@ -49092,16 +49092,16 @@
         <v>3.825731984040646</v>
       </c>
       <c r="D2067" t="n">
-        <v>-5.614229658581874</v>
+        <v>-5.542695982902242</v>
       </c>
       <c r="E2067" t="n">
-        <v>1.579683696294148</v>
+        <v>1.608297166566001</v>
       </c>
       <c r="F2067" t="n">
-        <v>0.6333152386752229</v>
+        <v>0.6563501644652346</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.20572112724578</v>
+        <v>4.219542082719787</v>
       </c>
     </row>
     <row r="2068">
@@ -49115,16 +49115,16 @@
         <v>3.808676390120023</v>
       </c>
       <c r="D2068" t="n">
-        <v>-5.542508211568023</v>
+        <v>-5.470974535888391</v>
       </c>
       <c r="E2068" t="n">
-        <v>1.591316681179066</v>
+        <v>1.619930151450919</v>
       </c>
       <c r="F2068" t="n">
-        <v>0.7050366856890735</v>
+        <v>0.7280716114790853</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.231698401533468</v>
+        <v>4.245519357007475</v>
       </c>
     </row>
     <row r="2069">
@@ -49138,16 +49138,16 @@
         <v>3.755592136041195</v>
       </c>
       <c r="D2069" t="n">
-        <v>-5.520135185960317</v>
+        <v>-5.448601510280685</v>
       </c>
       <c r="E2069" t="n">
-        <v>1.54718163734332</v>
+        <v>1.575795107615173</v>
       </c>
       <c r="F2069" t="n">
-        <v>0.7162924368019751</v>
+        <v>0.7393273625919868</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.18536759812238</v>
+        <v>4.199188553596387</v>
       </c>
     </row>
     <row r="2070">
@@ -49161,16 +49161,16 @@
         <v>3.94079034092655</v>
       </c>
       <c r="D2070" t="n">
-        <v>-5.553151481871062</v>
+        <v>-5.48161780619143</v>
       </c>
       <c r="E2070" t="n">
-        <v>1.719173323864377</v>
+        <v>1.74778679413623</v>
       </c>
       <c r="F2070" t="n">
-        <v>0.6468550601352234</v>
+        <v>0.6698899859252352</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.328903377007684</v>
+        <v>4.342724332481692</v>
       </c>
     </row>
     <row r="2071">
@@ -49184,16 +49184,16 @@
         <v>3.932711566754799</v>
       </c>
       <c r="D2071" t="n">
-        <v>-5.541623846221453</v>
+        <v>-5.470090170541821</v>
       </c>
       <c r="E2071" t="n">
-        <v>1.71570560395247</v>
+        <v>1.744319074224322</v>
       </c>
       <c r="F2071" t="n">
-        <v>0.7058557183365859</v>
+        <v>0.7288906441265977</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.356224997756751</v>
+        <v>4.370045953230758</v>
       </c>
     </row>
     <row r="2072">
@@ -49207,16 +49207,16 @@
         <v>3.936379679276587</v>
       </c>
       <c r="D2072" t="n">
-        <v>-5.638965347563822</v>
+        <v>-5.56743167188419</v>
       </c>
       <c r="E2072" t="n">
-        <v>1.680437115937311</v>
+        <v>1.709050586209163</v>
       </c>
       <c r="F2072" t="n">
-        <v>0.6614355361710975</v>
+        <v>0.6844704619611093</v>
       </c>
       <c r="G2072" t="n">
-        <v>4.333241000979246</v>
+        <v>4.347061956453254</v>
       </c>
     </row>
     <row r="2073">
@@ -49224,22 +49224,22 @@
         <v>45535</v>
       </c>
       <c r="B2073" t="n">
-        <v>3.70520107942769</v>
+        <v>3.705201079427689</v>
       </c>
       <c r="C2073" t="n">
         <v>3.937630761469426</v>
       </c>
       <c r="D2073" t="n">
-        <v>-5.724821376903789</v>
+        <v>-5.653287701224157</v>
       </c>
       <c r="E2073" t="n">
-        <v>1.647345786394162</v>
+        <v>1.675959256666015</v>
       </c>
       <c r="F2073" t="n">
-        <v>0.6190594669449625</v>
+        <v>0.6420943927349743</v>
       </c>
       <c r="G2073" t="n">
-        <v>4.309066441636404</v>
+        <v>4.322887397110411</v>
       </c>
     </row>
     <row r="2074">
@@ -49247,22 +49247,22 @@
         <v>45536</v>
       </c>
       <c r="B2074" t="n">
-        <v>3.691835499610381</v>
+        <v>3.69183549961038</v>
       </c>
       <c r="C2074" t="n">
         <v>3.920049963289927</v>
       </c>
       <c r="D2074" t="n">
-        <v>-5.733658174319908</v>
+        <v>-5.662124498640276</v>
       </c>
       <c r="E2074" t="n">
-        <v>1.626230269248216</v>
+        <v>1.654843739520069</v>
       </c>
       <c r="F2074" t="n">
-        <v>0.6116172943036118</v>
+        <v>0.6346522200936235</v>
       </c>
       <c r="G2074" t="n">
-        <v>4.287020339872095</v>
+        <v>4.300841295346101</v>
       </c>
     </row>
     <row r="2075">
@@ -49270,22 +49270,22 @@
         <v>45537</v>
       </c>
       <c r="B2075" t="n">
-        <v>3.71554441166746</v>
+        <v>3.715544411667459</v>
       </c>
       <c r="C2075" t="n">
         <v>3.930214474334977</v>
       </c>
       <c r="D2075" t="n">
-        <v>-5.825040736885366</v>
+        <v>-5.753507061205735</v>
       </c>
       <c r="E2075" t="n">
-        <v>1.599841755267082</v>
+        <v>1.628455225538935</v>
       </c>
       <c r="F2075" t="n">
-        <v>0.5750524095842671</v>
+        <v>0.5980873353742788</v>
       </c>
       <c r="G2075" t="n">
-        <v>4.275245920085537</v>
+        <v>4.289066875559545</v>
       </c>
     </row>
     <row r="2076">
@@ -49293,22 +49293,22 @@
         <v>45538</v>
       </c>
       <c r="B2076" t="n">
-        <v>3.673978374889197</v>
+        <v>3.673978374889196</v>
       </c>
       <c r="C2076" t="n">
         <v>4.032342732159245</v>
       </c>
       <c r="D2076" t="n">
-        <v>-5.81333401889836</v>
+        <v>-5.741800343218729</v>
       </c>
       <c r="E2076" t="n">
-        <v>1.706652700286153</v>
+        <v>1.735266170558006</v>
       </c>
       <c r="F2076" t="n">
-        <v>0.5867591275712735</v>
+        <v>0.6097940533612852</v>
       </c>
       <c r="G2076" t="n">
-        <v>4.384398208702009</v>
+        <v>4.398219164176017</v>
       </c>
     </row>
     <row r="2077">
@@ -49316,22 +49316,22 @@
         <v>45539</v>
       </c>
       <c r="B2077" t="n">
-        <v>3.682476099409573</v>
+        <v>3.682476099409572</v>
       </c>
       <c r="C2077" t="n">
         <v>4.03537507089065</v>
       </c>
       <c r="D2077" t="n">
-        <v>-5.884246092640637</v>
+        <v>-5.812712416961006</v>
       </c>
       <c r="E2077" t="n">
-        <v>1.681320209520647</v>
+        <v>1.7099336797925</v>
       </c>
       <c r="F2077" t="n">
-        <v>0.5867591275712735</v>
+        <v>0.6097940533612852</v>
       </c>
       <c r="G2077" t="n">
-        <v>4.387430547433414</v>
+        <v>4.401251502907422</v>
       </c>
     </row>
     <row r="2078">
@@ -49339,22 +49339,22 @@
         <v>45540</v>
       </c>
       <c r="B2078" t="n">
-        <v>3.672895177452572</v>
+        <v>3.67289517745257</v>
       </c>
       <c r="C2078" t="n">
         <v>4.036193896622915</v>
       </c>
       <c r="D2078" t="n">
-        <v>-5.894562190806989</v>
+        <v>-5.823028515127358</v>
       </c>
       <c r="E2078" t="n">
-        <v>1.678012595986371</v>
+        <v>1.706626066258223</v>
       </c>
       <c r="F2078" t="n">
-        <v>0.5867591275712735</v>
+        <v>0.6097940533612852</v>
       </c>
       <c r="G2078" t="n">
-        <v>4.388249373165679</v>
+        <v>4.402070328639686</v>
       </c>
     </row>
     <row r="2079">
@@ -49362,22 +49362,22 @@
         <v>45541</v>
       </c>
       <c r="B2079" t="n">
-        <v>3.623960959762293</v>
+        <v>3.623960959762292</v>
       </c>
       <c r="C2079" t="n">
         <v>4.035372563535004</v>
       </c>
       <c r="D2079" t="n">
-        <v>-5.894468222789617</v>
+        <v>-5.822934547109985</v>
       </c>
       <c r="E2079" t="n">
-        <v>1.67722885010541</v>
+        <v>1.705842320377262</v>
       </c>
       <c r="F2079" t="n">
-        <v>0.5871289889185914</v>
+        <v>0.6101639147086032</v>
       </c>
       <c r="G2079" t="n">
-        <v>4.387649956886159</v>
+        <v>4.401470912360167</v>
       </c>
     </row>
     <row r="2080">
@@ -49385,22 +49385,22 @@
         <v>45542</v>
       </c>
       <c r="B2080" t="n">
-        <v>3.800870306884086</v>
+        <v>3.800870306884084</v>
       </c>
       <c r="C2080" t="n">
         <v>4.029604549479358</v>
       </c>
       <c r="D2080" t="n">
-        <v>-6.038069386813002</v>
+        <v>-5.96653571113337</v>
       </c>
       <c r="E2080" t="n">
-        <v>1.614020370440409</v>
+        <v>1.642633840712262</v>
       </c>
       <c r="F2080" t="n">
-        <v>0.5871289889185914</v>
+        <v>0.6101639147086032</v>
       </c>
       <c r="G2080" t="n">
-        <v>4.381881942830513</v>
+        <v>4.395702898304521</v>
       </c>
     </row>
     <row r="2081">
@@ -49408,22 +49408,22 @@
         <v>45543</v>
       </c>
       <c r="B2081" t="n">
-        <v>3.67101569212965</v>
+        <v>3.671015692129648</v>
       </c>
       <c r="C2081" t="n">
         <v>4.029604549479358</v>
       </c>
       <c r="D2081" t="n">
-        <v>-6.037120963694964</v>
+        <v>-5.965587288015332</v>
       </c>
       <c r="E2081" t="n">
-        <v>1.614399739687625</v>
+        <v>1.643013209959477</v>
       </c>
       <c r="F2081" t="n">
-        <v>0.5871289889185914</v>
+        <v>0.6101639147086032</v>
       </c>
       <c r="G2081" t="n">
-        <v>4.381881942830513</v>
+        <v>4.395702898304521</v>
       </c>
     </row>
     <row r="2082">
@@ -49431,22 +49431,22 @@
         <v>45544</v>
       </c>
       <c r="B2082" t="n">
-        <v>3.904173816052353</v>
+        <v>3.904173816052351</v>
       </c>
       <c r="C2082" t="n">
         <v>4.04233215746045</v>
       </c>
       <c r="D2082" t="n">
-        <v>-6.137390781653984</v>
+        <v>-6.065857105974352</v>
       </c>
       <c r="E2082" t="n">
-        <v>1.587019420485108</v>
+        <v>1.615632890756961</v>
       </c>
       <c r="F2082" t="n">
-        <v>0.5871289889185914</v>
+        <v>0.6101639147086032</v>
       </c>
       <c r="G2082" t="n">
-        <v>4.394609550811605</v>
+        <v>4.408430506285613</v>
       </c>
     </row>
     <row r="2083">
@@ -49454,22 +49454,22 @@
         <v>45545</v>
       </c>
       <c r="B2083" t="n">
-        <v>3.740179607813497</v>
+        <v>3.740179607813495</v>
       </c>
       <c r="C2083" t="n">
         <v>4.044278155884838</v>
       </c>
       <c r="D2083" t="n">
-        <v>-6.131398534865173</v>
+        <v>-6.059864859185541</v>
       </c>
       <c r="E2083" t="n">
-        <v>1.591362317625021</v>
+        <v>1.619975787896873</v>
       </c>
       <c r="F2083" t="n">
-        <v>0.5871289889185914</v>
+        <v>0.6101639147086032</v>
       </c>
       <c r="G2083" t="n">
-        <v>4.396555549235993</v>
+        <v>4.41037650471</v>
       </c>
     </row>
     <row r="2084">
@@ -49477,22 +49477,22 @@
         <v>45546</v>
       </c>
       <c r="B2084" t="n">
-        <v>3.765050796537945</v>
+        <v>3.765050796537944</v>
       </c>
       <c r="C2084" t="n">
         <v>4.037932291902607</v>
       </c>
       <c r="D2084" t="n">
-        <v>-6.042840573734405</v>
+        <v>-5.971306898054773</v>
       </c>
       <c r="E2084" t="n">
-        <v>1.620439638095097</v>
+        <v>1.64905310836695</v>
       </c>
       <c r="F2084" t="n">
-        <v>0.5871289889185914</v>
+        <v>0.6101639147086032</v>
       </c>
       <c r="G2084" t="n">
-        <v>4.390209685253762</v>
+        <v>4.404030640727769</v>
       </c>
     </row>
     <row r="2085">
@@ -49500,22 +49500,22 @@
         <v>45547</v>
       </c>
       <c r="B2085" t="n">
-        <v>3.758409170771817</v>
+        <v>3.758409170771816</v>
       </c>
       <c r="C2085" t="n">
         <v>4.037240969341602</v>
       </c>
       <c r="D2085" t="n">
-        <v>-6.025081496231331</v>
+        <v>-5.953547820551699</v>
       </c>
       <c r="E2085" t="n">
-        <v>1.626851946535322</v>
+        <v>1.655465416807175</v>
       </c>
       <c r="F2085" t="n">
-        <v>0.5871289889185914</v>
+        <v>0.6101639147086032</v>
       </c>
       <c r="G2085" t="n">
-        <v>4.389518362692757</v>
+        <v>4.403339318166765</v>
       </c>
     </row>
     <row r="2086">
@@ -49523,22 +49523,22 @@
         <v>45548</v>
       </c>
       <c r="B2086" t="n">
-        <v>3.801340597109723</v>
+        <v>3.801340597109721</v>
       </c>
       <c r="C2086" t="n">
         <v>4.050023155250189</v>
       </c>
       <c r="D2086" t="n">
-        <v>-5.925451345182263</v>
+        <v>-5.853917669502631</v>
       </c>
       <c r="E2086" t="n">
-        <v>1.679486192863536</v>
+        <v>1.708099663135389</v>
       </c>
       <c r="F2086" t="n">
-        <v>0.6867591399676589</v>
+        <v>0.7097940657576707</v>
       </c>
       <c r="G2086" t="n">
-        <v>4.462078639230785</v>
+        <v>4.475899594704792</v>
       </c>
     </row>
     <row r="2087">
@@ -49546,22 +49546,22 @@
         <v>45549</v>
       </c>
       <c r="B2087" t="n">
-        <v>3.798465546843998</v>
+        <v>3.798465546843996</v>
       </c>
       <c r="C2087" t="n">
         <v>4.239177420748915</v>
       </c>
       <c r="D2087" t="n">
-        <v>-5.974850853871274</v>
+        <v>-5.903317178191642</v>
       </c>
       <c r="E2087" t="n">
-        <v>1.848880654886658</v>
+        <v>1.877494125158511</v>
       </c>
       <c r="F2087" t="n">
-        <v>0.6970179733994036</v>
+        <v>0.7200528991894154</v>
       </c>
       <c r="G2087" t="n">
-        <v>4.657388204788558</v>
+        <v>4.671209160262565</v>
       </c>
     </row>
     <row r="2088">
@@ -49569,22 +49569,22 @@
         <v>45550</v>
       </c>
       <c r="B2088" t="n">
-        <v>3.772186508351862</v>
+        <v>3.77218650835186</v>
       </c>
       <c r="C2088" t="n">
         <v>4.226366093851778</v>
       </c>
       <c r="D2088" t="n">
-        <v>-5.768166380228898</v>
+        <v>-5.696632704549266</v>
       </c>
       <c r="E2088" t="n">
-        <v>1.91874311744647</v>
+        <v>1.947356587718323</v>
       </c>
       <c r="F2088" t="n">
-        <v>0.9037024470417793</v>
+        <v>0.926737372831791</v>
       </c>
       <c r="G2088" t="n">
-        <v>4.768587562076846</v>
+        <v>4.782408517550852</v>
       </c>
     </row>
     <row r="2089">
@@ -49592,22 +49592,22 @@
         <v>45551</v>
       </c>
       <c r="B2089" t="n">
-        <v>3.763392838551272</v>
+        <v>3.76339283855127</v>
       </c>
       <c r="C2089" t="n">
         <v>4.228367607505882</v>
       </c>
       <c r="D2089" t="n">
-        <v>-5.802323275226424</v>
+        <v>-5.730789599546792</v>
       </c>
       <c r="E2089" t="n">
-        <v>1.907081873101565</v>
+        <v>1.935695343373418</v>
       </c>
       <c r="F2089" t="n">
-        <v>0.8201186775009668</v>
+        <v>0.8431536032909785</v>
       </c>
       <c r="G2089" t="n">
-        <v>4.720438814006463</v>
+        <v>4.73425976948047</v>
       </c>
     </row>
     <row r="2090">
@@ -49615,22 +49615,22 @@
         <v>45552</v>
       </c>
       <c r="B2090" t="n">
-        <v>3.805590565041113</v>
+        <v>3.805590565041111</v>
       </c>
       <c r="C2090" t="n">
         <v>4.58186472149555</v>
       </c>
       <c r="D2090" t="n">
-        <v>-5.709733796164968</v>
+        <v>-5.638200120485336</v>
       </c>
       <c r="E2090" t="n">
-        <v>2.297614778715815</v>
+        <v>2.326228248987668</v>
       </c>
       <c r="F2090" t="n">
-        <v>0.8201186775009668</v>
+        <v>0.8431536032909785</v>
       </c>
       <c r="G2090" t="n">
-        <v>5.07393592799613</v>
+        <v>5.087756883470138</v>
       </c>
     </row>
     <row r="2091">
@@ -49638,22 +49638,22 @@
         <v>45553</v>
       </c>
       <c r="B2091" t="n">
-        <v>3.832164354497404</v>
+        <v>3.832164354497403</v>
       </c>
       <c r="C2091" t="n">
         <v>4.586427833062654</v>
       </c>
       <c r="D2091" t="n">
-        <v>-5.782894399938113</v>
+        <v>-5.711360724258481</v>
       </c>
       <c r="E2091" t="n">
-        <v>2.272913648773661</v>
+        <v>2.301527119045514</v>
       </c>
       <c r="F2091" t="n">
-        <v>0.7920974774667238</v>
+        <v>0.8151324032567355</v>
       </c>
       <c r="G2091" t="n">
-        <v>5.061686319542688</v>
+        <v>5.075507275016696</v>
       </c>
     </row>
     <row r="2092">
@@ -49661,22 +49661,22 @@
         <v>45554</v>
       </c>
       <c r="B2092" t="n">
-        <v>3.858310890492298</v>
+        <v>3.858310890492296</v>
       </c>
       <c r="C2092" t="n">
         <v>4.636257774386181</v>
       </c>
       <c r="D2092" t="n">
-        <v>-5.730678090141771</v>
+        <v>-5.659144414462139</v>
       </c>
       <c r="E2092" t="n">
-        <v>2.343630114015725</v>
+        <v>2.372243584287578</v>
       </c>
       <c r="F2092" t="n">
-        <v>0.7920974774667238</v>
+        <v>0.8151324032567355</v>
       </c>
       <c r="G2092" t="n">
-        <v>5.111516260866216</v>
+        <v>5.125337216340223</v>
       </c>
     </row>
     <row r="2093">
@@ -49690,16 +49690,16 @@
         <v>4.645071744596192</v>
       </c>
       <c r="D2093" t="n">
-        <v>-5.678170762631276</v>
+        <v>-5.606637086951644</v>
       </c>
       <c r="E2093" t="n">
-        <v>2.373447015229934</v>
+        <v>2.402060485501787</v>
       </c>
       <c r="F2093" t="n">
-        <v>0.8446048049772187</v>
+        <v>0.8676397307672304</v>
       </c>
       <c r="G2093" t="n">
-        <v>5.151834627582524</v>
+        <v>5.165655583056531</v>
       </c>
     </row>
     <row r="2094">
@@ -49707,22 +49707,22 @@
         <v>45556</v>
       </c>
       <c r="B2094" t="n">
-        <v>3.848376866039488</v>
+        <v>3.848376866039487</v>
       </c>
       <c r="C2094" t="n">
         <v>4.640709328635389</v>
       </c>
       <c r="D2094" t="n">
-        <v>-5.692926086831417</v>
+        <v>-5.621392411151785</v>
       </c>
       <c r="E2094" t="n">
-        <v>2.363182469589075</v>
+        <v>2.391795939860927</v>
       </c>
       <c r="F2094" t="n">
-        <v>0.8446048049772187</v>
+        <v>0.8676397307672304</v>
       </c>
       <c r="G2094" t="n">
-        <v>5.147472211621721</v>
+        <v>5.161293167095728</v>
       </c>
     </row>
     <row r="2095">
@@ -49730,22 +49730,22 @@
         <v>45557</v>
       </c>
       <c r="B2095" t="n">
-        <v>3.868153115524483</v>
+        <v>3.868153115524482</v>
       </c>
       <c r="C2095" t="n">
         <v>4.631633832051669</v>
       </c>
       <c r="D2095" t="n">
-        <v>-5.643461463461505</v>
+        <v>-5.571927787781873</v>
       </c>
       <c r="E2095" t="n">
-        <v>2.373892822353319</v>
+        <v>2.402506292625172</v>
       </c>
       <c r="F2095" t="n">
-        <v>0.8940694283471303</v>
+        <v>0.9171043541371421</v>
       </c>
       <c r="G2095" t="n">
-        <v>5.168075489059948</v>
+        <v>5.181896444533955</v>
       </c>
     </row>
     <row r="2096">
@@ -49753,22 +49753,22 @@
         <v>45558</v>
       </c>
       <c r="B2096" t="n">
-        <v>3.849040239867957</v>
+        <v>3.849040239867955</v>
       </c>
       <c r="C2096" t="n">
         <v>4.628041499766604</v>
       </c>
       <c r="D2096" t="n">
-        <v>-5.48035347130789</v>
+        <v>-5.408819795628258</v>
       </c>
       <c r="E2096" t="n">
-        <v>2.4355436869297</v>
+        <v>2.464157157201553</v>
       </c>
       <c r="F2096" t="n">
-        <v>1.057177420500746</v>
+        <v>1.080212346290757</v>
       </c>
       <c r="G2096" t="n">
-        <v>5.262347952067051</v>
+        <v>5.276168907541058</v>
       </c>
     </row>
     <row r="2097">
@@ -49776,22 +49776,22 @@
         <v>45559</v>
       </c>
       <c r="B2097" t="n">
-        <v>3.870204928232973</v>
+        <v>3.870204928232971</v>
       </c>
       <c r="C2097" t="n">
         <v>4.637088536457732</v>
       </c>
       <c r="D2097" t="n">
-        <v>-5.459710380506662</v>
+        <v>-5.38817670482703</v>
       </c>
       <c r="E2097" t="n">
-        <v>2.452847959941319</v>
+        <v>2.481461430213172</v>
       </c>
       <c r="F2097" t="n">
-        <v>1.057177420500746</v>
+        <v>1.080212346290757</v>
       </c>
       <c r="G2097" t="n">
-        <v>5.271394988758179</v>
+        <v>5.285215944232187</v>
       </c>
     </row>
     <row r="2098">
@@ -49799,22 +49799,22 @@
         <v>45560</v>
       </c>
       <c r="B2098" t="n">
-        <v>3.855534437179677</v>
+        <v>3.855534437179674</v>
       </c>
       <c r="C2098" t="n">
         <v>4.637946001443853</v>
       </c>
       <c r="D2098" t="n">
-        <v>-5.52241829698122</v>
+        <v>-5.450884621301588</v>
       </c>
       <c r="E2098" t="n">
-        <v>2.428622258337617</v>
+        <v>2.45723572860947</v>
       </c>
       <c r="F2098" t="n">
-        <v>0.9944695040261879</v>
+        <v>1.0175044298162</v>
       </c>
       <c r="G2098" t="n">
-        <v>5.234627703859567</v>
+        <v>5.248448659333573</v>
       </c>
     </row>
     <row r="2099">
@@ -49822,22 +49822,22 @@
         <v>45561</v>
       </c>
       <c r="B2099" t="n">
-        <v>3.884687848967724</v>
+        <v>3.884687848967721</v>
       </c>
       <c r="C2099" t="n">
         <v>4.600855418234206</v>
       </c>
       <c r="D2099" t="n">
-        <v>-5.474410173137527</v>
+        <v>-5.402876497457895</v>
       </c>
       <c r="E2099" t="n">
-        <v>2.410734924665447</v>
+        <v>2.4393483949373</v>
       </c>
       <c r="F2099" t="n">
-        <v>0.9944695040261879</v>
+        <v>1.0175044298162</v>
       </c>
       <c r="G2099" t="n">
-        <v>5.197537120649919</v>
+        <v>5.211358076123926</v>
       </c>
     </row>
     <row r="2100">
@@ -49845,22 +49845,22 @@
         <v>45562</v>
       </c>
       <c r="B2100" t="n">
-        <v>3.895362357018615</v>
+        <v>3.895362357018612</v>
       </c>
       <c r="C2100" t="n">
         <v>4.604787671792156</v>
       </c>
       <c r="D2100" t="n">
-        <v>-5.32429211791563</v>
+        <v>-5.252758442235998</v>
       </c>
       <c r="E2100" t="n">
-        <v>2.474714400312156</v>
+        <v>2.503327870584009</v>
       </c>
       <c r="F2100" t="n">
-        <v>1.144587559248085</v>
+        <v>1.167622485038097</v>
       </c>
       <c r="G2100" t="n">
-        <v>5.291540207341007</v>
+        <v>5.305361162815014</v>
       </c>
     </row>
     <row r="2101">
@@ -49868,22 +49868,22 @@
         <v>45563</v>
       </c>
       <c r="B2101" t="n">
-        <v>3.891610981075138</v>
+        <v>3.891610981075135</v>
       </c>
       <c r="C2101" t="n">
         <v>4.599686764399193</v>
       </c>
       <c r="D2101" t="n">
-        <v>-5.132357316661756</v>
+        <v>-5.060823640982124</v>
       </c>
       <c r="E2101" t="n">
-        <v>2.546387413420743</v>
+        <v>2.575000883692595</v>
       </c>
       <c r="F2101" t="n">
-        <v>1.144587559248085</v>
+        <v>1.167622485038097</v>
       </c>
       <c r="G2101" t="n">
-        <v>5.286439299948044</v>
+        <v>5.300260255422051</v>
       </c>
     </row>
     <row r="2102">
@@ -49891,22 +49891,22 @@
         <v>45564</v>
       </c>
       <c r="B2102" t="n">
-        <v>3.872432493435449</v>
+        <v>3.872432493435445</v>
       </c>
       <c r="C2102" t="n">
         <v>4.595040673788288</v>
       </c>
       <c r="D2102" t="n">
-        <v>-5.014183938643828</v>
+        <v>-4.942650262964197</v>
       </c>
       <c r="E2102" t="n">
-        <v>2.589010674017009</v>
+        <v>2.617624144288862</v>
       </c>
       <c r="F2102" t="n">
-        <v>1.262760937266012</v>
+        <v>1.285795863056024</v>
       </c>
       <c r="G2102" t="n">
-        <v>5.352697236147896</v>
+        <v>5.366518191621903</v>
       </c>
     </row>
     <row r="2103">
@@ -49914,22 +49914,22 @@
         <v>45565</v>
       </c>
       <c r="B2103" t="n">
-        <v>3.859571723917736</v>
+        <v>3.859571723917734</v>
       </c>
       <c r="C2103" t="n">
         <v>4.624129266651315</v>
       </c>
       <c r="D2103" t="n">
-        <v>-4.925336821784331</v>
+        <v>-4.853803146104699</v>
       </c>
       <c r="E2103" t="n">
-        <v>2.653638113623835</v>
+        <v>2.682251583895687</v>
       </c>
       <c r="F2103" t="n">
-        <v>1.35160805412551</v>
+        <v>1.374642979915522</v>
       </c>
       <c r="G2103" t="n">
-        <v>5.435094099126621</v>
+        <v>5.448915054600628</v>
       </c>
     </row>
     <row r="2104">
@@ -49937,22 +49937,22 @@
         <v>45566</v>
       </c>
       <c r="B2104" t="n">
-        <v>3.828006274013642</v>
+        <v>3.82800627401364</v>
       </c>
       <c r="C2104" t="n">
         <v>4.617689489662492</v>
       </c>
       <c r="D2104" t="n">
-        <v>-4.898287784091077</v>
+        <v>-4.826754108411445</v>
       </c>
       <c r="E2104" t="n">
-        <v>2.658017951712313</v>
+        <v>2.686631421984166</v>
       </c>
       <c r="F2104" t="n">
-        <v>1.378657091818764</v>
+        <v>1.401692017608775</v>
       </c>
       <c r="G2104" t="n">
-        <v>5.444883744753751</v>
+        <v>5.458704700227758</v>
       </c>
     </row>
     <row r="2105">
@@ -49960,22 +49960,22 @@
         <v>45567</v>
       </c>
       <c r="B2105" t="n">
-        <v>3.823987445263773</v>
+        <v>3.82398744526377</v>
       </c>
       <c r="C2105" t="n">
         <v>4.617689489662492</v>
       </c>
       <c r="D2105" t="n">
-        <v>-4.904321064277847</v>
+        <v>-4.832787388598216</v>
       </c>
       <c r="E2105" t="n">
-        <v>2.655604639637605</v>
+        <v>2.684218109909458</v>
       </c>
       <c r="F2105" t="n">
-        <v>1.378657091818764</v>
+        <v>1.401692017608775</v>
       </c>
       <c r="G2105" t="n">
-        <v>5.444883744753751</v>
+        <v>5.458704700227758</v>
       </c>
     </row>
     <row r="2106">
@@ -49983,22 +49983,22 @@
         <v>45568</v>
       </c>
       <c r="B2106" t="n">
-        <v>3.815657203170847</v>
+        <v>3.815657203170844</v>
       </c>
       <c r="C2106" t="n">
         <v>4.621327656804905</v>
       </c>
       <c r="D2106" t="n">
-        <v>-4.956172839851009</v>
+        <v>-4.884639164171377</v>
       </c>
       <c r="E2106" t="n">
-        <v>2.638502096550753</v>
+        <v>2.667115566822606</v>
       </c>
       <c r="F2106" t="n">
-        <v>1.326805316245602</v>
+        <v>1.349840242035614</v>
       </c>
       <c r="G2106" t="n">
-        <v>5.417410846552267</v>
+        <v>5.431231802026273</v>
       </c>
     </row>
     <row r="2107">
@@ -50006,22 +50006,22 @@
         <v>45569</v>
       </c>
       <c r="B2107" t="n">
-        <v>3.830586986431411</v>
+        <v>3.830586986431407</v>
       </c>
       <c r="C2107" t="n">
         <v>4.584819403988742</v>
       </c>
       <c r="D2107" t="n">
-        <v>-4.947330653560489</v>
+        <v>-4.911696610303204</v>
       </c>
       <c r="E2107" t="n">
-        <v>2.605530718250798</v>
+        <v>2.619784335553712</v>
       </c>
       <c r="F2107" t="n">
-        <v>1.326805316245602</v>
+        <v>1.349840242035614</v>
       </c>
       <c r="G2107" t="n">
-        <v>5.380902593736103</v>
+        <v>5.39472354921011</v>
       </c>
     </row>
     <row r="2108">
@@ -50029,22 +50029,22 @@
         <v>45570</v>
       </c>
       <c r="B2108" t="n">
-        <v>3.830856457232461</v>
+        <v>3.830856457232457</v>
       </c>
       <c r="C2108" t="n">
         <v>4.586227353735933</v>
       </c>
       <c r="D2108" t="n">
-        <v>-5.020612005414365</v>
+        <v>-4.984977962157079</v>
       </c>
       <c r="E2108" t="n">
-        <v>2.577626127256439</v>
+        <v>2.591879744559353</v>
       </c>
       <c r="F2108" t="n">
-        <v>1.312893894114391</v>
+        <v>1.335928819904403</v>
       </c>
       <c r="G2108" t="n">
-        <v>5.373963690204568</v>
+        <v>5.387784645678575</v>
       </c>
     </row>
     <row r="2109">
@@ -50052,22 +50052,22 @@
         <v>45571</v>
       </c>
       <c r="B2109" t="n">
-        <v>3.786339171305453</v>
+        <v>3.824710234932232</v>
       </c>
       <c r="C2109" t="n">
-        <v>4.599336815855964</v>
+        <v>4.581615023825965</v>
       </c>
       <c r="D2109" t="n">
-        <v>-5.020612005414365</v>
+        <v>-5.004254674722739</v>
       </c>
       <c r="E2109" t="n">
-        <v>2.577626127256439</v>
+        <v>2.579556729623121</v>
       </c>
       <c r="F2109" t="n">
-        <v>1.312893894114391</v>
+        <v>1.344126702747099</v>
       </c>
       <c r="G2109" t="n">
-        <v>4.592400612842332</v>
+        <v>5.388091045474225</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20241006.xlsx
+++ b/tame_output/ON/bt/strategyON_20241006.xlsx
@@ -600,26 +600,26 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>54.9%</t>
+          <t>55.1%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.6%</t>
+          <t>66.4%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.1%</t>
+          <t>53.0%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2106</v>
+        <v>2105</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,17 +628,17 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-10-06</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.1%</t>
+          <t>64.9%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>68.0%</t>
+          <t>67.9%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>54.4%</t>
+          <t>54.5%</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>101.7%</t>
+          <t>102.6%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -768,16 +768,16 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>58.5%</t>
+          <t>58.6%</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2106</v>
+        <v>2105</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,12 +786,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-10-06</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>39.9%</t>
+          <t>39.8%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -849,12 +849,12 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>85.0%</t>
+          <t>85.6%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>35.4%</t>
+          <t>35.3%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-7.9%</t>
+          <t>-8.0%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.6%</t>
+          <t>39.7%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>146.5%</t>
+          <t>149.0%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-77.9%</t>
+          <t>-77.4%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>107.1%</t>
+          <t>106.1%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2106</v>
+        <v>2105</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,17 +944,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-10-06</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.2%</t>
+          <t>121.8%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>90.1%</t>
+          <t>89.3%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-34.7%</t>
+          <t>-33.7%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>21.6%</t>
+          <t>21.7%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-47.8%</t>
+          <t>-47.7%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-74.2%</t>
+          <t>-73.9%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>88.8%</t>
+          <t>88.0%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>421.1%</t>
+          <t>422.0%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-662.0%</t>
+          <t>-656.7%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>30.8%</t>
+          <t>32.2%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>59.4%</t>
+          <t>59.1%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2106</v>
+        <v>2105</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,17 +1102,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-10-06</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.5%</t>
+          <t>63.1%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>56.2%</t>
+          <t>55.9%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1140,7 +1140,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-10.2%</t>
+          <t>-9.5%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>14.0%</t>
+          <t>14.1%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-31.2%</t>
+          <t>-31.1%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>26.6%</t>
+          <t>27.3%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>49.6%</t>
+          <t>49.3%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-4.4%</t>
+          <t>-4.5%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14.0%</t>
+          <t>14.1%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-118.3%</t>
+          <t>-113.7%</t>
         </is>
       </c>
     </row>
@@ -1232,26 +1232,26 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-1.8%</t>
+          <t>-6.8%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>67.0%</t>
+          <t>66.5%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.9%</t>
+          <t>54.6%</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2106</v>
+        <v>2105</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,17 +1260,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-10-06</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>62.8%</t>
+          <t>62.7%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>74.5%</t>
+          <t>73.4%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1298,22 +1298,22 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>-5.5%</t>
+          <t>-6.3%</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>-3.1%</t>
+          <t>-3.2%</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>10.6%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-23.9%</t>
+          <t>-23.0%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>4.8%</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.8%</t>
+          <t>55.4%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>-0.0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>41.5%</t>
+          <t>47.7%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-205.0%</t>
+          <t>-204.4%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-89.6%</t>
+          <t>-121.9%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>114.6%</t>
+          <t>108.8%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>57.6%</t>
+          <t>57.4%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2106</v>
+        <v>2105</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,17 +1418,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-10-06</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>60.2%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>56.1%</t>
+          <t>55.7%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1447,7 +1447,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-7.6%</t>
+          <t>-7.3%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>14.0%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>104.0%</t>
+          <t>98.0%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>48.0%</t>
+          <t>47.8%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.6%</t>
+          <t>-16.4%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>92.8%</t>
+          <t>75.9%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2109"/>
+  <dimension ref="A1:G2108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -48540,16 +48540,16 @@
         <v>3.483185067816559</v>
       </c>
       <c r="D2043" t="n">
-        <v>-5.036469644204036</v>
+        <v>-5.090109512328855</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.468240785821196</v>
+        <v>1.446784838571269</v>
       </c>
       <c r="F2043" t="n">
-        <v>0.6539204178473598</v>
+        <v>0.6002805497225409</v>
       </c>
       <c r="G2043" t="n">
-        <v>3.875537318524975</v>
+        <v>3.843353397650084</v>
       </c>
     </row>
     <row r="2044">
@@ -48557,22 +48557,22 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.743767956539898</v>
+        <v>3.743767956539899</v>
       </c>
       <c r="C2044" t="n">
         <v>3.476871635717997</v>
       </c>
       <c r="D2044" t="n">
-        <v>-5.005276696352669</v>
+        <v>-5.078055385415892</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.474404532863181</v>
+        <v>1.445293057237892</v>
       </c>
       <c r="F2044" t="n">
-        <v>0.6851133656987265</v>
+        <v>0.6123346766355037</v>
       </c>
       <c r="G2044" t="n">
-        <v>3.887939655137233</v>
+        <v>3.844272441699299</v>
       </c>
     </row>
     <row r="2045">
@@ -48580,22 +48580,22 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.725010844811013</v>
+        <v>3.725010844811014</v>
       </c>
       <c r="C2045" t="n">
         <v>3.478752265902132</v>
       </c>
       <c r="D2045" t="n">
-        <v>-5.082632186480638</v>
+        <v>-5.155410875543861</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.445342966996129</v>
+        <v>1.41623149137084</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.6077578755707571</v>
+        <v>0.5349791865075343</v>
       </c>
       <c r="G2045" t="n">
-        <v>3.843406991244587</v>
+        <v>3.799739777806653</v>
       </c>
     </row>
     <row r="2046">
@@ -48603,22 +48603,22 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.612322444382924</v>
+        <v>3.680768315791503</v>
       </c>
       <c r="C2046" t="n">
         <v>3.491603291780015</v>
       </c>
       <c r="D2046" t="n">
-        <v>-5.014583623789108</v>
+        <v>-5.172501909154726</v>
       </c>
       <c r="E2046" t="n">
-        <v>1.485413417950623</v>
+        <v>1.422246103804377</v>
       </c>
       <c r="F2046" t="n">
-        <v>0.6758064382622869</v>
+        <v>0.5178881528966695</v>
       </c>
       <c r="G2046" t="n">
-        <v>3.897087154737387</v>
+        <v>3.802336183518017</v>
       </c>
     </row>
     <row r="2047">
@@ -48626,22 +48626,22 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.645256780013431</v>
+        <v>3.680768315791503</v>
       </c>
       <c r="C2047" t="n">
-        <v>3.511805961953609</v>
+        <v>3.491603291780015</v>
       </c>
       <c r="D2047" t="n">
-        <v>-5.246184016958609</v>
+        <v>-5.172501909154726</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.412975930856418</v>
+        <v>1.422246103804377</v>
       </c>
       <c r="F2047" t="n">
-        <v>0.6758064382622869</v>
+        <v>0.5178881528966695</v>
       </c>
       <c r="G2047" t="n">
-        <v>3.917289824910982</v>
+        <v>3.802336183518017</v>
       </c>
     </row>
     <row r="2048">
@@ -48649,22 +48649,22 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666747201498968</v>
+        <v>3.660338302180338</v>
       </c>
       <c r="C2048" t="n">
-        <v>3.495412198020491</v>
+        <v>3.491603291780015</v>
       </c>
       <c r="D2048" t="n">
-        <v>-5.296235562487828</v>
+        <v>-5.190574417446338</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.376561548711612</v>
+        <v>1.415017100487732</v>
       </c>
       <c r="F2048" t="n">
-        <v>0.6758064382622869</v>
+        <v>0.5178881528966695</v>
       </c>
       <c r="G2048" t="n">
-        <v>3.900896060977864</v>
+        <v>3.802336183518017</v>
       </c>
     </row>
     <row r="2049">
@@ -48672,22 +48672,22 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.670048702800097</v>
+        <v>3.663639803481468</v>
       </c>
       <c r="C2049" t="n">
-        <v>3.455664111613958</v>
+        <v>3.451855205373481</v>
       </c>
       <c r="D2049" t="n">
-        <v>-5.471342395064273</v>
+        <v>-5.365681250022783</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.266770729274501</v>
+        <v>1.30522628105062</v>
       </c>
       <c r="F2049" t="n">
-        <v>0.6758064382622869</v>
+        <v>0.5178881528966695</v>
       </c>
       <c r="G2049" t="n">
-        <v>3.86114797457133</v>
+        <v>3.762588097111483</v>
       </c>
     </row>
     <row r="2050">
@@ -48695,22 +48695,22 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.745573148660849</v>
+        <v>3.73916424934222</v>
       </c>
       <c r="C2050" t="n">
-        <v>3.462686730610898</v>
+        <v>3.458877824370421</v>
       </c>
       <c r="D2050" t="n">
-        <v>-5.27524224163375</v>
+        <v>-5.16958109659226</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.35223340964365</v>
+        <v>1.390688961419769</v>
       </c>
       <c r="F2050" t="n">
-        <v>0.8719065916928098</v>
+        <v>0.7139883063271923</v>
       </c>
       <c r="G2050" t="n">
-        <v>3.985830685626584</v>
+        <v>3.887270808166737</v>
       </c>
     </row>
     <row r="2051">
@@ -48718,22 +48718,22 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.730570473395087</v>
+        <v>3.724161574076458</v>
       </c>
       <c r="C2051" t="n">
-        <v>3.561857730183802</v>
+        <v>3.558048823943326</v>
       </c>
       <c r="D2051" t="n">
-        <v>-5.122216849520465</v>
+        <v>-5.016555704478976</v>
       </c>
       <c r="E2051" t="n">
-        <v>1.512614566061868</v>
+        <v>1.551070117837988</v>
       </c>
       <c r="F2051" t="n">
-        <v>1.024931983806094</v>
+        <v>0.8670136984404765</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.176816920467459</v>
+        <v>4.078257043007612</v>
       </c>
     </row>
     <row r="2052">
@@ -48741,22 +48741,22 @@
         <v>45514</v>
       </c>
       <c r="B2052" t="n">
-        <v>3.741278332791149</v>
+        <v>3.73486943347252</v>
       </c>
       <c r="C2052" t="n">
-        <v>3.749323955092095</v>
+        <v>3.745515048851618</v>
       </c>
       <c r="D2052" t="n">
-        <v>-5.150524163393736</v>
+        <v>-5.044863018352246</v>
       </c>
       <c r="E2052" t="n">
-        <v>1.688757865420853</v>
+        <v>1.727213417196972</v>
       </c>
       <c r="F2052" t="n">
-        <v>1.024931983806094</v>
+        <v>0.8670136984404765</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.364283145375751</v>
+        <v>4.265723267915905</v>
       </c>
     </row>
     <row r="2053">
@@ -48764,22 +48764,22 @@
         <v>45515</v>
       </c>
       <c r="B2053" t="n">
-        <v>3.699115615620435</v>
+        <v>3.692706716301806</v>
       </c>
       <c r="C2053" t="n">
-        <v>3.718726906446177</v>
+        <v>3.714918000205701</v>
       </c>
       <c r="D2053" t="n">
-        <v>-5.317117388507258</v>
+        <v>-5.211456243465769</v>
       </c>
       <c r="E2053" t="n">
-        <v>1.591523526729526</v>
+        <v>1.629979078505646</v>
       </c>
       <c r="F2053" t="n">
-        <v>0.8583387586925715</v>
+        <v>0.7004204733269541</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.233730161661721</v>
+        <v>4.135170284201874</v>
       </c>
     </row>
     <row r="2054">
@@ -48787,22 +48787,22 @@
         <v>45516</v>
       </c>
       <c r="B2054" t="n">
-        <v>3.708182519285647</v>
+        <v>3.701773619967019</v>
       </c>
       <c r="C2054" t="n">
-        <v>3.722403309107895</v>
+        <v>3.718594402867419</v>
       </c>
       <c r="D2054" t="n">
-        <v>-5.294081595145692</v>
+        <v>-5.188420450104203</v>
       </c>
       <c r="E2054" t="n">
-        <v>1.60441424673587</v>
+        <v>1.64286979851199</v>
       </c>
       <c r="F2054" t="n">
-        <v>0.8583387586925715</v>
+        <v>0.7004204733269541</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.237406564323439</v>
+        <v>4.138846686863592</v>
       </c>
     </row>
     <row r="2055">
@@ -48810,22 +48810,22 @@
         <v>45517</v>
       </c>
       <c r="B2055" t="n">
-        <v>3.740581401399469</v>
+        <v>3.734172502080841</v>
       </c>
       <c r="C2055" t="n">
-        <v>3.72002136423139</v>
+        <v>3.716212457990914</v>
       </c>
       <c r="D2055" t="n">
-        <v>-5.264835614689996</v>
+        <v>-5.159174469648506</v>
       </c>
       <c r="E2055" t="n">
-        <v>1.613730694041644</v>
+        <v>1.652186245817764</v>
       </c>
       <c r="F2055" t="n">
-        <v>0.8583387586925715</v>
+        <v>0.7004204733269541</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.235024619446934</v>
+        <v>4.136464741987087</v>
       </c>
     </row>
     <row r="2056">
@@ -48833,22 +48833,22 @@
         <v>45518</v>
       </c>
       <c r="B2056" t="n">
-        <v>3.699404642256372</v>
+        <v>3.692995742937744</v>
       </c>
       <c r="C2056" t="n">
-        <v>3.717314603389025</v>
+        <v>3.713505697148549</v>
       </c>
       <c r="D2056" t="n">
-        <v>-5.371761162567847</v>
+        <v>-5.266100017526357</v>
       </c>
       <c r="E2056" t="n">
-        <v>1.568253714048139</v>
+        <v>1.606709265824259</v>
       </c>
       <c r="F2056" t="n">
-        <v>0.7514132108147201</v>
+        <v>0.5934949254491028</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.168162529877858</v>
+        <v>4.069602652418011</v>
       </c>
     </row>
     <row r="2057">
@@ -48856,22 +48856,22 @@
         <v>45519</v>
       </c>
       <c r="B2057" t="n">
-        <v>3.689942600701002</v>
+        <v>3.683533701382375</v>
       </c>
       <c r="C2057" t="n">
-        <v>3.71874340553226</v>
+        <v>3.714934499291783</v>
       </c>
       <c r="D2057" t="n">
-        <v>-5.516779721075095</v>
+        <v>-5.411118576033606</v>
       </c>
       <c r="E2057" t="n">
-        <v>1.511675092788474</v>
+        <v>1.550130644564593</v>
       </c>
       <c r="F2057" t="n">
-        <v>0.6063946523074716</v>
+        <v>0.4484763669418542</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.082580196916743</v>
+        <v>3.984020319456897</v>
       </c>
     </row>
     <row r="2058">
@@ -48879,22 +48879,22 @@
         <v>45520</v>
       </c>
       <c r="B2058" t="n">
-        <v>3.711852429687013</v>
+        <v>3.705443530368386</v>
       </c>
       <c r="C2058" t="n">
-        <v>3.818674644790013</v>
+        <v>3.814865738549536</v>
       </c>
       <c r="D2058" t="n">
-        <v>-5.635121486859813</v>
+        <v>-5.529460341818323</v>
       </c>
       <c r="E2058" t="n">
-        <v>1.56426962573234</v>
+        <v>1.602725177508459</v>
       </c>
       <c r="F2058" t="n">
-        <v>0.6170806908703617</v>
+        <v>0.4591624055047443</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.18892305931223</v>
+        <v>4.090363181852383</v>
       </c>
     </row>
     <row r="2059">
@@ -48902,22 +48902,22 @@
         <v>45521</v>
       </c>
       <c r="B2059" t="n">
-        <v>3.714879051790806</v>
+        <v>3.708470152472179</v>
       </c>
       <c r="C2059" t="n">
-        <v>3.816460341915952</v>
+        <v>3.812651435675475</v>
       </c>
       <c r="D2059" t="n">
-        <v>-5.686531909180521</v>
+        <v>-5.580870764139031</v>
       </c>
       <c r="E2059" t="n">
-        <v>1.541491153929996</v>
+        <v>1.579946705706115</v>
       </c>
       <c r="F2059" t="n">
-        <v>0.6170806908703617</v>
+        <v>0.4591624055047443</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.186708756438169</v>
+        <v>4.088148878978322</v>
       </c>
     </row>
     <row r="2060">
@@ -48925,22 +48925,22 @@
         <v>45522</v>
       </c>
       <c r="B2060" t="n">
-        <v>3.704757949437335</v>
+        <v>3.698349050118708</v>
       </c>
       <c r="C2060" t="n">
-        <v>3.816363469990241</v>
+        <v>3.812554563749764</v>
       </c>
       <c r="D2060" t="n">
-        <v>-5.765951360388272</v>
+        <v>-5.660290215346783</v>
       </c>
       <c r="E2060" t="n">
-        <v>1.509626501521184</v>
+        <v>1.548082053297303</v>
       </c>
       <c r="F2060" t="n">
-        <v>0.6170806908703617</v>
+        <v>0.4591624055047443</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.186611884512458</v>
+        <v>4.088052007052611</v>
       </c>
     </row>
     <row r="2061">
@@ -48948,22 +48948,22 @@
         <v>45523</v>
       </c>
       <c r="B2061" t="n">
-        <v>3.736804952298403</v>
+        <v>3.730396052979776</v>
       </c>
       <c r="C2061" t="n">
-        <v>3.816357363548284</v>
+        <v>3.812548457307807</v>
       </c>
       <c r="D2061" t="n">
-        <v>-5.86141435830549</v>
+        <v>-5.755753213264001</v>
       </c>
       <c r="E2061" t="n">
-        <v>1.47143519591234</v>
+        <v>1.509890747688459</v>
       </c>
       <c r="F2061" t="n">
-        <v>0.6170806908703617</v>
+        <v>0.4591624055047443</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.186605778070501</v>
+        <v>4.088045900610654</v>
       </c>
     </row>
     <row r="2062">
@@ -48971,22 +48971,22 @@
         <v>45524</v>
       </c>
       <c r="B2062" t="n">
-        <v>3.715372960218006</v>
+        <v>3.708964060899379</v>
       </c>
       <c r="C2062" t="n">
-        <v>3.814453760110895</v>
+        <v>3.810644853870418</v>
       </c>
       <c r="D2062" t="n">
-        <v>-5.797038447454775</v>
+        <v>-5.691377302413286</v>
       </c>
       <c r="E2062" t="n">
-        <v>1.495281956815237</v>
+        <v>1.533737508591356</v>
       </c>
       <c r="F2062" t="n">
-        <v>0.6814566017210768</v>
+        <v>0.5235383163554594</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.223327721143541</v>
+        <v>4.124767843683694</v>
       </c>
     </row>
     <row r="2063">
@@ -48994,22 +48994,22 @@
         <v>45525</v>
       </c>
       <c r="B2063" t="n">
-        <v>3.736089413353541</v>
+        <v>3.729680514034914</v>
       </c>
       <c r="C2063" t="n">
-        <v>3.820187577858621</v>
+        <v>3.816378671618144</v>
       </c>
       <c r="D2063" t="n">
-        <v>-5.852407609586969</v>
+        <v>-5.746746464545479</v>
       </c>
       <c r="E2063" t="n">
-        <v>1.478868109710086</v>
+        <v>1.517323661486205</v>
       </c>
       <c r="F2063" t="n">
-        <v>0.6814566017210768</v>
+        <v>0.5235383163554594</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.229061538891267</v>
+        <v>4.130501661431421</v>
       </c>
     </row>
     <row r="2064">
@@ -49017,22 +49017,22 @@
         <v>45526</v>
       </c>
       <c r="B2064" t="n">
-        <v>3.736822870113285</v>
+        <v>3.730413970794658</v>
       </c>
       <c r="C2064" t="n">
-        <v>3.819725941201554</v>
+        <v>3.815917034961077</v>
       </c>
       <c r="D2064" t="n">
-        <v>-5.870626076584577</v>
+        <v>-5.764964931543088</v>
       </c>
       <c r="E2064" t="n">
-        <v>1.471119086253974</v>
+        <v>1.509574638030094</v>
       </c>
       <c r="F2064" t="n">
-        <v>0.6563501644652346</v>
+        <v>0.4984318790996173</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.213536039880695</v>
+        <v>4.114976162420848</v>
       </c>
     </row>
     <row r="2065">
@@ -49040,22 +49040,22 @@
         <v>45527</v>
       </c>
       <c r="B2065" t="n">
-        <v>3.790272500113693</v>
+        <v>3.732888336364058</v>
       </c>
       <c r="C2065" t="n">
-        <v>3.839600334051872</v>
+        <v>3.835791427811396</v>
       </c>
       <c r="D2065" t="n">
-        <v>-5.831942641240647</v>
+        <v>-5.730252837534286</v>
       </c>
       <c r="E2065" t="n">
-        <v>1.506466853241866</v>
+        <v>1.543333868483933</v>
       </c>
       <c r="F2065" t="n">
-        <v>0.6563501644652346</v>
+        <v>0.4984318790996173</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.233410432731013</v>
+        <v>4.134850555271166</v>
       </c>
     </row>
     <row r="2066">
@@ -49063,22 +49063,22 @@
         <v>45528</v>
       </c>
       <c r="B2066" t="n">
-        <v>3.794486844016438</v>
+        <v>3.788166421629185</v>
       </c>
       <c r="C2066" t="n">
-        <v>3.8233010345766</v>
+        <v>3.835791427811396</v>
       </c>
       <c r="D2066" t="n">
-        <v>-5.725907646035338</v>
+        <v>-5.727561984334103</v>
       </c>
       <c r="E2066" t="n">
-        <v>1.532581551848717</v>
+        <v>1.544410209764007</v>
       </c>
       <c r="F2066" t="n">
-        <v>0.6563501644652346</v>
+        <v>0.4984318790996173</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.217111133255741</v>
+        <v>4.134850555271166</v>
       </c>
     </row>
     <row r="2067">
@@ -49086,22 +49086,22 @@
         <v>45529</v>
       </c>
       <c r="B2067" t="n">
-        <v>3.79470509330767</v>
+        <v>3.788384670920417</v>
       </c>
       <c r="C2067" t="n">
-        <v>3.825731984040646</v>
+        <v>3.838222377275442</v>
       </c>
       <c r="D2067" t="n">
-        <v>-5.542695982902242</v>
+        <v>-5.544350321201008</v>
       </c>
       <c r="E2067" t="n">
-        <v>1.608297166566001</v>
+        <v>1.620125824481291</v>
       </c>
       <c r="F2067" t="n">
-        <v>0.6563501644652346</v>
+        <v>0.4984318790996173</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.219542082719787</v>
+        <v>4.137281504735213</v>
       </c>
     </row>
     <row r="2068">
@@ -49109,22 +49109,22 @@
         <v>45530</v>
       </c>
       <c r="B2068" t="n">
-        <v>3.776846557863551</v>
+        <v>3.770526135476298</v>
       </c>
       <c r="C2068" t="n">
-        <v>3.808676390120023</v>
+        <v>3.821166783354819</v>
       </c>
       <c r="D2068" t="n">
-        <v>-5.470974535888391</v>
+        <v>-5.472628874187157</v>
       </c>
       <c r="E2068" t="n">
-        <v>1.619930151450919</v>
+        <v>1.631758809366208</v>
       </c>
       <c r="F2068" t="n">
-        <v>0.7280716114790853</v>
+        <v>0.5701533261134679</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.245519357007475</v>
+        <v>4.163258779022899</v>
       </c>
     </row>
     <row r="2069">
@@ -49132,22 +49132,22 @@
         <v>45531</v>
       </c>
       <c r="B2069" t="n">
-        <v>3.723789705394113</v>
+        <v>3.71746928300686</v>
       </c>
       <c r="C2069" t="n">
-        <v>3.755592136041195</v>
+        <v>3.76808252927599</v>
       </c>
       <c r="D2069" t="n">
-        <v>-5.448601510280685</v>
+        <v>-5.450255848579451</v>
       </c>
       <c r="E2069" t="n">
-        <v>1.575795107615173</v>
+        <v>1.587623765530462</v>
       </c>
       <c r="F2069" t="n">
-        <v>0.7393273625919868</v>
+        <v>0.5814090772263695</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.199188553596387</v>
+        <v>4.116927975611812</v>
       </c>
     </row>
     <row r="2070">
@@ -49155,22 +49155,22 @@
         <v>45532</v>
       </c>
       <c r="B2070" t="n">
-        <v>3.715607446456731</v>
+        <v>3.709287024069478</v>
       </c>
       <c r="C2070" t="n">
-        <v>3.94079034092655</v>
+        <v>3.953280734161345</v>
       </c>
       <c r="D2070" t="n">
-        <v>-5.48161780619143</v>
+        <v>-5.483272144490195</v>
       </c>
       <c r="E2070" t="n">
-        <v>1.74778679413623</v>
+        <v>1.759615452051519</v>
       </c>
       <c r="F2070" t="n">
-        <v>0.6698899859252352</v>
+        <v>0.5119717005596178</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.342724332481692</v>
+        <v>4.260463754497116</v>
       </c>
     </row>
     <row r="2071">
@@ -49178,22 +49178,22 @@
         <v>45533</v>
       </c>
       <c r="B2071" t="n">
-        <v>3.713762536883682</v>
+        <v>3.707442114496429</v>
       </c>
       <c r="C2071" t="n">
-        <v>3.932711566754799</v>
+        <v>3.945201959989594</v>
       </c>
       <c r="D2071" t="n">
-        <v>-5.470090170541821</v>
+        <v>-5.471744508840587</v>
       </c>
       <c r="E2071" t="n">
-        <v>1.744319074224322</v>
+        <v>1.756147732139612</v>
       </c>
       <c r="F2071" t="n">
-        <v>0.7288906441265977</v>
+        <v>0.5709723587609803</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.370045953230758</v>
+        <v>4.287785375246183</v>
       </c>
     </row>
     <row r="2072">
@@ -49201,22 +49201,22 @@
         <v>45534</v>
       </c>
       <c r="B2072" t="n">
-        <v>3.717150699236303</v>
+        <v>3.71083027684905</v>
       </c>
       <c r="C2072" t="n">
-        <v>3.936379679276587</v>
+        <v>3.948870072511383</v>
       </c>
       <c r="D2072" t="n">
-        <v>-5.56743167188419</v>
+        <v>-5.569086010182955</v>
       </c>
       <c r="E2072" t="n">
-        <v>1.709050586209163</v>
+        <v>1.720879244124453</v>
       </c>
       <c r="F2072" t="n">
-        <v>0.6844704619611093</v>
+        <v>0.5265521765954919</v>
       </c>
       <c r="G2072" t="n">
-        <v>4.347061956453254</v>
+        <v>4.264801378468678</v>
       </c>
     </row>
     <row r="2073">
@@ -49224,22 +49224,22 @@
         <v>45535</v>
       </c>
       <c r="B2073" t="n">
-        <v>3.705201079427689</v>
+        <v>3.698880657040437</v>
       </c>
       <c r="C2073" t="n">
-        <v>3.937630761469426</v>
+        <v>3.950121154704221</v>
       </c>
       <c r="D2073" t="n">
-        <v>-5.653287701224157</v>
+        <v>-5.654942039522922</v>
       </c>
       <c r="E2073" t="n">
-        <v>1.675959256666015</v>
+        <v>1.687787914581305</v>
       </c>
       <c r="F2073" t="n">
-        <v>0.6420943927349743</v>
+        <v>0.4841761073693569</v>
       </c>
       <c r="G2073" t="n">
-        <v>4.322887397110411</v>
+        <v>4.240626819125835</v>
       </c>
     </row>
     <row r="2074">
@@ -49247,22 +49247,22 @@
         <v>45536</v>
       </c>
       <c r="B2074" t="n">
-        <v>3.69183549961038</v>
+        <v>3.685515077223128</v>
       </c>
       <c r="C2074" t="n">
-        <v>3.920049963289927</v>
+        <v>3.942412188439345</v>
       </c>
       <c r="D2074" t="n">
-        <v>-5.662124498640276</v>
+        <v>-5.65869140544152</v>
       </c>
       <c r="E2074" t="n">
-        <v>1.654843739520069</v>
+        <v>1.678579201948989</v>
       </c>
       <c r="F2074" t="n">
-        <v>0.6346522200936235</v>
+        <v>0.482074587247221</v>
       </c>
       <c r="G2074" t="n">
-        <v>4.300841295346101</v>
+        <v>4.231656940787678</v>
       </c>
     </row>
     <row r="2075">
@@ -49270,22 +49270,22 @@
         <v>45537</v>
       </c>
       <c r="B2075" t="n">
-        <v>3.715544411667459</v>
+        <v>3.709223989280206</v>
       </c>
       <c r="C2075" t="n">
-        <v>3.930214474334977</v>
+        <v>3.952576699484394</v>
       </c>
       <c r="D2075" t="n">
-        <v>-5.753507061205735</v>
+        <v>-5.750073968006978</v>
       </c>
       <c r="E2075" t="n">
-        <v>1.628455225538935</v>
+        <v>1.652190687967855</v>
       </c>
       <c r="F2075" t="n">
-        <v>0.5980873353742788</v>
+        <v>0.4455097025278763</v>
       </c>
       <c r="G2075" t="n">
-        <v>4.289066875559545</v>
+        <v>4.219882521001121</v>
       </c>
     </row>
     <row r="2076">
@@ -49293,22 +49293,22 @@
         <v>45538</v>
       </c>
       <c r="B2076" t="n">
-        <v>3.673978374889196</v>
+        <v>3.697658460021693</v>
       </c>
       <c r="C2076" t="n">
-        <v>4.032342732159245</v>
+        <v>4.054704957308662</v>
       </c>
       <c r="D2076" t="n">
-        <v>-5.741800343218729</v>
+        <v>-5.752207736372894</v>
       </c>
       <c r="E2076" t="n">
-        <v>1.735266170558006</v>
+        <v>1.753465438445756</v>
       </c>
       <c r="F2076" t="n">
-        <v>0.6097940533612852</v>
+        <v>0.4433759341619611</v>
       </c>
       <c r="G2076" t="n">
-        <v>4.398219164176017</v>
+        <v>4.320730517805838</v>
       </c>
     </row>
     <row r="2077">
@@ -49316,22 +49316,22 @@
         <v>45539</v>
       </c>
       <c r="B2077" t="n">
-        <v>3.682476099409572</v>
+        <v>3.675546726390101</v>
       </c>
       <c r="C2077" t="n">
-        <v>4.03537507089065</v>
+        <v>4.054704957308662</v>
       </c>
       <c r="D2077" t="n">
-        <v>-5.812712416961006</v>
+        <v>-5.751131414472647</v>
       </c>
       <c r="E2077" t="n">
-        <v>1.7099336797925</v>
+        <v>1.753895967205855</v>
       </c>
       <c r="F2077" t="n">
-        <v>0.6097940533612852</v>
+        <v>0.4433759341619611</v>
       </c>
       <c r="G2077" t="n">
-        <v>4.401251502907422</v>
+        <v>4.320730517805838</v>
       </c>
     </row>
     <row r="2078">
@@ -49339,22 +49339,22 @@
         <v>45540</v>
       </c>
       <c r="B2078" t="n">
-        <v>3.67289517745257</v>
+        <v>3.6659658044331</v>
       </c>
       <c r="C2078" t="n">
-        <v>4.036193896622915</v>
+        <v>4.055523783040926</v>
       </c>
       <c r="D2078" t="n">
-        <v>-5.823028515127358</v>
+        <v>-5.761447512638999</v>
       </c>
       <c r="E2078" t="n">
-        <v>1.706626066258223</v>
+        <v>1.750588353671579</v>
       </c>
       <c r="F2078" t="n">
-        <v>0.6097940533612852</v>
+        <v>0.4433759341619611</v>
       </c>
       <c r="G2078" t="n">
-        <v>4.402070328639686</v>
+        <v>4.321549343538103</v>
       </c>
     </row>
     <row r="2079">
@@ -49362,22 +49362,22 @@
         <v>45541</v>
       </c>
       <c r="B2079" t="n">
-        <v>3.623960959762292</v>
+        <v>3.782194843058067</v>
       </c>
       <c r="C2079" t="n">
-        <v>4.035372563535004</v>
+        <v>4.055523783040926</v>
       </c>
       <c r="D2079" t="n">
-        <v>-5.822934547109985</v>
+        <v>-5.761447512638999</v>
       </c>
       <c r="E2079" t="n">
-        <v>1.705842320377262</v>
+        <v>1.750588353671579</v>
       </c>
       <c r="F2079" t="n">
-        <v>0.6101639147086032</v>
+        <v>0.4433759341619611</v>
       </c>
       <c r="G2079" t="n">
-        <v>4.401470912360167</v>
+        <v>4.321549343538103</v>
       </c>
     </row>
     <row r="2080">
@@ -49385,22 +49385,22 @@
         <v>45542</v>
       </c>
       <c r="B2080" t="n">
-        <v>3.800870306884084</v>
+        <v>3.782194843058067</v>
       </c>
       <c r="C2080" t="n">
-        <v>4.029604549479358</v>
+        <v>4.055523783040926</v>
       </c>
       <c r="D2080" t="n">
-        <v>-5.96653571113337</v>
+        <v>-5.761447512638999</v>
       </c>
       <c r="E2080" t="n">
-        <v>1.642633840712262</v>
+        <v>1.750588353671579</v>
       </c>
       <c r="F2080" t="n">
-        <v>0.6101639147086032</v>
+        <v>0.4433759341619611</v>
       </c>
       <c r="G2080" t="n">
-        <v>4.395702898304521</v>
+        <v>4.321549343538103</v>
       </c>
     </row>
     <row r="2081">
@@ -49408,22 +49408,22 @@
         <v>45543</v>
       </c>
       <c r="B2081" t="n">
-        <v>3.671015692129648</v>
+        <v>3.654748360676483</v>
       </c>
       <c r="C2081" t="n">
-        <v>4.029604549479358</v>
+        <v>4.055523783040926</v>
       </c>
       <c r="D2081" t="n">
-        <v>-5.965587288015332</v>
+        <v>-5.760499089520961</v>
       </c>
       <c r="E2081" t="n">
-        <v>1.643013209959477</v>
+        <v>1.750967722918794</v>
       </c>
       <c r="F2081" t="n">
-        <v>0.6101639147086032</v>
+        <v>0.4433759341619611</v>
       </c>
       <c r="G2081" t="n">
-        <v>4.395702898304521</v>
+        <v>4.321549343538103</v>
       </c>
     </row>
     <row r="2082">
@@ -49431,22 +49431,22 @@
         <v>45544</v>
       </c>
       <c r="B2082" t="n">
-        <v>3.904173816052351</v>
+        <v>3.887906484599187</v>
       </c>
       <c r="C2082" t="n">
-        <v>4.04233215746045</v>
+        <v>4.068251391022018</v>
       </c>
       <c r="D2082" t="n">
-        <v>-6.065857105974352</v>
+        <v>-5.860768907479981</v>
       </c>
       <c r="E2082" t="n">
-        <v>1.615632890756961</v>
+        <v>1.723587403716278</v>
       </c>
       <c r="F2082" t="n">
-        <v>0.6101639147086032</v>
+        <v>0.4433759341619611</v>
       </c>
       <c r="G2082" t="n">
-        <v>4.408430506285613</v>
+        <v>4.334276951519195</v>
       </c>
     </row>
     <row r="2083">
@@ -49454,22 +49454,22 @@
         <v>45545</v>
       </c>
       <c r="B2083" t="n">
-        <v>3.740179607813495</v>
+        <v>3.723912276360331</v>
       </c>
       <c r="C2083" t="n">
-        <v>4.044278155884838</v>
+        <v>4.070197389446406</v>
       </c>
       <c r="D2083" t="n">
-        <v>-6.059864859185541</v>
+        <v>-5.85477666069117</v>
       </c>
       <c r="E2083" t="n">
-        <v>1.619975787896873</v>
+        <v>1.72793030085619</v>
       </c>
       <c r="F2083" t="n">
-        <v>0.6101639147086032</v>
+        <v>0.4433759341619611</v>
       </c>
       <c r="G2083" t="n">
-        <v>4.41037650471</v>
+        <v>4.336222949943583</v>
       </c>
     </row>
     <row r="2084">
@@ -49477,22 +49477,22 @@
         <v>45546</v>
       </c>
       <c r="B2084" t="n">
-        <v>3.765050796537944</v>
+        <v>3.748783465084779</v>
       </c>
       <c r="C2084" t="n">
-        <v>4.037932291902607</v>
+        <v>4.063851525464175</v>
       </c>
       <c r="D2084" t="n">
-        <v>-5.971306898054773</v>
+        <v>-5.766218699560402</v>
       </c>
       <c r="E2084" t="n">
-        <v>1.64905310836695</v>
+        <v>1.757007621326266</v>
       </c>
       <c r="F2084" t="n">
-        <v>0.6101639147086032</v>
+        <v>0.4433759341619611</v>
       </c>
       <c r="G2084" t="n">
-        <v>4.404030640727769</v>
+        <v>4.329877085961352</v>
       </c>
     </row>
     <row r="2085">
@@ -49500,22 +49500,22 @@
         <v>45547</v>
       </c>
       <c r="B2085" t="n">
-        <v>3.758409170771816</v>
+        <v>3.742141839318651</v>
       </c>
       <c r="C2085" t="n">
-        <v>4.037240969341602</v>
+        <v>4.063160202903171</v>
       </c>
       <c r="D2085" t="n">
-        <v>-5.953547820551699</v>
+        <v>-5.748459622057328</v>
       </c>
       <c r="E2085" t="n">
-        <v>1.655465416807175</v>
+        <v>1.763419929766492</v>
       </c>
       <c r="F2085" t="n">
-        <v>0.6101639147086032</v>
+        <v>0.4433759341619611</v>
       </c>
       <c r="G2085" t="n">
-        <v>4.403339318166765</v>
+        <v>4.329185763400347</v>
       </c>
     </row>
     <row r="2086">
@@ -49523,22 +49523,22 @@
         <v>45548</v>
       </c>
       <c r="B2086" t="n">
-        <v>3.801340597109721</v>
+        <v>3.785073265656557</v>
       </c>
       <c r="C2086" t="n">
-        <v>4.050023155250189</v>
+        <v>4.075942388811757</v>
       </c>
       <c r="D2086" t="n">
-        <v>-5.853917669502631</v>
+        <v>-5.64882947100826</v>
       </c>
       <c r="E2086" t="n">
-        <v>1.708099663135389</v>
+        <v>1.816054176094705</v>
       </c>
       <c r="F2086" t="n">
-        <v>0.7097940657576707</v>
+        <v>0.5430060852110286</v>
       </c>
       <c r="G2086" t="n">
-        <v>4.475899594704792</v>
+        <v>4.401746039938375</v>
       </c>
     </row>
     <row r="2087">
@@ -49546,22 +49546,22 @@
         <v>45549</v>
       </c>
       <c r="B2087" t="n">
-        <v>3.798465546843996</v>
+        <v>3.782198215390832</v>
       </c>
       <c r="C2087" t="n">
-        <v>4.239177420748915</v>
+        <v>4.265096654310484</v>
       </c>
       <c r="D2087" t="n">
-        <v>-5.903317178191642</v>
+        <v>-5.698228979697271</v>
       </c>
       <c r="E2087" t="n">
-        <v>1.877494125158511</v>
+        <v>1.985448638117827</v>
       </c>
       <c r="F2087" t="n">
-        <v>0.7200528991894154</v>
+        <v>0.5532649186427733</v>
       </c>
       <c r="G2087" t="n">
-        <v>4.671209160262565</v>
+        <v>4.597055605496148</v>
       </c>
     </row>
     <row r="2088">
@@ -49569,22 +49569,22 @@
         <v>45550</v>
       </c>
       <c r="B2088" t="n">
-        <v>3.77218650835186</v>
+        <v>3.755919176898695</v>
       </c>
       <c r="C2088" t="n">
-        <v>4.226366093851778</v>
+        <v>4.252285327413346</v>
       </c>
       <c r="D2088" t="n">
-        <v>-5.696632704549266</v>
+        <v>-5.491544506054895</v>
       </c>
       <c r="E2088" t="n">
-        <v>1.947356587718323</v>
+        <v>2.05531110067764</v>
       </c>
       <c r="F2088" t="n">
-        <v>0.926737372831791</v>
+        <v>0.7599493922851489</v>
       </c>
       <c r="G2088" t="n">
-        <v>4.782408517550852</v>
+        <v>4.708254962784435</v>
       </c>
     </row>
     <row r="2089">
@@ -49592,22 +49592,22 @@
         <v>45551</v>
       </c>
       <c r="B2089" t="n">
-        <v>3.76339283855127</v>
+        <v>3.747125507098105</v>
       </c>
       <c r="C2089" t="n">
-        <v>4.228367607505882</v>
+        <v>4.254286841067451</v>
       </c>
       <c r="D2089" t="n">
-        <v>-5.730789599546792</v>
+        <v>-5.525701401052421</v>
       </c>
       <c r="E2089" t="n">
-        <v>1.935695343373418</v>
+        <v>2.043649856332734</v>
       </c>
       <c r="F2089" t="n">
-        <v>0.8431536032909785</v>
+        <v>0.6763656227443364</v>
       </c>
       <c r="G2089" t="n">
-        <v>4.73425976948047</v>
+        <v>4.660106214714053</v>
       </c>
     </row>
     <row r="2090">
@@ -49615,22 +49615,22 @@
         <v>45552</v>
       </c>
       <c r="B2090" t="n">
-        <v>3.805590565041111</v>
+        <v>3.789323233587947</v>
       </c>
       <c r="C2090" t="n">
-        <v>4.58186472149555</v>
+        <v>4.607783955057118</v>
       </c>
       <c r="D2090" t="n">
-        <v>-5.638200120485336</v>
+        <v>-5.433111921990965</v>
       </c>
       <c r="E2090" t="n">
-        <v>2.326228248987668</v>
+        <v>2.434182761946984</v>
       </c>
       <c r="F2090" t="n">
-        <v>0.8431536032909785</v>
+        <v>0.6763656227443364</v>
       </c>
       <c r="G2090" t="n">
-        <v>5.087756883470138</v>
+        <v>5.01360332870372</v>
       </c>
     </row>
     <row r="2091">
@@ -49638,22 +49638,22 @@
         <v>45553</v>
       </c>
       <c r="B2091" t="n">
-        <v>3.832164354497403</v>
+        <v>3.815897023044238</v>
       </c>
       <c r="C2091" t="n">
-        <v>4.586427833062654</v>
+        <v>4.612347066624222</v>
       </c>
       <c r="D2091" t="n">
-        <v>-5.711360724258481</v>
+        <v>-5.50627252576411</v>
       </c>
       <c r="E2091" t="n">
-        <v>2.301527119045514</v>
+        <v>2.409481632004831</v>
       </c>
       <c r="F2091" t="n">
-        <v>0.8151324032567355</v>
+        <v>0.6483444227100934</v>
       </c>
       <c r="G2091" t="n">
-        <v>5.075507275016696</v>
+        <v>5.001353720250279</v>
       </c>
     </row>
     <row r="2092">
@@ -49661,22 +49661,22 @@
         <v>45554</v>
       </c>
       <c r="B2092" t="n">
-        <v>3.858310890492296</v>
+        <v>3.842043559039132</v>
       </c>
       <c r="C2092" t="n">
-        <v>4.636257774386181</v>
+        <v>4.66217700794775</v>
       </c>
       <c r="D2092" t="n">
-        <v>-5.659144414462139</v>
+        <v>-5.454056215967768</v>
       </c>
       <c r="E2092" t="n">
-        <v>2.372243584287578</v>
+        <v>2.480198097246895</v>
       </c>
       <c r="F2092" t="n">
-        <v>0.8151324032567355</v>
+        <v>0.6483444227100934</v>
       </c>
       <c r="G2092" t="n">
-        <v>5.125337216340223</v>
+        <v>5.051183661573806</v>
       </c>
     </row>
     <row r="2093">
@@ -49684,22 +49684,22 @@
         <v>45555</v>
       </c>
       <c r="B2093" t="n">
-        <v>3.844935596436478</v>
+        <v>3.828668264983313</v>
       </c>
       <c r="C2093" t="n">
-        <v>4.645071744596192</v>
+        <v>4.670990978157761</v>
       </c>
       <c r="D2093" t="n">
-        <v>-5.606637086951644</v>
+        <v>-5.401548888457273</v>
       </c>
       <c r="E2093" t="n">
-        <v>2.402060485501787</v>
+        <v>2.510014998461104</v>
       </c>
       <c r="F2093" t="n">
-        <v>0.8676397307672304</v>
+        <v>0.7008517502205883</v>
       </c>
       <c r="G2093" t="n">
-        <v>5.165655583056531</v>
+        <v>5.091502028290114</v>
       </c>
     </row>
     <row r="2094">
@@ -49707,22 +49707,22 @@
         <v>45556</v>
       </c>
       <c r="B2094" t="n">
-        <v>3.848376866039487</v>
+        <v>3.832109534586323</v>
       </c>
       <c r="C2094" t="n">
-        <v>4.640709328635389</v>
+        <v>4.666628562196958</v>
       </c>
       <c r="D2094" t="n">
-        <v>-5.621392411151785</v>
+        <v>-5.416304212657414</v>
       </c>
       <c r="E2094" t="n">
-        <v>2.391795939860927</v>
+        <v>2.499750452820244</v>
       </c>
       <c r="F2094" t="n">
-        <v>0.8676397307672304</v>
+        <v>0.7008517502205883</v>
       </c>
       <c r="G2094" t="n">
-        <v>5.161293167095728</v>
+        <v>5.087139612329311</v>
       </c>
     </row>
     <row r="2095">
@@ -49730,22 +49730,22 @@
         <v>45557</v>
       </c>
       <c r="B2095" t="n">
-        <v>3.868153115524482</v>
+        <v>3.761426556739526</v>
       </c>
       <c r="C2095" t="n">
-        <v>4.631633832051669</v>
+        <v>4.657553065613238</v>
       </c>
       <c r="D2095" t="n">
-        <v>-5.571927787781873</v>
+        <v>-5.364966447988894</v>
       </c>
       <c r="E2095" t="n">
-        <v>2.402506292625172</v>
+        <v>2.511210062103932</v>
       </c>
       <c r="F2095" t="n">
-        <v>0.9171043541371421</v>
+        <v>0.7521895148891085</v>
       </c>
       <c r="G2095" t="n">
-        <v>5.181896444533955</v>
+        <v>5.108866774546703</v>
       </c>
     </row>
     <row r="2096">
@@ -49753,22 +49753,22 @@
         <v>45558</v>
       </c>
       <c r="B2096" t="n">
-        <v>3.849040239867955</v>
+        <v>3.761426556739526</v>
       </c>
       <c r="C2096" t="n">
-        <v>4.628041499766604</v>
+        <v>4.657553065613238</v>
       </c>
       <c r="D2096" t="n">
-        <v>-5.408819795628258</v>
+        <v>-5.364966447988894</v>
       </c>
       <c r="E2096" t="n">
-        <v>2.464157157201553</v>
+        <v>2.511210062103932</v>
       </c>
       <c r="F2096" t="n">
-        <v>1.080212346290757</v>
+        <v>0.7521895148891085</v>
       </c>
       <c r="G2096" t="n">
-        <v>5.276168907541058</v>
+        <v>5.108866774546703</v>
       </c>
     </row>
     <row r="2097">
@@ -49776,22 +49776,22 @@
         <v>45559</v>
       </c>
       <c r="B2097" t="n">
-        <v>3.870204928232971</v>
+        <v>3.860573669185362</v>
       </c>
       <c r="C2097" t="n">
-        <v>4.637088536457732</v>
+        <v>4.657553065613238</v>
       </c>
       <c r="D2097" t="n">
-        <v>-5.38817670482703</v>
+        <v>-5.367716563978221</v>
       </c>
       <c r="E2097" t="n">
-        <v>2.481461430213172</v>
+        <v>2.510110015708201</v>
       </c>
       <c r="F2097" t="n">
-        <v>1.080212346290757</v>
+        <v>0.7521895148891085</v>
       </c>
       <c r="G2097" t="n">
-        <v>5.285215944232187</v>
+        <v>5.108866774546703</v>
       </c>
     </row>
     <row r="2098">
@@ -49799,22 +49799,22 @@
         <v>45560</v>
       </c>
       <c r="B2098" t="n">
-        <v>3.855534437179674</v>
+        <v>3.845903178132065</v>
       </c>
       <c r="C2098" t="n">
-        <v>4.637946001443853</v>
+        <v>4.658410530599359</v>
       </c>
       <c r="D2098" t="n">
-        <v>-5.450884621301588</v>
+        <v>-5.430424480452779</v>
       </c>
       <c r="E2098" t="n">
-        <v>2.45723572860947</v>
+        <v>2.485884314104499</v>
       </c>
       <c r="F2098" t="n">
-        <v>1.0175044298162</v>
+        <v>0.6894815984145507</v>
       </c>
       <c r="G2098" t="n">
-        <v>5.248448659333573</v>
+        <v>5.07209948964809</v>
       </c>
     </row>
     <row r="2099">
@@ -49822,22 +49822,22 @@
         <v>45561</v>
       </c>
       <c r="B2099" t="n">
-        <v>3.884687848967721</v>
+        <v>3.875056589920112</v>
       </c>
       <c r="C2099" t="n">
-        <v>4.600855418234206</v>
+        <v>4.621319947389711</v>
       </c>
       <c r="D2099" t="n">
-        <v>-5.402876497457895</v>
+        <v>-5.382416356609086</v>
       </c>
       <c r="E2099" t="n">
-        <v>2.4393483949373</v>
+        <v>2.467996980432329</v>
       </c>
       <c r="F2099" t="n">
-        <v>1.0175044298162</v>
+        <v>0.6894815984145507</v>
       </c>
       <c r="G2099" t="n">
-        <v>5.211358076123926</v>
+        <v>5.035008906438442</v>
       </c>
     </row>
     <row r="2100">
@@ -49845,22 +49845,22 @@
         <v>45562</v>
       </c>
       <c r="B2100" t="n">
-        <v>3.895362357018612</v>
+        <v>3.885731097971003</v>
       </c>
       <c r="C2100" t="n">
-        <v>4.604787671792156</v>
+        <v>4.625252200947662</v>
       </c>
       <c r="D2100" t="n">
-        <v>-5.252758442235998</v>
+        <v>-5.232298301387189</v>
       </c>
       <c r="E2100" t="n">
-        <v>2.503327870584009</v>
+        <v>2.531976456079038</v>
       </c>
       <c r="F2100" t="n">
-        <v>1.167622485038097</v>
+        <v>0.8395996536364477</v>
       </c>
       <c r="G2100" t="n">
-        <v>5.305361162815014</v>
+        <v>5.129011993129531</v>
       </c>
     </row>
     <row r="2101">
@@ -49868,22 +49868,22 @@
         <v>45563</v>
       </c>
       <c r="B2101" t="n">
-        <v>3.891610981075135</v>
+        <v>3.881979722027526</v>
       </c>
       <c r="C2101" t="n">
-        <v>4.599686764399193</v>
+        <v>4.620151293554699</v>
       </c>
       <c r="D2101" t="n">
-        <v>-5.060823640982124</v>
+        <v>-5.040363500133315</v>
       </c>
       <c r="E2101" t="n">
-        <v>2.575000883692595</v>
+        <v>2.603649469187625</v>
       </c>
       <c r="F2101" t="n">
-        <v>1.167622485038097</v>
+        <v>0.8395996536364477</v>
       </c>
       <c r="G2101" t="n">
-        <v>5.300260255422051</v>
+        <v>5.123911085736568</v>
       </c>
     </row>
     <row r="2102">
@@ -49891,22 +49891,22 @@
         <v>45564</v>
       </c>
       <c r="B2102" t="n">
-        <v>3.872432493435445</v>
+        <v>3.862801234387836</v>
       </c>
       <c r="C2102" t="n">
-        <v>4.595040673788288</v>
+        <v>4.615505202943794</v>
       </c>
       <c r="D2102" t="n">
-        <v>-4.942650262964197</v>
+        <v>-4.922190122115389</v>
       </c>
       <c r="E2102" t="n">
-        <v>2.617624144288862</v>
+        <v>2.646272729783891</v>
       </c>
       <c r="F2102" t="n">
-        <v>1.285795863056024</v>
+        <v>0.957773031654375</v>
       </c>
       <c r="G2102" t="n">
-        <v>5.366518191621903</v>
+        <v>5.190169021936419</v>
       </c>
     </row>
     <row r="2103">
@@ -49914,22 +49914,22 @@
         <v>45565</v>
       </c>
       <c r="B2103" t="n">
-        <v>3.859571723917734</v>
+        <v>3.849940464870125</v>
       </c>
       <c r="C2103" t="n">
-        <v>4.624129266651315</v>
+        <v>4.644593795806821</v>
       </c>
       <c r="D2103" t="n">
-        <v>-4.853803146104699</v>
+        <v>-4.833343005255891</v>
       </c>
       <c r="E2103" t="n">
-        <v>2.682251583895687</v>
+        <v>2.710900169390716</v>
       </c>
       <c r="F2103" t="n">
-        <v>1.374642979915522</v>
+        <v>1.046620148513873</v>
       </c>
       <c r="G2103" t="n">
-        <v>5.448915054600628</v>
+        <v>5.272565884915145</v>
       </c>
     </row>
     <row r="2104">
@@ -49937,22 +49937,22 @@
         <v>45566</v>
       </c>
       <c r="B2104" t="n">
-        <v>3.82800627401364</v>
+        <v>3.77540795745959</v>
       </c>
       <c r="C2104" t="n">
-        <v>4.617689489662492</v>
+        <v>4.638154018817998</v>
       </c>
       <c r="D2104" t="n">
-        <v>-4.826754108411445</v>
+        <v>-4.793461419251798</v>
       </c>
       <c r="E2104" t="n">
-        <v>2.686631421984166</v>
+        <v>2.720413026803531</v>
       </c>
       <c r="F2104" t="n">
-        <v>1.401692017608775</v>
+        <v>1.086501734517965</v>
       </c>
       <c r="G2104" t="n">
-        <v>5.458704700227758</v>
+        <v>5.290055059528777</v>
       </c>
     </row>
     <row r="2105">
@@ -49960,22 +49960,22 @@
         <v>45567</v>
       </c>
       <c r="B2105" t="n">
-        <v>3.82398744526377</v>
+        <v>3.817629953593475</v>
       </c>
       <c r="C2105" t="n">
-        <v>4.617689489662492</v>
+        <v>4.638154018817998</v>
       </c>
       <c r="D2105" t="n">
-        <v>-4.832787388598216</v>
+        <v>-4.799494699438569</v>
       </c>
       <c r="E2105" t="n">
-        <v>2.684218109909458</v>
+        <v>2.717999714728823</v>
       </c>
       <c r="F2105" t="n">
-        <v>1.401692017608775</v>
+        <v>1.086501734517965</v>
       </c>
       <c r="G2105" t="n">
-        <v>5.458704700227758</v>
+        <v>5.290055059528777</v>
       </c>
     </row>
     <row r="2106">
@@ -49983,22 +49983,22 @@
         <v>45568</v>
       </c>
       <c r="B2106" t="n">
-        <v>3.815657203170844</v>
+        <v>3.809299711500548</v>
       </c>
       <c r="C2106" t="n">
-        <v>4.621327656804905</v>
+        <v>4.64179218596041</v>
       </c>
       <c r="D2106" t="n">
-        <v>-4.884639164171377</v>
+        <v>-4.85134647501173</v>
       </c>
       <c r="E2106" t="n">
-        <v>2.667115566822606</v>
+        <v>2.70089717164197</v>
       </c>
       <c r="F2106" t="n">
-        <v>1.349840242035614</v>
+        <v>1.034649958944804</v>
       </c>
       <c r="G2106" t="n">
-        <v>5.431231802026273</v>
+        <v>5.262582161327293</v>
       </c>
     </row>
     <row r="2107">
@@ -50006,22 +50006,22 @@
         <v>45569</v>
       </c>
       <c r="B2107" t="n">
-        <v>3.830586986431407</v>
+        <v>3.824229494761112</v>
       </c>
       <c r="C2107" t="n">
-        <v>4.584819403988742</v>
+        <v>4.605283933144247</v>
       </c>
       <c r="D2107" t="n">
-        <v>-4.911696610303204</v>
+        <v>-4.878403921143557</v>
       </c>
       <c r="E2107" t="n">
-        <v>2.619784335553712</v>
+        <v>2.653565940373077</v>
       </c>
       <c r="F2107" t="n">
-        <v>1.349840242035614</v>
+        <v>1.034649958944804</v>
       </c>
       <c r="G2107" t="n">
-        <v>5.39472354921011</v>
+        <v>5.22607390851113</v>
       </c>
     </row>
     <row r="2108">
@@ -50029,45 +50029,22 @@
         <v>45570</v>
       </c>
       <c r="B2108" t="n">
-        <v>3.830856457232457</v>
+        <v>3.826040138097996</v>
       </c>
       <c r="C2108" t="n">
-        <v>4.586227353735933</v>
+        <v>4.606691882891439</v>
       </c>
       <c r="D2108" t="n">
-        <v>-4.984977962157079</v>
+        <v>-4.951685272997432</v>
       </c>
       <c r="E2108" t="n">
-        <v>2.591879744559353</v>
+        <v>2.625661349378718</v>
       </c>
       <c r="F2108" t="n">
-        <v>1.335928819904403</v>
+        <v>1.020738536813592</v>
       </c>
       <c r="G2108" t="n">
-        <v>5.387784645678575</v>
-      </c>
-    </row>
-    <row r="2109">
-      <c r="A2109" s="2" t="n">
-        <v>45571</v>
-      </c>
-      <c r="B2109" t="n">
-        <v>3.824710234932232</v>
-      </c>
-      <c r="C2109" t="n">
-        <v>4.581615023825965</v>
-      </c>
-      <c r="D2109" t="n">
-        <v>-5.004254674722739</v>
-      </c>
-      <c r="E2109" t="n">
-        <v>2.579556729623121</v>
-      </c>
-      <c r="F2109" t="n">
-        <v>1.344126702747099</v>
-      </c>
-      <c r="G2109" t="n">
-        <v>5.388091045474225</v>
+        <v>5.219135004979594</v>
       </c>
     </row>
   </sheetData>
